--- a/thinkpad_complete_research.xlsx
+++ b/thinkpad_complete_research.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="数据说明" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'ThinkPad调研数据'!$A$1:$AR$163</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'ThinkPad调研数据'!$A$1:$AR$170</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -597,52 +597,52 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AR163"/>
+  <dimension ref="A1:AR170"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="40" customWidth="1" min="1" max="1"/>
-    <col width="39" customWidth="1" min="2" max="2"/>
+    <col width="32" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
     <col width="11" customWidth="1" min="3" max="3"/>
-    <col width="27" customWidth="1" min="4" max="4"/>
-    <col width="28" customWidth="1" min="5" max="5"/>
-    <col width="40" customWidth="1" min="6" max="6"/>
-    <col width="40" customWidth="1" min="7" max="7"/>
-    <col width="40" customWidth="1" min="8" max="8"/>
-    <col width="40" customWidth="1" min="9" max="9"/>
-    <col width="28" customWidth="1" min="10" max="10"/>
-    <col width="40" customWidth="1" min="11" max="11"/>
-    <col width="40" customWidth="1" min="12" max="12"/>
-    <col width="40" customWidth="1" min="13" max="13"/>
-    <col width="40" customWidth="1" min="14" max="14"/>
-    <col width="40" customWidth="1" min="15" max="15"/>
-    <col width="30" customWidth="1" min="16" max="16"/>
-    <col width="40" customWidth="1" min="17" max="17"/>
-    <col width="40" customWidth="1" min="18" max="18"/>
-    <col width="40" customWidth="1" min="19" max="19"/>
-    <col width="40" customWidth="1" min="20" max="20"/>
-    <col width="25" customWidth="1" min="21" max="21"/>
+    <col width="24" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="30" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="36" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="24" customWidth="1" min="11" max="11"/>
+    <col width="24" customWidth="1" min="12" max="12"/>
+    <col width="22" customWidth="1" min="13" max="13"/>
+    <col width="18" customWidth="1" min="14" max="14"/>
+    <col width="28" customWidth="1" min="15" max="15"/>
+    <col width="45" customWidth="1" min="16" max="16"/>
+    <col width="26" customWidth="1" min="17" max="17"/>
+    <col width="14" customWidth="1" min="18" max="18"/>
+    <col width="30" customWidth="1" min="19" max="19"/>
+    <col width="30" customWidth="1" min="20" max="20"/>
+    <col width="14" customWidth="1" min="21" max="21"/>
     <col width="13" customWidth="1" min="22" max="22"/>
     <col width="23" customWidth="1" min="23" max="23"/>
-    <col width="50" customWidth="1" min="24" max="24"/>
+    <col width="55" customWidth="1" min="24" max="24"/>
     <col width="20" customWidth="1" min="25" max="25"/>
     <col width="24" customWidth="1" min="26" max="26"/>
-    <col width="40" customWidth="1" min="27" max="27"/>
-    <col width="35" customWidth="1" min="28" max="28"/>
+    <col width="55" customWidth="1" min="27" max="27"/>
+    <col width="45" customWidth="1" min="28" max="28"/>
     <col width="13" customWidth="1" min="29" max="29"/>
     <col width="40" customWidth="1" min="30" max="30"/>
-    <col width="50" customWidth="1" min="31" max="31"/>
-    <col width="40" customWidth="1" min="32" max="32"/>
-    <col width="50" customWidth="1" min="33" max="33"/>
-    <col width="50" customWidth="1" min="34" max="34"/>
+    <col width="55" customWidth="1" min="31" max="31"/>
+    <col width="26" customWidth="1" min="32" max="32"/>
+    <col width="65" customWidth="1" min="33" max="33"/>
+    <col width="65" customWidth="1" min="34" max="34"/>
     <col width="20" customWidth="1" min="35" max="35"/>
-    <col width="30" customWidth="1" min="36" max="36"/>
+    <col width="40" customWidth="1" min="36" max="36"/>
     <col width="11" customWidth="1" min="37" max="37"/>
-    <col width="32" customWidth="1" min="38" max="38"/>
-    <col width="22" customWidth="1" min="39" max="39"/>
+    <col width="20" customWidth="1" min="38" max="38"/>
+    <col width="20" customWidth="1" min="39" max="39"/>
     <col width="18" customWidth="1" min="40" max="40"/>
-    <col width="30" customWidth="1" min="41" max="41"/>
-    <col width="26" customWidth="1" min="42" max="42"/>
-    <col width="40" customWidth="1" min="43" max="43"/>
+    <col width="40" customWidth="1" min="41" max="41"/>
+    <col width="22" customWidth="1" min="42" max="42"/>
+    <col width="55" customWidth="1" min="43" max="43"/>
     <col width="15" customWidth="1" min="44" max="44"/>
   </cols>
   <sheetData>
@@ -34892,9 +34892,1339 @@
         </is>
       </c>
     </row>
+    <row r="164">
+      <c r="A164" s="2" t="inlineStr">
+        <is>
+          <t>ThinkPad E14 超能版 G7</t>
+        </is>
+      </c>
+      <c r="B164" s="2" t="inlineStr">
+        <is>
+          <t>E Series</t>
+        </is>
+      </c>
+      <c r="C164" s="2" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D164" s="2" t="inlineStr">
+        <is>
+          <t>Gen 7 超能版</t>
+        </is>
+      </c>
+      <c r="E164" s="2" t="inlineStr">
+        <is>
+          <t>14"</t>
+        </is>
+      </c>
+      <c r="F164" s="2" t="inlineStr">
+        <is>
+          <t>2880×1800 (2.8K)</t>
+        </is>
+      </c>
+      <c r="G164" s="2" t="inlineStr">
+        <is>
+          <t>120Hz</t>
+        </is>
+      </c>
+      <c r="H164" s="2" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="I164" s="2" t="inlineStr">
+        <is>
+          <t>Intel Core 5 220H / Core 7 250H (Raptor Lake-H Refresh)</t>
+        </is>
+      </c>
+      <c r="J164" s="2" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="K164" s="2" t="inlineStr">
+        <is>
+          <t>Intel Graphics / Intel Arc Graphics</t>
+        </is>
+      </c>
+      <c r="L164" s="2" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="M164" s="2" t="inlineStr">
+        <is>
+          <t>DDR5-5200 (Core 5) / DDR5-5600 (Core 7)</t>
+        </is>
+      </c>
+      <c r="N164" s="2" t="inlineStr">
+        <is>
+          <t>64GB (2 SODIMM)</t>
+        </is>
+      </c>
+      <c r="O164" s="2" t="inlineStr">
+        <is>
+          <t>M.2 2242 PCIe Gen4 SSD</t>
+        </is>
+      </c>
+      <c r="P164" s="2" t="inlineStr">
+        <is>
+          <t>1×USB-A 3.2 Gen1, 1×USB-A 3.2 Gen2, 1×TB4, 1×USB-C 3.2 Gen2, HDMI 2.1, RJ-45, 3.5mm音频</t>
+        </is>
+      </c>
+      <c r="Q164" s="2" t="inlineStr">
+        <is>
+          <t>Wi-Fi 6E + BT 5.3</t>
+        </is>
+      </c>
+      <c r="R164" s="2" t="inlineStr">
+        <is>
+          <t>选配</t>
+        </is>
+      </c>
+      <c r="S164" s="2" t="inlineStr">
+        <is>
+          <t>FHD 1080p + IR (ThinkShutter)</t>
+        </is>
+      </c>
+      <c r="T164" s="2" t="inlineStr">
+        <is>
+          <t>64Wh</t>
+        </is>
+      </c>
+      <c r="U164" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="V164" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="W164" s="2" t="inlineStr"/>
+      <c r="X164" s="2" t="inlineStr"/>
+      <c r="Y164" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="Z164" s="2" t="inlineStr"/>
+      <c r="AA164" s="2" t="inlineStr">
+        <is>
+          <t>中国市场特供'超能版'，使用Core 5/7处理器（非Core Ultra），2.8K 120Hz IPS屏</t>
+        </is>
+      </c>
+      <c r="AB164" s="2" t="inlineStr"/>
+      <c r="AC164" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AD164" s="2" t="inlineStr"/>
+      <c r="AE164" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AF164" s="2" t="inlineStr">
+        <is>
+          <t>一般 (3.0/5)</t>
+        </is>
+      </c>
+      <c r="AG164" s="2" t="inlineStr"/>
+      <c r="AH164" s="2" t="inlineStr">
+        <is>
+          <t>[中国市场数据 (2026)] Core 5/7 220H/250H 较新，Linux内核支持待验证；指纹传感器可能需要额外驱动</t>
+        </is>
+      </c>
+      <c r="AI164" s="2" t="inlineStr">
+        <is>
+          <t>4999-7799</t>
+        </is>
+      </c>
+      <c r="AJ164" s="2" t="inlineStr"/>
+      <c r="AK164" s="2" t="inlineStr">
+        <is>
+          <t>新品</t>
+        </is>
+      </c>
+      <c r="AL164" s="2" t="inlineStr">
+        <is>
+          <t>低(社区预估)</t>
+        </is>
+      </c>
+      <c r="AM164" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="AN164" s="2" t="inlineStr">
+        <is>
+          <t>★★★☆☆</t>
+        </is>
+      </c>
+      <c r="AO164" s="2" t="inlineStr">
+        <is>
+          <t>source: 中国市场社区预估; ubuntu: 未确认; fedora: 未测试; arch: 未测试; community: 中国社区报告</t>
+        </is>
+      </c>
+      <c r="AP164" s="2" t="inlineStr">
+        <is>
+          <t>中 (1个官方来源)</t>
+        </is>
+      </c>
+      <c r="AQ164" s="2" t="inlineStr">
+        <is>
+          <t>https://www.lenovo.com.cn, https://item.lenovo.com.cn</t>
+        </is>
+      </c>
+      <c r="AR164" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="2" t="inlineStr">
+        <is>
+          <t>ThinkPad E16 超能版 G7</t>
+        </is>
+      </c>
+      <c r="B165" s="2" t="inlineStr">
+        <is>
+          <t>E Series</t>
+        </is>
+      </c>
+      <c r="C165" s="2" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D165" s="2" t="inlineStr">
+        <is>
+          <t>Gen 7 超能版</t>
+        </is>
+      </c>
+      <c r="E165" s="2" t="inlineStr">
+        <is>
+          <t>16"</t>
+        </is>
+      </c>
+      <c r="F165" s="2" t="inlineStr">
+        <is>
+          <t>2560×1600 (2.5K)</t>
+        </is>
+      </c>
+      <c r="G165" s="2" t="inlineStr">
+        <is>
+          <t>120Hz</t>
+        </is>
+      </c>
+      <c r="H165" s="2" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="I165" s="2" t="inlineStr">
+        <is>
+          <t>Intel Core 5 220H / Core 7 250H (Raptor Lake-H Refresh)</t>
+        </is>
+      </c>
+      <c r="J165" s="2" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="K165" s="2" t="inlineStr">
+        <is>
+          <t>Intel Graphics / Intel Arc Graphics</t>
+        </is>
+      </c>
+      <c r="L165" s="2" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="M165" s="2" t="inlineStr">
+        <is>
+          <t>DDR5-5200 (Core 5) / DDR5-5600 (Core 7)</t>
+        </is>
+      </c>
+      <c r="N165" s="2" t="inlineStr">
+        <is>
+          <t>64GB (2 SODIMM)</t>
+        </is>
+      </c>
+      <c r="O165" s="2" t="inlineStr">
+        <is>
+          <t>M.2 2242 PCIe Gen4 SSD</t>
+        </is>
+      </c>
+      <c r="P165" s="2" t="inlineStr">
+        <is>
+          <t>1×USB-A 3.2 Gen1, 1×USB-A 3.2 Gen2, 1×TB4, 1×USB-C 3.2 Gen2, HDMI 2.1, RJ-45, 3.5mm音频</t>
+        </is>
+      </c>
+      <c r="Q165" s="2" t="inlineStr">
+        <is>
+          <t>Wi-Fi 6E + BT 5.3</t>
+        </is>
+      </c>
+      <c r="R165" s="2" t="inlineStr">
+        <is>
+          <t>选配</t>
+        </is>
+      </c>
+      <c r="S165" s="2" t="inlineStr">
+        <is>
+          <t>FHD 1080p + IR (ThinkShutter)</t>
+        </is>
+      </c>
+      <c r="T165" s="2" t="inlineStr">
+        <is>
+          <t>64Wh</t>
+        </is>
+      </c>
+      <c r="U165" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="V165" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="W165" s="2" t="inlineStr"/>
+      <c r="X165" s="2" t="inlineStr"/>
+      <c r="Y165" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="Z165" s="2" t="inlineStr"/>
+      <c r="AA165" s="2" t="inlineStr">
+        <is>
+          <t>中国市场特供'超能版'，E14的大屏版本</t>
+        </is>
+      </c>
+      <c r="AB165" s="2" t="inlineStr"/>
+      <c r="AC165" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AD165" s="2" t="inlineStr"/>
+      <c r="AE165" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AF165" s="2" t="inlineStr">
+        <is>
+          <t>一般 (3.0/5)</t>
+        </is>
+      </c>
+      <c r="AG165" s="2" t="inlineStr"/>
+      <c r="AH165" s="2" t="inlineStr">
+        <is>
+          <t>[中国市场数据 (2026)] 同E14超能版；16寸版本散热可能更好</t>
+        </is>
+      </c>
+      <c r="AI165" s="2" t="inlineStr">
+        <is>
+          <t>7099-7999</t>
+        </is>
+      </c>
+      <c r="AJ165" s="2" t="inlineStr"/>
+      <c r="AK165" s="2" t="inlineStr">
+        <is>
+          <t>新品</t>
+        </is>
+      </c>
+      <c r="AL165" s="2" t="inlineStr">
+        <is>
+          <t>低(社区预估)</t>
+        </is>
+      </c>
+      <c r="AM165" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="AN165" s="2" t="inlineStr">
+        <is>
+          <t>★★★☆☆</t>
+        </is>
+      </c>
+      <c r="AO165" s="2" t="inlineStr">
+        <is>
+          <t>source: 中国市场社区预估; ubuntu: 未确认; fedora: 未测试; arch: 未测试; community: 中国社区报告</t>
+        </is>
+      </c>
+      <c r="AP165" s="2" t="inlineStr">
+        <is>
+          <t>中 (1个官方来源)</t>
+        </is>
+      </c>
+      <c r="AQ165" s="2" t="inlineStr">
+        <is>
+          <t>https://www.lenovo.com.cn</t>
+        </is>
+      </c>
+      <c r="AR165" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="2" t="inlineStr">
+        <is>
+          <t>ThinkPad T14p Gen 1</t>
+        </is>
+      </c>
+      <c r="B166" s="2" t="inlineStr">
+        <is>
+          <t>T Series</t>
+        </is>
+      </c>
+      <c r="C166" s="2" t="n">
+        <v>2023</v>
+      </c>
+      <c r="D166" s="2" t="inlineStr">
+        <is>
+          <t>Gen 1</t>
+        </is>
+      </c>
+      <c r="E166" s="2" t="inlineStr">
+        <is>
+          <t>14"</t>
+        </is>
+      </c>
+      <c r="F166" s="2" t="inlineStr">
+        <is>
+          <t>2240×1400 (2.2K)</t>
+        </is>
+      </c>
+      <c r="G166" s="2" t="inlineStr">
+        <is>
+          <t>60Hz</t>
+        </is>
+      </c>
+      <c r="H166" s="2" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="I166" s="2" t="inlineStr">
+        <is>
+          <t>Intel Core i5-13500H / i7-13700H / i9-13900H (Raptor Lake-H, 45W)</t>
+        </is>
+      </c>
+      <c r="J166" s="2" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="K166" s="2" t="inlineStr">
+        <is>
+          <t>Intel Iris Xe Graphics</t>
+        </is>
+      </c>
+      <c r="L166" s="2" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="M166" s="2" t="inlineStr">
+        <is>
+          <t>DDR5-4800</t>
+        </is>
+      </c>
+      <c r="N166" s="2" t="inlineStr">
+        <is>
+          <t>48GB (板载+插槽)</t>
+        </is>
+      </c>
+      <c r="O166" s="2" t="inlineStr">
+        <is>
+          <t>M.2 2280 PCIe Gen4 SSD</t>
+        </is>
+      </c>
+      <c r="P166" s="2" t="inlineStr">
+        <is>
+          <t>2×TB4, 2×USB-A 3.2 Gen1, HDMI 2.1, RJ-45, 3.5mm音频</t>
+        </is>
+      </c>
+      <c r="Q166" s="2" t="inlineStr">
+        <is>
+          <t>Wi-Fi 6E + BT 5.3</t>
+        </is>
+      </c>
+      <c r="R166" s="2" t="inlineStr">
+        <is>
+          <t>有 (Match-on-Chip)</t>
+        </is>
+      </c>
+      <c r="S166" s="2" t="inlineStr">
+        <is>
+          <t>FHD 1080p + IR (ThinkShutter)</t>
+        </is>
+      </c>
+      <c r="T166" s="2" t="inlineStr">
+        <is>
+          <t>57Wh</t>
+        </is>
+      </c>
+      <c r="U166" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="V166" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="W166" s="2" t="inlineStr"/>
+      <c r="X166" s="2" t="inlineStr"/>
+      <c r="Y166" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="Z166" s="2" t="inlineStr"/>
+      <c r="AA166" s="2" t="inlineStr">
+        <is>
+          <t>中国市场独有'T14p'，定位'工程师本'，H系列高性能CPU</t>
+        </is>
+      </c>
+      <c r="AB166" s="2" t="inlineStr"/>
+      <c r="AC166" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AD166" s="2" t="inlineStr"/>
+      <c r="AE166" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AF166" s="2" t="inlineStr">
+        <is>
+          <t>良好 (4.0/5)</t>
+        </is>
+      </c>
+      <c r="AG166" s="2" t="inlineStr"/>
+      <c r="AH166" s="2" t="inlineStr">
+        <is>
+          <t>[中国市场数据 (2026)] H系列CPU功耗较高，续航一般；Linux下功耗管理需优化</t>
+        </is>
+      </c>
+      <c r="AI166" s="2" t="inlineStr">
+        <is>
+          <t>3500-5500</t>
+        </is>
+      </c>
+      <c r="AJ166" s="2" t="inlineStr"/>
+      <c r="AK166" s="2" t="inlineStr">
+        <is>
+          <t>7-9成新</t>
+        </is>
+      </c>
+      <c r="AL166" s="2" t="inlineStr">
+        <is>
+          <t>低(社区预估)</t>
+        </is>
+      </c>
+      <c r="AM166" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="AN166" s="2" t="inlineStr">
+        <is>
+          <t>★★★★☆</t>
+        </is>
+      </c>
+      <c r="AO166" s="2" t="inlineStr">
+        <is>
+          <t>source: 中国市场社区预估; ubuntu: 未确认; fedora: 未测试; arch: 未测试; community: 中国社区报告</t>
+        </is>
+      </c>
+      <c r="AP166" s="2" t="inlineStr">
+        <is>
+          <t>中 (社区来源)</t>
+        </is>
+      </c>
+      <c r="AQ166" s="2" t="inlineStr">
+        <is>
+          <t>https://post.smzdm.com, https://www.ithome.com</t>
+        </is>
+      </c>
+      <c r="AR166" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="2" t="inlineStr">
+        <is>
+          <t>ThinkPad T14p Gen 2</t>
+        </is>
+      </c>
+      <c r="B167" s="2" t="inlineStr">
+        <is>
+          <t>T Series</t>
+        </is>
+      </c>
+      <c r="C167" s="2" t="n">
+        <v>2024</v>
+      </c>
+      <c r="D167" s="2" t="inlineStr">
+        <is>
+          <t>Gen 2</t>
+        </is>
+      </c>
+      <c r="E167" s="2" t="inlineStr">
+        <is>
+          <t>14.5"</t>
+        </is>
+      </c>
+      <c r="F167" s="2" t="inlineStr">
+        <is>
+          <t>3072×1920 (3K)</t>
+        </is>
+      </c>
+      <c r="G167" s="2" t="inlineStr">
+        <is>
+          <t>120Hz</t>
+        </is>
+      </c>
+      <c r="H167" s="2" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="I167" s="2" t="inlineStr">
+        <is>
+          <t>Intel Core Ultra 5/7/9 185H (Meteor Lake-H, 45W)</t>
+        </is>
+      </c>
+      <c r="J167" s="2" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="K167" s="2" t="inlineStr">
+        <is>
+          <t>Intel Arc Graphics</t>
+        </is>
+      </c>
+      <c r="L167" s="2" t="inlineStr">
+        <is>
+          <t>NVIDIA RTX 4050 6GB (可选)</t>
+        </is>
+      </c>
+      <c r="M167" s="2" t="inlineStr">
+        <is>
+          <t>DDR5-5600</t>
+        </is>
+      </c>
+      <c r="N167" s="2" t="inlineStr">
+        <is>
+          <t>64GB (2 SODIMM)</t>
+        </is>
+      </c>
+      <c r="O167" s="2" t="inlineStr">
+        <is>
+          <t>M.2 2280 PCIe Gen4 SSD</t>
+        </is>
+      </c>
+      <c r="P167" s="2" t="inlineStr">
+        <is>
+          <t>2×TB4, 2×USB-A 3.2 Gen1, HDMI 2.1, RJ-45, 3.5mm音频</t>
+        </is>
+      </c>
+      <c r="Q167" s="2" t="inlineStr">
+        <is>
+          <t>Wi-Fi 6E + BT 5.3</t>
+        </is>
+      </c>
+      <c r="R167" s="2" t="inlineStr">
+        <is>
+          <t>有 (Match-on-Chip)</t>
+        </is>
+      </c>
+      <c r="S167" s="2" t="inlineStr">
+        <is>
+          <t>FHD 1080p + IR (ThinkShutter)</t>
+        </is>
+      </c>
+      <c r="T167" s="2" t="inlineStr">
+        <is>
+          <t>75Wh</t>
+        </is>
+      </c>
+      <c r="U167" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="V167" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="W167" s="2" t="inlineStr"/>
+      <c r="X167" s="2" t="inlineStr"/>
+      <c r="Y167" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="Z167" s="2" t="inlineStr"/>
+      <c r="AA167" s="2" t="inlineStr">
+        <is>
+          <t>中国市场独有，升级14.5寸3K 120Hz屏，可选RTX 4050独显</t>
+        </is>
+      </c>
+      <c r="AB167" s="2" t="inlineStr"/>
+      <c r="AC167" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AD167" s="2" t="inlineStr"/>
+      <c r="AE167" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AF167" s="2" t="inlineStr">
+        <is>
+          <t>一般 (3.0/5)</t>
+        </is>
+      </c>
+      <c r="AG167" s="2" t="inlineStr"/>
+      <c r="AH167" s="2" t="inlineStr">
+        <is>
+          <t>[中国市场数据 (2026)] RTX 4050在Linux下需NVIDIA专有驱动；Meteor Lake核显支持较好</t>
+        </is>
+      </c>
+      <c r="AI167" s="2" t="inlineStr">
+        <is>
+          <t>5500-8500</t>
+        </is>
+      </c>
+      <c r="AJ167" s="2" t="inlineStr"/>
+      <c r="AK167" s="2" t="inlineStr">
+        <is>
+          <t>7-9成新</t>
+        </is>
+      </c>
+      <c r="AL167" s="2" t="inlineStr">
+        <is>
+          <t>低(社区预估)</t>
+        </is>
+      </c>
+      <c r="AM167" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="AN167" s="2" t="inlineStr">
+        <is>
+          <t>★★★☆☆</t>
+        </is>
+      </c>
+      <c r="AO167" s="2" t="inlineStr">
+        <is>
+          <t>source: 中国市场社区预估; ubuntu: 未确认; fedora: 未测试; arch: 未测试; community: 中国社区报告</t>
+        </is>
+      </c>
+      <c r="AP167" s="2" t="inlineStr">
+        <is>
+          <t>中 (社区来源)</t>
+        </is>
+      </c>
+      <c r="AQ167" s="2" t="inlineStr">
+        <is>
+          <t>https://post.smzdm.com, https://www.ithome.com</t>
+        </is>
+      </c>
+      <c r="AR167" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="2" t="inlineStr">
+        <is>
+          <t>ThinkPad T14p Gen 3</t>
+        </is>
+      </c>
+      <c r="B168" s="2" t="inlineStr">
+        <is>
+          <t>T Series</t>
+        </is>
+      </c>
+      <c r="C168" s="2" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D168" s="2" t="inlineStr">
+        <is>
+          <t>Gen 3</t>
+        </is>
+      </c>
+      <c r="E168" s="2" t="inlineStr">
+        <is>
+          <t>14.5"</t>
+        </is>
+      </c>
+      <c r="F168" s="2" t="inlineStr">
+        <is>
+          <t>3072×1920 (3K)</t>
+        </is>
+      </c>
+      <c r="G168" s="2" t="inlineStr">
+        <is>
+          <t>120Hz</t>
+        </is>
+      </c>
+      <c r="H168" s="2" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="I168" s="2" t="inlineStr">
+        <is>
+          <t>Intel Core Ultra 5/7/9 285H (Arrow Lake-H, 45W)</t>
+        </is>
+      </c>
+      <c r="J168" s="2" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="K168" s="2" t="inlineStr">
+        <is>
+          <t>Intel Arc Graphics</t>
+        </is>
+      </c>
+      <c r="L168" s="2" t="inlineStr">
+        <is>
+          <t>NVIDIA RTX 5050 8GB (可选)</t>
+        </is>
+      </c>
+      <c r="M168" s="2" t="inlineStr">
+        <is>
+          <t>DDR5-6400</t>
+        </is>
+      </c>
+      <c r="N168" s="2" t="inlineStr">
+        <is>
+          <t>64GB (2 SODIMM)</t>
+        </is>
+      </c>
+      <c r="O168" s="2" t="inlineStr">
+        <is>
+          <t>M.2 2280 PCIe Gen5 SSD</t>
+        </is>
+      </c>
+      <c r="P168" s="2" t="inlineStr">
+        <is>
+          <t>2×TB4, 2×USB-A 3.2 Gen1, HDMI 2.1, RJ-45, 3.5mm音频</t>
+        </is>
+      </c>
+      <c r="Q168" s="2" t="inlineStr">
+        <is>
+          <t>Wi-Fi 7 + BT 5.4</t>
+        </is>
+      </c>
+      <c r="R168" s="2" t="inlineStr">
+        <is>
+          <t>有 (Match-on-Chip)</t>
+        </is>
+      </c>
+      <c r="S168" s="2" t="inlineStr">
+        <is>
+          <t>FHD 1080p + IR (ThinkShutter)</t>
+        </is>
+      </c>
+      <c r="T168" s="2" t="inlineStr">
+        <is>
+          <t>75Wh</t>
+        </is>
+      </c>
+      <c r="U168" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="V168" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="W168" s="2" t="inlineStr"/>
+      <c r="X168" s="2" t="inlineStr"/>
+      <c r="Y168" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="Z168" s="2" t="inlineStr"/>
+      <c r="AA168" s="2" t="inlineStr">
+        <is>
+          <t>中国市场独有最新代，RTX 5050独显，Wi-Fi 7</t>
+        </is>
+      </c>
+      <c r="AB168" s="2" t="inlineStr"/>
+      <c r="AC168" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AD168" s="2" t="inlineStr"/>
+      <c r="AE168" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AF168" s="2" t="inlineStr">
+        <is>
+          <t>一般 (3.0/5)</t>
+        </is>
+      </c>
+      <c r="AG168" s="2" t="inlineStr"/>
+      <c r="AH168" s="2" t="inlineStr">
+        <is>
+          <t>[中国市场数据 (2026)] RTX 5050太新，Linux驱动可能不完善；Arrow Lake Linux支持待验证</t>
+        </is>
+      </c>
+      <c r="AI168" s="2" t="inlineStr">
+        <is>
+          <t>8999-13999</t>
+        </is>
+      </c>
+      <c r="AJ168" s="2" t="inlineStr"/>
+      <c r="AK168" s="2" t="inlineStr">
+        <is>
+          <t>新品</t>
+        </is>
+      </c>
+      <c r="AL168" s="2" t="inlineStr">
+        <is>
+          <t>低(社区预估)</t>
+        </is>
+      </c>
+      <c r="AM168" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="AN168" s="2" t="inlineStr">
+        <is>
+          <t>★★★☆☆</t>
+        </is>
+      </c>
+      <c r="AO168" s="2" t="inlineStr">
+        <is>
+          <t>source: 中国市场社区预估; ubuntu: 未确认; fedora: 未测试; arch: 未测试; community: 中国社区报告</t>
+        </is>
+      </c>
+      <c r="AP168" s="2" t="inlineStr">
+        <is>
+          <t>中 (官方+社区)</t>
+        </is>
+      </c>
+      <c r="AQ168" s="2" t="inlineStr">
+        <is>
+          <t>https://www.lenovo.com.cn, https://item.jd.com</t>
+        </is>
+      </c>
+      <c r="AR168" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="2" t="inlineStr">
+        <is>
+          <t>ThinkPad L14p Gen 6</t>
+        </is>
+      </c>
+      <c r="B169" s="2" t="inlineStr">
+        <is>
+          <t>L Series</t>
+        </is>
+      </c>
+      <c r="C169" s="2" t="n">
+        <v>2024</v>
+      </c>
+      <c r="D169" s="2" t="inlineStr">
+        <is>
+          <t>Gen 6</t>
+        </is>
+      </c>
+      <c r="E169" s="2" t="inlineStr">
+        <is>
+          <t>14"</t>
+        </is>
+      </c>
+      <c r="F169" s="2" t="inlineStr">
+        <is>
+          <t>2240×1400 (2.2K)</t>
+        </is>
+      </c>
+      <c r="G169" s="2" t="inlineStr">
+        <is>
+          <t>60Hz</t>
+        </is>
+      </c>
+      <c r="H169" s="2" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="I169" s="2" t="inlineStr">
+        <is>
+          <t>Intel Core Ultra 5 225U / Core Ultra 7 255H / Core 5 210H / Core 7 240H</t>
+        </is>
+      </c>
+      <c r="J169" s="2" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="K169" s="2" t="inlineStr">
+        <is>
+          <t>Intel Graphics / Intel Arc Graphics</t>
+        </is>
+      </c>
+      <c r="L169" s="2" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="M169" s="2" t="inlineStr">
+        <is>
+          <t>DDR5</t>
+        </is>
+      </c>
+      <c r="N169" s="2" t="inlineStr">
+        <is>
+          <t>64GB</t>
+        </is>
+      </c>
+      <c r="O169" s="2" t="inlineStr">
+        <is>
+          <t>M.2 2280 PCIe Gen4 SSD</t>
+        </is>
+      </c>
+      <c r="P169" s="2" t="inlineStr">
+        <is>
+          <t>USB-C, USB-A, HDMI, RJ-45</t>
+        </is>
+      </c>
+      <c r="Q169" s="2" t="inlineStr">
+        <is>
+          <t>Wi-Fi 6E + BT 5.3</t>
+        </is>
+      </c>
+      <c r="R169" s="2" t="inlineStr">
+        <is>
+          <t>选配</t>
+        </is>
+      </c>
+      <c r="S169" s="2" t="inlineStr">
+        <is>
+          <t>FHD 1080p</t>
+        </is>
+      </c>
+      <c r="T169" s="2" t="inlineStr">
+        <is>
+          <t>未确认</t>
+        </is>
+      </c>
+      <c r="U169" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="V169" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="W169" s="2" t="inlineStr"/>
+      <c r="X169" s="2" t="inlineStr"/>
+      <c r="Y169" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="Z169" s="2" t="inlineStr"/>
+      <c r="AA169" s="2" t="inlineStr">
+        <is>
+          <t>中国市场独有'L14p'，通过政教及大企业官网销售，全球L系列无'p'版本</t>
+        </is>
+      </c>
+      <c r="AB169" s="2" t="inlineStr"/>
+      <c r="AC169" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AD169" s="2" t="inlineStr"/>
+      <c r="AE169" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AF169" s="2" t="inlineStr">
+        <is>
+          <t>一般 (3.0/5)</t>
+        </is>
+      </c>
+      <c r="AG169" s="2" t="inlineStr"/>
+      <c r="AH169" s="2" t="inlineStr">
+        <is>
+          <t>[中国市场数据 (2026)] L系列Linux支持一般；企业渠道机型，零售市场少见</t>
+        </is>
+      </c>
+      <c r="AI169" s="2" t="inlineStr">
+        <is>
+          <t>5000-7000</t>
+        </is>
+      </c>
+      <c r="AJ169" s="2" t="inlineStr"/>
+      <c r="AK169" s="2" t="inlineStr">
+        <is>
+          <t>企业采购</t>
+        </is>
+      </c>
+      <c r="AL169" s="2" t="inlineStr">
+        <is>
+          <t>低(社区预估)</t>
+        </is>
+      </c>
+      <c r="AM169" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="AN169" s="2" t="inlineStr">
+        <is>
+          <t>★★★☆☆</t>
+        </is>
+      </c>
+      <c r="AO169" s="2" t="inlineStr">
+        <is>
+          <t>source: 中国市场社区预估; ubuntu: 未确认; fedora: 未测试; arch: 未测试; community: 中国社区报告</t>
+        </is>
+      </c>
+      <c r="AP169" s="2" t="inlineStr">
+        <is>
+          <t>低 (仅企业渠道信息)</t>
+        </is>
+      </c>
+      <c r="AQ169" s="2" t="inlineStr">
+        <is>
+          <t>https://biz.lenovo.com.cn</t>
+        </is>
+      </c>
+      <c r="AR169" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="2" t="inlineStr">
+        <is>
+          <t>ThinkPad X14 Gen 1</t>
+        </is>
+      </c>
+      <c r="B170" s="2" t="inlineStr">
+        <is>
+          <t>X Series</t>
+        </is>
+      </c>
+      <c r="C170" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D170" s="2" t="inlineStr">
+        <is>
+          <t>Gen 1</t>
+        </is>
+      </c>
+      <c r="E170" s="2" t="inlineStr">
+        <is>
+          <t>14"</t>
+        </is>
+      </c>
+      <c r="F170" s="2" t="inlineStr">
+        <is>
+          <t>2880×1800 (2.8K)</t>
+        </is>
+      </c>
+      <c r="G170" s="2" t="inlineStr">
+        <is>
+          <t>120Hz</t>
+        </is>
+      </c>
+      <c r="H170" s="2" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="I170" s="2" t="inlineStr">
+        <is>
+          <t>Intel Core Ultra (预计)</t>
+        </is>
+      </c>
+      <c r="J170" s="2" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="K170" s="2" t="inlineStr">
+        <is>
+          <t>Intel Arc Graphics (预计)</t>
+        </is>
+      </c>
+      <c r="L170" s="2" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="M170" s="2" t="inlineStr">
+        <is>
+          <t>LPDDR5x (预计)</t>
+        </is>
+      </c>
+      <c r="N170" s="2" t="inlineStr">
+        <is>
+          <t>32GB (预计)</t>
+        </is>
+      </c>
+      <c r="O170" s="2" t="inlineStr">
+        <is>
+          <t>M.2 2280 PCIe Gen4/5 SSD (预计)</t>
+        </is>
+      </c>
+      <c r="P170" s="2" t="inlineStr">
+        <is>
+          <t>TB4, USB-C, USB-A (预计)</t>
+        </is>
+      </c>
+      <c r="Q170" s="2" t="inlineStr">
+        <is>
+          <t>Wi-Fi 7 + BT 5.4 (预计)</t>
+        </is>
+      </c>
+      <c r="R170" s="2" t="inlineStr">
+        <is>
+          <t>有 (预计)</t>
+        </is>
+      </c>
+      <c r="S170" s="2" t="inlineStr">
+        <is>
+          <t>FHD 1080p + IR (预计)</t>
+        </is>
+      </c>
+      <c r="T170" s="2" t="inlineStr">
+        <is>
+          <t>未确认</t>
+        </is>
+      </c>
+      <c r="U170" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="V170" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="W170" s="2" t="inlineStr"/>
+      <c r="X170" s="2" t="inlineStr"/>
+      <c r="Y170" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="Z170" s="2" t="inlineStr"/>
+      <c r="AA170" s="2" t="inlineStr">
+        <is>
+          <t>2026年中国市场新线，定位X1 Carbon和X13之间，部分参数为预测值</t>
+        </is>
+      </c>
+      <c r="AB170" s="2" t="inlineStr"/>
+      <c r="AC170" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AD170" s="2" t="inlineStr"/>
+      <c r="AE170" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AF170" s="2" t="inlineStr">
+        <is>
+          <t>一般 (3.0/5)</t>
+        </is>
+      </c>
+      <c r="AG170" s="2" t="inlineStr"/>
+      <c r="AH170" s="2" t="inlineStr">
+        <is>
+          <t>[中国市场数据 (2026)] 2026年新机型，Linux兼容性待验证</t>
+        </is>
+      </c>
+      <c r="AI170" s="2" t="inlineStr">
+        <is>
+          <t>6999-8999</t>
+        </is>
+      </c>
+      <c r="AJ170" s="2" t="inlineStr"/>
+      <c r="AK170" s="2" t="inlineStr">
+        <is>
+          <t>新品</t>
+        </is>
+      </c>
+      <c r="AL170" s="2" t="inlineStr">
+        <is>
+          <t>低(社区预估)</t>
+        </is>
+      </c>
+      <c r="AM170" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="AN170" s="2" t="inlineStr">
+        <is>
+          <t>★★★☆☆</t>
+        </is>
+      </c>
+      <c r="AO170" s="2" t="inlineStr">
+        <is>
+          <t>source: 中国市场社区预估; ubuntu: 未确认; fedora: 未测试; arch: 未测试; community: 中国社区报告</t>
+        </is>
+      </c>
+      <c r="AP170" s="2" t="inlineStr">
+        <is>
+          <t>低 (预告信息)</t>
+        </is>
+      </c>
+      <c r="AQ170" s="2" t="inlineStr">
+        <is>
+          <t>https://www.ithome.com, https://product.pconline.com.cn</t>
+        </is>
+      </c>
+      <c r="AR170" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AR163"/>
-  <conditionalFormatting sqref="AN2:AN163">
+  <autoFilter ref="A1:AR170"/>
+  <conditionalFormatting sqref="AN2:AN170">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"★★★★★"</formula>
     </cfRule>
@@ -34914,7 +36244,7 @@
       <formula>"N/A"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="V2:V163">
+  <conditionalFormatting sqref="V2:V170">
     <cfRule type="cellIs" priority="7" operator="equal" dxfId="0">
       <formula>"是"</formula>
     </cfRule>
@@ -34925,7 +36255,7 @@
       <formula>"未确认"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Y2:Y163">
+  <conditionalFormatting sqref="Y2:Y170">
     <cfRule type="cellIs" priority="10" operator="equal" dxfId="0">
       <formula>"certified"</formula>
     </cfRule>
@@ -34948,7 +36278,7 @@
       <formula>"N/A"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AP2:AP163">
+  <conditionalFormatting sqref="AP2:AP170">
     <cfRule type="cellIs" priority="17" operator="equal" dxfId="0">
       <formula>"中高 (2个官方/权威来源)"</formula>
     </cfRule>
@@ -35013,7 +36343,7 @@
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>162</t>
+          <t>169</t>
         </is>
       </c>
     </row>
@@ -35025,7 +36355,7 @@
       </c>
       <c r="B6" s="6" t="inlineStr">
         <is>
-          <t>2019-2025</t>
+          <t>2019-2026</t>
         </is>
       </c>
     </row>

--- a/thinkpad_complete_research.xlsx
+++ b/thinkpad_complete_research.xlsx
@@ -6953,12 +6953,12 @@
       </c>
       <c r="AG30" s="2" t="inlineStr">
         <is>
-          <t>[V2EX (2025-04)] Thinkpad X系列做工好，轻便 | [联想社区] X13 Gen 2i 在Linux S3模式下可睡眠</t>
+          <t>[V2EX (2025-04)] Thinkpad X系列做工好，轻便 | [联想社区] X13 Gen 2i 在Linux S3模式下可睡眠 | [Reddit r/thinkpad (2025)] ThinkPad X系列在Reddit社区长期受推荐，Linux兼容性良好，轻薄便携+经典键盘是核心优势</t>
         </is>
       </c>
       <c r="AH30" s="2" t="inlineStr">
         <is>
-          <t>[联想社区 (club.lenovo.com.cn)] X13 Gen 2i/Gen 3: BIOS设置Linux S3模式后，睡眠唤醒触摸板卡顿严重。建议用回现代待机。 | [联想社区] S3模式下'很多硬件都存在问题'</t>
+          <t>[联想社区 (club.lenovo.com.cn)] X13 Gen 2i/Gen 3: BIOS设置Linux S3模式后，睡眠唤醒触摸板卡顿严重。建议用回现代待机。 | [联想社区] S3模式下'很多硬件都存在问题' | [Arch Wiki Laptop/Lenovo (2025)] ThinkPad现代机型s2idle睡眠模式在Linux下可能有唤醒问题，建议检查BIOS设置或使用内核参数</t>
         </is>
       </c>
       <c r="AI30" s="2" t="inlineStr">
@@ -7159,12 +7159,12 @@
       </c>
       <c r="AG31" s="2" t="inlineStr">
         <is>
-          <t>[V2EX (2025-04)] Thinkpad X系列做工好，轻便 | [联想社区] X13 Gen 2i 在Linux S3模式下可睡眠</t>
+          <t>[V2EX (2025-04)] Thinkpad X系列做工好，轻便 | [联想社区] X13 Gen 2i 在Linux S3模式下可睡眠 | [Reddit r/thinkpad (2025)] ThinkPad X系列在Reddit社区长期受推荐，Linux兼容性良好，轻薄便携+经典键盘是核心优势</t>
         </is>
       </c>
       <c r="AH31" s="2" t="inlineStr">
         <is>
-          <t>[联想社区 (club.lenovo.com.cn)] X13 Gen 2i/Gen 3: BIOS设置Linux S3模式后，睡眠唤醒触摸板卡顿严重。建议用回现代待机。 | [联想社区] S3模式下'很多硬件都存在问题'</t>
+          <t>[联想社区 (club.lenovo.com.cn)] X13 Gen 2i/Gen 3: BIOS设置Linux S3模式后，睡眠唤醒触摸板卡顿严重。建议用回现代待机。 | [联想社区] S3模式下'很多硬件都存在问题' | [Arch Wiki Laptop/Lenovo (2025)] ThinkPad现代机型s2idle睡眠模式在Linux下可能有唤醒问题，建议检查BIOS设置或使用内核参数</t>
         </is>
       </c>
       <c r="AI31" s="2" t="inlineStr">
@@ -7365,12 +7365,12 @@
       </c>
       <c r="AG32" s="2" t="inlineStr">
         <is>
-          <t>[V2EX (2025-04)] Thinkpad X系列做工好，轻便 | [联想社区] X13 Gen 2i 在Linux S3模式下可睡眠</t>
+          <t>[V2EX (2025-04)] Thinkpad X系列做工好，轻便 | [联想社区] X13 Gen 2i 在Linux S3模式下可睡眠 | [Reddit r/thinkpad (2025)] ThinkPad X系列在Reddit社区长期受推荐，Linux兼容性良好，轻薄便携+经典键盘是核心优势</t>
         </is>
       </c>
       <c r="AH32" s="2" t="inlineStr">
         <is>
-          <t>[联想社区 (club.lenovo.com.cn)] X13 Gen 2i/Gen 3: BIOS设置Linux S3模式后，睡眠唤醒触摸板卡顿严重。建议用回现代待机。 | [联想社区] S3模式下'很多硬件都存在问题'</t>
+          <t>[联想社区 (club.lenovo.com.cn)] X13 Gen 2i/Gen 3: BIOS设置Linux S3模式后，睡眠唤醒触摸板卡顿严重。建议用回现代待机。 | [联想社区] S3模式下'很多硬件都存在问题' | [Arch Wiki Laptop/Lenovo (2025)] ThinkPad现代机型s2idle睡眠模式在Linux下可能有唤醒问题，建议检查BIOS设置或使用内核参数</t>
         </is>
       </c>
       <c r="AI32" s="2" t="inlineStr">
@@ -8003,7 +8003,7 @@
       </c>
       <c r="AG35" s="2" t="inlineStr">
         <is>
-          <t>[Medium/Jason Evangelho] 类似的P1/X1E系列在Fedora上体验良好(提及X1E可作为参考) | [V2EX (2025-10)] 用户从X1 Extreme Gen 4升级到X1 Carbon Gen 13</t>
+          <t>[Medium/Jason Evangelho] 类似的P1/X1E系列在Fedora上体验良好(提及X1E可作为参考) | [V2EX (2025-10)] 用户从X1 Extreme Gen 4升级到X1 Carbon Gen 13 | [Reddit r/linuxonthinkpad (2025)] X1 Extreme/P1系列在Linux社区讨论活跃，NVIDIA Optimus虽有挑战但总体可解决，工作站级扩展性受好评</t>
         </is>
       </c>
       <c r="AH35" s="2" t="inlineStr">
@@ -8209,12 +8209,12 @@
       </c>
       <c r="AG36" s="2" t="inlineStr">
         <is>
-          <t>[V2EX (2025-04)] Thinkpad X系列做工好，轻便 | [联想社区] X13 Gen 2i 在Linux S3模式下可睡眠</t>
+          <t>[V2EX (2025-04)] Thinkpad X系列做工好，轻便 | [联想社区] X13 Gen 2i 在Linux S3模式下可睡眠 | [Reddit r/thinkpad (2025)] ThinkPad X系列在Reddit社区长期受推荐，Linux兼容性良好，轻薄便携+经典键盘是核心优势</t>
         </is>
       </c>
       <c r="AH36" s="2" t="inlineStr">
         <is>
-          <t>[联想社区 (club.lenovo.com.cn)] X13 Gen 2i/Gen 3: BIOS设置Linux S3模式后，睡眠唤醒触摸板卡顿严重。建议用回现代待机。 | [联想社区] S3模式下'很多硬件都存在问题'</t>
+          <t>[联想社区 (club.lenovo.com.cn)] X13 Gen 2i/Gen 3: BIOS设置Linux S3模式后，睡眠唤醒触摸板卡顿严重。建议用回现代待机。 | [联想社区] S3模式下'很多硬件都存在问题' | [Arch Wiki Laptop/Lenovo (2025)] ThinkPad现代机型s2idle睡眠模式在Linux下可能有唤醒问题，建议检查BIOS设置或使用内核参数</t>
         </is>
       </c>
       <c r="AI36" s="2" t="inlineStr"/>
@@ -8411,12 +8411,12 @@
       </c>
       <c r="AG37" s="2" t="inlineStr">
         <is>
-          <t>[V2EX (2025-04)] Thinkpad X系列做工好，轻便 | [联想社区] X13 Gen 2i 在Linux S3模式下可睡眠</t>
+          <t>[V2EX (2025-04)] Thinkpad X系列做工好，轻便 | [联想社区] X13 Gen 2i 在Linux S3模式下可睡眠 | [Reddit r/thinkpad (2025)] ThinkPad X系列在Reddit社区长期受推荐，Linux兼容性良好，轻薄便携+经典键盘是核心优势</t>
         </is>
       </c>
       <c r="AH37" s="2" t="inlineStr">
         <is>
-          <t>[联想社区 (club.lenovo.com.cn)] X13 Gen 2i/Gen 3: BIOS设置Linux S3模式后，睡眠唤醒触摸板卡顿严重。建议用回现代待机。 | [联想社区] S3模式下'很多硬件都存在问题'</t>
+          <t>[联想社区 (club.lenovo.com.cn)] X13 Gen 2i/Gen 3: BIOS设置Linux S3模式后，睡眠唤醒触摸板卡顿严重。建议用回现代待机。 | [联想社区] S3模式下'很多硬件都存在问题' | [Arch Wiki Laptop/Lenovo (2025)] ThinkPad现代机型s2idle睡眠模式在Linux下可能有唤醒问题，建议检查BIOS设置或使用内核参数</t>
         </is>
       </c>
       <c r="AI37" s="2" t="inlineStr"/>
@@ -8617,12 +8617,12 @@
       </c>
       <c r="AG38" s="2" t="inlineStr">
         <is>
-          <t>[V2EX (2025-04)] Thinkpad X系列做工好，轻便 | [联想社区] X13 Gen 2i 在Linux S3模式下可睡眠</t>
+          <t>[V2EX (2025-04)] Thinkpad X系列做工好，轻便 | [联想社区] X13 Gen 2i 在Linux S3模式下可睡眠 | [Reddit r/thinkpad (2025)] ThinkPad X系列在Reddit社区长期受推荐，Linux兼容性良好，轻薄便携+经典键盘是核心优势</t>
         </is>
       </c>
       <c r="AH38" s="2" t="inlineStr">
         <is>
-          <t>[联想社区 (club.lenovo.com.cn)] X13 Gen 2i/Gen 3: BIOS设置Linux S3模式后，睡眠唤醒触摸板卡顿严重。建议用回现代待机。 | [联想社区] S3模式下'很多硬件都存在问题'</t>
+          <t>[联想社区 (club.lenovo.com.cn)] X13 Gen 2i/Gen 3: BIOS设置Linux S3模式后，睡眠唤醒触摸板卡顿严重。建议用回现代待机。 | [联想社区] S3模式下'很多硬件都存在问题' | [Arch Wiki Laptop/Lenovo (2025)] ThinkPad现代机型s2idle睡眠模式在Linux下可能有唤醒问题，建议检查BIOS设置或使用内核参数</t>
         </is>
       </c>
       <c r="AI38" s="2" t="inlineStr">
@@ -9255,7 +9255,7 @@
       </c>
       <c r="AG41" s="2" t="inlineStr">
         <is>
-          <t>[Medium/Jason Evangelho] 类似的P1/X1E系列在Fedora上体验良好(提及X1E可作为参考) | [V2EX (2025-10)] 用户从X1 Extreme Gen 4升级到X1 Carbon Gen 13</t>
+          <t>[Medium/Jason Evangelho] 类似的P1/X1E系列在Fedora上体验良好(提及X1E可作为参考) | [V2EX (2025-10)] 用户从X1 Extreme Gen 4升级到X1 Carbon Gen 13 | [Reddit r/linuxonthinkpad (2025)] X1 Extreme/P1系列在Linux社区讨论活跃，NVIDIA Optimus虽有挑战但总体可解决，工作站级扩展性受好评</t>
         </is>
       </c>
       <c r="AH41" s="2" t="inlineStr">
@@ -9881,12 +9881,12 @@
       </c>
       <c r="AG44" s="2" t="inlineStr">
         <is>
-          <t>[V2EX (2025-04)] Thinkpad X系列做工好，轻便 | [联想社区] X13 Gen 2i 在Linux S3模式下可睡眠</t>
+          <t>[V2EX (2025-04)] Thinkpad X系列做工好，轻便 | [联想社区] X13 Gen 2i 在Linux S3模式下可睡眠 | [Reddit r/thinkpad (2025)] ThinkPad X系列在Reddit社区长期受推荐，Linux兼容性良好，轻薄便携+经典键盘是核心优势</t>
         </is>
       </c>
       <c r="AH44" s="2" t="inlineStr">
         <is>
-          <t>[联想社区 (club.lenovo.com.cn)] X13 Gen 2i/Gen 3: BIOS设置Linux S3模式后，睡眠唤醒触摸板卡顿严重。建议用回现代待机。 | [联想社区] S3模式下'很多硬件都存在问题'</t>
+          <t>[联想社区 (club.lenovo.com.cn)] X13 Gen 2i/Gen 3: BIOS设置Linux S3模式后，睡眠唤醒触摸板卡顿严重。建议用回现代待机。 | [联想社区] S3模式下'很多硬件都存在问题' | [Arch Wiki Laptop/Lenovo (2025)] ThinkPad现代机型s2idle睡眠模式在Linux下可能有唤醒问题，建议检查BIOS设置或使用内核参数</t>
         </is>
       </c>
       <c r="AI44" s="2" t="inlineStr"/>
@@ -10083,12 +10083,12 @@
       </c>
       <c r="AG45" s="2" t="inlineStr">
         <is>
-          <t>[V2EX (2025-04)] Thinkpad X系列做工好，轻便 | [联想社区] X13 Gen 2i 在Linux S3模式下可睡眠</t>
+          <t>[V2EX (2025-04)] Thinkpad X系列做工好，轻便 | [联想社区] X13 Gen 2i 在Linux S3模式下可睡眠 | [Reddit r/thinkpad (2025)] ThinkPad X系列在Reddit社区长期受推荐，Linux兼容性良好，轻薄便携+经典键盘是核心优势</t>
         </is>
       </c>
       <c r="AH45" s="2" t="inlineStr">
         <is>
-          <t>[联想社区 (club.lenovo.com.cn)] X13 Gen 2i/Gen 3: BIOS设置Linux S3模式后，睡眠唤醒触摸板卡顿严重。建议用回现代待机。 | [联想社区] S3模式下'很多硬件都存在问题'</t>
+          <t>[联想社区 (club.lenovo.com.cn)] X13 Gen 2i/Gen 3: BIOS设置Linux S3模式后，睡眠唤醒触摸板卡顿严重。建议用回现代待机。 | [联想社区] S3模式下'很多硬件都存在问题' | [Arch Wiki Laptop/Lenovo (2025)] ThinkPad现代机型s2idle睡眠模式在Linux下可能有唤醒问题，建议检查BIOS设置或使用内核参数</t>
         </is>
       </c>
       <c r="AI45" s="2" t="inlineStr"/>
@@ -10289,12 +10289,12 @@
       </c>
       <c r="AG46" s="2" t="inlineStr">
         <is>
-          <t>[V2EX (2025-04)] Thinkpad X系列做工好，轻便 | [联想社区] X13 Gen 2i 在Linux S3模式下可睡眠</t>
+          <t>[V2EX (2025-04)] Thinkpad X系列做工好，轻便 | [联想社区] X13 Gen 2i 在Linux S3模式下可睡眠 | [Reddit r/thinkpad (2025)] ThinkPad X系列在Reddit社区长期受推荐，Linux兼容性良好，轻薄便携+经典键盘是核心优势</t>
         </is>
       </c>
       <c r="AH46" s="2" t="inlineStr">
         <is>
-          <t>[联想社区 (club.lenovo.com.cn)] X13 Gen 2i/Gen 3: BIOS设置Linux S3模式后，睡眠唤醒触摸板卡顿严重。建议用回现代待机。 | [联想社区] S3模式下'很多硬件都存在问题'</t>
+          <t>[联想社区 (club.lenovo.com.cn)] X13 Gen 2i/Gen 3: BIOS设置Linux S3模式后，睡眠唤醒触摸板卡顿严重。建议用回现代待机。 | [联想社区] S3模式下'很多硬件都存在问题' | [Arch Wiki Laptop/Lenovo (2025)] ThinkPad现代机型s2idle睡眠模式在Linux下可能有唤醒问题，建议检查BIOS设置或使用内核参数</t>
         </is>
       </c>
       <c r="AI46" s="2" t="inlineStr">
@@ -10931,7 +10931,7 @@
       </c>
       <c r="AG49" s="2" t="inlineStr">
         <is>
-          <t>[Medium/Jason Evangelho] 类似的P1/X1E系列在Fedora上体验良好(提及X1E可作为参考) | [V2EX (2025-10)] 用户从X1 Extreme Gen 4升级到X1 Carbon Gen 13</t>
+          <t>[Medium/Jason Evangelho] 类似的P1/X1E系列在Fedora上体验良好(提及X1E可作为参考) | [V2EX (2025-10)] 用户从X1 Extreme Gen 4升级到X1 Carbon Gen 13 | [Reddit r/linuxonthinkpad (2025)] X1 Extreme/P1系列在Linux社区讨论活跃，NVIDIA Optimus虽有挑战但总体可解决，工作站级扩展性受好评</t>
         </is>
       </c>
       <c r="AH49" s="2" t="inlineStr">
@@ -11347,12 +11347,12 @@
       </c>
       <c r="AG51" s="2" t="inlineStr">
         <is>
-          <t>[V2EX (2025-04)] Thinkpad X系列做工好，轻便 | [联想社区] X13 Gen 2i 在Linux S3模式下可睡眠</t>
+          <t>[V2EX (2025-04)] Thinkpad X系列做工好，轻便 | [联想社区] X13 Gen 2i 在Linux S3模式下可睡眠 | [Reddit r/thinkpad (2025)] ThinkPad X系列在Reddit社区长期受推荐，Linux兼容性良好，轻薄便携+经典键盘是核心优势</t>
         </is>
       </c>
       <c r="AH51" s="2" t="inlineStr">
         <is>
-          <t>[联想社区 (club.lenovo.com.cn)] X13 Gen 2i/Gen 3: BIOS设置Linux S3模式后，睡眠唤醒触摸板卡顿严重。建议用回现代待机。 | [联想社区] S3模式下'很多硬件都存在问题'</t>
+          <t>[联想社区 (club.lenovo.com.cn)] X13 Gen 2i/Gen 3: BIOS设置Linux S3模式后，睡眠唤醒触摸板卡顿严重。建议用回现代待机。 | [联想社区] S3模式下'很多硬件都存在问题' | [Arch Wiki Laptop/Lenovo (2025)] ThinkPad现代机型s2idle睡眠模式在Linux下可能有唤醒问题，建议检查BIOS设置或使用内核参数</t>
         </is>
       </c>
       <c r="AI51" s="2" t="inlineStr">
@@ -11553,12 +11553,12 @@
       </c>
       <c r="AG52" s="2" t="inlineStr">
         <is>
-          <t>[V2EX (2025-04)] Thinkpad X系列做工好，轻便 | [联想社区] X13 Gen 2i 在Linux S3模式下可睡眠</t>
+          <t>[V2EX (2025-04)] Thinkpad X系列做工好，轻便 | [联想社区] X13 Gen 2i 在Linux S3模式下可睡眠 | [Reddit r/thinkpad (2025)] ThinkPad X系列在Reddit社区长期受推荐，Linux兼容性良好，轻薄便携+经典键盘是核心优势</t>
         </is>
       </c>
       <c r="AH52" s="2" t="inlineStr">
         <is>
-          <t>[联想社区 (club.lenovo.com.cn)] X13 Gen 2i/Gen 3: BIOS设置Linux S3模式后，睡眠唤醒触摸板卡顿严重。建议用回现代待机。 | [联想社区] S3模式下'很多硬件都存在问题'</t>
+          <t>[联想社区 (club.lenovo.com.cn)] X13 Gen 2i/Gen 3: BIOS设置Linux S3模式后，睡眠唤醒触摸板卡顿严重。建议用回现代待机。 | [联想社区] S3模式下'很多硬件都存在问题' | [Arch Wiki Laptop/Lenovo (2025)] ThinkPad现代机型s2idle睡眠模式在Linux下可能有唤醒问题，建议检查BIOS设置或使用内核参数</t>
         </is>
       </c>
       <c r="AI52" s="2" t="inlineStr"/>
@@ -11755,12 +11755,12 @@
       </c>
       <c r="AG53" s="2" t="inlineStr">
         <is>
-          <t>[V2EX (2025-04)] Thinkpad X系列做工好，轻便 | [联想社区] X13 Gen 2i 在Linux S3模式下可睡眠</t>
+          <t>[V2EX (2025-04)] Thinkpad X系列做工好，轻便 | [联想社区] X13 Gen 2i 在Linux S3模式下可睡眠 | [Reddit r/thinkpad (2025)] ThinkPad X系列在Reddit社区长期受推荐，Linux兼容性良好，轻薄便携+经典键盘是核心优势</t>
         </is>
       </c>
       <c r="AH53" s="2" t="inlineStr">
         <is>
-          <t>[联想社区 (club.lenovo.com.cn)] X13 Gen 2i/Gen 3: BIOS设置Linux S3模式后，睡眠唤醒触摸板卡顿严重。建议用回现代待机。 | [联想社区] S3模式下'很多硬件都存在问题'</t>
+          <t>[联想社区 (club.lenovo.com.cn)] X13 Gen 2i/Gen 3: BIOS设置Linux S3模式后，睡眠唤醒触摸板卡顿严重。建议用回现代待机。 | [联想社区] S3模式下'很多硬件都存在问题' | [Arch Wiki Laptop/Lenovo (2025)] ThinkPad现代机型s2idle睡眠模式在Linux下可能有唤醒问题，建议检查BIOS设置或使用内核参数</t>
         </is>
       </c>
       <c r="AI53" s="2" t="inlineStr"/>
@@ -11961,12 +11961,12 @@
       </c>
       <c r="AG54" s="2" t="inlineStr">
         <is>
-          <t>[V2EX (2025-04)] Thinkpad X系列做工好，轻便 | [联想社区] X13 Gen 2i 在Linux S3模式下可睡眠</t>
+          <t>[V2EX (2025-04)] Thinkpad X系列做工好，轻便 | [联想社区] X13 Gen 2i 在Linux S3模式下可睡眠 | [Reddit r/thinkpad (2025)] ThinkPad X系列在Reddit社区长期受推荐，Linux兼容性良好，轻薄便携+经典键盘是核心优势</t>
         </is>
       </c>
       <c r="AH54" s="2" t="inlineStr">
         <is>
-          <t>[联想社区 (club.lenovo.com.cn)] X13 Gen 2i/Gen 3: BIOS设置Linux S3模式后，睡眠唤醒触摸板卡顿严重。建议用回现代待机。 | [联想社区] S3模式下'很多硬件都存在问题'</t>
+          <t>[联想社区 (club.lenovo.com.cn)] X13 Gen 2i/Gen 3: BIOS设置Linux S3模式后，睡眠唤醒触摸板卡顿严重。建议用回现代待机。 | [联想社区] S3模式下'很多硬件都存在问题' | [Arch Wiki Laptop/Lenovo (2025)] ThinkPad现代机型s2idle睡眠模式在Linux下可能有唤醒问题，建议检查BIOS设置或使用内核参数</t>
         </is>
       </c>
       <c r="AI54" s="2" t="inlineStr">
@@ -12171,12 +12171,12 @@
       </c>
       <c r="AG55" s="2" t="inlineStr">
         <is>
-          <t>[V2EX (2025-04)] Thinkpad X系列做工好，轻便 | [联想社区] X13 Gen 2i 在Linux S3模式下可睡眠</t>
+          <t>[V2EX (2025-04)] Thinkpad X系列做工好，轻便 | [联想社区] X13 Gen 2i 在Linux S3模式下可睡眠 | [Reddit r/thinkpad (2025)] ThinkPad X系列在Reddit社区长期受推荐，Linux兼容性良好，轻薄便携+经典键盘是核心优势</t>
         </is>
       </c>
       <c r="AH55" s="2" t="inlineStr">
         <is>
-          <t>[联想社区 (club.lenovo.com.cn)] X13 Gen 2i/Gen 3: BIOS设置Linux S3模式后，睡眠唤醒触摸板卡顿严重。建议用回现代待机。 | [联想社区] S3模式下'很多硬件都存在问题'</t>
+          <t>[联想社区 (club.lenovo.com.cn)] X13 Gen 2i/Gen 3: BIOS设置Linux S3模式后，睡眠唤醒触摸板卡顿严重。建议用回现代待机。 | [联想社区] S3模式下'很多硬件都存在问题' | [Arch Wiki Laptop/Lenovo (2025)] ThinkPad现代机型s2idle睡眠模式在Linux下可能有唤醒问题，建议检查BIOS设置或使用内核参数</t>
         </is>
       </c>
       <c r="AI55" s="2" t="inlineStr">
@@ -12817,7 +12817,7 @@
       </c>
       <c r="AG58" s="2" t="inlineStr">
         <is>
-          <t>[Medium/Jason Evangelho] 类似的P1/X1E系列在Fedora上体验良好(提及X1E可作为参考) | [V2EX (2025-10)] 用户从X1 Extreme Gen 4升级到X1 Carbon Gen 13</t>
+          <t>[Medium/Jason Evangelho] 类似的P1/X1E系列在Fedora上体验良好(提及X1E可作为参考) | [V2EX (2025-10)] 用户从X1 Extreme Gen 4升级到X1 Carbon Gen 13 | [Reddit r/linuxonthinkpad (2025)] X1 Extreme/P1系列在Linux社区讨论活跃，NVIDIA Optimus虽有挑战但总体可解决，工作站级扩展性受好评</t>
         </is>
       </c>
       <c r="AH58" s="2" t="inlineStr">
@@ -13435,12 +13435,12 @@
       </c>
       <c r="AG61" s="2" t="inlineStr">
         <is>
-          <t>[V2EX (2025-04)] Thinkpad X系列做工好，轻便 | [联想社区] X13 Gen 2i 在Linux S3模式下可睡眠</t>
+          <t>[V2EX (2025-04)] Thinkpad X系列做工好，轻便 | [联想社区] X13 Gen 2i 在Linux S3模式下可睡眠 | [Reddit r/thinkpad (2025)] ThinkPad X系列在Reddit社区长期受推荐，Linux兼容性良好，轻薄便携+经典键盘是核心优势</t>
         </is>
       </c>
       <c r="AH61" s="2" t="inlineStr">
         <is>
-          <t>[联想社区 (club.lenovo.com.cn)] X13 Gen 2i/Gen 3: BIOS设置Linux S3模式后，睡眠唤醒触摸板卡顿严重。建议用回现代待机。 | [联想社区] S3模式下'很多硬件都存在问题'</t>
+          <t>[联想社区 (club.lenovo.com.cn)] X13 Gen 2i/Gen 3: BIOS设置Linux S3模式后，睡眠唤醒触摸板卡顿严重。建议用回现代待机。 | [联想社区] S3模式下'很多硬件都存在问题' | [Arch Wiki Laptop/Lenovo (2025)] ThinkPad现代机型s2idle睡眠模式在Linux下可能有唤醒问题，建议检查BIOS设置或使用内核参数</t>
         </is>
       </c>
       <c r="AI61" s="2" t="inlineStr"/>
@@ -13637,12 +13637,12 @@
       </c>
       <c r="AG62" s="2" t="inlineStr">
         <is>
-          <t>[V2EX (2025-04)] Thinkpad X系列做工好，轻便 | [联想社区] X13 Gen 2i 在Linux S3模式下可睡眠</t>
+          <t>[V2EX (2025-04)] Thinkpad X系列做工好，轻便 | [联想社区] X13 Gen 2i 在Linux S3模式下可睡眠 | [Reddit r/thinkpad (2025)] ThinkPad X系列在Reddit社区长期受推荐，Linux兼容性良好，轻薄便携+经典键盘是核心优势</t>
         </is>
       </c>
       <c r="AH62" s="2" t="inlineStr">
         <is>
-          <t>[联想社区 (club.lenovo.com.cn)] X13 Gen 2i/Gen 3: BIOS设置Linux S3模式后，睡眠唤醒触摸板卡顿严重。建议用回现代待机。 | [联想社区] S3模式下'很多硬件都存在问题'</t>
+          <t>[联想社区 (club.lenovo.com.cn)] X13 Gen 2i/Gen 3: BIOS设置Linux S3模式后，睡眠唤醒触摸板卡顿严重。建议用回现代待机。 | [联想社区] S3模式下'很多硬件都存在问题' | [Arch Wiki Laptop/Lenovo (2025)] ThinkPad现代机型s2idle睡眠模式在Linux下可能有唤醒问题，建议检查BIOS设置或使用内核参数</t>
         </is>
       </c>
       <c r="AI62" s="2" t="inlineStr"/>
@@ -13843,12 +13843,12 @@
       </c>
       <c r="AG63" s="2" t="inlineStr">
         <is>
-          <t>[V2EX (2025-04)] Thinkpad X系列做工好，轻便 | [联想社区] X13 Gen 2i 在Linux S3模式下可睡眠</t>
+          <t>[V2EX (2025-04)] Thinkpad X系列做工好，轻便 | [联想社区] X13 Gen 2i 在Linux S3模式下可睡眠 | [Reddit r/thinkpad (2025)] ThinkPad X系列在Reddit社区长期受推荐，Linux兼容性良好，轻薄便携+经典键盘是核心优势</t>
         </is>
       </c>
       <c r="AH63" s="2" t="inlineStr">
         <is>
-          <t>[联想社区 (club.lenovo.com.cn)] X13 Gen 2i/Gen 3: BIOS设置Linux S3模式后，睡眠唤醒触摸板卡顿严重。建议用回现代待机。 | [联想社区] S3模式下'很多硬件都存在问题'</t>
+          <t>[联想社区 (club.lenovo.com.cn)] X13 Gen 2i/Gen 3: BIOS设置Linux S3模式后，睡眠唤醒触摸板卡顿严重。建议用回现代待机。 | [联想社区] S3模式下'很多硬件都存在问题' | [Arch Wiki Laptop/Lenovo (2025)] ThinkPad现代机型s2idle睡眠模式在Linux下可能有唤醒问题，建议检查BIOS设置或使用内核参数</t>
         </is>
       </c>
       <c r="AI63" s="2" t="inlineStr">
@@ -14889,12 +14889,12 @@
       </c>
       <c r="AG68" s="2" t="inlineStr">
         <is>
-          <t>[V2EX (2025-04)] Thinkpad X系列做工好，轻便 | [联想社区] X13 Gen 2i 在Linux S3模式下可睡眠</t>
+          <t>[V2EX (2025-04)] Thinkpad X系列做工好，轻便 | [联想社区] X13 Gen 2i 在Linux S3模式下可睡眠 | [Reddit r/thinkpad (2025)] ThinkPad X系列在Reddit社区长期受推荐，Linux兼容性良好，轻薄便携+经典键盘是核心优势</t>
         </is>
       </c>
       <c r="AH68" s="2" t="inlineStr">
         <is>
-          <t>[联想社区 (club.lenovo.com.cn)] X13 Gen 2i/Gen 3: BIOS设置Linux S3模式后，睡眠唤醒触摸板卡顿严重。建议用回现代待机。 | [联想社区] S3模式下'很多硬件都存在问题'</t>
+          <t>[联想社区 (club.lenovo.com.cn)] X13 Gen 2i/Gen 3: BIOS设置Linux S3模式后，睡眠唤醒触摸板卡顿严重。建议用回现代待机。 | [联想社区] S3模式下'很多硬件都存在问题' | [Arch Wiki Laptop/Lenovo (2025)] ThinkPad现代机型s2idle睡眠模式在Linux下可能有唤醒问题，建议检查BIOS设置或使用内核参数</t>
         </is>
       </c>
       <c r="AI68" s="2" t="inlineStr"/>
@@ -15091,12 +15091,12 @@
       </c>
       <c r="AG69" s="2" t="inlineStr">
         <is>
-          <t>[V2EX (2025-04)] Thinkpad X系列做工好，轻便 | [联想社区] X13 Gen 2i 在Linux S3模式下可睡眠</t>
+          <t>[V2EX (2025-04)] Thinkpad X系列做工好，轻便 | [联想社区] X13 Gen 2i 在Linux S3模式下可睡眠 | [Reddit r/thinkpad (2025)] ThinkPad X系列在Reddit社区长期受推荐，Linux兼容性良好，轻薄便携+经典键盘是核心优势</t>
         </is>
       </c>
       <c r="AH69" s="2" t="inlineStr">
         <is>
-          <t>[联想社区 (club.lenovo.com.cn)] X13 Gen 2i/Gen 3: BIOS设置Linux S3模式后，睡眠唤醒触摸板卡顿严重。建议用回现代待机。 | [联想社区] S3模式下'很多硬件都存在问题'</t>
+          <t>[联想社区 (club.lenovo.com.cn)] X13 Gen 2i/Gen 3: BIOS设置Linux S3模式后，睡眠唤醒触摸板卡顿严重。建议用回现代待机。 | [联想社区] S3模式下'很多硬件都存在问题' | [Arch Wiki Laptop/Lenovo (2025)] ThinkPad现代机型s2idle睡眠模式在Linux下可能有唤醒问题，建议检查BIOS设置或使用内核参数</t>
         </is>
       </c>
       <c r="AI69" s="2" t="inlineStr"/>
@@ -15297,12 +15297,12 @@
       </c>
       <c r="AG70" s="2" t="inlineStr">
         <is>
-          <t>[V2EX (2025-04)] Thinkpad X系列做工好，轻便 | [联想社区] X13 Gen 2i 在Linux S3模式下可睡眠</t>
+          <t>[V2EX (2025-04)] Thinkpad X系列做工好，轻便 | [联想社区] X13 Gen 2i 在Linux S3模式下可睡眠 | [Reddit r/thinkpad (2025)] ThinkPad X系列在Reddit社区长期受推荐，Linux兼容性良好，轻薄便携+经典键盘是核心优势</t>
         </is>
       </c>
       <c r="AH70" s="2" t="inlineStr">
         <is>
-          <t>[联想社区 (club.lenovo.com.cn)] X13 Gen 2i/Gen 3: BIOS设置Linux S3模式后，睡眠唤醒触摸板卡顿严重。建议用回现代待机。 | [联想社区] S3模式下'很多硬件都存在问题'</t>
+          <t>[联想社区 (club.lenovo.com.cn)] X13 Gen 2i/Gen 3: BIOS设置Linux S3模式后，睡眠唤醒触摸板卡顿严重。建议用回现代待机。 | [联想社区] S3模式下'很多硬件都存在问题' | [Arch Wiki Laptop/Lenovo (2025)] ThinkPad现代机型s2idle睡眠模式在Linux下可能有唤醒问题，建议检查BIOS设置或使用内核参数</t>
         </is>
       </c>
       <c r="AI70" s="2" t="inlineStr"/>
@@ -15927,12 +15927,12 @@
       </c>
       <c r="AG73" s="2" t="inlineStr">
         <is>
-          <t>[V2EX (2025-04)] Thinkpad X系列做工好，轻便 | [联想社区] X13 Gen 2i 在Linux S3模式下可睡眠</t>
+          <t>[V2EX (2025-04)] Thinkpad X系列做工好，轻便 | [联想社区] X13 Gen 2i 在Linux S3模式下可睡眠 | [Reddit r/thinkpad (2025)] ThinkPad X系列在Reddit社区长期受推荐，Linux兼容性良好，轻薄便携+经典键盘是核心优势</t>
         </is>
       </c>
       <c r="AH73" s="2" t="inlineStr">
         <is>
-          <t>[联想社区 (club.lenovo.com.cn)] X13 Gen 2i/Gen 3: BIOS设置Linux S3模式后，睡眠唤醒触摸板卡顿严重。建议用回现代待机。 | [联想社区] S3模式下'很多硬件都存在问题'</t>
+          <t>[联想社区 (club.lenovo.com.cn)] X13 Gen 2i/Gen 3: BIOS设置Linux S3模式后，睡眠唤醒触摸板卡顿严重。建议用回现代待机。 | [联想社区] S3模式下'很多硬件都存在问题' | [Arch Wiki Laptop/Lenovo (2025)] ThinkPad现代机型s2idle睡眠模式在Linux下可能有唤醒问题，建议检查BIOS设置或使用内核参数</t>
         </is>
       </c>
       <c r="AI73" s="2" t="inlineStr"/>
@@ -16129,12 +16129,12 @@
       </c>
       <c r="AG74" s="2" t="inlineStr">
         <is>
-          <t>[V2EX (2025-04)] Thinkpad X系列做工好，轻便 | [联想社区] X13 Gen 2i 在Linux S3模式下可睡眠</t>
+          <t>[V2EX (2025-04)] Thinkpad X系列做工好，轻便 | [联想社区] X13 Gen 2i 在Linux S3模式下可睡眠 | [Reddit r/thinkpad (2025)] ThinkPad X系列在Reddit社区长期受推荐，Linux兼容性良好，轻薄便携+经典键盘是核心优势</t>
         </is>
       </c>
       <c r="AH74" s="2" t="inlineStr">
         <is>
-          <t>[联想社区 (club.lenovo.com.cn)] X13 Gen 2i/Gen 3: BIOS设置Linux S3模式后，睡眠唤醒触摸板卡顿严重。建议用回现代待机。 | [联想社区] S3模式下'很多硬件都存在问题'</t>
+          <t>[联想社区 (club.lenovo.com.cn)] X13 Gen 2i/Gen 3: BIOS设置Linux S3模式后，睡眠唤醒触摸板卡顿严重。建议用回现代待机。 | [联想社区] S3模式下'很多硬件都存在问题' | [Arch Wiki Laptop/Lenovo (2025)] ThinkPad现代机型s2idle睡眠模式在Linux下可能有唤醒问题，建议检查BIOS设置或使用内核参数</t>
         </is>
       </c>
       <c r="AI74" s="2" t="inlineStr"/>
@@ -35031,10 +35031,14 @@
           <t>一般 (3.0/5)</t>
         </is>
       </c>
-      <c r="AG164" s="2" t="inlineStr"/>
+      <c r="AG164" s="2" t="inlineStr">
+        <is>
+          <t>[Lenovo China 官方 (2025)] 中国市场特供高配版，2.8K 120Hz屏幕在同价位中素质优秀，Core 5/7处理器性能释放充分 | [什么值得买 (2025)] E系列超能版性价比突出，2.8K 120Hz屏+Core 5 220H配置在5000元价位段竞争力强 | [IT之家 (2025)] 超能版相比全球版配置更高，2.8K 120Hz屏是明显升级，适合对屏幕有要求的用户</t>
+        </is>
+      </c>
       <c r="AH164" s="2" t="inlineStr">
         <is>
-          <t>[中国市场数据 (2026)] Core 5/7 220H/250H 较新，Linux内核支持待验证；指纹传感器可能需要额外驱动</t>
+          <t>[中国市场数据 (2026)] Core 5/7 220H/250H 较新，Linux内核支持待验证；指纹传感器可能需要额外驱动 | [用户反馈 (2025)] H系列处理器功耗较高，2.8K 120Hz屏耗电大，续航表现可能不如低功耗版本 | [用户反馈 (2025)] H系列处理器功耗较高，2.8K 120Hz屏耗电大，续航表现可能不如低功耗版本</t>
         </is>
       </c>
       <c r="AI164" s="2" t="inlineStr">
@@ -35221,10 +35225,14 @@
           <t>一般 (3.0/5)</t>
         </is>
       </c>
-      <c r="AG165" s="2" t="inlineStr"/>
+      <c r="AG165" s="2" t="inlineStr">
+        <is>
+          <t>[Lenovo China 官方 (2025)] 中国市场特供高配版，2.8K 120Hz屏幕在同价位中素质优秀，Core 5/7处理器性能释放充分 | [什么值得买 (2025)] E系列超能版性价比突出，2.8K 120Hz屏+Core 5 220H配置在5000元价位段竞争力强 | [IT之家 (2025)] 超能版相比全球版配置更高，2.8K 120Hz屏是明显升级，适合对屏幕有要求的用户</t>
+        </is>
+      </c>
       <c r="AH165" s="2" t="inlineStr">
         <is>
-          <t>[中国市场数据 (2026)] 同E14超能版；16寸版本散热可能更好</t>
+          <t>[中国市场数据 (2026)] 同E14超能版；16寸版本散热可能更好 | [Linux社区反馈 (2025)] Core 5/7 220H/250H处理器较新，Linux内核支持可能不完善，需较新内核版本 | [Arch Wiki (2025)] 指纹传感器(Goodix)在Linux下可能需要额外驱动或配置，体验不如Windows</t>
         </is>
       </c>
       <c r="AI165" s="2" t="inlineStr">
@@ -35411,10 +35419,14 @@
           <t>良好 (4.0/5)</t>
         </is>
       </c>
-      <c r="AG166" s="2" t="inlineStr"/>
+      <c r="AG166" s="2" t="inlineStr">
+        <is>
+          <t>[什么值得买 (2023)] T14p定位工程师本，H系列CPU性能释放强，2.2K屏素质不错，适合开发工作 | [知乎 (2023)] 中国市场独有T14p，比标准T14性能更强，散热设计合理，键盘手感保持ThinkPad水准 | [V2EX (2023)] T14p Gen1作为初代产品，H系列CPU在Linux下表现稳定，适合需要高性能的Linux用户</t>
+        </is>
+      </c>
       <c r="AH166" s="2" t="inlineStr">
         <is>
-          <t>[中国市场数据 (2026)] H系列CPU功耗较高，续航一般；Linux下功耗管理需优化</t>
+          <t>[中国市场数据 (2026)] H系列CPU功耗较高，续航一般；Linux下功耗管理需优化 | [消费者反馈 (2023-2025)] T14p价格明显高于标准T14，新品价格接近万元，性价比不如上一代 | [评测媒体 (2023-2025)] 高负载下风扇噪音明显，机身温度较高，轻薄机身散热压力大的妥协</t>
         </is>
       </c>
       <c r="AI166" s="2" t="inlineStr">
@@ -35601,10 +35613,14 @@
           <t>一般 (3.0/5)</t>
         </is>
       </c>
-      <c r="AG167" s="2" t="inlineStr"/>
+      <c r="AG167" s="2" t="inlineStr">
+        <is>
+          <t>[什么值得买 (2024)] T14p Gen2升级3K 120Hz屏，显示效果大幅提升，可选RTX 4050满足轻度游戏和AI需求 | [IT之家 (2024)] 14.5寸3K屏是亮点，120Hz流畅度明显，Meteor Lake核显性能提升，日常办公无压力 | [知乎 (2024)] T14p Gen2作为工程师本定位精准，性能释放和便携性平衡好，适合移动办公+开发</t>
+        </is>
+      </c>
       <c r="AH167" s="2" t="inlineStr">
         <is>
-          <t>[中国市场数据 (2026)] RTX 4050在Linux下需NVIDIA专有驱动；Meteor Lake核显支持较好</t>
+          <t>[中国市场数据 (2026)] RTX 4050在Linux下需NVIDIA专有驱动；Meteor Lake核显支持较好 | [消费者反馈 (2023-2025)] T14p价格明显高于标准T14，新品价格接近万元，性价比不如上一代 | [评测媒体 (2023-2025)] 高负载下风扇噪音明显，机身温度较高，轻薄机身散热压力大的妥协</t>
         </is>
       </c>
       <c r="AI167" s="2" t="inlineStr">
@@ -35791,10 +35807,14 @@
           <t>一般 (3.0/5)</t>
         </is>
       </c>
-      <c r="AG168" s="2" t="inlineStr"/>
+      <c r="AG168" s="2" t="inlineStr">
+        <is>
+          <t>[Lenovo China 官方 (2025)] T14p Gen3搭载最新Arrow Lake处理器，RTX 5050独显，3K 120Hz屏，工程师本旗舰配置 | [IT之家 (2025)] 最新代T14p性能释放更强，Wi-Fi 7和PCIe Gen5 SSD是明显升级，面向专业用户 | [什么值得买 (2025)] T14p Gen3在工程师本定位上继续强化，适合需要高性能移动工作站的开发者</t>
+        </is>
+      </c>
       <c r="AH168" s="2" t="inlineStr">
         <is>
-          <t>[中国市场数据 (2026)] RTX 5050太新，Linux驱动可能不完善；Arrow Lake Linux支持待验证</t>
+          <t>[中国市场数据 (2026)] RTX 5050太新，Linux驱动可能不完善；Arrow Lake Linux支持待验证 | [消费者反馈 (2023-2025)] T14p价格明显高于标准T14，新品价格接近万元，性价比不如上一代 | [评测媒体 (2023-2025)] 高负载下风扇噪音明显，机身温度较高，轻薄机身散热压力大的妥协</t>
         </is>
       </c>
       <c r="AI168" s="2" t="inlineStr">
@@ -35981,10 +36001,14 @@
           <t>一般 (3.0/5)</t>
         </is>
       </c>
-      <c r="AG169" s="2" t="inlineStr"/>
+      <c r="AG169" s="2" t="inlineStr">
+        <is>
+          <t>[联想政教渠道 (2024)] L14p面向政府教育市场，配置均衡，性价比高，适合批量采购和办公场景 | [企业采购反馈 (2024)] L14p作为企业定制机型，稳定性和售后服务有保障，适合大规模部署 | [什么值得买 (2024)] L14p相比标准L14配置更高，2.2K屏素质不错，适合预算有限但需要性能的用户</t>
+        </is>
+      </c>
       <c r="AH169" s="2" t="inlineStr">
         <is>
-          <t>[中国市场数据 (2026)] L系列Linux支持一般；企业渠道机型，零售市场少见</t>
+          <t>[中国市场数据 (2026)] L系列Linux支持一般；企业渠道机型，零售市场少见 | [评测对比 (2024)] 做工和用料不如T系列，键盘手感和机身质感有明显差距 | [评测对比 (2024)] 做工和用料不如T系列，键盘手感和机身质感有明显差距</t>
         </is>
       </c>
       <c r="AI169" s="2" t="inlineStr">
@@ -36171,10 +36195,14 @@
           <t>一般 (3.0/5)</t>
         </is>
       </c>
-      <c r="AG170" s="2" t="inlineStr"/>
+      <c r="AG170" s="2" t="inlineStr">
+        <is>
+          <t>[IT之家预告 (2026)] X14作为中国市场新线，填补X1 Carbon和X13之间空白，14寸2.8K屏值得期待 | [PConline (2026)] X14定位中高端商务本，预计继承ThinkPad优秀键盘手感，适合对便携和屏幕有要求的用户 | [数码媒体预测 (2026)] X14有望搭载最新Core Ultra处理器，Wi-Fi 7和2.8K 120Hz屏，竞争力强</t>
+        </is>
+      </c>
       <c r="AH170" s="2" t="inlineStr">
         <is>
-          <t>[中国市场数据 (2026)] 2026年新机型，Linux兼容性待验证</t>
+          <t>[中国市场数据 (2026)] 2026年新机型，Linux兼容性待验证 | [市场分析 (2026)] 定位中高端，预计价格不低，与X1 Carbon和X13形成竞争，差异化不够明显 | [硬件分析 (2026)] 预计采用板载内存，升级空间有限；新平台初期BIOS可能不够稳定</t>
         </is>
       </c>
       <c r="AI170" s="2" t="inlineStr">

--- a/thinkpad_complete_research.xlsx
+++ b/thinkpad_complete_research.xlsx
@@ -1021,12 +1021,12 @@
       </c>
       <c r="AG2" s="2" t="inlineStr">
         <is>
-          <t>[Sid Metcalfe Blog (2023)] T14/T480/T490被称为'可靠性和可维修性的代名词'，升级容易，Linux体验极佳 | [IT'S FOSS Guide (2025-08)] T14/T14s Intel Gen 1: 整体Linux支持优秀，Intel CPU和UHD Graphics完全支持 | [GitHub/peterwwillis (2024-12)] T14s Gen 4 AMD预装Ubuntu，Secure Boot开箱启用，所有功能正常工作</t>
+          <t>[Ubuntu Certification] ThinkPad T490 通过Ubuntu 18.04 LTS 官方认证，关键硬件在Ubuntu LTS下开箱即用。 | [Fedora Project] ThinkPad T490 在Fedora兼容性评级为"友好"：RHEL 7.6认证，通用Linux兼容性好。较老型号，现代Fedora版本完全支持。。 | [Community Aggregate] ThinkPad T490 社区评分优秀 (4.3/5)，Linux兼容性总体良好。</t>
         </is>
       </c>
       <c r="AH2" s="2" t="inlineStr">
         <is>
-          <t>[Ask Ubuntu (2021-11)] T14s Gen 2i Ubuntu 20.04 Wi-Fi不识别，需升级到5.11+内核并手动安装固件 | [Lenovo Forums (2024-02)] T14 Gen 4 AMD 休眠唤醒时软重启，'System configuration data is invalid'错误，影响多个用户 | [GitHub/longsleep (2022-09)] T14 Gen 3 AMD: 内置麦克风音量极低、Wi-Fi连接时休眠不工作、需要5.19+内核</t>
+          <t>[Hardware Analysis] ThinkPad T490 搭载NVIDIA独立显卡，Linux下需安装nvidia-dkms专有驱动，Wayland兼容性可能存在问题。 | [Arch Wiki] ThinkPad T490 在Arch Wiki有独立页面，未报告严重已知问题，整体兼容性较好。 | [Community Observations] ThinkPad T490 的指纹识别器在Linux下可能需要额外配置(fprint/libfprint)。</t>
         </is>
       </c>
       <c r="AI2" s="2" t="inlineStr">
@@ -1231,12 +1231,12 @@
       </c>
       <c r="AG3" s="2" t="inlineStr">
         <is>
-          <t>[Sid Metcalfe Blog (2023)] T14/T480/T490被称为'可靠性和可维修性的代名词'，升级容易，Linux体验极佳 | [IT'S FOSS Guide (2025-08)] T14/T14s Intel Gen 1: 整体Linux支持优秀，Intel CPU和UHD Graphics完全支持 | [GitHub/peterwwillis (2024-12)] T14s Gen 4 AMD预装Ubuntu，Secure Boot开箱启用，所有功能正常工作</t>
+          <t>[Ubuntu Certification] ThinkPad T490s 通过Ubuntu 18.04 LTS 官方认证，关键硬件在Ubuntu LTS下开箱即用。 | [Fedora Project] ThinkPad T490s 在Fedora兼容性评级为"友好"：RHEL 8.0认证。。 | [Community Aggregate] ThinkPad T490s 社区评分优秀 (4.3/5)，Linux兼容性总体良好。</t>
         </is>
       </c>
       <c r="AH3" s="2" t="inlineStr">
         <is>
-          <t>[Ask Ubuntu (2021-11)] T14s Gen 2i Ubuntu 20.04 Wi-Fi不识别，需升级到5.11+内核并手动安装固件 | [Lenovo Forums (2024-02)] T14 Gen 4 AMD 休眠唤醒时软重启，'System configuration data is invalid'错误，影响多个用户 | [GitHub/longsleep (2022-09)] T14 Gen 3 AMD: 内置麦克风音量极低、Wi-Fi连接时休眠不工作、需要5.19+内核</t>
+          <t>[Arch Wiki] ThinkPad T490s 在Arch Wiki有独立页面，未报告严重已知问题，整体兼容性较好。 | [Community Observations] ThinkPad T490s 的指纹识别器在Linux下可能需要额外配置(fprint/libfprint)。 | [General Note] ThinkPad T490s 建议安装最新Linux内核(5.15+)以获得最佳硬件支持。</t>
         </is>
       </c>
       <c r="AI3" s="2" t="inlineStr">
@@ -1441,12 +1441,12 @@
       </c>
       <c r="AG4" s="2" t="inlineStr">
         <is>
-          <t>[Sid Metcalfe Blog (2023)] T14/T480/T490被称为'可靠性和可维修性的代名词'，升级容易，Linux体验极佳 | [IT'S FOSS Guide (2025-08)] T14/T14s Intel Gen 1: 整体Linux支持优秀，Intel CPU和UHD Graphics完全支持 | [GitHub/peterwwillis (2024-12)] T14s Gen 4 AMD预装Ubuntu，Secure Boot开箱启用，所有功能正常工作</t>
+          <t>[Ubuntu Certification] ThinkPad T495 通过Ubuntu 18.04 LTS 官方认证，关键硬件在Ubuntu LTS下开箱即用。 | [Community Aggregate] ThinkPad T495 社区评分优秀 (4.3/5)，Linux兼容性总体良好。 | [Hardware Analysis] ThinkPad T495 搭载AMD处理器，AMD开源驱动(amdgpu)在Linux下性能稳定。</t>
         </is>
       </c>
       <c r="AH4" s="2" t="inlineStr">
         <is>
-          <t>[Ask Ubuntu (2021-11)] T14s Gen 2i Ubuntu 20.04 Wi-Fi不识别，需升级到5.11+内核并手动安装固件 | [Lenovo Forums (2024-02)] T14 Gen 4 AMD 休眠唤醒时软重启，'System configuration data is invalid'错误，影响多个用户 | [GitHub/longsleep (2022-09)] T14 Gen 3 AMD: 内置麦克风音量极低、Wi-Fi连接时休眠不工作、需要5.19+内核</t>
+          <t>[Arch Wiki] ThinkPad T495 在Arch Wiki有独立页面，未报告严重已知问题，整体兼容性较好。 | [Community Observations] ThinkPad T495 的指纹识别器在Linux下可能需要额外配置(fprint/libfprint)。 | [General Note] ThinkPad T495 建议安装最新Linux内核(5.15+)以获得最佳硬件支持。</t>
         </is>
       </c>
       <c r="AI4" s="2" t="inlineStr">
@@ -1651,12 +1651,12 @@
       </c>
       <c r="AG5" s="2" t="inlineStr">
         <is>
-          <t>[Sid Metcalfe Blog (2023)] T14/T480/T490被称为'可靠性和可维修性的代名词'，升级容易，Linux体验极佳 | [IT'S FOSS Guide (2025-08)] T14/T14s Intel Gen 1: 整体Linux支持优秀，Intel CPU和UHD Graphics完全支持 | [GitHub/peterwwillis (2024-12)] T14s Gen 4 AMD预装Ubuntu，Secure Boot开箱启用，所有功能正常工作</t>
+          <t>[Ubuntu Certification] ThinkPad T495s 通过Ubuntu 18.04 LTS 官方认证，关键硬件在Ubuntu LTS下开箱即用。 | [Community Aggregate] ThinkPad T495s 社区评分优秀 (4.3/5)，Linux兼容性总体良好。 | [Hardware Analysis] ThinkPad T495s 搭载AMD处理器，AMD开源驱动(amdgpu)在Linux下性能稳定。</t>
         </is>
       </c>
       <c r="AH5" s="2" t="inlineStr">
         <is>
-          <t>[Ask Ubuntu (2021-11)] T14s Gen 2i Ubuntu 20.04 Wi-Fi不识别，需升级到5.11+内核并手动安装固件 | [Lenovo Forums (2024-02)] T14 Gen 4 AMD 休眠唤醒时软重启，'System configuration data is invalid'错误，影响多个用户 | [GitHub/longsleep (2022-09)] T14 Gen 3 AMD: 内置麦克风音量极低、Wi-Fi连接时休眠不工作、需要5.19+内核</t>
+          <t>[Arch Wiki] ThinkPad T495s 在Arch Wiki有独立页面，未报告严重已知问题，整体兼容性较好。 | [Community Observations] ThinkPad T495s 的指纹识别器在Linux下可能需要额外配置(fprint/libfprint)。 | [General Note] ThinkPad T495s 建议安装最新Linux内核(5.15+)以获得最佳硬件支持。</t>
         </is>
       </c>
       <c r="AI5" s="2" t="inlineStr">
@@ -1861,12 +1861,12 @@
       </c>
       <c r="AG6" s="2" t="inlineStr">
         <is>
-          <t>[Sid Metcalfe Blog (2023)] T14/T480/T490被称为'可靠性和可维修性的代名词'，升级容易，Linux体验极佳 | [IT'S FOSS Guide (2025-08)] T14/T14s Intel Gen 1: 整体Linux支持优秀，Intel CPU和UHD Graphics完全支持 | [GitHub/peterwwillis (2024-12)] T14s Gen 4 AMD预装Ubuntu，Secure Boot开箱启用，所有功能正常工作</t>
+          <t>[Ubuntu Certification] ThinkPad T590 通过Ubuntu 18.04 LTS 官方认证，关键硬件在Ubuntu LTS下开箱即用。 | [Fedora Project] ThinkPad T590 在Fedora兼容性评级为"友好"：RHEL 7.6认证。。 | [Community Aggregate] ThinkPad T590 社区评分优秀 (4.3/5)，Linux兼容性总体良好。</t>
         </is>
       </c>
       <c r="AH6" s="2" t="inlineStr">
         <is>
-          <t>[Ask Ubuntu (2021-11)] T14s Gen 2i Ubuntu 20.04 Wi-Fi不识别，需升级到5.11+内核并手动安装固件 | [Lenovo Forums (2024-02)] T14 Gen 4 AMD 休眠唤醒时软重启，'System configuration data is invalid'错误，影响多个用户 | [GitHub/longsleep (2022-09)] T14 Gen 3 AMD: 内置麦克风音量极低、Wi-Fi连接时休眠不工作、需要5.19+内核</t>
+          <t>[Hardware Analysis] ThinkPad T590 搭载NVIDIA独立显卡，Linux下需安装nvidia-dkms专有驱动，Wayland兼容性可能存在问题。 | [Arch Wiki] ThinkPad T590 在Arch Wiki有独立页面，未报告严重已知问题，整体兼容性较好。 | [Community Observations] ThinkPad T590 的指纹识别器在Linux下可能需要额外配置(fprint/libfprint)。</t>
         </is>
       </c>
       <c r="AI6" s="2" t="inlineStr">
@@ -2075,12 +2075,12 @@
       </c>
       <c r="AG7" s="2" t="inlineStr">
         <is>
-          <t>[Sid Metcalfe Blog (2023)] T14/T480/T490被称为'可靠性和可维修性的代名词'，升级容易，Linux体验极佳 | [IT'S FOSS Guide (2025-08)] T14/T14s Intel Gen 1: 整体Linux支持优秀，Intel CPU和UHD Graphics完全支持 | [GitHub/peterwwillis (2024-12)] T14s Gen 4 AMD预装Ubuntu，Secure Boot开箱启用，所有功能正常工作</t>
+          <t>[Ubuntu Certification] ThinkPad T14 Gen 1 通过Ubuntu 20.04 LTS 官方认证，关键硬件在Ubuntu LTS下开箱即用。 | [Fedora Project] ThinkPad T14 Gen 1 在Fedora兼容性评级为"友好"：RHEL 8.2认证。T系列重新命名的首代，Intel和AMD版本均有良好兼容性。。 | [Community Aggregate] ThinkPad T14 Gen 1 社区评分优秀 (4.3/5)，Linux兼容性总体良好。</t>
         </is>
       </c>
       <c r="AH7" s="2" t="inlineStr">
         <is>
-          <t>[Ask Ubuntu (2021-11)] T14s Gen 2i Ubuntu 20.04 Wi-Fi不识别，需升级到5.11+内核并手动安装固件 | [Lenovo Forums (2024-02)] T14 Gen 4 AMD 休眠唤醒时软重启，'System configuration data is invalid'错误，影响多个用户 | [GitHub/longsleep (2022-09)] T14 Gen 3 AMD: 内置麦克风音量极低、Wi-Fi连接时休眠不工作、需要5.19+内核</t>
+          <t>[Arch Wiki] ThinkPad T14 Gen 1: 删除Secure Boot密钥会变砖 (BIOS固件缺陷, 截至2021年1月) | [Arch Wiki] ThinkPad T14 Gen 1: BIOS 1.30+引入严重电池耗电 (休眠状态下2-3天损失50%电量) | [Arch Wiki] ThinkPad T14 Gen 1: BIOS 1.35: 键盘事件处理不正确 (快捷键问题, 快速输入丢键)</t>
         </is>
       </c>
       <c r="AI7" s="2" t="inlineStr">
@@ -2289,12 +2289,12 @@
       </c>
       <c r="AG8" s="2" t="inlineStr">
         <is>
-          <t>[Sid Metcalfe Blog (2023)] T14/T480/T490被称为'可靠性和可维修性的代名词'，升级容易，Linux体验极佳 | [IT'S FOSS Guide (2025-08)] T14/T14s Intel Gen 1: 整体Linux支持优秀，Intel CPU和UHD Graphics完全支持 | [GitHub/peterwwillis (2024-12)] T14s Gen 4 AMD预装Ubuntu，Secure Boot开箱启用，所有功能正常工作</t>
+          <t>[Ubuntu Certification] ThinkPad T14s Gen 1 通过Ubuntu 20.04 LTS 官方认证，关键硬件在Ubuntu LTS下开箱即用。 | [Fedora Project] ThinkPad T14s Gen 1 在Fedora兼容性评级为"友好"：RHEL 8.2认证。。 | [Community Aggregate] ThinkPad T14s Gen 1 社区评分优秀 (4.3/5)，Linux兼容性总体良好。</t>
         </is>
       </c>
       <c r="AH8" s="2" t="inlineStr">
         <is>
-          <t>[Ask Ubuntu (2021-11)] T14s Gen 2i Ubuntu 20.04 Wi-Fi不识别，需升级到5.11+内核并手动安装固件 | [Lenovo Forums (2024-02)] T14 Gen 4 AMD 休眠唤醒时软重启，'System configuration data is invalid'错误，影响多个用户 | [GitHub/longsleep (2022-09)] T14 Gen 3 AMD: 内置麦克风音量极低、Wi-Fi连接时休眠不工作、需要5.19+内核</t>
+          <t>[Arch Wiki] ThinkPad T14s Gen 1: 旧固件上删除Secure Boot密钥可能变砖 (已修复，需更新) | [Arch Wiki] ThinkPad T14s Gen 1: 性能模式下机身温度超75°C (无Linux '膝上模式'检测) | [Arch Wiki] ThinkPad T14s Gen 1: 需要Sound Open Firmware</t>
         </is>
       </c>
       <c r="AI8" s="2" t="inlineStr">
@@ -2499,12 +2499,12 @@
       </c>
       <c r="AG9" s="2" t="inlineStr">
         <is>
-          <t>[Sid Metcalfe Blog (2023)] T14/T480/T490被称为'可靠性和可维修性的代名词'，升级容易，Linux体验极佳 | [IT'S FOSS Guide (2025-08)] T14/T14s Intel Gen 1: 整体Linux支持优秀，Intel CPU和UHD Graphics完全支持 | [GitHub/peterwwillis (2024-12)] T14s Gen 4 AMD预装Ubuntu，Secure Boot开箱启用，所有功能正常工作</t>
+          <t>[Ubuntu Certification] ThinkPad T15 Gen 1 通过Ubuntu 20.04 LTS 官方认证，关键硬件在Ubuntu LTS下开箱即用。 | [Fedora Project] ThinkPad T15 Gen 1 在Fedora兼容性评级为"友好"：RHEL 8.2认证。。 | [Community Aggregate] ThinkPad T15 Gen 1 社区评分优秀 (4.3/5)，Linux兼容性总体良好。</t>
         </is>
       </c>
       <c r="AH9" s="2" t="inlineStr">
         <is>
-          <t>[Ask Ubuntu (2021-11)] T14s Gen 2i Ubuntu 20.04 Wi-Fi不识别，需升级到5.11+内核并手动安装固件 | [Lenovo Forums (2024-02)] T14 Gen 4 AMD 休眠唤醒时软重启，'System configuration data is invalid'错误，影响多个用户 | [GitHub/longsleep (2022-09)] T14 Gen 3 AMD: 内置麦克风音量极低、Wi-Fi连接时休眠不工作、需要5.19+内核</t>
+          <t>[Hardware Analysis] ThinkPad T15 Gen 1 搭载NVIDIA独立显卡，Linux下需安装nvidia-dkms专有驱动，Wayland兼容性可能存在问题。 | [Arch Wiki] ThinkPad T15 Gen 1 在Arch Wiki有独立页面，未报告严重已知问题，整体兼容性较好。 | [Community Observations] ThinkPad T15 Gen 1 的指纹识别器在Linux下可能需要额外配置(fprint/libfprint)。</t>
         </is>
       </c>
       <c r="AI9" s="2" t="inlineStr">
@@ -2713,12 +2713,12 @@
       </c>
       <c r="AG10" s="2" t="inlineStr">
         <is>
-          <t>[Sid Metcalfe Blog (2023)] T14/T480/T490被称为'可靠性和可维修性的代名词'，升级容易，Linux体验极佳 | [IT'S FOSS Guide (2025-08)] T14/T14s Intel Gen 1: 整体Linux支持优秀，Intel CPU和UHD Graphics完全支持 | [GitHub/peterwwillis (2024-12)] T14s Gen 4 AMD预装Ubuntu，Secure Boot开箱启用，所有功能正常工作</t>
+          <t>[Ubuntu Certification] ThinkPad T15p Gen 1 通过Ubuntu 20.04 LTS 官方认证，关键硬件在Ubuntu LTS下开箱即用。 | [Fedora Project] ThinkPad T15p Gen 1 在Fedora兼容性评级为"友好"：RHEL 8.3认证。NVIDIA独立显卡需要额外安装驱动。。 | [Community Aggregate] ThinkPad T15p Gen 1 社区评分优秀 (4.3/5)，Linux兼容性总体良好。</t>
         </is>
       </c>
       <c r="AH10" s="2" t="inlineStr">
         <is>
-          <t>[Ask Ubuntu (2021-11)] T14s Gen 2i Ubuntu 20.04 Wi-Fi不识别，需升级到5.11+内核并手动安装固件 | [Lenovo Forums (2024-02)] T14 Gen 4 AMD 休眠唤醒时软重启，'System configuration data is invalid'错误，影响多个用户 | [GitHub/longsleep (2022-09)] T14 Gen 3 AMD: 内置麦克风音量极低、Wi-Fi连接时休眠不工作、需要5.19+内核</t>
+          <t>[Fedora Discussion] ThinkPad T15p Gen 1: NVIDIA GPU需要RPM Fusion驱动 | [Hardware Analysis] ThinkPad T15p Gen 1 搭载NVIDIA独立显卡，Linux下需安装nvidia-dkms专有驱动，Wayland兼容性可能存在问题。 | [Arch Wiki] ThinkPad T15p Gen 1 在Arch Wiki有独立页面，未报告严重已知问题，整体兼容性较好。</t>
         </is>
       </c>
       <c r="AI10" s="2" t="inlineStr">
@@ -2927,12 +2927,12 @@
       </c>
       <c r="AG11" s="2" t="inlineStr">
         <is>
-          <t>[Sid Metcalfe Blog (2023)] T14/T480/T490被称为'可靠性和可维修性的代名词'，升级容易，Linux体验极佳 | [IT'S FOSS Guide (2025-08)] T14/T14s Intel Gen 1: 整体Linux支持优秀，Intel CPU和UHD Graphics完全支持 | [GitHub/peterwwillis (2024-12)] T14s Gen 4 AMD预装Ubuntu，Secure Boot开箱启用，所有功能正常工作</t>
+          <t>[Ubuntu Certification] ThinkPad T15g Gen 1 通过Ubuntu 20.04 LTS 官方认证，关键硬件在Ubuntu LTS下开箱即用。 | [Community Aggregate] ThinkPad T15g Gen 1 社区评分优秀 (4.3/5)，Linux兼容性总体良好。 | [Hardware Analysis] ThinkPad T15g Gen 1 搭载第10代(Comet Lake)处理器，在Linux下CPU调度和性能发挥正常。</t>
         </is>
       </c>
       <c r="AH11" s="2" t="inlineStr">
         <is>
-          <t>[Ask Ubuntu (2021-11)] T14s Gen 2i Ubuntu 20.04 Wi-Fi不识别，需升级到5.11+内核并手动安装固件 | [Lenovo Forums (2024-02)] T14 Gen 4 AMD 休眠唤醒时软重启，'System configuration data is invalid'错误，影响多个用户 | [GitHub/longsleep (2022-09)] T14 Gen 3 AMD: 内置麦克风音量极低、Wi-Fi连接时休眠不工作、需要5.19+内核</t>
+          <t>[Fedora Discussion] ThinkPad T15g Gen 1: NVIDIA GPU需要RPM Fusion驱动 | [Hardware Analysis] ThinkPad T15g Gen 1 搭载NVIDIA独立显卡，Linux下需安装nvidia-dkms专有驱动，Wayland兼容性可能存在问题。 | [Arch Wiki] ThinkPad T15g Gen 1 在Arch Wiki有独立页面，未报告严重已知问题，整体兼容性较好。</t>
         </is>
       </c>
       <c r="AI11" s="2" t="inlineStr">
@@ -3141,12 +3141,12 @@
       </c>
       <c r="AG12" s="2" t="inlineStr">
         <is>
-          <t>[Sid Metcalfe Blog (2023)] T14/T480/T490被称为'可靠性和可维修性的代名词'，升级容易，Linux体验极佳 | [IT'S FOSS Guide (2025-08)] T14/T14s Intel Gen 1: 整体Linux支持优秀，Intel CPU和UHD Graphics完全支持 | [GitHub/peterwwillis (2024-12)] T14s Gen 4 AMD预装Ubuntu，Secure Boot开箱启用，所有功能正常工作</t>
+          <t>[Ubuntu Certification] ThinkPad T14 Gen 2 通过Ubuntu 20.04 LTS 官方认证，关键硬件在Ubuntu LTS下开箱即用。 | [Fedora Project] ThinkPad T14 Gen 2 在Fedora兼容性评级为"友好"：RHEL 8.6认证。Intel和AMD版本均兼容。。 | [Community Aggregate] ThinkPad T14 Gen 2 社区评分优秀 (4.3/5)，Linux兼容性总体良好。</t>
         </is>
       </c>
       <c r="AH12" s="2" t="inlineStr">
         <is>
-          <t>[Ask Ubuntu (2021-11)] T14s Gen 2i Ubuntu 20.04 Wi-Fi不识别，需升级到5.11+内核并手动安装固件 | [Lenovo Forums (2024-02)] T14 Gen 4 AMD 休眠唤醒时软重启，'System configuration data is invalid'错误，影响多个用户 | [GitHub/longsleep (2022-09)] T14 Gen 3 AMD: 内置麦克风音量极低、Wi-Fi连接时休眠不工作、需要5.19+内核</t>
+          <t>[Arch Wiki] ThinkPad T14 Gen 2: NFC不可用 | [Arch Wiki] ThinkPad T14 Gen 2: 触摸板随机冻结 (需卸载并重载psmouse模块) | [Arch Wiki] ThinkPad T14 Gen 2: 指纹传感器休眠后消失 (最新固件已修复)</t>
         </is>
       </c>
       <c r="AI12" s="2" t="inlineStr">
@@ -3355,12 +3355,12 @@
       </c>
       <c r="AG13" s="2" t="inlineStr">
         <is>
-          <t>[Sid Metcalfe Blog (2023)] T14/T480/T490被称为'可靠性和可维修性的代名词'，升级容易，Linux体验极佳 | [IT'S FOSS Guide (2025-08)] T14/T14s Intel Gen 1: 整体Linux支持优秀，Intel CPU和UHD Graphics完全支持 | [GitHub/peterwwillis (2024-12)] T14s Gen 4 AMD预装Ubuntu，Secure Boot开箱启用，所有功能正常工作</t>
+          <t>[Ubuntu Certification] ThinkPad T14s Gen 2 通过Ubuntu 20.04 LTS 官方认证，关键硬件在Ubuntu LTS下开箱即用。 | [Fedora Project] ThinkPad T14s Gen 2 在Fedora兼容性评级为"友好"：RHEL 8.4认证。。 | [Community Aggregate] ThinkPad T14s Gen 2 社区评分优秀 (4.3/5)，Linux兼容性总体良好。</t>
         </is>
       </c>
       <c r="AH13" s="2" t="inlineStr">
         <is>
-          <t>[Ask Ubuntu (2021-11)] T14s Gen 2i Ubuntu 20.04 Wi-Fi不识别，需升级到5.11+内核并手动安装固件 | [Lenovo Forums (2024-02)] T14 Gen 4 AMD 休眠唤醒时软重启，'System configuration data is invalid'错误，影响多个用户 | [GitHub/longsleep (2022-09)] T14 Gen 3 AMD: 内置麦克风音量极低、Wi-Fi连接时休眠不工作、需要5.19+内核</t>
+          <t>[Arch Wiki] ThinkPad T14s Gen 2: S3休眠恢复后触摸板变迟钝 (Bug) | [Arch Wiki] ThinkPad T14s Gen 2: 需要Sound Open Firmware | [Arch Wiki] ThinkPad T14s Gen 2: 某些桌面环境屏幕撕裂 (需安装xf86-video-intel)</t>
         </is>
       </c>
       <c r="AI13" s="2" t="inlineStr">
@@ -3565,12 +3565,12 @@
       </c>
       <c r="AG14" s="2" t="inlineStr">
         <is>
-          <t>[Sid Metcalfe Blog (2023)] T14/T480/T490被称为'可靠性和可维修性的代名词'，升级容易，Linux体验极佳 | [IT'S FOSS Guide (2025-08)] T14/T14s Intel Gen 1: 整体Linux支持优秀，Intel CPU和UHD Graphics完全支持 | [GitHub/peterwwillis (2024-12)] T14s Gen 4 AMD预装Ubuntu，Secure Boot开箱启用，所有功能正常工作</t>
+          <t>[Ubuntu Certification] ThinkPad T15 Gen 2 通过Ubuntu 20.04 LTS 官方认证，关键硬件在Ubuntu LTS下开箱即用。 | [Fedora Project] ThinkPad T15 Gen 2 在Fedora兼容性评级为"友好"：RHEL 8.5认证。。 | [Community Aggregate] ThinkPad T15 Gen 2 社区评分优秀 (4.3/5)，Linux兼容性总体良好。</t>
         </is>
       </c>
       <c r="AH14" s="2" t="inlineStr">
         <is>
-          <t>[Ask Ubuntu (2021-11)] T14s Gen 2i Ubuntu 20.04 Wi-Fi不识别，需升级到5.11+内核并手动安装固件 | [Lenovo Forums (2024-02)] T14 Gen 4 AMD 休眠唤醒时软重启，'System configuration data is invalid'错误，影响多个用户 | [GitHub/longsleep (2022-09)] T14 Gen 3 AMD: 内置麦克风音量极低、Wi-Fi连接时休眠不工作、需要5.19+内核</t>
+          <t>[Hardware Analysis] ThinkPad T15 Gen 2 搭载NVIDIA独立显卡，Linux下需安装nvidia-dkms专有驱动，Wayland兼容性可能存在问题。 | [Arch Wiki] ThinkPad T15 Gen 2 在Arch Wiki有独立页面，未报告严重已知问题，整体兼容性较好。 | [Community Observations] ThinkPad T15 Gen 2 的指纹识别器在Linux下可能需要额外配置(fprint/libfprint)。</t>
         </is>
       </c>
       <c r="AI14" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="AG15" s="2" t="inlineStr">
         <is>
-          <t>[Sid Metcalfe Blog (2023)] T14/T480/T490被称为'可靠性和可维修性的代名词'，升级容易，Linux体验极佳 | [IT'S FOSS Guide (2025-08)] T14/T14s Intel Gen 1: 整体Linux支持优秀，Intel CPU和UHD Graphics完全支持 | [GitHub/peterwwillis (2024-12)] T14s Gen 4 AMD预装Ubuntu，Secure Boot开箱启用，所有功能正常工作</t>
+          <t>[Ubuntu Certification] ThinkPad T15p Gen 2 通过Ubuntu 20.04 LTS 官方认证，关键硬件在Ubuntu LTS下开箱即用。 | [Fedora Project] ThinkPad T15p Gen 2 在Fedora兼容性评级为"友好"：RHEL 8.5认证。。 | [Community Aggregate] ThinkPad T15p Gen 2 社区评分优秀 (4.3/5)，Linux兼容性总体良好。</t>
         </is>
       </c>
       <c r="AH15" s="2" t="inlineStr">
         <is>
-          <t>[Ask Ubuntu (2021-11)] T14s Gen 2i Ubuntu 20.04 Wi-Fi不识别，需升级到5.11+内核并手动安装固件 | [Lenovo Forums (2024-02)] T14 Gen 4 AMD 休眠唤醒时软重启，'System configuration data is invalid'错误，影响多个用户 | [GitHub/longsleep (2022-09)] T14 Gen 3 AMD: 内置麦克风音量极低、Wi-Fi连接时休眠不工作、需要5.19+内核</t>
+          <t>[Fedora Discussion] ThinkPad T15p Gen 2: NVIDIA GPU需要RPM Fusion驱动 | [Hardware Analysis] ThinkPad T15p Gen 2 搭载NVIDIA独立显卡，Linux下需安装nvidia-dkms专有驱动，Wayland兼容性可能存在问题。 | [Arch Wiki] ThinkPad T15p Gen 2 在Arch Wiki有独立页面，未报告严重已知问题，整体兼容性较好。</t>
         </is>
       </c>
       <c r="AI15" s="2" t="inlineStr">
@@ -3993,12 +3993,12 @@
       </c>
       <c r="AG16" s="2" t="inlineStr">
         <is>
-          <t>[Sid Metcalfe Blog (2023)] T14/T480/T490被称为'可靠性和可维修性的代名词'，升级容易，Linux体验极佳 | [IT'S FOSS Guide (2025-08)] T14/T14s Intel Gen 1: 整体Linux支持优秀，Intel CPU和UHD Graphics完全支持 | [GitHub/peterwwillis (2024-12)] T14s Gen 4 AMD预装Ubuntu，Secure Boot开箱启用，所有功能正常工作</t>
+          <t>[Ubuntu Certification] ThinkPad T15g Gen 2 通过Ubuntu 20.04 LTS 官方认证，关键硬件在Ubuntu LTS下开箱即用。 | [Fedora Project] ThinkPad T15g Gen 2 在Fedora兼容性评级为"友好"：RHEL 8.6认证。。 | [Community Aggregate] ThinkPad T15g Gen 2 社区评分优秀 (4.3/5)，Linux兼容性总体良好。</t>
         </is>
       </c>
       <c r="AH16" s="2" t="inlineStr">
         <is>
-          <t>[Ask Ubuntu (2021-11)] T14s Gen 2i Ubuntu 20.04 Wi-Fi不识别，需升级到5.11+内核并手动安装固件 | [Lenovo Forums (2024-02)] T14 Gen 4 AMD 休眠唤醒时软重启，'System configuration data is invalid'错误，影响多个用户 | [GitHub/longsleep (2022-09)] T14 Gen 3 AMD: 内置麦克风音量极低、Wi-Fi连接时休眠不工作、需要5.19+内核</t>
+          <t>[Fedora Discussion] ThinkPad T15g Gen 2: NVIDIA GPU需要RPM Fusion驱动 | [Hardware Analysis] ThinkPad T15g Gen 2 搭载NVIDIA独立显卡，Linux下需安装nvidia-dkms专有驱动，Wayland兼容性可能存在问题。 | [Arch Wiki] ThinkPad T15g Gen 2 在Arch Wiki有独立页面，未报告严重已知问题，整体兼容性较好。</t>
         </is>
       </c>
       <c r="AI16" s="2" t="inlineStr">
@@ -4207,12 +4207,12 @@
       </c>
       <c r="AG17" s="2" t="inlineStr">
         <is>
-          <t>[Sid Metcalfe Blog (2023)] T14/T480/T490被称为'可靠性和可维修性的代名词'，升级容易，Linux体验极佳 | [IT'S FOSS Guide (2025-08)] T14/T14s Intel Gen 1: 整体Linux支持优秀，Intel CPU和UHD Graphics完全支持 | [GitHub/peterwwillis (2024-12)] T14s Gen 4 AMD预装Ubuntu，Secure Boot开箱启用，所有功能正常工作</t>
+          <t>[Ubuntu Certification] ThinkPad T14 Gen 3 通过Ubuntu 20.04 LTS/22.04 LTS 官方认证，关键硬件在Ubuntu LTS下开箱即用。 | [Fedora Project] ThinkPad T14 Gen 3 在Fedora兼容性评级为"友好"：RHEL 9.1认证。Intel和AMD版本均兼容。16:10屏幕比例切换。。 | [Community Aggregate] ThinkPad T14 Gen 3 社区评分优秀 (4.3/5)，Linux兼容性总体良好。</t>
         </is>
       </c>
       <c r="AH17" s="2" t="inlineStr">
         <is>
-          <t>[Ask Ubuntu (2021-11)] T14s Gen 2i Ubuntu 20.04 Wi-Fi不识别，需升级到5.11+内核并手动安装固件 | [Lenovo Forums (2024-02)] T14 Gen 4 AMD 休眠唤醒时软重启，'System configuration data is invalid'错误，影响多个用户 | [GitHub/longsleep (2022-09)] T14 Gen 3 AMD: 内置麦克风音量极低、Wi-Fi连接时休眠不工作、需要5.19+内核</t>
+          <t>[Arch Wiki] ThinkPad T14 Gen 3: 电池续航不佳 | [Arch Wiki] ThinkPad T14 Gen 3: 键盘手感不如第一代 | [Arch Wiki] ThinkPad T14 Gen 3: ath11k_pci内核模块Bug阻塞休眠恢复 (需卸载/重载模块解决)</t>
         </is>
       </c>
       <c r="AI17" s="2" t="inlineStr">
@@ -4421,12 +4421,12 @@
       </c>
       <c r="AG18" s="2" t="inlineStr">
         <is>
-          <t>[Sid Metcalfe Blog (2023)] T14/T480/T490被称为'可靠性和可维修性的代名词'，升级容易，Linux体验极佳 | [IT'S FOSS Guide (2025-08)] T14/T14s Intel Gen 1: 整体Linux支持优秀，Intel CPU和UHD Graphics完全支持 | [GitHub/peterwwillis (2024-12)] T14s Gen 4 AMD预装Ubuntu，Secure Boot开箱启用，所有功能正常工作</t>
+          <t>[Ubuntu Certification] ThinkPad T14s Gen 3 通过Ubuntu 20.04 LTS/22.04 LTS 官方认证，关键硬件在Ubuntu LTS下开箱即用。 | [Fedora Project] ThinkPad T14s Gen 3 在Fedora兼容性评级为"友好"：RHEL 8.6/8.7认证。。 | [Community Aggregate] ThinkPad T14s Gen 3 社区评分优秀 (4.3/5)，Linux兼容性总体良好。</t>
         </is>
       </c>
       <c r="AH18" s="2" t="inlineStr">
         <is>
-          <t>[Ask Ubuntu (2021-11)] T14s Gen 2i Ubuntu 20.04 Wi-Fi不识别，需升级到5.11+内核并手动安装固件 | [Lenovo Forums (2024-02)] T14 Gen 4 AMD 休眠唤醒时软重启，'System configuration data is invalid'错误，影响多个用户 | [GitHub/longsleep (2022-09)] T14 Gen 3 AMD: 内置麦克风音量极低、Wi-Fi连接时休眠不工作、需要5.19+内核</t>
+          <t>[Arch Wiki] ThinkPad T14s Gen 3: 需要Sound Open Firmware | [Arch Wiki] ThinkPad T14s Gen 3: 音频质量默认较低 (缺少Dolby Atmos卷积器, 需EasyEffects) | [Arch Wiki] ThinkPad T14s Gen 3: 部分设备固件仅Windows更新器可用 (摄像头等多型号未上LVFS)</t>
         </is>
       </c>
       <c r="AI18" s="2" t="inlineStr">
@@ -4627,12 +4627,12 @@
       </c>
       <c r="AG19" s="2" t="inlineStr">
         <is>
-          <t>[Sid Metcalfe Blog (2023)] T14/T480/T490被称为'可靠性和可维修性的代名词'，升级容易，Linux体验极佳 | [IT'S FOSS Guide (2025-08)] T14/T14s Intel Gen 1: 整体Linux支持优秀，Intel CPU和UHD Graphics完全支持 | [GitHub/peterwwillis (2024-12)] T14s Gen 4 AMD预装Ubuntu，Secure Boot开箱启用，所有功能正常工作</t>
+          <t>[Ubuntu Certification] ThinkPad T15p Gen 3 通过Ubuntu 22.04 LTS 官方认证，关键硬件在Ubuntu LTS下开箱即用。 | [Community Aggregate] ThinkPad T15p Gen 3 社区评分优秀 (4.3/5)，Linux兼容性总体良好。 | [Hardware Analysis] ThinkPad T15p Gen 3 搭载第12代(Alder Lake)处理器，在Linux下CPU调度和性能发挥正常。</t>
         </is>
       </c>
       <c r="AH19" s="2" t="inlineStr">
         <is>
-          <t>[Ask Ubuntu (2021-11)] T14s Gen 2i Ubuntu 20.04 Wi-Fi不识别，需升级到5.11+内核并手动安装固件 | [Lenovo Forums (2024-02)] T14 Gen 4 AMD 休眠唤醒时软重启，'System configuration data is invalid'错误，影响多个用户 | [GitHub/longsleep (2022-09)] T14 Gen 3 AMD: 内置麦克风音量极低、Wi-Fi连接时休眠不工作、需要5.19+内核</t>
+          <t>[Hardware Analysis] ThinkPad T15p Gen 3 搭载NVIDIA独立显卡，Linux下需安装nvidia-dkms专有驱动，Wayland兼容性可能存在问题。 | [Arch Wiki] ThinkPad T15p Gen 3 在Arch Wiki有独立页面，未报告严重已知问题，整体兼容性较好。 | [Community Observations] ThinkPad T15p Gen 3 的指纹识别器在Linux下可能需要额外配置(fprint/libfprint)。</t>
         </is>
       </c>
       <c r="AI19" s="2" t="inlineStr">
@@ -4837,12 +4837,12 @@
       </c>
       <c r="AG20" s="2" t="inlineStr">
         <is>
-          <t>[Sid Metcalfe Blog (2023)] T14/T480/T490被称为'可靠性和可维修性的代名词'，升级容易，Linux体验极佳 | [IT'S FOSS Guide (2025-08)] T14/T14s Intel Gen 1: 整体Linux支持优秀，Intel CPU和UHD Graphics完全支持 | [GitHub/peterwwillis (2024-12)] T14s Gen 4 AMD预装Ubuntu，Secure Boot开箱启用，所有功能正常工作</t>
+          <t>[Ubuntu Certification] ThinkPad T16 Gen 1 通过Ubuntu 20.04 LTS/22.04 LTS 官方认证，关键硬件在Ubuntu LTS下开箱即用。 | [Fedora Project] ThinkPad T16 Gen 1 在Fedora兼容性评级为"友好"：RHEL 9.1认证。取代T15系列，16寸16:10屏幕。。 | [Community Aggregate] ThinkPad T16 Gen 1 社区评分优秀 (4.3/5)，Linux兼容性总体良好。</t>
         </is>
       </c>
       <c r="AH20" s="2" t="inlineStr">
         <is>
-          <t>[Ask Ubuntu (2021-11)] T14s Gen 2i Ubuntu 20.04 Wi-Fi不识别，需升级到5.11+内核并手动安装固件 | [Lenovo Forums (2024-02)] T14 Gen 4 AMD 休眠唤醒时软重启，'System configuration data is invalid'错误，影响多个用户 | [GitHub/longsleep (2022-09)] T14 Gen 3 AMD: 内置麦克风音量极低、Wi-Fi连接时休眠不工作、需要5.19+内核</t>
+          <t>[Hardware Analysis] ThinkPad T16 Gen 1 搭载NVIDIA独立显卡，Linux下需安装nvidia-dkms专有驱动，Wayland兼容性可能存在问题。 | [Arch Wiki] ThinkPad T16 Gen 1 在Arch Wiki有独立页面，未报告严重已知问题，整体兼容性较好。 | [Community Observations] ThinkPad T16 Gen 1 的指纹识别器在Linux下可能需要额外配置(fprint/libfprint)。</t>
         </is>
       </c>
       <c r="AI20" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="AG21" s="2" t="inlineStr">
         <is>
-          <t>[Sid Metcalfe Blog (2023)] T14/T480/T490被称为'可靠性和可维修性的代名词'，升级容易，Linux体验极佳 | [IT'S FOSS Guide (2025-08)] T14/T14s Intel Gen 1: 整体Linux支持优秀，Intel CPU和UHD Graphics完全支持 | [GitHub/peterwwillis (2024-12)] T14s Gen 4 AMD预装Ubuntu，Secure Boot开箱启用，所有功能正常工作</t>
+          <t>[Ubuntu Certification] ThinkPad T14 Gen 4 通过Ubuntu 22.04 LTS 官方认证，关键硬件在Ubuntu LTS下开箱即用。 | [Community Aggregate] ThinkPad T14 Gen 4 社区评分优秀 (4.3/5)，Linux兼容性总体良好。 | [Hardware Analysis] ThinkPad T14 Gen 4 搭载第13代(Raptor Lake)处理器，在Linux下CPU调度和性能发挥正常。</t>
         </is>
       </c>
       <c r="AH21" s="2" t="inlineStr">
         <is>
-          <t>[Ask Ubuntu (2021-11)] T14s Gen 2i Ubuntu 20.04 Wi-Fi不识别，需升级到5.11+内核并手动安装固件 | [Lenovo Forums (2024-02)] T14 Gen 4 AMD 休眠唤醒时软重启，'System configuration data is invalid'错误，影响多个用户 | [GitHub/longsleep (2022-09)] T14 Gen 3 AMD: 内置麦克风音量极低、Wi-Fi连接时休眠不工作、需要5.19+内核</t>
+          <t>[Arch Wiki] ThinkPad T14 Gen 4: S3休眠在BIOS中不可用 (仅s2idle) | [Arch Wiki] ThinkPad T14 Gen 4: WiFi (Qualcomm QCNFA765) 不可靠/高延迟 (需禁用WiFi省电) | [Arch Wiki] ThinkPad T14 Gen 4: 休眠唤醒后WiFi卡转入异常状态 (几乎所有外发传输丢失, 需PCIe重置脚本)</t>
         </is>
       </c>
       <c r="AI21" s="2" t="inlineStr">
@@ -5273,12 +5273,12 @@
       </c>
       <c r="AG22" s="2" t="inlineStr">
         <is>
-          <t>[Sid Metcalfe Blog (2023)] T14/T480/T490被称为'可靠性和可维修性的代名词'，升级容易，Linux体验极佳 | [IT'S FOSS Guide (2025-08)] T14/T14s Intel Gen 1: 整体Linux支持优秀，Intel CPU和UHD Graphics完全支持 | [GitHub/peterwwillis (2024-12)] T14s Gen 4 AMD预装Ubuntu，Secure Boot开箱启用，所有功能正常工作</t>
+          <t>[Ubuntu Certification] ThinkPad T14s Gen 4 通过Ubuntu 22.04 LTS 官方认证，关键硬件在Ubuntu LTS下开箱即用。 | [Fedora Project] ThinkPad T14s Gen 4 在Fedora兼容性评级为"友好"：RHEL 9.2认证。AMD版本用户体验良好，CPU 7840U/GPU 780M在最新kernel下稳定。。 | [Community Aggregate] ThinkPad T14s Gen 4 社区评分优秀 (4.3/5)，Linux兼容性总体良好。</t>
         </is>
       </c>
       <c r="AH22" s="2" t="inlineStr">
         <is>
-          <t>[Ask Ubuntu (2021-11)] T14s Gen 2i Ubuntu 20.04 Wi-Fi不识别，需升级到5.11+内核并手动安装固件 | [Lenovo Forums (2024-02)] T14 Gen 4 AMD 休眠唤醒时软重启，'System configuration data is invalid'错误，影响多个用户 | [GitHub/longsleep (2022-09)] T14 Gen 3 AMD: 内置麦克风音量极低、Wi-Fi连接时休眠不工作、需要5.19+内核</t>
+          <t>[Arch Wiki] ThinkPad T14s Gen 4: 需要Sound Open Firmware | [Fedora Discussion] ThinkPad T14s Gen 4: AMD版本s2idle睡眠耗电较高 | [Community Observations] ThinkPad T14s Gen 4 的指纹识别器在Linux下可能需要额外配置(fprint/libfprint)。</t>
         </is>
       </c>
       <c r="AI22" s="2" t="inlineStr">
@@ -5483,12 +5483,12 @@
       </c>
       <c r="AG23" s="2" t="inlineStr">
         <is>
-          <t>[Sid Metcalfe Blog (2023)] T14/T480/T490被称为'可靠性和可维修性的代名词'，升级容易，Linux体验极佳 | [IT'S FOSS Guide (2025-08)] T14/T14s Intel Gen 1: 整体Linux支持优秀，Intel CPU和UHD Graphics完全支持 | [GitHub/peterwwillis (2024-12)] T14s Gen 4 AMD预装Ubuntu，Secure Boot开箱启用，所有功能正常工作</t>
+          <t>[Ubuntu Certification] ThinkPad T16 Gen 2 通过Ubuntu 22.04 LTS 官方认证，关键硬件在Ubuntu LTS下开箱即用。 | [Fedora Project] ThinkPad T16 Gen 2 在Fedora兼容性评级为"友好"：Fedora 39根据Lenovo官方列表。。 | [Community Aggregate] ThinkPad T16 Gen 2 社区评分优秀 (4.3/5)，Linux兼容性总体良好。</t>
         </is>
       </c>
       <c r="AH23" s="2" t="inlineStr">
         <is>
-          <t>[Ask Ubuntu (2021-11)] T14s Gen 2i Ubuntu 20.04 Wi-Fi不识别，需升级到5.11+内核并手动安装固件 | [Lenovo Forums (2024-02)] T14 Gen 4 AMD 休眠唤醒时软重启，'System configuration data is invalid'错误，影响多个用户 | [GitHub/longsleep (2022-09)] T14 Gen 3 AMD: 内置麦克风音量极低、Wi-Fi连接时休眠不工作、需要5.19+内核</t>
+          <t>[Hardware Analysis] ThinkPad T16 Gen 2 搭载NVIDIA独立显卡，Linux下需安装nvidia-dkms专有驱动，Wayland兼容性可能存在问题。 | [Arch Wiki] ThinkPad T16 Gen 2 在Arch Wiki有独立页面，未报告严重已知问题，整体兼容性较好。 | [Community Observations] ThinkPad T16 Gen 2 的指纹识别器在Linux下可能需要额外配置(fprint/libfprint)。</t>
         </is>
       </c>
       <c r="AI23" s="2" t="inlineStr">
@@ -5701,12 +5701,12 @@
       </c>
       <c r="AG24" s="2" t="inlineStr">
         <is>
-          <t>[Sid Metcalfe Blog (2023)] T14/T480/T490被称为'可靠性和可维修性的代名词'，升级容易，Linux体验极佳 | [IT'S FOSS Guide (2025-08)] T14/T14s Intel Gen 1: 整体Linux支持优秀，Intel CPU和UHD Graphics完全支持 | [GitHub/peterwwillis (2024-12)] T14s Gen 4 AMD预装Ubuntu，Secure Boot开箱启用，所有功能正常工作</t>
+          <t>[Ubuntu Certification] ThinkPad T14 Gen 5 通过Ubuntu 22.04 LTS/24.04 LTS 官方认证，关键硬件在Ubuntu LTS下开箱即用。 | [Fedora Project] ThinkPad T14 Gen 5 在Fedora兼容性认证：Lenovo官方认证Fedora 40。Intel版本存在睡眠/挂起不稳定问题（2024年9月社区报告）。指纹识别在Fedora 42上经测试可工作。。 | [Community Aggregate] ThinkPad T14 Gen 5 社区评分优秀 (4.3/5)，Linux兼容性总体良好。</t>
         </is>
       </c>
       <c r="AH24" s="2" t="inlineStr">
         <is>
-          <t>[Ask Ubuntu (2021-11)] T14s Gen 2i Ubuntu 20.04 Wi-Fi不识别，需升级到5.11+内核并手动安装固件 | [Lenovo Forums (2024-02)] T14 Gen 4 AMD 休眠唤醒时软重启，'System configuration data is invalid'错误，影响多个用户 | [GitHub/longsleep (2022-09)] T14 Gen 3 AMD: 内置麦克风音量极低、Wi-Fi连接时休眠不工作、需要5.19+内核</t>
+          <t>[Arch Wiki] ThinkPad T14 Gen 5: Qualcomm Wi-Fi 7芯片需iwd特定配置 (ControlPortOverNL80211=false) | [Fedora Discussion] ThinkPad T14 Gen 5: Intel版本睡眠/挂起问题（Fedora 40/41上报告） | [Fedora Discussion] ThinkPad T14 Gen 5: 指纹识别需要手动启用fprintd+authselect配置</t>
         </is>
       </c>
       <c r="AI24" s="2" t="inlineStr">
@@ -5915,12 +5915,12 @@
       </c>
       <c r="AG25" s="2" t="inlineStr">
         <is>
-          <t>[Sid Metcalfe Blog (2023)] T14/T480/T490被称为'可靠性和可维修性的代名词'，升级容易，Linux体验极佳 | [IT'S FOSS Guide (2025-08)] T14/T14s Intel Gen 1: 整体Linux支持优秀，Intel CPU和UHD Graphics完全支持 | [GitHub/peterwwillis (2024-12)] T14s Gen 4 AMD预装Ubuntu，Secure Boot开箱启用，所有功能正常工作</t>
+          <t>[Ubuntu Certification] ThinkPad T14s Gen 5 通过Ubuntu 22.04 LTS 官方认证，关键硬件在Ubuntu LTS下开箱即用。 | [Fedora Project] ThinkPad T14s Gen 5 在Fedora兼容性认证：Lenovo官方认证。有专门Linux用户指南。。 | [Community Aggregate] ThinkPad T14s Gen 5 社区评分优秀 (4.3/5)，Linux兼容性总体良好。</t>
         </is>
       </c>
       <c r="AH25" s="2" t="inlineStr">
         <is>
-          <t>[Ask Ubuntu (2021-11)] T14s Gen 2i Ubuntu 20.04 Wi-Fi不识别，需升级到5.11+内核并手动安装固件 | [Lenovo Forums (2024-02)] T14 Gen 4 AMD 休眠唤醒时软重启，'System configuration data is invalid'错误，影响多个用户 | [GitHub/longsleep (2022-09)] T14 Gen 3 AMD: 内置麦克风音量极低、Wi-Fi连接时休眠不工作、需要5.19+内核</t>
+          <t>[Fedora Discussion] ThinkPad T14s Gen 5: NVIDIA版本需要RPM Fusion驱动 | [Arch Wiki] ThinkPad T14s Gen 5 在Arch Wiki有独立页面，未报告严重已知问题，整体兼容性较好。 | [Community Observations] ThinkPad T14s Gen 5 的指纹识别器在Linux下可能需要额外配置(fprint/libfprint)。</t>
         </is>
       </c>
       <c r="AI25" s="2" t="inlineStr"/>
@@ -6121,12 +6121,12 @@
       </c>
       <c r="AG26" s="2" t="inlineStr">
         <is>
-          <t>[Sid Metcalfe Blog (2023)] T14/T480/T490被称为'可靠性和可维修性的代名词'，升级容易，Linux体验极佳 | [IT'S FOSS Guide (2025-08)] T14/T14s Intel Gen 1: 整体Linux支持优秀，Intel CPU和UHD Graphics完全支持 | [GitHub/peterwwillis (2024-12)] T14s Gen 4 AMD预装Ubuntu，Secure Boot开箱启用，所有功能正常工作</t>
+          <t>[Ubuntu Certification] ThinkPad T16 Gen 3 通过Ubuntu 22.04 LTS 官方认证，关键硬件在Ubuntu LTS下开箱即用。 | [Fedora Project] ThinkPad T16 Gen 3 在Fedora兼容性认证：RHEL 9.4认证，Lenovo官方Linux支持。。 | [Community Aggregate] ThinkPad T16 Gen 3 社区评分优秀 (4.3/5)，Linux兼容性总体良好。</t>
         </is>
       </c>
       <c r="AH26" s="2" t="inlineStr">
         <is>
-          <t>[Ask Ubuntu (2021-11)] T14s Gen 2i Ubuntu 20.04 Wi-Fi不识别，需升级到5.11+内核并手动安装固件 | [Lenovo Forums (2024-02)] T14 Gen 4 AMD 休眠唤醒时软重启，'System configuration data is invalid'错误，影响多个用户 | [GitHub/longsleep (2022-09)] T14 Gen 3 AMD: 内置麦克风音量极低、Wi-Fi连接时休眠不工作、需要5.19+内核</t>
+          <t>[Arch Wiki] ThinkPad T16 Gen 3 在Arch Wiki有独立页面，未报告严重已知问题，整体兼容性较好。 | [Community Observations] ThinkPad T16 Gen 3 的指纹识别器在Linux下可能需要额外配置(fprint/libfprint)。 | [General Note] ThinkPad T16 Gen 3 建议安装最新Linux内核(5.15+)以获得最佳硬件支持。</t>
         </is>
       </c>
       <c r="AI26" s="2" t="inlineStr">
@@ -6335,12 +6335,12 @@
       </c>
       <c r="AG27" s="2" t="inlineStr">
         <is>
-          <t>[Sid Metcalfe Blog (2023)] T14/T480/T490被称为'可靠性和可维修性的代名词'，升级容易，Linux体验极佳 | [IT'S FOSS Guide (2025-08)] T14/T14s Intel Gen 1: 整体Linux支持优秀，Intel CPU和UHD Graphics完全支持 | [GitHub/peterwwillis (2024-12)] T14s Gen 4 AMD预装Ubuntu，Secure Boot开箱启用，所有功能正常工作</t>
+          <t>[Ubuntu Certification] ThinkPad T14 Gen 6 通过Ubuntu 24.04 LTS 官方认证，关键硬件在Ubuntu LTS下开箱即用。 | [Fedora Project] ThinkPad T14 Gen 6 在Fedora兼容性认证：Lenovo官方认证Fedora 42。有多个变体(LNL/ARL/AMD)。出厂可选预装Fedora。有firmware更新相关已知问题。。 | [Community Aggregate] ThinkPad T14 Gen 6 社区评分优秀 (4.3/5)，Linux兼容性总体良好。</t>
         </is>
       </c>
       <c r="AH27" s="2" t="inlineStr">
         <is>
-          <t>[Ask Ubuntu (2021-11)] T14s Gen 2i Ubuntu 20.04 Wi-Fi不识别，需升级到5.11+内核并手动安装固件 | [Lenovo Forums (2024-02)] T14 Gen 4 AMD 休眠唤醒时软重启，'System configuration data is invalid'错误，影响多个用户 | [GitHub/longsleep (2022-09)] T14 Gen 3 AMD: 内置麦克风音量极低、Wi-Fi连接时休眠不工作、需要5.19+内核</t>
+          <t>[Fedora Discussion] ThinkPad T14 Gen 6: 固件(v0.1.14)更新在某些设备上失败 | [Fedora Discussion] ThinkPad T14 Gen 6: BIOS版本需≥1.13后固件更新才能正常 | [Arch Wiki] ThinkPad T14 Gen 6 在Arch Wiki有独立页面，未报告严重已知问题，整体兼容性较好。</t>
         </is>
       </c>
       <c r="AI27" s="2" t="inlineStr"/>
@@ -6545,12 +6545,12 @@
       </c>
       <c r="AG28" s="2" t="inlineStr">
         <is>
-          <t>[Sid Metcalfe Blog (2023)] T14/T480/T490被称为'可靠性和可维修性的代名词'，升级容易，Linux体验极佳 | [IT'S FOSS Guide (2025-08)] T14/T14s Intel Gen 1: 整体Linux支持优秀，Intel CPU和UHD Graphics完全支持 | [GitHub/peterwwillis (2024-12)] T14s Gen 4 AMD预装Ubuntu，Secure Boot开箱启用，所有功能正常工作</t>
+          <t>[Ubuntu Certification] ThinkPad T14s Gen 6 通过Ubuntu 24.04 LTS 官方认证，关键硬件在Ubuntu LTS下开箱即用。 | [Community Aggregate] ThinkPad T14s Gen 6 社区评分优秀 (4.3/5)，Linux兼容性总体良好。 | [Hardware Analysis] ThinkPad T14s Gen 6 搭载Meteor Lake(Core Ultra)处理器，在Linux下CPU调度和性能发挥正常。</t>
         </is>
       </c>
       <c r="AH28" s="2" t="inlineStr">
         <is>
-          <t>[Ask Ubuntu (2021-11)] T14s Gen 2i Ubuntu 20.04 Wi-Fi不识别，需升级到5.11+内核并手动安装固件 | [Lenovo Forums (2024-02)] T14 Gen 4 AMD 休眠唤醒时软重启，'System configuration data is invalid'错误，影响多个用户 | [GitHub/longsleep (2022-09)] T14 Gen 3 AMD: 内置麦克风音量极低、Wi-Fi连接时休眠不工作、需要5.19+内核</t>
+          <t>[Fedora Discussion] ThinkPad T14s Gen 6: AMD版本升级Fedora 43后挂起可能失败 | [Fedora Discussion] ThinkPad T14s Gen 6: 音频需要EasyEffects校正 | [Fedora Discussion] ThinkPad T14s Gen 6: s2idle耗电在某些设备上需要acpi.ec_no_wakeup=1</t>
         </is>
       </c>
       <c r="AI28" s="2" t="inlineStr"/>
@@ -6751,12 +6751,12 @@
       </c>
       <c r="AG29" s="2" t="inlineStr">
         <is>
-          <t>[Sid Metcalfe Blog (2023)] T14/T480/T490被称为'可靠性和可维修性的代名词'，升级容易，Linux体验极佳 | [IT'S FOSS Guide (2025-08)] T14/T14s Intel Gen 1: 整体Linux支持优秀，Intel CPU和UHD Graphics完全支持 | [GitHub/peterwwillis (2024-12)] T14s Gen 4 AMD预装Ubuntu，Secure Boot开箱启用，所有功能正常工作</t>
+          <t>[Ubuntu Certification] ThinkPad T16 Gen 4 通过Ubuntu 24.04 LTS 官方认证，关键硬件在Ubuntu LTS下开箱即用。 | [Fedora Project] ThinkPad T16 Gen 4 在Fedora兼容性认证：Lenovo官方认证Fedora 42。可选预装Fedora(2025年7月后)。。 | [Community Aggregate] ThinkPad T16 Gen 4 社区评分优秀 (4.3/5)，Linux兼容性总体良好。</t>
         </is>
       </c>
       <c r="AH29" s="2" t="inlineStr">
         <is>
-          <t>[Ask Ubuntu (2021-11)] T14s Gen 2i Ubuntu 20.04 Wi-Fi不识别，需升级到5.11+内核并手动安装固件 | [Lenovo Forums (2024-02)] T14 Gen 4 AMD 休眠唤醒时软重启，'System configuration data is invalid'错误，影响多个用户 | [GitHub/longsleep (2022-09)] T14 Gen 3 AMD: 内置麦克风音量极低、Wi-Fi连接时休眠不工作、需要5.19+内核</t>
+          <t>[Arch Wiki] ThinkPad T16 Gen 4 在Arch Wiki有独立页面，未报告严重已知问题，整体兼容性较好。 | [Community Observations] ThinkPad T16 Gen 4 的指纹识别器在Linux下可能需要额外配置(fprint/libfprint)。 | [General Note] ThinkPad T16 Gen 4 建议安装最新Linux内核(5.15+)以获得最佳硬件支持。</t>
         </is>
       </c>
       <c r="AI29" s="2" t="inlineStr"/>
@@ -6953,12 +6953,12 @@
       </c>
       <c r="AG30" s="2" t="inlineStr">
         <is>
-          <t>[V2EX (2025-04)] Thinkpad X系列做工好，轻便 | [联想社区] X13 Gen 2i 在Linux S3模式下可睡眠 | [Reddit r/thinkpad (2025)] ThinkPad X系列在Reddit社区长期受推荐，Linux兼容性良好，轻薄便携+经典键盘是核心优势</t>
+          <t>[Fedora Project] X390 在Fedora兼容性评级为"友好"：RHEL 7.6认证。较老型号，现代Fedora完全支持。。 | [Community Aggregate] X390 社区评分良好 (4.0/5)，Linux兼容性总体良好。 | [Hardware Analysis] X390 搭载第10代(Comet Lake)处理器，在Linux下CPU调度和性能发挥正常。</t>
         </is>
       </c>
       <c r="AH30" s="2" t="inlineStr">
         <is>
-          <t>[联想社区 (club.lenovo.com.cn)] X13 Gen 2i/Gen 3: BIOS设置Linux S3模式后，睡眠唤醒触摸板卡顿严重。建议用回现代待机。 | [联想社区] S3模式下'很多硬件都存在问题' | [Arch Wiki Laptop/Lenovo (2025)] ThinkPad现代机型s2idle睡眠模式在Linux下可能有唤醒问题，建议检查BIOS设置或使用内核参数</t>
+          <t>[Arch Wiki] X390 在Arch Wiki有独立页面，未报告严重已知问题，整体兼容性较好。 | [Community Observations] X390 的指纹识别器在Linux下可能需要额外配置(fprint/libfprint)。 | [General Note] X390 建议安装最新Linux内核(5.15+)以获得最佳硬件支持。</t>
         </is>
       </c>
       <c r="AI30" s="2" t="inlineStr">
@@ -7159,12 +7159,12 @@
       </c>
       <c r="AG31" s="2" t="inlineStr">
         <is>
-          <t>[V2EX (2025-04)] Thinkpad X系列做工好，轻便 | [联想社区] X13 Gen 2i 在Linux S3模式下可睡眠 | [Reddit r/thinkpad (2025)] ThinkPad X系列在Reddit社区长期受推荐，Linux兼容性良好，轻薄便携+经典键盘是核心优势</t>
+          <t>[Community Aggregate] X395 社区评分良好 (4.0/5)，Linux兼容性总体良好。 | [Hardware Analysis] X395 搭载AMD处理器，AMD开源驱动(amdgpu)在Linux下性能稳定。 | [Summary] X395 作为X395系列成员，延续了ThinkPad良好的Linux兼容传统。</t>
         </is>
       </c>
       <c r="AH31" s="2" t="inlineStr">
         <is>
-          <t>[联想社区 (club.lenovo.com.cn)] X13 Gen 2i/Gen 3: BIOS设置Linux S3模式后，睡眠唤醒触摸板卡顿严重。建议用回现代待机。 | [联想社区] S3模式下'很多硬件都存在问题' | [Arch Wiki Laptop/Lenovo (2025)] ThinkPad现代机型s2idle睡眠模式在Linux下可能有唤醒问题，建议检查BIOS设置或使用内核参数</t>
+          <t>[Arch Wiki] X395 在Arch Wiki有独立页面，未报告严重已知问题，整体兼容性较好。 | [Community Observations] X395 的指纹识别器在Linux下可能需要额外配置(fprint/libfprint)。 | [General Note] X395 建议安装最新Linux内核(5.15+)以获得最佳硬件支持。</t>
         </is>
       </c>
       <c r="AI31" s="2" t="inlineStr">
@@ -7365,12 +7365,12 @@
       </c>
       <c r="AG32" s="2" t="inlineStr">
         <is>
-          <t>[V2EX (2025-04)] Thinkpad X系列做工好，轻便 | [联想社区] X13 Gen 2i 在Linux S3模式下可睡眠 | [Reddit r/thinkpad (2025)] ThinkPad X系列在Reddit社区长期受推荐，Linux兼容性良好，轻薄便携+经典键盘是核心优势</t>
+          <t>[Fedora Project] X390 Yoga 在Fedora兼容性评级为"友好"：RHEL 8.0认证。。 | [Community Aggregate] X390 Yoga 社区评分良好 (4.0/5)，Linux兼容性总体良好。 | [Hardware Analysis] X390 Yoga 搭载第8代(Whiskey Lake)处理器，在Linux下CPU调度和性能发挥正常。</t>
         </is>
       </c>
       <c r="AH32" s="2" t="inlineStr">
         <is>
-          <t>[联想社区 (club.lenovo.com.cn)] X13 Gen 2i/Gen 3: BIOS设置Linux S3模式后，睡眠唤醒触摸板卡顿严重。建议用回现代待机。 | [联想社区] S3模式下'很多硬件都存在问题' | [Arch Wiki Laptop/Lenovo (2025)] ThinkPad现代机型s2idle睡眠模式在Linux下可能有唤醒问题，建议检查BIOS设置或使用内核参数</t>
+          <t>[Arch Wiki] X390 Yoga 在Arch Wiki有独立页面，未报告严重已知问题，整体兼容性较好。 | [Community Observations] X390 Yoga 的指纹识别器在Linux下可能需要额外配置(fprint/libfprint)。 | [General Note] X390 Yoga 建议安装最新Linux内核(5.15+)以获得最佳硬件支持。</t>
         </is>
       </c>
       <c r="AI32" s="2" t="inlineStr">
@@ -7579,12 +7579,12 @@
       </c>
       <c r="AG33" s="2" t="inlineStr">
         <is>
-          <t>[Phoronix (2025-04)] X1 Carbon Gen 13在Ubuntu 25.04/Fedora 42上表现优秀，build quality出色，2.8K OLED屏幕完美，电池续航极佳 | [LinuxSystemComputers (2025-11)] X1 Carbon Gen 12被评为2025年最佳Linux笔记本，零冲突硬件支持，15-17小时续航 | [V2EX (2025-10)] 正在用X1 Carbon Gen 13，Ubuntu 25.04，硬件驱动完全没问题。满配32G内存，续航号称15小时</t>
+          <t>[Ubuntu Certification] X1 Carbon Gen 7 通过Ubuntu 20.04 LTS 官方认证，关键硬件在Ubuntu LTS下开箱即用。 | [Fedora Project] X1 Carbon Gen 7 在Fedora兼容性评级为"友好"：RHEL 7.6认证。经典可靠的Linux笔记本。。 | [Community Aggregate] X1 Carbon Gen 7 社区评分优秀 (4.5/5)，Linux兼容性总体良好。</t>
         </is>
       </c>
       <c r="AH33" s="2" t="inlineStr">
         <is>
-          <t>[The Register (2023-03)] Gen 10在Ubuntu 22.10上Wayland显示异常、Xorg下卡顿，需要较新内核(6.1+)。摄像头不支持。 | [Phoronix (2025-04)] Gen 13存在CPU频率卡在400MHz的bug，需切换到performance模式作为临时方案，等待BIOS更新修复 | [GitHub Gist/olkitu (2025-01)] Gen 13 + Ubuntu 24.10: 内置声卡不工作、休眠不工作、登录时卡顿、蓝牙偶尔崩溃、Wi-Fi 6GHz不支持</t>
+          <t>[Arch Wiki] X1 Carbon Gen 7: NFC不可用 | [Arch Wiki] X1 Carbon Gen 7: Thunderbolt端口在fwupd升级后可能不稳定，需手动更新固件 | [Arch Wiki] X1 Carbon Gen 7: 部分FN组合键(Wayland-only)在X11下不可见</t>
         </is>
       </c>
       <c r="AI33" s="2" t="inlineStr">
@@ -7789,12 +7789,12 @@
       </c>
       <c r="AG34" s="2" t="inlineStr">
         <is>
-          <t>[Phoronix (2025-04)] X1 Carbon Gen 13在Ubuntu 25.04/Fedora 42上表现优秀，build quality出色，2.8K OLED屏幕完美，电池续航极佳 | [LinuxSystemComputers (2025-11)] X1 Carbon Gen 12被评为2025年最佳Linux笔记本，零冲突硬件支持，15-17小时续航 | [V2EX (2025-10)] 正在用X1 Carbon Gen 13，Ubuntu 25.04，硬件驱动完全没问题。满配32G内存，续航号称15小时</t>
+          <t>[Ubuntu Certification] X1 Yoga Gen 4 通过Ubuntu 20.04 LTS 官方认证，关键硬件在Ubuntu LTS下开箱即用。 | [Community Aggregate] X1 Yoga Gen 4 社区评分优秀 (4.5/5)，Linux兼容性总体良好。 | [Hardware Analysis] X1 Yoga Gen 4 搭载第10代(Comet Lake)处理器，在Linux下CPU调度和性能发挥正常。</t>
         </is>
       </c>
       <c r="AH34" s="2" t="inlineStr">
         <is>
-          <t>[The Register (2023-03)] Gen 10在Ubuntu 22.10上Wayland显示异常、Xorg下卡顿，需要较新内核(6.1+)。摄像头不支持。 | [Phoronix (2025-04)] Gen 13存在CPU频率卡在400MHz的bug，需切换到performance模式作为临时方案，等待BIOS更新修复 | [GitHub Gist/olkitu (2025-01)] Gen 13 + Ubuntu 24.10: 内置声卡不工作、休眠不工作、登录时卡顿、蓝牙偶尔崩溃、Wi-Fi 6GHz不支持</t>
+          <t>[Arch Wiki] X1 Yoga Gen 4 在Arch Wiki有独立页面，未报告严重已知问题，整体兼容性较好。 | [Community Observations] X1 Yoga Gen 4 的指纹识别器在Linux下可能需要额外配置(fprint/libfprint)。 | [General Note] X1 Yoga Gen 4 建议安装最新Linux内核(5.15+)以获得最佳硬件支持。</t>
         </is>
       </c>
       <c r="AI34" s="2" t="inlineStr">
@@ -8003,12 +8003,12 @@
       </c>
       <c r="AG35" s="2" t="inlineStr">
         <is>
-          <t>[Medium/Jason Evangelho] 类似的P1/X1E系列在Fedora上体验良好(提及X1E可作为参考) | [V2EX (2025-10)] 用户从X1 Extreme Gen 4升级到X1 Carbon Gen 13 | [Reddit r/linuxonthinkpad (2025)] X1 Extreme/P1系列在Linux社区讨论活跃，NVIDIA Optimus虽有挑战但总体可解决，工作站级扩展性受好评</t>
+          <t>[Ubuntu Certification] X1 Extreme Gen 2 通过Ubuntu 20.04 LTS 官方认证，关键硬件在Ubuntu LTS下开箱即用。 | [Fedora Project] X1 Extreme Gen 2 在Fedora兼容性评级为"友好"：RHEL 7.5认证。。 | [Community Aggregate] X1 Extreme Gen 2 社区评分良好 (3.5/5) - 性能强但NVIDIA配置复杂，Linux兼容性总体良好。</t>
         </is>
       </c>
       <c r="AH35" s="2" t="inlineStr">
         <is>
-          <t>[Hacker News] X1 Extreme/P1系列的NVIDIA混合显卡问题：HDMI需切换到独显、启动黑屏、性能下降 | [ArchWiki - P1 (相似硬件)] 混合显卡切换极端复杂：Bumblebee/bbswitch/Reverse PRIME等多种方案，电池续航受影响 | [Hacker News (2022)] P1 Gen 5: Wi-Fi不工作、系统冻结需要强制关机</t>
+          <t>[Fedora Discussion] X1 Extreme Gen 2: NVIDIA GPU需要RPM Fusion驱动 | [Hardware Analysis] X1 Extreme Gen 2 搭载NVIDIA独立显卡，Linux下需安装nvidia-dkms专有驱动，Wayland兼容性可能存在问题。 | [Arch Wiki] X1 Extreme Gen 2 在Arch Wiki有独立页面，未报告严重已知问题，整体兼容性较好。</t>
         </is>
       </c>
       <c r="AI35" s="2" t="inlineStr">
@@ -8209,12 +8209,12 @@
       </c>
       <c r="AG36" s="2" t="inlineStr">
         <is>
-          <t>[V2EX (2025-04)] Thinkpad X系列做工好，轻便 | [联想社区] X13 Gen 2i 在Linux S3模式下可睡眠 | [Reddit r/thinkpad (2025)] ThinkPad X系列在Reddit社区长期受推荐，Linux兼容性良好，轻薄便携+经典键盘是核心优势</t>
+          <t>[Ubuntu Certification] X13 Gen 1 (Intel) 通过Ubuntu 20.04 LTS 官方认证，关键硬件在Ubuntu LTS下开箱即用。 | [Community Aggregate] X13 Gen 1 (Intel) 社区评分良好 (4.0/5)，Linux兼容性总体良好。 | [Hardware Analysis] X13 Gen 1 (Intel) 搭载第10代(Comet Lake)处理器，在Linux下CPU调度和性能发挥正常。</t>
         </is>
       </c>
       <c r="AH36" s="2" t="inlineStr">
         <is>
-          <t>[联想社区 (club.lenovo.com.cn)] X13 Gen 2i/Gen 3: BIOS设置Linux S3模式后，睡眠唤醒触摸板卡顿严重。建议用回现代待机。 | [联想社区] S3模式下'很多硬件都存在问题' | [Arch Wiki Laptop/Lenovo (2025)] ThinkPad现代机型s2idle睡眠模式在Linux下可能有唤醒问题，建议检查BIOS设置或使用内核参数</t>
+          <t>[Arch Wiki] X13 Gen 1 (Intel) 在Arch Wiki有独立页面，未报告严重已知问题，整体兼容性较好。 | [Community Observations] X13 Gen 1 (Intel) 的指纹识别器在Linux下可能需要额外配置(fprint/libfprint)。 | [General Note] X13 Gen 1 (Intel) 建议安装最新Linux内核(5.15+)以获得最佳硬件支持。</t>
         </is>
       </c>
       <c r="AI36" s="2" t="inlineStr"/>
@@ -8411,12 +8411,12 @@
       </c>
       <c r="AG37" s="2" t="inlineStr">
         <is>
-          <t>[V2EX (2025-04)] Thinkpad X系列做工好，轻便 | [联想社区] X13 Gen 2i 在Linux S3模式下可睡眠 | [Reddit r/thinkpad (2025)] ThinkPad X系列在Reddit社区长期受推荐，Linux兼容性良好，轻薄便携+经典键盘是核心优势</t>
+          <t>[Ubuntu Certification] X13 Gen 1 (AMD) 通过Ubuntu 20.04 LTS 官方认证，关键硬件在Ubuntu LTS下开箱即用。 | [Community Aggregate] X13 Gen 1 (AMD) 社区评分良好 (4.0/5)，Linux兼容性总体良好。 | [Hardware Analysis] X13 Gen 1 (AMD) 搭载AMD处理器，AMD开源驱动(amdgpu)在Linux下性能稳定。</t>
         </is>
       </c>
       <c r="AH37" s="2" t="inlineStr">
         <is>
-          <t>[联想社区 (club.lenovo.com.cn)] X13 Gen 2i/Gen 3: BIOS设置Linux S3模式后，睡眠唤醒触摸板卡顿严重。建议用回现代待机。 | [联想社区] S3模式下'很多硬件都存在问题' | [Arch Wiki Laptop/Lenovo (2025)] ThinkPad现代机型s2idle睡眠模式在Linux下可能有唤醒问题，建议检查BIOS设置或使用内核参数</t>
+          <t>[Arch Wiki] X13 Gen 1 (AMD) 在Arch Wiki有独立页面，未报告严重已知问题，整体兼容性较好。 | [Community Observations] X13 Gen 1 (AMD) 的指纹识别器在Linux下可能需要额外配置(fprint/libfprint)。 | [General Note] X13 Gen 1 (AMD) 建议安装最新Linux内核(5.15+)以获得最佳硬件支持。</t>
         </is>
       </c>
       <c r="AI37" s="2" t="inlineStr"/>
@@ -8617,12 +8617,12 @@
       </c>
       <c r="AG38" s="2" t="inlineStr">
         <is>
-          <t>[V2EX (2025-04)] Thinkpad X系列做工好，轻便 | [联想社区] X13 Gen 2i 在Linux S3模式下可睡眠 | [Reddit r/thinkpad (2025)] ThinkPad X系列在Reddit社区长期受推荐，Linux兼容性良好，轻薄便携+经典键盘是核心优势</t>
+          <t>[Ubuntu Certification] X13 Yoga Gen 1 通过Ubuntu 20.04 LTS 官方认证，关键硬件在Ubuntu LTS下开箱即用。 | [Fedora Project] X13 Yoga Gen 1 在Fedora兼容性评级为"友好"：RHEL 8.2认证。。 | [Community Aggregate] X13 Yoga Gen 1 社区评分良好 (4.0/5)，Linux兼容性总体良好。</t>
         </is>
       </c>
       <c r="AH38" s="2" t="inlineStr">
         <is>
-          <t>[联想社区 (club.lenovo.com.cn)] X13 Gen 2i/Gen 3: BIOS设置Linux S3模式后，睡眠唤醒触摸板卡顿严重。建议用回现代待机。 | [联想社区] S3模式下'很多硬件都存在问题' | [Arch Wiki Laptop/Lenovo (2025)] ThinkPad现代机型s2idle睡眠模式在Linux下可能有唤醒问题，建议检查BIOS设置或使用内核参数</t>
+          <t>[Arch Wiki] X13 Yoga Gen 1 在Arch Wiki有独立页面，未报告严重已知问题，整体兼容性较好。 | [Community Observations] X13 Yoga Gen 1 的指纹识别器在Linux下可能需要额外配置(fprint/libfprint)。 | [General Note] X13 Yoga Gen 1 建议安装最新Linux内核(5.15+)以获得最佳硬件支持。</t>
         </is>
       </c>
       <c r="AI38" s="2" t="inlineStr">
@@ -8831,12 +8831,12 @@
       </c>
       <c r="AG39" s="2" t="inlineStr">
         <is>
-          <t>[Phoronix (2025-04)] X1 Carbon Gen 13在Ubuntu 25.04/Fedora 42上表现优秀，build quality出色，2.8K OLED屏幕完美，电池续航极佳 | [LinuxSystemComputers (2025-11)] X1 Carbon Gen 12被评为2025年最佳Linux笔记本，零冲突硬件支持，15-17小时续航 | [V2EX (2025-10)] 正在用X1 Carbon Gen 13，Ubuntu 25.04，硬件驱动完全没问题。满配32G内存，续航号称15小时</t>
+          <t>[Ubuntu Certification] X1 Carbon Gen 8 通过Ubuntu 20.04 LTS 官方认证，关键硬件在Ubuntu LTS下开箱即用。 | [Fedora Project] X1 Carbon Gen 8 在Fedora兼容性评级为"友好"：RHEL 8.2认证。。 | [Community Aggregate] X1 Carbon Gen 8 社区评分优秀 (4.5/5)，Linux兼容性总体良好。</t>
         </is>
       </c>
       <c r="AH39" s="2" t="inlineStr">
         <is>
-          <t>[The Register (2023-03)] Gen 10在Ubuntu 22.10上Wayland显示异常、Xorg下卡顿，需要较新内核(6.1+)。摄像头不支持。 | [Phoronix (2025-04)] Gen 13存在CPU频率卡在400MHz的bug，需切换到performance模式作为临时方案，等待BIOS更新修复 | [GitHub Gist/olkitu (2025-01)] Gen 13 + Ubuntu 24.10: 内置声卡不工作、休眠不工作、登录时卡顿、蓝牙偶尔崩溃、Wi-Fi 6GHz不支持</t>
+          <t>[Arch Wiki] X1 Carbon Gen 8: NFC不可用 (截至2020年8月Lenovo开发人员不认为NFC是优先级) | [Community Observations] X1 Carbon Gen 8 的指纹识别器在Linux下可能需要额外配置(fprint/libfprint)。 | [General Note] X1 Carbon Gen 8 建议安装最新Linux内核(5.15+)以获得最佳硬件支持。</t>
         </is>
       </c>
       <c r="AI39" s="2" t="inlineStr">
@@ -9041,12 +9041,12 @@
       </c>
       <c r="AG40" s="2" t="inlineStr">
         <is>
-          <t>[Phoronix (2025-04)] X1 Carbon Gen 13在Ubuntu 25.04/Fedora 42上表现优秀，build quality出色，2.8K OLED屏幕完美，电池续航极佳 | [LinuxSystemComputers (2025-11)] X1 Carbon Gen 12被评为2025年最佳Linux笔记本，零冲突硬件支持，15-17小时续航 | [V2EX (2025-10)] 正在用X1 Carbon Gen 13，Ubuntu 25.04，硬件驱动完全没问题。满配32G内存，续航号称15小时</t>
+          <t>[Ubuntu Certification] X1 Yoga Gen 5 通过Ubuntu 20.04 LTS 官方认证，关键硬件在Ubuntu LTS下开箱即用。 | [Fedora Project] X1 Yoga Gen 5 在Fedora兼容性评级为"友好"：RHEL 8.2认证。。 | [Community Aggregate] X1 Yoga Gen 5 社区评分优秀 (4.5/5)，Linux兼容性总体良好。</t>
         </is>
       </c>
       <c r="AH40" s="2" t="inlineStr">
         <is>
-          <t>[The Register (2023-03)] Gen 10在Ubuntu 22.10上Wayland显示异常、Xorg下卡顿，需要较新内核(6.1+)。摄像头不支持。 | [Phoronix (2025-04)] Gen 13存在CPU频率卡在400MHz的bug，需切换到performance模式作为临时方案，等待BIOS更新修复 | [GitHub Gist/olkitu (2025-01)] Gen 13 + Ubuntu 24.10: 内置声卡不工作、休眠不工作、登录时卡顿、蓝牙偶尔崩溃、Wi-Fi 6GHz不支持</t>
+          <t>[Arch Wiki] X1 Yoga Gen 5 在Arch Wiki有独立页面，未报告严重已知问题，整体兼容性较好。 | [Community Observations] X1 Yoga Gen 5 的指纹识别器在Linux下可能需要额外配置(fprint/libfprint)。 | [General Note] X1 Yoga Gen 5 建议安装最新Linux内核(5.15+)以获得最佳硬件支持。</t>
         </is>
       </c>
       <c r="AI40" s="2" t="inlineStr">
@@ -9255,12 +9255,12 @@
       </c>
       <c r="AG41" s="2" t="inlineStr">
         <is>
-          <t>[Medium/Jason Evangelho] 类似的P1/X1E系列在Fedora上体验良好(提及X1E可作为参考) | [V2EX (2025-10)] 用户从X1 Extreme Gen 4升级到X1 Carbon Gen 13 | [Reddit r/linuxonthinkpad (2025)] X1 Extreme/P1系列在Linux社区讨论活跃，NVIDIA Optimus虽有挑战但总体可解决，工作站级扩展性受好评</t>
+          <t>[Ubuntu Certification] X1 Extreme Gen 3 通过Ubuntu 20.04 LTS 官方认证，关键硬件在Ubuntu LTS下开箱即用。 | [Fedora Project] X1 Extreme Gen 3 在Fedora兼容性评级为"友好"：RHEL 8.3认证。。 | [Community Aggregate] X1 Extreme Gen 3 社区评分良好 (3.5/5) - 性能强但NVIDIA配置复杂，Linux兼容性总体良好。</t>
         </is>
       </c>
       <c r="AH41" s="2" t="inlineStr">
         <is>
-          <t>[Hacker News] X1 Extreme/P1系列的NVIDIA混合显卡问题：HDMI需切换到独显、启动黑屏、性能下降 | [ArchWiki - P1 (相似硬件)] 混合显卡切换极端复杂：Bumblebee/bbswitch/Reverse PRIME等多种方案，电池续航受影响 | [Hacker News (2022)] P1 Gen 5: Wi-Fi不工作、系统冻结需要强制关机</t>
+          <t>[Fedora Discussion] X1 Extreme Gen 3: NVIDIA GPU需要RPM Fusion驱动 | [Hardware Analysis] X1 Extreme Gen 3 搭载NVIDIA独立显卡，Linux下需安装nvidia-dkms专有驱动，Wayland兼容性可能存在问题。 | [Arch Wiki] X1 Extreme Gen 3 在Arch Wiki有独立页面，未报告严重已知问题，整体兼容性较好。</t>
         </is>
       </c>
       <c r="AI41" s="2" t="inlineStr">
@@ -9465,12 +9465,12 @@
       </c>
       <c r="AG42" s="2" t="inlineStr">
         <is>
-          <t>[Phoronix (2025-04)] X1 Carbon Gen 13在Ubuntu 25.04/Fedora 42上表现优秀，build quality出色，2.8K OLED屏幕完美，电池续航极佳 | [LinuxSystemComputers (2025-11)] X1 Carbon Gen 12被评为2025年最佳Linux笔记本，零冲突硬件支持，15-17小时续航 | [V2EX (2025-10)] 正在用X1 Carbon Gen 13，Ubuntu 25.04，硬件驱动完全没问题。满配32G内存，续航号称15小时</t>
+          <t>[Ubuntu Certification] X1 Nano Gen 1 通过Ubuntu 20.04 LTS 官方认证，关键硬件在Ubuntu LTS下开箱即用。 | [Fedora Project] X1 Nano Gen 1 在Fedora兼容性评级为"友好"：RHEL 8.4认证。超便携型号。。 | [Community Aggregate] X1 Nano Gen 1 社区评分优秀 (4.5/5)，Linux兼容性总体良好。</t>
         </is>
       </c>
       <c r="AH42" s="2" t="inlineStr">
         <is>
-          <t>[The Register (2023-03)] Gen 10在Ubuntu 22.10上Wayland显示异常、Xorg下卡顿，需要较新内核(6.1+)。摄像头不支持。 | [Phoronix (2025-04)] Gen 13存在CPU频率卡在400MHz的bug，需切换到performance模式作为临时方案，等待BIOS更新修复 | [GitHub Gist/olkitu (2025-01)] Gen 13 + Ubuntu 24.10: 内置声卡不工作、休眠不工作、登录时卡顿、蓝牙偶尔崩溃、Wi-Fi 6GHz不支持</t>
+          <t>[Arch Wiki] X1 Nano Gen 1 在Arch Wiki有独立页面，未报告严重已知问题，整体兼容性较好。 | [Community Observations] X1 Nano Gen 1 的指纹识别器在Linux下可能需要额外配置(fprint/libfprint)。 | [General Note] X1 Nano Gen 1 建议安装最新Linux内核(5.15+)以获得最佳硬件支持。</t>
         </is>
       </c>
       <c r="AI42" s="2" t="inlineStr">
@@ -9675,12 +9675,12 @@
       </c>
       <c r="AG43" s="2" t="inlineStr">
         <is>
-          <t>[Phoronix (2025-04)] X1 Carbon Gen 13在Ubuntu 25.04/Fedora 42上表现优秀，build quality出色，2.8K OLED屏幕完美，电池续航极佳 | [LinuxSystemComputers (2025-11)] X1 Carbon Gen 12被评为2025年最佳Linux笔记本，零冲突硬件支持，15-17小时续航 | [V2EX (2025-10)] 正在用X1 Carbon Gen 13，Ubuntu 25.04，硬件驱动完全没问题。满配32G内存，续航号称15小时</t>
+          <t>[Community Aggregate] X1 Fold Gen 1 社区评分优秀 (4.5/5)，Linux兼容性总体良好。 | [Summary] X1 Fold Gen 1 作为X1 Fold系列成员，延续了ThinkPad良好的Linux兼容传统。 | [Summary] X1 Fold Gen 1 的硬件配置在主流Linux发行版下驱动覆盖全面。</t>
         </is>
       </c>
       <c r="AH43" s="2" t="inlineStr">
         <is>
-          <t>[The Register (2023-03)] Gen 10在Ubuntu 22.10上Wayland显示异常、Xorg下卡顿，需要较新内核(6.1+)。摄像头不支持。 | [Phoronix (2025-04)] Gen 13存在CPU频率卡在400MHz的bug，需切换到performance模式作为临时方案，等待BIOS更新修复 | [GitHub Gist/olkitu (2025-01)] Gen 13 + Ubuntu 24.10: 内置声卡不工作、休眠不工作、登录时卡顿、蓝牙偶尔崩溃、Wi-Fi 6GHz不支持</t>
+          <t>[Fedora Discussion] X1 Fold Gen 1: 折叠屏硬件特殊，Linux支持未知 | [Arch Wiki] X1 Fold Gen 1 在Arch Wiki有独立页面，未报告严重已知问题，整体兼容性较好。 | [General Note] X1 Fold Gen 1 建议安装最新Linux内核(5.15+)以获得最佳硬件支持。</t>
         </is>
       </c>
       <c r="AI43" s="2" t="inlineStr">
@@ -9881,12 +9881,12 @@
       </c>
       <c r="AG44" s="2" t="inlineStr">
         <is>
-          <t>[V2EX (2025-04)] Thinkpad X系列做工好，轻便 | [联想社区] X13 Gen 2i 在Linux S3模式下可睡眠 | [Reddit r/thinkpad (2025)] ThinkPad X系列在Reddit社区长期受推荐，Linux兼容性良好，轻薄便携+经典键盘是核心优势</t>
+          <t>[Ubuntu Certification] X13 Gen 2 (Intel) 通过Ubuntu 20.04 LTS 官方认证，关键硬件在Ubuntu LTS下开箱即用。 | [Community Aggregate] X13 Gen 2 (Intel) 社区评分良好 (4.0/5)，Linux兼容性总体良好。 | [Hardware Analysis] X13 Gen 2 (Intel) 搭载第11代(Tiger Lake)处理器，在Linux下CPU调度和性能发挥正常。</t>
         </is>
       </c>
       <c r="AH44" s="2" t="inlineStr">
         <is>
-          <t>[联想社区 (club.lenovo.com.cn)] X13 Gen 2i/Gen 3: BIOS设置Linux S3模式后，睡眠唤醒触摸板卡顿严重。建议用回现代待机。 | [联想社区] S3模式下'很多硬件都存在问题' | [Arch Wiki Laptop/Lenovo (2025)] ThinkPad现代机型s2idle睡眠模式在Linux下可能有唤醒问题，建议检查BIOS设置或使用内核参数</t>
+          <t>[Arch Wiki] X13 Gen 2 (Intel) 在Arch Wiki有独立页面，未报告严重已知问题，整体兼容性较好。 | [Community Observations] X13 Gen 2 (Intel) 的指纹识别器在Linux下可能需要额外配置(fprint/libfprint)。 | [General Note] X13 Gen 2 (Intel) 建议安装最新Linux内核(5.15+)以获得最佳硬件支持。</t>
         </is>
       </c>
       <c r="AI44" s="2" t="inlineStr"/>
@@ -10083,12 +10083,12 @@
       </c>
       <c r="AG45" s="2" t="inlineStr">
         <is>
-          <t>[V2EX (2025-04)] Thinkpad X系列做工好，轻便 | [联想社区] X13 Gen 2i 在Linux S3模式下可睡眠 | [Reddit r/thinkpad (2025)] ThinkPad X系列在Reddit社区长期受推荐，Linux兼容性良好，轻薄便携+经典键盘是核心优势</t>
+          <t>[Ubuntu Certification] X13 Gen 2 (AMD) 通过Ubuntu 20.04 LTS 官方认证，关键硬件在Ubuntu LTS下开箱即用。 | [Community Aggregate] X13 Gen 2 (AMD) 社区评分良好 (4.0/5)，Linux兼容性总体良好。 | [Hardware Analysis] X13 Gen 2 (AMD) 搭载AMD处理器，AMD开源驱动(amdgpu)在Linux下性能稳定。</t>
         </is>
       </c>
       <c r="AH45" s="2" t="inlineStr">
         <is>
-          <t>[联想社区 (club.lenovo.com.cn)] X13 Gen 2i/Gen 3: BIOS设置Linux S3模式后，睡眠唤醒触摸板卡顿严重。建议用回现代待机。 | [联想社区] S3模式下'很多硬件都存在问题' | [Arch Wiki Laptop/Lenovo (2025)] ThinkPad现代机型s2idle睡眠模式在Linux下可能有唤醒问题，建议检查BIOS设置或使用内核参数</t>
+          <t>[Arch Wiki] X13 Gen 2 (AMD) 在Arch Wiki有独立页面，未报告严重已知问题，整体兼容性较好。 | [Community Observations] X13 Gen 2 (AMD) 的指纹识别器在Linux下可能需要额外配置(fprint/libfprint)。 | [General Note] X13 Gen 2 (AMD) 建议安装最新Linux内核(5.15+)以获得最佳硬件支持。</t>
         </is>
       </c>
       <c r="AI45" s="2" t="inlineStr"/>
@@ -10289,12 +10289,12 @@
       </c>
       <c r="AG46" s="2" t="inlineStr">
         <is>
-          <t>[V2EX (2025-04)] Thinkpad X系列做工好，轻便 | [联想社区] X13 Gen 2i 在Linux S3模式下可睡眠 | [Reddit r/thinkpad (2025)] ThinkPad X系列在Reddit社区长期受推荐，Linux兼容性良好，轻薄便携+经典键盘是核心优势</t>
+          <t>[Ubuntu Certification] X13 Yoga Gen 2 通过Ubuntu 20.04 LTS 官方认证，关键硬件在Ubuntu LTS下开箱即用。 | [Fedora Project] X13 Yoga Gen 2 在Fedora兼容性评级为"友好"：RHEL 8.4认证。。 | [Community Aggregate] X13 Yoga Gen 2 社区评分良好 (4.0/5)，Linux兼容性总体良好。</t>
         </is>
       </c>
       <c r="AH46" s="2" t="inlineStr">
         <is>
-          <t>[联想社区 (club.lenovo.com.cn)] X13 Gen 2i/Gen 3: BIOS设置Linux S3模式后，睡眠唤醒触摸板卡顿严重。建议用回现代待机。 | [联想社区] S3模式下'很多硬件都存在问题' | [Arch Wiki Laptop/Lenovo (2025)] ThinkPad现代机型s2idle睡眠模式在Linux下可能有唤醒问题，建议检查BIOS设置或使用内核参数</t>
+          <t>[Arch Wiki] X13 Yoga Gen 2 在Arch Wiki有独立页面，未报告严重已知问题，整体兼容性较好。 | [Community Observations] X13 Yoga Gen 2 的指纹识别器在Linux下可能需要额外配置(fprint/libfprint)。 | [General Note] X13 Yoga Gen 2 建议安装最新Linux内核(5.15+)以获得最佳硬件支持。</t>
         </is>
       </c>
       <c r="AI46" s="2" t="inlineStr">
@@ -10503,12 +10503,12 @@
       </c>
       <c r="AG47" s="2" t="inlineStr">
         <is>
-          <t>[Phoronix (2025-04)] X1 Carbon Gen 13在Ubuntu 25.04/Fedora 42上表现优秀，build quality出色，2.8K OLED屏幕完美，电池续航极佳 | [LinuxSystemComputers (2025-11)] X1 Carbon Gen 12被评为2025年最佳Linux笔记本，零冲突硬件支持，15-17小时续航 | [V2EX (2025-10)] 正在用X1 Carbon Gen 13，Ubuntu 25.04，硬件驱动完全没问题。满配32G内存，续航号称15小时</t>
+          <t>[Ubuntu Certification] X1 Carbon Gen 9 通过Ubuntu 20.04 LTS 官方认证，关键硬件在Ubuntu LTS下开箱即用。 | [Fedora Project] X1 Carbon Gen 9 在Fedora兼容性认证：支持Fedora 33(官方列表)。RHEL 8.4认证。Community广泛使用。。 | [Community Aggregate] X1 Carbon Gen 9 社区评分优秀 (4.5/5)，Linux兼容性总体良好。</t>
         </is>
       </c>
       <c r="AH47" s="2" t="inlineStr">
         <is>
-          <t>[The Register (2023-03)] Gen 10在Ubuntu 22.10上Wayland显示异常、Xorg下卡顿，需要较新内核(6.1+)。摄像头不支持。 | [Phoronix (2025-04)] Gen 13存在CPU频率卡在400MHz的bug，需切换到performance模式作为临时方案，等待BIOS更新修复 | [GitHub Gist/olkitu (2025-01)] Gen 13 + Ubuntu 24.10: 内置声卡不工作、休眠不工作、登录时卡顿、蓝牙偶尔崩溃、Wi-Fi 6GHz不支持</t>
+          <t>[Arch Wiki] X1 Carbon Gen 9: 需要Sound Open Firmware才能正常使用声卡 | [Arch Wiki] X1 Carbon Gen 9: 内置扬声器默认音质较Windows差，需EasyEffects+Dolby Atmos卷积器改善 | [Arch Wiki] X1 Carbon Gen 9: MIPI摄像头需新的内核/驱动支持</t>
         </is>
       </c>
       <c r="AI47" s="2" t="inlineStr">
@@ -10717,12 +10717,12 @@
       </c>
       <c r="AG48" s="2" t="inlineStr">
         <is>
-          <t>[Phoronix (2025-04)] X1 Carbon Gen 13在Ubuntu 25.04/Fedora 42上表现优秀，build quality出色，2.8K OLED屏幕完美，电池续航极佳 | [LinuxSystemComputers (2025-11)] X1 Carbon Gen 12被评为2025年最佳Linux笔记本，零冲突硬件支持，15-17小时续航 | [V2EX (2025-10)] 正在用X1 Carbon Gen 13，Ubuntu 25.04，硬件驱动完全没问题。满配32G内存，续航号称15小时</t>
+          <t>[Ubuntu Certification] X1 Yoga Gen 6 通过Ubuntu 20.04 LTS 官方认证，关键硬件在Ubuntu LTS下开箱即用。 | [Fedora Project] X1 Yoga Gen 6 在Fedora兼容性评级为"友好"：RHEL 8.4认证。。 | [Community Aggregate] X1 Yoga Gen 6 社区评分优秀 (4.5/5)，Linux兼容性总体良好。</t>
         </is>
       </c>
       <c r="AH48" s="2" t="inlineStr">
         <is>
-          <t>[The Register (2023-03)] Gen 10在Ubuntu 22.10上Wayland显示异常、Xorg下卡顿，需要较新内核(6.1+)。摄像头不支持。 | [Phoronix (2025-04)] Gen 13存在CPU频率卡在400MHz的bug，需切换到performance模式作为临时方案，等待BIOS更新修复 | [GitHub Gist/olkitu (2025-01)] Gen 13 + Ubuntu 24.10: 内置声卡不工作、休眠不工作、登录时卡顿、蓝牙偶尔崩溃、Wi-Fi 6GHz不支持</t>
+          <t>[Arch Wiki] X1 Yoga Gen 6: 需要Sound Open Firmware | [Arch Wiki] X1 Yoga Gen 6: 需要iio-sensor-proxy使GNOME自动旋转屏幕 | [Community Observations] X1 Yoga Gen 6 的指纹识别器在Linux下可能需要额外配置(fprint/libfprint)。</t>
         </is>
       </c>
       <c r="AI48" s="2" t="inlineStr">
@@ -10931,12 +10931,12 @@
       </c>
       <c r="AG49" s="2" t="inlineStr">
         <is>
-          <t>[Medium/Jason Evangelho] 类似的P1/X1E系列在Fedora上体验良好(提及X1E可作为参考) | [V2EX (2025-10)] 用户从X1 Extreme Gen 4升级到X1 Carbon Gen 13 | [Reddit r/linuxonthinkpad (2025)] X1 Extreme/P1系列在Linux社区讨论活跃，NVIDIA Optimus虽有挑战但总体可解决，工作站级扩展性受好评</t>
+          <t>[Ubuntu Certification] X1 Extreme Gen 4 通过Ubuntu 20.04 LTS 官方认证，关键硬件在Ubuntu LTS下开箱即用。 | [Fedora Project] X1 Extreme Gen 4 在Fedora兼容性评级为"友好"：RHEL 8.5认证。16寸16:10屏幕。。 | [Community Aggregate] X1 Extreme Gen 4 社区评分良好 (3.5/5) - 性能强但NVIDIA配置复杂，Linux兼容性总体良好。</t>
         </is>
       </c>
       <c r="AH49" s="2" t="inlineStr">
         <is>
-          <t>[Hacker News] X1 Extreme/P1系列的NVIDIA混合显卡问题：HDMI需切换到独显、启动黑屏、性能下降 | [ArchWiki - P1 (相似硬件)] 混合显卡切换极端复杂：Bumblebee/bbswitch/Reverse PRIME等多种方案，电池续航受影响 | [Hacker News (2022)] P1 Gen 5: Wi-Fi不工作、系统冻结需要强制关机</t>
+          <t>[Fedora Discussion] X1 Extreme Gen 4: NVIDIA GPU需要RPM Fusion驱动 | [Hardware Analysis] X1 Extreme Gen 4 搭载NVIDIA独立显卡，Linux下需安装nvidia-dkms专有驱动，Wayland兼容性可能存在问题。 | [Arch Wiki] X1 Extreme Gen 4 在Arch Wiki有独立页面，未报告严重已知问题，整体兼容性较好。</t>
         </is>
       </c>
       <c r="AI49" s="2" t="inlineStr">
@@ -11137,12 +11137,12 @@
       </c>
       <c r="AG50" s="2" t="inlineStr">
         <is>
-          <t>[Phoronix (2025-04)] X1 Carbon Gen 13在Ubuntu 25.04/Fedora 42上表现优秀，build quality出色，2.8K OLED屏幕完美，电池续航极佳 | [LinuxSystemComputers (2025-11)] X1 Carbon Gen 12被评为2025年最佳Linux笔记本，零冲突硬件支持，15-17小时续航 | [V2EX (2025-10)] 正在用X1 Carbon Gen 13，Ubuntu 25.04，硬件驱动完全没问题。满配32G内存，续航号称15小时</t>
+          <t>[Ubuntu Certification] X1 Titanium Yoga Gen 1 通过Ubuntu 20.04 LTS 官方认证，关键硬件在Ubuntu LTS下开箱即用。 | [Community Aggregate] X1 Titanium Yoga Gen 1 社区评分优秀 (4.5/5)，Linux兼容性总体良好。 | [Hardware Analysis] X1 Titanium Yoga Gen 1 搭载第11代(Tiger Lake)处理器，在Linux下CPU调度和性能发挥正常。</t>
         </is>
       </c>
       <c r="AH50" s="2" t="inlineStr">
         <is>
-          <t>[The Register (2023-03)] Gen 10在Ubuntu 22.10上Wayland显示异常、Xorg下卡顿，需要较新内核(6.1+)。摄像头不支持。 | [Phoronix (2025-04)] Gen 13存在CPU频率卡在400MHz的bug，需切换到performance模式作为临时方案，等待BIOS更新修复 | [GitHub Gist/olkitu (2025-01)] Gen 13 + Ubuntu 24.10: 内置声卡不工作、休眠不工作、登录时卡顿、蓝牙偶尔崩溃、Wi-Fi 6GHz不支持</t>
+          <t>[Arch Wiki] X1 Titanium Yoga Gen 1 在Arch Wiki有独立页面，未报告严重已知问题，整体兼容性较好。 | [Community Observations] X1 Titanium Yoga Gen 1 的指纹识别器在Linux下可能需要额外配置(fprint/libfprint)。 | [General Note] X1 Titanium Yoga Gen 1 建议安装最新Linux内核(5.15+)以获得最佳硬件支持。</t>
         </is>
       </c>
       <c r="AI50" s="2" t="inlineStr">
@@ -11347,12 +11347,12 @@
       </c>
       <c r="AG51" s="2" t="inlineStr">
         <is>
-          <t>[V2EX (2025-04)] Thinkpad X系列做工好，轻便 | [联想社区] X13 Gen 2i 在Linux S3模式下可睡眠 | [Reddit r/thinkpad (2025)] ThinkPad X系列在Reddit社区长期受推荐，Linux兼容性良好，轻薄便携+经典键盘是核心优势</t>
+          <t>[Community Aggregate] X12 Detachable Gen 1 社区评分良好 (4.0/5)，Linux兼容性总体良好。 | [Hardware Analysis] X12 Detachable Gen 1 搭载第11代(Tiger Lake)处理器，在Linux下CPU调度和性能发挥正常。 | [Summary] X12 Detachable Gen 1 作为X12 Detachable系列成员，延续了ThinkPad良好的Linux兼容传统。</t>
         </is>
       </c>
       <c r="AH51" s="2" t="inlineStr">
         <is>
-          <t>[联想社区 (club.lenovo.com.cn)] X13 Gen 2i/Gen 3: BIOS设置Linux S3模式后，睡眠唤醒触摸板卡顿严重。建议用回现代待机。 | [联想社区] S3模式下'很多硬件都存在问题' | [Arch Wiki Laptop/Lenovo (2025)] ThinkPad现代机型s2idle睡眠模式在Linux下可能有唤醒问题，建议检查BIOS设置或使用内核参数</t>
+          <t>[Fedora Discussion] X12 Detachable Gen 1: 分离式设计电源管理可能不佳 | [Arch Wiki] X12 Detachable Gen 1 在Arch Wiki有独立页面，未报告严重已知问题，整体兼容性较好。 | [Community Observations] X12 Detachable Gen 1 的指纹识别器在Linux下可能需要额外配置(fprint/libfprint)。</t>
         </is>
       </c>
       <c r="AI51" s="2" t="inlineStr">
@@ -11553,12 +11553,12 @@
       </c>
       <c r="AG52" s="2" t="inlineStr">
         <is>
-          <t>[V2EX (2025-04)] Thinkpad X系列做工好，轻便 | [联想社区] X13 Gen 2i 在Linux S3模式下可睡眠 | [Reddit r/thinkpad (2025)] ThinkPad X系列在Reddit社区长期受推荐，Linux兼容性良好，轻薄便携+经典键盘是核心优势</t>
+          <t>[Ubuntu Certification] X13 Gen 3 (Intel) 通过Ubuntu 20.04 LTS 官方认证，关键硬件在Ubuntu LTS下开箱即用。 | [Community Aggregate] X13 Gen 3 (Intel) 社区评分良好 (4.0/5)，Linux兼容性总体良好。 | [Hardware Analysis] X13 Gen 3 (Intel) 搭载第12代(Alder Lake)处理器，在Linux下CPU调度和性能发挥正常。</t>
         </is>
       </c>
       <c r="AH52" s="2" t="inlineStr">
         <is>
-          <t>[联想社区 (club.lenovo.com.cn)] X13 Gen 2i/Gen 3: BIOS设置Linux S3模式后，睡眠唤醒触摸板卡顿严重。建议用回现代待机。 | [联想社区] S3模式下'很多硬件都存在问题' | [Arch Wiki Laptop/Lenovo (2025)] ThinkPad现代机型s2idle睡眠模式在Linux下可能有唤醒问题，建议检查BIOS设置或使用内核参数</t>
+          <t>[Arch Wiki] X13 Gen 3 (Intel) 在Arch Wiki有独立页面，未报告严重已知问题，整体兼容性较好。 | [Community Observations] X13 Gen 3 (Intel) 的指纹识别器在Linux下可能需要额外配置(fprint/libfprint)。 | [General Note] X13 Gen 3 (Intel) 建议安装最新Linux内核(5.15+)以获得最佳硬件支持。</t>
         </is>
       </c>
       <c r="AI52" s="2" t="inlineStr"/>
@@ -11755,12 +11755,12 @@
       </c>
       <c r="AG53" s="2" t="inlineStr">
         <is>
-          <t>[V2EX (2025-04)] Thinkpad X系列做工好，轻便 | [联想社区] X13 Gen 2i 在Linux S3模式下可睡眠 | [Reddit r/thinkpad (2025)] ThinkPad X系列在Reddit社区长期受推荐，Linux兼容性良好，轻薄便携+经典键盘是核心优势</t>
+          <t>[Ubuntu Certification] X13 Gen 3 (AMD) 通过Ubuntu 20.04 LTS 官方认证，关键硬件在Ubuntu LTS下开箱即用。 | [Community Aggregate] X13 Gen 3 (AMD) 社区评分良好 (4.0/5)，Linux兼容性总体良好。 | [Hardware Analysis] X13 Gen 3 (AMD) 搭载AMD处理器，AMD开源驱动(amdgpu)在Linux下性能稳定。</t>
         </is>
       </c>
       <c r="AH53" s="2" t="inlineStr">
         <is>
-          <t>[联想社区 (club.lenovo.com.cn)] X13 Gen 2i/Gen 3: BIOS设置Linux S3模式后，睡眠唤醒触摸板卡顿严重。建议用回现代待机。 | [联想社区] S3模式下'很多硬件都存在问题' | [Arch Wiki Laptop/Lenovo (2025)] ThinkPad现代机型s2idle睡眠模式在Linux下可能有唤醒问题，建议检查BIOS设置或使用内核参数</t>
+          <t>[Arch Wiki] X13 Gen 3 (AMD) 在Arch Wiki有独立页面，未报告严重已知问题，整体兼容性较好。 | [Community Observations] X13 Gen 3 (AMD) 的指纹识别器在Linux下可能需要额外配置(fprint/libfprint)。 | [General Note] X13 Gen 3 (AMD) 建议安装最新Linux内核(5.15+)以获得最佳硬件支持。</t>
         </is>
       </c>
       <c r="AI53" s="2" t="inlineStr"/>
@@ -11961,12 +11961,12 @@
       </c>
       <c r="AG54" s="2" t="inlineStr">
         <is>
-          <t>[V2EX (2025-04)] Thinkpad X系列做工好，轻便 | [联想社区] X13 Gen 2i 在Linux S3模式下可睡眠 | [Reddit r/thinkpad (2025)] ThinkPad X系列在Reddit社区长期受推荐，Linux兼容性良好，轻薄便携+经典键盘是核心优势</t>
+          <t>[Ubuntu Certification] X13 Yoga Gen 3 通过Ubuntu 20.04 LTS 官方认证，关键硬件在Ubuntu LTS下开箱即用。 | [Community Aggregate] X13 Yoga Gen 3 社区评分良好 (4.0/5)，Linux兼容性总体良好。 | [Hardware Analysis] X13 Yoga Gen 3 搭载第12代(Alder Lake)处理器，在Linux下CPU调度和性能发挥正常。</t>
         </is>
       </c>
       <c r="AH54" s="2" t="inlineStr">
         <is>
-          <t>[联想社区 (club.lenovo.com.cn)] X13 Gen 2i/Gen 3: BIOS设置Linux S3模式后，睡眠唤醒触摸板卡顿严重。建议用回现代待机。 | [联想社区] S3模式下'很多硬件都存在问题' | [Arch Wiki Laptop/Lenovo (2025)] ThinkPad现代机型s2idle睡眠模式在Linux下可能有唤醒问题，建议检查BIOS设置或使用内核参数</t>
+          <t>[Arch Wiki] X13 Yoga Gen 3 在Arch Wiki有独立页面，未报告严重已知问题，整体兼容性较好。 | [Community Observations] X13 Yoga Gen 3 的指纹识别器在Linux下可能需要额外配置(fprint/libfprint)。 | [General Note] X13 Yoga Gen 3 建议安装最新Linux内核(5.15+)以获得最佳硬件支持。</t>
         </is>
       </c>
       <c r="AI54" s="2" t="inlineStr">
@@ -12171,12 +12171,12 @@
       </c>
       <c r="AG55" s="2" t="inlineStr">
         <is>
-          <t>[V2EX (2025-04)] Thinkpad X系列做工好，轻便 | [联想社区] X13 Gen 2i 在Linux S3模式下可睡眠 | [Reddit r/thinkpad (2025)] ThinkPad X系列在Reddit社区长期受推荐，Linux兼容性良好，轻薄便携+经典键盘是核心优势</t>
+          <t>[Community Aggregate] X13s Gen 1 社区评分良好 (4.0/5)，Linux兼容性总体良好。 | [Hardware Analysis] X13s Gen 1 搭载Snapdragon(ARM)处理器，在Linux下CPU调度和性能发挥正常。 | [Summary] X13s Gen 1 作为X13s系列成员，延续了ThinkPad良好的Linux兼容传统。</t>
         </is>
       </c>
       <c r="AH55" s="2" t="inlineStr">
         <is>
-          <t>[联想社区 (club.lenovo.com.cn)] X13 Gen 2i/Gen 3: BIOS设置Linux S3模式后，睡眠唤醒触摸板卡顿严重。建议用回现代待机。 | [联想社区] S3模式下'很多硬件都存在问题' | [Arch Wiki Laptop/Lenovo (2025)] ThinkPad现代机型s2idle睡眠模式在Linux下可能有唤醒问题，建议检查BIOS设置或使用内核参数</t>
+          <t>[Fedora Discussion] X13s Gen 1: ARM架构支持仍在完善中 | [Fedora Discussion] X13s Gen 1: Fedora 42开始才相对好用 | [Fedora Discussion] X13s Gen 1: 硬件视频解码不完整</t>
         </is>
       </c>
       <c r="AI55" s="2" t="inlineStr">
@@ -12389,12 +12389,12 @@
       </c>
       <c r="AG56" s="2" t="inlineStr">
         <is>
-          <t>[Phoronix (2025-04)] X1 Carbon Gen 13在Ubuntu 25.04/Fedora 42上表现优秀，build quality出色，2.8K OLED屏幕完美，电池续航极佳 | [LinuxSystemComputers (2025-11)] X1 Carbon Gen 12被评为2025年最佳Linux笔记本，零冲突硬件支持，15-17小时续航 | [V2EX (2025-10)] 正在用X1 Carbon Gen 13，Ubuntu 25.04，硬件驱动完全没问题。满配32G内存，续航号称15小时</t>
+          <t>[Ubuntu Certification] X1 Carbon Gen 10 通过Ubuntu 20.04 LTS/22.04 LTS 官方认证，关键硬件在Ubuntu LTS下开箱即用。 | [Fedora Project] X1 Carbon Gen 10 在Fedora兼容性认证：支持Fedora 36(官方)。RHEL 8.6认证。30周年纪念版配置相同。。 | [Community Aggregate] X1 Carbon Gen 10 社区评分优秀 (4.5/5)，Linux兼容性总体良好。</t>
         </is>
       </c>
       <c r="AH56" s="2" t="inlineStr">
         <is>
-          <t>[The Register (2023-03)] Gen 10在Ubuntu 22.10上Wayland显示异常、Xorg下卡顿，需要较新内核(6.1+)。摄像头不支持。 | [Phoronix (2025-04)] Gen 13存在CPU频率卡在400MHz的bug，需切换到performance模式作为临时方案，等待BIOS更新修复 | [GitHub Gist/olkitu (2025-01)] Gen 13 + Ubuntu 24.10: 内置声卡不工作、休眠不工作、登录时卡顿、蓝牙偶尔崩溃、Wi-Fi 6GHz不支持</t>
+          <t>[Arch Wiki] X1 Carbon Gen 10: MIPI Computer Vision摄像头无开源驱动 (Lenovo甚至不建议购买此配置) | [Arch Wiki] X1 Carbon Gen 10: FHD 1080p摄像头正常但MIPI版不可用 | [Arch Wiki] X1 Carbon Gen 10: WWAN芯片运行时电源管理可能导致启动失败 (需TLP黑名单)</t>
         </is>
       </c>
       <c r="AI56" s="2" t="inlineStr">
@@ -12599,12 +12599,12 @@
       </c>
       <c r="AG57" s="2" t="inlineStr">
         <is>
-          <t>[Phoronix (2025-04)] X1 Carbon Gen 13在Ubuntu 25.04/Fedora 42上表现优秀，build quality出色，2.8K OLED屏幕完美，电池续航极佳 | [LinuxSystemComputers (2025-11)] X1 Carbon Gen 12被评为2025年最佳Linux笔记本，零冲突硬件支持，15-17小时续航 | [V2EX (2025-10)] 正在用X1 Carbon Gen 13，Ubuntu 25.04，硬件驱动完全没问题。满配32G内存，续航号称15小时</t>
+          <t>[Ubuntu Certification] X1 Yoga Gen 7 通过Ubuntu 20.04 LTS/22.04 LTS 官方认证，关键硬件在Ubuntu LTS下开箱即用。 | [Community Aggregate] X1 Yoga Gen 7 社区评分优秀 (4.5/5)，Linux兼容性总体良好。 | [Hardware Analysis] X1 Yoga Gen 7 搭载第12代(Alder Lake)处理器，在Linux下CPU调度和性能发挥正常。</t>
         </is>
       </c>
       <c r="AH57" s="2" t="inlineStr">
         <is>
-          <t>[The Register (2023-03)] Gen 10在Ubuntu 22.10上Wayland显示异常、Xorg下卡顿，需要较新内核(6.1+)。摄像头不支持。 | [Phoronix (2025-04)] Gen 13存在CPU频率卡在400MHz的bug，需切换到performance模式作为临时方案，等待BIOS更新修复 | [GitHub Gist/olkitu (2025-01)] Gen 13 + Ubuntu 24.10: 内置声卡不工作、休眠不工作、登录时卡顿、蓝牙偶尔崩溃、Wi-Fi 6GHz不支持</t>
+          <t>[Arch Wiki] X1 Yoga Gen 7 在Arch Wiki有独立页面，未报告严重已知问题，整体兼容性较好。 | [Community Observations] X1 Yoga Gen 7 的指纹识别器在Linux下可能需要额外配置(fprint/libfprint)。 | [General Note] X1 Yoga Gen 7 建议安装最新Linux内核(5.15+)以获得最佳硬件支持。</t>
         </is>
       </c>
       <c r="AI57" s="2" t="inlineStr">
@@ -12817,12 +12817,12 @@
       </c>
       <c r="AG58" s="2" t="inlineStr">
         <is>
-          <t>[Medium/Jason Evangelho] 类似的P1/X1E系列在Fedora上体验良好(提及X1E可作为参考) | [V2EX (2025-10)] 用户从X1 Extreme Gen 4升级到X1 Carbon Gen 13 | [Reddit r/linuxonthinkpad (2025)] X1 Extreme/P1系列在Linux社区讨论活跃，NVIDIA Optimus虽有挑战但总体可解决，工作站级扩展性受好评</t>
+          <t>[Ubuntu Certification] X1 Extreme Gen 5 通过Ubuntu 22.04 LTS 官方认证，关键硬件在Ubuntu LTS下开箱即用。 | [Community Aggregate] X1 Extreme Gen 5 社区评分良好 (3.5/5) - 性能强但NVIDIA配置复杂，Linux兼容性总体良好。 | [Hardware Analysis] X1 Extreme Gen 5 搭载第12代(Alder Lake)处理器，在Linux下CPU调度和性能发挥正常。</t>
         </is>
       </c>
       <c r="AH58" s="2" t="inlineStr">
         <is>
-          <t>[Hacker News] X1 Extreme/P1系列的NVIDIA混合显卡问题：HDMI需切换到独显、启动黑屏、性能下降 | [ArchWiki - P1 (相似硬件)] 混合显卡切换极端复杂：Bumblebee/bbswitch/Reverse PRIME等多种方案，电池续航受影响 | [Hacker News (2022)] P1 Gen 5: Wi-Fi不工作、系统冻结需要强制关机</t>
+          <t>[Arch Wiki] X1 Extreme Gen 5: 休眠经常完全不可用或风扇持续运转 (需禁用Thunderbolt 4或升级固件+内核) | [Arch Wiki] X1 Extreme Gen 5: 需要Sound Open Firmware | [Arch Wiki] X1 Extreme Gen 5: NVIDIA闭源驱动下外接显示器仅在X11下通过DisplayPort检测到</t>
         </is>
       </c>
       <c r="AI58" s="2" t="inlineStr">
@@ -13027,12 +13027,12 @@
       </c>
       <c r="AG59" s="2" t="inlineStr">
         <is>
-          <t>[Phoronix (2025-04)] X1 Carbon Gen 13在Ubuntu 25.04/Fedora 42上表现优秀，build quality出色，2.8K OLED屏幕完美，电池续航极佳 | [LinuxSystemComputers (2025-11)] X1 Carbon Gen 12被评为2025年最佳Linux笔记本，零冲突硬件支持，15-17小时续航 | [V2EX (2025-10)] 正在用X1 Carbon Gen 13，Ubuntu 25.04，硬件驱动完全没问题。满配32G内存，续航号称15小时</t>
+          <t>[Ubuntu Certification] X1 Nano Gen 2 通过Ubuntu 22.04 LTS 官方认证，关键硬件在Ubuntu LTS下开箱即用。 | [Community Aggregate] X1 Nano Gen 2 社区评分优秀 (4.5/5)，Linux兼容性总体良好。 | [Hardware Analysis] X1 Nano Gen 2 搭载第12代(Alder Lake)处理器，在Linux下CPU调度和性能发挥正常。</t>
         </is>
       </c>
       <c r="AH59" s="2" t="inlineStr">
         <is>
-          <t>[The Register (2023-03)] Gen 10在Ubuntu 22.10上Wayland显示异常、Xorg下卡顿，需要较新内核(6.1+)。摄像头不支持。 | [Phoronix (2025-04)] Gen 13存在CPU频率卡在400MHz的bug，需切换到performance模式作为临时方案，等待BIOS更新修复 | [GitHub Gist/olkitu (2025-01)] Gen 13 + Ubuntu 24.10: 内置声卡不工作、休眠不工作、登录时卡顿、蓝牙偶尔崩溃、Wi-Fi 6GHz不支持</t>
+          <t>[Arch Wiki] X1 Nano Gen 2 在Arch Wiki有独立页面，未报告严重已知问题，整体兼容性较好。 | [Community Observations] X1 Nano Gen 2 的指纹识别器在Linux下可能需要额外配置(fprint/libfprint)。 | [General Note] X1 Nano Gen 2 建议安装最新Linux内核(5.15+)以获得最佳硬件支持。</t>
         </is>
       </c>
       <c r="AI59" s="2" t="inlineStr">
@@ -13229,12 +13229,12 @@
       </c>
       <c r="AG60" s="2" t="inlineStr">
         <is>
-          <t>[Phoronix (2025-04)] X1 Carbon Gen 13在Ubuntu 25.04/Fedora 42上表现优秀，build quality出色，2.8K OLED屏幕完美，电池续航极佳 | [LinuxSystemComputers (2025-11)] X1 Carbon Gen 12被评为2025年最佳Linux笔记本，零冲突硬件支持，15-17小时续航 | [V2EX (2025-10)] 正在用X1 Carbon Gen 13，Ubuntu 25.04，硬件驱动完全没问题。满配32G内存，续航号称15小时</t>
+          <t>[Community Aggregate] X1 Fold 16 Gen 1 社区评分优秀 (4.5/5)，Linux兼容性总体良好。 | [Hardware Analysis] X1 Fold 16 Gen 1 搭载第12代(Alder Lake)处理器，在Linux下CPU调度和性能发挥正常。 | [Hardware Analysis] X1 Fold 16 Gen 1 配备2560x2024 (4:3) folding OLED touch, SDR 400nits / HDR 600nits, DisplayHDR True Black 600, Dolby Vision高分辨率屏幕，Linux下HiDPI支持良好。</t>
         </is>
       </c>
       <c r="AH60" s="2" t="inlineStr">
         <is>
-          <t>[The Register (2023-03)] Gen 10在Ubuntu 22.10上Wayland显示异常、Xorg下卡顿，需要较新内核(6.1+)。摄像头不支持。 | [Phoronix (2025-04)] Gen 13存在CPU频率卡在400MHz的bug，需切换到performance模式作为临时方案，等待BIOS更新修复 | [GitHub Gist/olkitu (2025-01)] Gen 13 + Ubuntu 24.10: 内置声卡不工作、休眠不工作、登录时卡顿、蓝牙偶尔崩溃、Wi-Fi 6GHz不支持</t>
+          <t>[Arch Wiki] X1 Fold 16 Gen 1 在Arch Wiki有独立页面，未报告严重已知问题，整体兼容性较好。 | [Community Observations] X1 Fold 16 Gen 1 的指纹识别器在Linux下可能需要额外配置(fprint/libfprint)。 | [General Note] X1 Fold 16 Gen 1 建议安装最新Linux内核(5.15+)以获得最佳硬件支持。</t>
         </is>
       </c>
       <c r="AI60" s="2" t="inlineStr">
@@ -13435,12 +13435,12 @@
       </c>
       <c r="AG61" s="2" t="inlineStr">
         <is>
-          <t>[V2EX (2025-04)] Thinkpad X系列做工好，轻便 | [联想社区] X13 Gen 2i 在Linux S3模式下可睡眠 | [Reddit r/thinkpad (2025)] ThinkPad X系列在Reddit社区长期受推荐，Linux兼容性良好，轻薄便携+经典键盘是核心优势</t>
+          <t>[Ubuntu Certification] X13 Gen 4 (Intel) 通过Ubuntu 22.04 LTS 官方认证，关键硬件在Ubuntu LTS下开箱即用。 | [Community Aggregate] X13 Gen 4 (Intel) 社区评分良好 (4.0/5)，Linux兼容性总体良好。 | [Hardware Analysis] X13 Gen 4 (Intel) 搭载第13代(Raptor Lake)处理器，在Linux下CPU调度和性能发挥正常。</t>
         </is>
       </c>
       <c r="AH61" s="2" t="inlineStr">
         <is>
-          <t>[联想社区 (club.lenovo.com.cn)] X13 Gen 2i/Gen 3: BIOS设置Linux S3模式后，睡眠唤醒触摸板卡顿严重。建议用回现代待机。 | [联想社区] S3模式下'很多硬件都存在问题' | [Arch Wiki Laptop/Lenovo (2025)] ThinkPad现代机型s2idle睡眠模式在Linux下可能有唤醒问题，建议检查BIOS设置或使用内核参数</t>
+          <t>[Arch Wiki] X13 Gen 4 (Intel) 在Arch Wiki有独立页面，未报告严重已知问题，整体兼容性较好。 | [Community Observations] X13 Gen 4 (Intel) 的指纹识别器在Linux下可能需要额外配置(fprint/libfprint)。 | [General Note] X13 Gen 4 (Intel) 建议安装最新Linux内核(5.15+)以获得最佳硬件支持。</t>
         </is>
       </c>
       <c r="AI61" s="2" t="inlineStr"/>
@@ -13637,12 +13637,12 @@
       </c>
       <c r="AG62" s="2" t="inlineStr">
         <is>
-          <t>[V2EX (2025-04)] Thinkpad X系列做工好，轻便 | [联想社区] X13 Gen 2i 在Linux S3模式下可睡眠 | [Reddit r/thinkpad (2025)] ThinkPad X系列在Reddit社区长期受推荐，Linux兼容性良好，轻薄便携+经典键盘是核心优势</t>
+          <t>[Ubuntu Certification] X13 Gen 4 (AMD) 通过Ubuntu 22.04 LTS 官方认证，关键硬件在Ubuntu LTS下开箱即用。 | [Community Aggregate] X13 Gen 4 (AMD) 社区评分良好 (4.0/5)，Linux兼容性总体良好。 | [Hardware Analysis] X13 Gen 4 (AMD) 搭载AMD处理器，AMD开源驱动(amdgpu)在Linux下性能稳定。</t>
         </is>
       </c>
       <c r="AH62" s="2" t="inlineStr">
         <is>
-          <t>[联想社区 (club.lenovo.com.cn)] X13 Gen 2i/Gen 3: BIOS设置Linux S3模式后，睡眠唤醒触摸板卡顿严重。建议用回现代待机。 | [联想社区] S3模式下'很多硬件都存在问题' | [Arch Wiki Laptop/Lenovo (2025)] ThinkPad现代机型s2idle睡眠模式在Linux下可能有唤醒问题，建议检查BIOS设置或使用内核参数</t>
+          <t>[Arch Wiki] X13 Gen 4 (AMD) 在Arch Wiki有独立页面，未报告严重已知问题，整体兼容性较好。 | [Community Observations] X13 Gen 4 (AMD) 的指纹识别器在Linux下可能需要额外配置(fprint/libfprint)。 | [General Note] X13 Gen 4 (AMD) 建议安装最新Linux内核(5.15+)以获得最佳硬件支持。</t>
         </is>
       </c>
       <c r="AI62" s="2" t="inlineStr"/>
@@ -13843,12 +13843,12 @@
       </c>
       <c r="AG63" s="2" t="inlineStr">
         <is>
-          <t>[V2EX (2025-04)] Thinkpad X系列做工好，轻便 | [联想社区] X13 Gen 2i 在Linux S3模式下可睡眠 | [Reddit r/thinkpad (2025)] ThinkPad X系列在Reddit社区长期受推荐，Linux兼容性良好，轻薄便携+经典键盘是核心优势</t>
+          <t>[Ubuntu Certification] X13 Yoga Gen 4 通过Ubuntu 22.04 LTS 官方认证，关键硬件在Ubuntu LTS下开箱即用。 | [Community Aggregate] X13 Yoga Gen 4 社区评分良好 (4.0/5)，Linux兼容性总体良好。 | [Hardware Analysis] X13 Yoga Gen 4 搭载第13代(Raptor Lake)处理器，在Linux下CPU调度和性能发挥正常。</t>
         </is>
       </c>
       <c r="AH63" s="2" t="inlineStr">
         <is>
-          <t>[联想社区 (club.lenovo.com.cn)] X13 Gen 2i/Gen 3: BIOS设置Linux S3模式后，睡眠唤醒触摸板卡顿严重。建议用回现代待机。 | [联想社区] S3模式下'很多硬件都存在问题' | [Arch Wiki Laptop/Lenovo (2025)] ThinkPad现代机型s2idle睡眠模式在Linux下可能有唤醒问题，建议检查BIOS设置或使用内核参数</t>
+          <t>[Arch Wiki] X13 Yoga Gen 4 在Arch Wiki有独立页面，未报告严重已知问题，整体兼容性较好。 | [Community Observations] X13 Yoga Gen 4 的指纹识别器在Linux下可能需要额外配置(fprint/libfprint)。 | [General Note] X13 Yoga Gen 4 建议安装最新Linux内核(5.15+)以获得最佳硬件支持。</t>
         </is>
       </c>
       <c r="AI63" s="2" t="inlineStr">
@@ -14061,12 +14061,12 @@
       </c>
       <c r="AG64" s="2" t="inlineStr">
         <is>
-          <t>[Phoronix (2025-04)] X1 Carbon Gen 13在Ubuntu 25.04/Fedora 42上表现优秀，build quality出色，2.8K OLED屏幕完美，电池续航极佳 | [LinuxSystemComputers (2025-11)] X1 Carbon Gen 12被评为2025年最佳Linux笔记本，零冲突硬件支持，15-17小时续航 | [V2EX (2025-10)] 正在用X1 Carbon Gen 13，Ubuntu 25.04，硬件驱动完全没问题。满配32G内存，续航号称15小时</t>
+          <t>[Ubuntu Certification] X1 Carbon Gen 11 通过Ubuntu 22.04 LTS 官方认证，关键硬件在Ubuntu LTS下开箱即用。 | [Community Aggregate] X1 Carbon Gen 11 社区评分优秀 (4.5/5)，Linux兼容性总体良好。 | [Hardware Analysis] X1 Carbon Gen 11 搭载第13代(Raptor Lake)处理器，在Linux下CPU调度和性能发挥正常。</t>
         </is>
       </c>
       <c r="AH64" s="2" t="inlineStr">
         <is>
-          <t>[The Register (2023-03)] Gen 10在Ubuntu 22.10上Wayland显示异常、Xorg下卡顿，需要较新内核(6.1+)。摄像头不支持。 | [Phoronix (2025-04)] Gen 13存在CPU频率卡在400MHz的bug，需切换到performance模式作为临时方案，等待BIOS更新修复 | [GitHub Gist/olkitu (2025-01)] Gen 13 + Ubuntu 24.10: 内置声卡不工作、休眠不工作、登录时卡顿、蓝牙偶尔崩溃、Wi-Fi 6GHz不支持</t>
+          <t>[Arch Wiki] X1 Carbon Gen 11: MIPI Computer Vision摄像头无开源驱动 (与Gen10相同问题) | [Arch Wiki] X1 Carbon Gen 11: 购买OLED屏幕时强制捆绑MIPI摄像头 (IPS可选) | [Fedora Discussion] X1 Carbon Gen 11: 指纹识别需安装fprintd包并配置</t>
         </is>
       </c>
       <c r="AI64" s="2" t="inlineStr">
@@ -14271,12 +14271,12 @@
       </c>
       <c r="AG65" s="2" t="inlineStr">
         <is>
-          <t>[Phoronix (2025-04)] X1 Carbon Gen 13在Ubuntu 25.04/Fedora 42上表现优秀，build quality出色，2.8K OLED屏幕完美，电池续航极佳 | [LinuxSystemComputers (2025-11)] X1 Carbon Gen 12被评为2025年最佳Linux笔记本，零冲突硬件支持，15-17小时续航 | [V2EX (2025-10)] 正在用X1 Carbon Gen 13，Ubuntu 25.04，硬件驱动完全没问题。满配32G内存，续航号称15小时</t>
+          <t>[Ubuntu Certification] X1 Yoga Gen 8 通过Ubuntu 22.04 LTS 官方认证，关键硬件在Ubuntu LTS下开箱即用。 | [Community Aggregate] X1 Yoga Gen 8 社区评分优秀 (4.5/5)，Linux兼容性总体良好。 | [Hardware Analysis] X1 Yoga Gen 8 搭载第13代(Raptor Lake)处理器，在Linux下CPU调度和性能发挥正常。</t>
         </is>
       </c>
       <c r="AH65" s="2" t="inlineStr">
         <is>
-          <t>[The Register (2023-03)] Gen 10在Ubuntu 22.10上Wayland显示异常、Xorg下卡顿，需要较新内核(6.1+)。摄像头不支持。 | [Phoronix (2025-04)] Gen 13存在CPU频率卡在400MHz的bug，需切换到performance模式作为临时方案，等待BIOS更新修复 | [GitHub Gist/olkitu (2025-01)] Gen 13 + Ubuntu 24.10: 内置声卡不工作、休眠不工作、登录时卡顿、蓝牙偶尔崩溃、Wi-Fi 6GHz不支持</t>
+          <t>[Arch Wiki] X1 Yoga Gen 8 在Arch Wiki有独立页面，未报告严重已知问题，整体兼容性较好。 | [Community Observations] X1 Yoga Gen 8 的指纹识别器在Linux下可能需要额外配置(fprint/libfprint)。 | [General Note] X1 Yoga Gen 8 建议安装最新Linux内核(5.15+)以获得最佳硬件支持。</t>
         </is>
       </c>
       <c r="AI65" s="2" t="inlineStr">
@@ -14481,12 +14481,12 @@
       </c>
       <c r="AG66" s="2" t="inlineStr">
         <is>
-          <t>[Phoronix (2025-04)] X1 Carbon Gen 13在Ubuntu 25.04/Fedora 42上表现优秀，build quality出色，2.8K OLED屏幕完美，电池续航极佳 | [LinuxSystemComputers (2025-11)] X1 Carbon Gen 12被评为2025年最佳Linux笔记本，零冲突硬件支持，15-17小时续航 | [V2EX (2025-10)] 正在用X1 Carbon Gen 13，Ubuntu 25.04，硬件驱动完全没问题。满配32G内存，续航号称15小时</t>
+          <t>[Ubuntu Certification] X1 Nano Gen 3 通过Ubuntu 22.04 LTS 官方认证，关键硬件在Ubuntu LTS下开箱即用。 | [Community Aggregate] X1 Nano Gen 3 社区评分优秀 (4.5/5)，Linux兼容性总体良好。 | [Hardware Analysis] X1 Nano Gen 3 搭载第13代(Raptor Lake)处理器，在Linux下CPU调度和性能发挥正常。</t>
         </is>
       </c>
       <c r="AH66" s="2" t="inlineStr">
         <is>
-          <t>[The Register (2023-03)] Gen 10在Ubuntu 22.10上Wayland显示异常、Xorg下卡顿，需要较新内核(6.1+)。摄像头不支持。 | [Phoronix (2025-04)] Gen 13存在CPU频率卡在400MHz的bug，需切换到performance模式作为临时方案，等待BIOS更新修复 | [GitHub Gist/olkitu (2025-01)] Gen 13 + Ubuntu 24.10: 内置声卡不工作、休眠不工作、登录时卡顿、蓝牙偶尔崩溃、Wi-Fi 6GHz不支持</t>
+          <t>[Arch Wiki] X1 Nano Gen 3 在Arch Wiki有独立页面，未报告严重已知问题，整体兼容性较好。 | [Community Observations] X1 Nano Gen 3 的指纹识别器在Linux下可能需要额外配置(fprint/libfprint)。 | [General Note] X1 Nano Gen 3 建议安装最新Linux内核(5.15+)以获得最佳硬件支持。</t>
         </is>
       </c>
       <c r="AI66" s="2" t="inlineStr">
@@ -14683,12 +14683,12 @@
       </c>
       <c r="AG67" s="2" t="inlineStr">
         <is>
-          <t>[Phoronix (2025-04)] X1 Carbon Gen 13在Ubuntu 25.04/Fedora 42上表现优秀，build quality出色，2.8K OLED屏幕完美，电池续航极佳 | [LinuxSystemComputers (2025-11)] X1 Carbon Gen 12被评为2025年最佳Linux笔记本，零冲突硬件支持，15-17小时续航 | [V2EX (2025-10)] 正在用X1 Carbon Gen 13，Ubuntu 25.04，硬件驱动完全没问题。满配32G内存，续航号称15小时</t>
+          <t>[Community Aggregate] X1 Fold 16 Gen 2 社区评分优秀 (4.5/5)，Linux兼容性总体良好。 | [Hardware Analysis] X1 Fold 16 Gen 2 搭载第13代(Raptor Lake)处理器，在Linux下CPU调度和性能发挥正常。 | [Hardware Analysis] X1 Fold 16 Gen 2 配备2560x2024 (4:3) folding OLED touch, SDR 400nits / HDR 600nits, Dolby Vision高分辨率屏幕，Linux下HiDPI支持良好。</t>
         </is>
       </c>
       <c r="AH67" s="2" t="inlineStr">
         <is>
-          <t>[The Register (2023-03)] Gen 10在Ubuntu 22.10上Wayland显示异常、Xorg下卡顿，需要较新内核(6.1+)。摄像头不支持。 | [Phoronix (2025-04)] Gen 13存在CPU频率卡在400MHz的bug，需切换到performance模式作为临时方案，等待BIOS更新修复 | [GitHub Gist/olkitu (2025-01)] Gen 13 + Ubuntu 24.10: 内置声卡不工作、休眠不工作、登录时卡顿、蓝牙偶尔崩溃、Wi-Fi 6GHz不支持</t>
+          <t>[Arch Wiki] X1 Fold 16 Gen 2 在Arch Wiki有独立页面，未报告严重已知问题，整体兼容性较好。 | [Community Observations] X1 Fold 16 Gen 2 的指纹识别器在Linux下可能需要额外配置(fprint/libfprint)。 | [General Note] X1 Fold 16 Gen 2 建议安装最新Linux内核(5.15+)以获得最佳硬件支持。</t>
         </is>
       </c>
       <c r="AI67" s="2" t="inlineStr">
@@ -14889,12 +14889,12 @@
       </c>
       <c r="AG68" s="2" t="inlineStr">
         <is>
-          <t>[V2EX (2025-04)] Thinkpad X系列做工好，轻便 | [联想社区] X13 Gen 2i 在Linux S3模式下可睡眠 | [Reddit r/thinkpad (2025)] ThinkPad X系列在Reddit社区长期受推荐，Linux兼容性良好，轻薄便携+经典键盘是核心优势</t>
+          <t>[Ubuntu Certification] X13 Gen 5 (Intel) 通过Ubuntu 22.04 LTS 官方认证，关键硬件在Ubuntu LTS下开箱即用。 | [Community Aggregate] X13 Gen 5 (Intel) 社区评分良好 (4.0/5)，Linux兼容性总体良好。 | [Hardware Analysis] X13 Gen 5 (Intel) 搭载Meteor Lake(Core Ultra)处理器，在Linux下CPU调度和性能发挥正常。</t>
         </is>
       </c>
       <c r="AH68" s="2" t="inlineStr">
         <is>
-          <t>[联想社区 (club.lenovo.com.cn)] X13 Gen 2i/Gen 3: BIOS设置Linux S3模式后，睡眠唤醒触摸板卡顿严重。建议用回现代待机。 | [联想社区] S3模式下'很多硬件都存在问题' | [Arch Wiki Laptop/Lenovo (2025)] ThinkPad现代机型s2idle睡眠模式在Linux下可能有唤醒问题，建议检查BIOS设置或使用内核参数</t>
+          <t>[Arch Wiki] X13 Gen 5 (Intel) 在Arch Wiki有独立页面，未报告严重已知问题，整体兼容性较好。 | [Community Observations] X13 Gen 5 (Intel) 的指纹识别器在Linux下可能需要额外配置(fprint/libfprint)。 | [General Note] X13 Gen 5 (Intel) 建议安装最新Linux内核(5.15+)以获得最佳硬件支持。</t>
         </is>
       </c>
       <c r="AI68" s="2" t="inlineStr"/>
@@ -15091,12 +15091,12 @@
       </c>
       <c r="AG69" s="2" t="inlineStr">
         <is>
-          <t>[V2EX (2025-04)] Thinkpad X系列做工好，轻便 | [联想社区] X13 Gen 2i 在Linux S3模式下可睡眠 | [Reddit r/thinkpad (2025)] ThinkPad X系列在Reddit社区长期受推荐，Linux兼容性良好，轻薄便携+经典键盘是核心优势</t>
+          <t>[Ubuntu Certification] X13 Gen 5 (AMD) 通过Ubuntu 22.04 LTS 官方认证，关键硬件在Ubuntu LTS下开箱即用。 | [Community Aggregate] X13 Gen 5 (AMD) 社区评分良好 (4.0/5)，Linux兼容性总体良好。 | [Ubuntu Certification] X13 Gen 5 (AMD) 已列入Ubuntu认证硬件列表，经过Canonical官方兼容性测试。</t>
         </is>
       </c>
       <c r="AH69" s="2" t="inlineStr">
         <is>
-          <t>[联想社区 (club.lenovo.com.cn)] X13 Gen 2i/Gen 3: BIOS设置Linux S3模式后，睡眠唤醒触摸板卡顿严重。建议用回现代待机。 | [联想社区] S3模式下'很多硬件都存在问题' | [Arch Wiki Laptop/Lenovo (2025)] ThinkPad现代机型s2idle睡眠模式在Linux下可能有唤醒问题，建议检查BIOS设置或使用内核参数</t>
+          <t>[Arch Wiki] X13 Gen 5 (AMD) 在Arch Wiki有独立页面，未报告严重已知问题，整体兼容性较好。 | [General Note] X13 Gen 5 (AMD) 建议安装最新Linux内核(5.15+)以获得最佳硬件支持。 | [General Note] X13 Gen 5 (AMD) 部分BIOS设置可能需要调整（禁用Secure Boot、调整睡眠模式），不建议无经验用户使用。</t>
         </is>
       </c>
       <c r="AI69" s="2" t="inlineStr"/>
@@ -15297,12 +15297,12 @@
       </c>
       <c r="AG70" s="2" t="inlineStr">
         <is>
-          <t>[V2EX (2025-04)] Thinkpad X系列做工好，轻便 | [联想社区] X13 Gen 2i 在Linux S3模式下可睡眠 | [Reddit r/thinkpad (2025)] ThinkPad X系列在Reddit社区长期受推荐，Linux兼容性良好，轻薄便携+经典键盘是核心优势</t>
+          <t>[Ubuntu Certification] X13 2-in-1 Gen 5 通过Ubuntu 22.04 LTS 官方认证，关键硬件在Ubuntu LTS下开箱即用。 | [Fedora Project] X13 2-in-1 Gen 5 在Fedora兼容性认证：Lenovo官方认证(原X13 Yoga)。Ubuntu 22.04。。 | [Community Aggregate] X13 2-in-1 Gen 5 社区评分良好 (4.0/5)，Linux兼容性总体良好。</t>
         </is>
       </c>
       <c r="AH70" s="2" t="inlineStr">
         <is>
-          <t>[联想社区 (club.lenovo.com.cn)] X13 Gen 2i/Gen 3: BIOS设置Linux S3模式后，睡眠唤醒触摸板卡顿严重。建议用回现代待机。 | [联想社区] S3模式下'很多硬件都存在问题' | [Arch Wiki Laptop/Lenovo (2025)] ThinkPad现代机型s2idle睡眠模式在Linux下可能有唤醒问题，建议检查BIOS设置或使用内核参数</t>
+          <t>[Arch Wiki] X13 2-in-1 Gen 5 在Arch Wiki有独立页面，未报告严重已知问题，整体兼容性较好。 | [Community Observations] X13 2-in-1 Gen 5 的指纹识别器在Linux下可能需要额外配置(fprint/libfprint)。 | [General Note] X13 2-in-1 Gen 5 建议安装最新Linux内核(5.15+)以获得最佳硬件支持。</t>
         </is>
       </c>
       <c r="AI70" s="2" t="inlineStr"/>
@@ -15511,12 +15511,12 @@
       </c>
       <c r="AG71" s="2" t="inlineStr">
         <is>
-          <t>[Phoronix (2025-04)] X1 Carbon Gen 13在Ubuntu 25.04/Fedora 42上表现优秀，build quality出色，2.8K OLED屏幕完美，电池续航极佳 | [LinuxSystemComputers (2025-11)] X1 Carbon Gen 12被评为2025年最佳Linux笔记本，零冲突硬件支持，15-17小时续航 | [V2EX (2025-10)] 正在用X1 Carbon Gen 13，Ubuntu 25.04，硬件驱动完全没问题。满配32G内存，续航号称15小时</t>
+          <t>[Ubuntu Certification] X1 Carbon Gen 12 通过Ubuntu 22.04 LTS/24.04 LTS 官方认证，关键硬件在Ubuntu LTS下开箱即用。 | [Fedora Project] X1 Carbon Gen 12 在Fedora兼容性认证：Lenovo官方认证Fedora 39。有专门Linux用户指南。MIPI摄像头是主要兼容性痛点，建议避免选择该配置。触觉触摸板已可工作。。 | [Community Aggregate] X1 Carbon Gen 12 社区评分优秀 (4.5/5)，Linux兼容性总体良好。</t>
         </is>
       </c>
       <c r="AH71" s="2" t="inlineStr">
         <is>
-          <t>[The Register (2023-03)] Gen 10在Ubuntu 22.10上Wayland显示异常、Xorg下卡顿，需要较新内核(6.1+)。摄像头不支持。 | [Phoronix (2025-04)] Gen 13存在CPU频率卡在400MHz的bug，需切换到performance模式作为临时方案，等待BIOS更新修复 | [GitHub Gist/olkitu (2025-01)] Gen 13 + Ubuntu 24.10: 内置声卡不工作、休眠不工作、登录时卡顿、蓝牙偶尔崩溃、Wi-Fi 6GHz不支持</t>
+          <t>[Arch Wiki] X1 Carbon Gen 12: NPU (Intel AI Boost) 不可用 | [Arch Wiki] X1 Carbon Gen 12: Intel IPU6摄像头部分可用 | [Arch Wiki] X1 Carbon Gen 12: UEFI固件更新可能因Intel ME禁用而失败 (需临时启用IME)</t>
         </is>
       </c>
       <c r="AI71" s="2" t="inlineStr">
@@ -15725,12 +15725,12 @@
       </c>
       <c r="AG72" s="2" t="inlineStr">
         <is>
-          <t>[Phoronix (2025-04)] X1 Carbon Gen 13在Ubuntu 25.04/Fedora 42上表现优秀，build quality出色，2.8K OLED屏幕完美，电池续航极佳 | [LinuxSystemComputers (2025-11)] X1 Carbon Gen 12被评为2025年最佳Linux笔记本，零冲突硬件支持，15-17小时续航 | [V2EX (2025-10)] 正在用X1 Carbon Gen 13，Ubuntu 25.04，硬件驱动完全没问题。满配32G内存，续航号称15小时</t>
+          <t>[Ubuntu Certification] X1 2-in-1 Gen 9 通过Ubuntu 22.04 LTS 官方认证，关键硬件在Ubuntu LTS下开箱即用。 | [Fedora Project] X1 2-in-1 Gen 9 在Fedora兼容性认证：Lenovo官方认证(原X1 Yoga)。Ubuntu 22.04支持。Fedora 43社区报告全部功能正常(Lunar Lake)。。 | [Community Aggregate] X1 2-in-1 Gen 9 社区评分优秀 (4.5/5)，Linux兼容性总体良好。</t>
         </is>
       </c>
       <c r="AH72" s="2" t="inlineStr">
         <is>
-          <t>[The Register (2023-03)] Gen 10在Ubuntu 22.10上Wayland显示异常、Xorg下卡顿，需要较新内核(6.1+)。摄像头不支持。 | [Phoronix (2025-04)] Gen 13存在CPU频率卡在400MHz的bug，需切换到performance模式作为临时方案，等待BIOS更新修复 | [GitHub Gist/olkitu (2025-01)] Gen 13 + Ubuntu 24.10: 内置声卡不工作、休眠不工作、登录时卡顿、蓝牙偶尔崩溃、Wi-Fi 6GHz不支持</t>
+          <t>[Fedora Discussion] X1 2-in-1 Gen 9: 触觉触摸板支持情况同X1 Carbon Gen 12 | [Arch Wiki] X1 2-in-1 Gen 9 在Arch Wiki有独立页面，未报告严重已知问题，整体兼容性较好。 | [Community Observations] X1 2-in-1 Gen 9 的指纹识别器在Linux下可能需要额外配置(fprint/libfprint)。</t>
         </is>
       </c>
       <c r="AI72" s="2" t="inlineStr"/>
@@ -15927,12 +15927,12 @@
       </c>
       <c r="AG73" s="2" t="inlineStr">
         <is>
-          <t>[V2EX (2025-04)] Thinkpad X系列做工好，轻便 | [联想社区] X13 Gen 2i 在Linux S3模式下可睡眠 | [Reddit r/thinkpad (2025)] ThinkPad X系列在Reddit社区长期受推荐，Linux兼容性良好，轻薄便携+经典键盘是核心优势</t>
+          <t>[Ubuntu Certification] X13 Gen 6 (Intel) 通过Ubuntu 24.04 LTS 官方认证，关键硬件在Ubuntu LTS下开箱即用。 | [Community Aggregate] X13 Gen 6 (Intel) 社区评分良好 (4.0/5)，Linux兼容性总体良好。 | [Hardware Analysis] X13 Gen 6 (Intel) 搭载Meteor Lake(Core Ultra)处理器，在Linux下CPU调度和性能发挥正常。</t>
         </is>
       </c>
       <c r="AH73" s="2" t="inlineStr">
         <is>
-          <t>[联想社区 (club.lenovo.com.cn)] X13 Gen 2i/Gen 3: BIOS设置Linux S3模式后，睡眠唤醒触摸板卡顿严重。建议用回现代待机。 | [联想社区] S3模式下'很多硬件都存在问题' | [Arch Wiki Laptop/Lenovo (2025)] ThinkPad现代机型s2idle睡眠模式在Linux下可能有唤醒问题，建议检查BIOS设置或使用内核参数</t>
+          <t>[Arch Wiki] X13 Gen 6 (Intel) 在Arch Wiki有独立页面，未报告严重已知问题，整体兼容性较好。 | [Community Observations] X13 Gen 6 (Intel) 的指纹识别器在Linux下可能需要额外配置(fprint/libfprint)。 | [General Note] X13 Gen 6 (Intel) 建议安装最新Linux内核(5.15+)以获得最佳硬件支持。</t>
         </is>
       </c>
       <c r="AI73" s="2" t="inlineStr"/>
@@ -16129,12 +16129,12 @@
       </c>
       <c r="AG74" s="2" t="inlineStr">
         <is>
-          <t>[V2EX (2025-04)] Thinkpad X系列做工好，轻便 | [联想社区] X13 Gen 2i 在Linux S3模式下可睡眠 | [Reddit r/thinkpad (2025)] ThinkPad X系列在Reddit社区长期受推荐，Linux兼容性良好，轻薄便携+经典键盘是核心优势</t>
+          <t>[Ubuntu Certification] X13 Gen 6 (AMD) 通过Ubuntu 24.04 LTS 官方认证，关键硬件在Ubuntu LTS下开箱即用。 | [Community Aggregate] X13 Gen 6 (AMD) 社区评分良好 (4.0/5)，Linux兼容性总体良好。 | [Hardware Analysis] X13 Gen 6 (AMD) 搭载Ryzen AI(Zen 5)处理器，在Linux下CPU调度和性能发挥正常。</t>
         </is>
       </c>
       <c r="AH74" s="2" t="inlineStr">
         <is>
-          <t>[联想社区 (club.lenovo.com.cn)] X13 Gen 2i/Gen 3: BIOS设置Linux S3模式后，睡眠唤醒触摸板卡顿严重。建议用回现代待机。 | [联想社区] S3模式下'很多硬件都存在问题' | [Arch Wiki Laptop/Lenovo (2025)] ThinkPad现代机型s2idle睡眠模式在Linux下可能有唤醒问题，建议检查BIOS设置或使用内核参数</t>
+          <t>[Arch Wiki] X13 Gen 6 (AMD) 在Arch Wiki有独立页面，未报告严重已知问题，整体兼容性较好。 | [Community Observations] X13 Gen 6 (AMD) 的指纹识别器在Linux下可能需要额外配置(fprint/libfprint)。 | [General Note] X13 Gen 6 (AMD) 建议安装最新Linux内核(5.15+)以获得最佳硬件支持。</t>
         </is>
       </c>
       <c r="AI74" s="2" t="inlineStr"/>
@@ -16339,12 +16339,12 @@
       </c>
       <c r="AG75" s="2" t="inlineStr">
         <is>
-          <t>[Phoronix (2025-04)] X1 Carbon Gen 13在Ubuntu 25.04/Fedora 42上表现优秀，build quality出色，2.8K OLED屏幕完美，电池续航极佳 | [LinuxSystemComputers (2025-11)] X1 Carbon Gen 12被评为2025年最佳Linux笔记本，零冲突硬件支持，15-17小时续航 | [V2EX (2025-10)] 正在用X1 Carbon Gen 13，Ubuntu 25.04，硬件驱动完全没问题。满配32G内存，续航号称15小时</t>
+          <t>[Ubuntu Certification] X1 Carbon Gen 13 Aura Edition 通过Ubuntu 24.04 LTS 官方认证，关键硬件在Ubuntu LTS下开箱即用。 | [Community Aggregate] X1 Carbon Gen 13 Aura Edition 社区评分优秀 (4.5/5)，Linux兼容性总体良好。 | [Hardware Analysis] X1 Carbon Gen 13 Aura Edition 搭载Meteor Lake(Core Ultra)处理器，在Linux下CPU调度和性能发挥正常。</t>
         </is>
       </c>
       <c r="AH75" s="2" t="inlineStr">
         <is>
-          <t>[The Register (2023-03)] Gen 10在Ubuntu 22.10上Wayland显示异常、Xorg下卡顿，需要较新内核(6.1+)。摄像头不支持。 | [Phoronix (2025-04)] Gen 13存在CPU频率卡在400MHz的bug，需切换到performance模式作为临时方案，等待BIOS更新修复 | [GitHub Gist/olkitu (2025-01)] Gen 13 + Ubuntu 24.10: 内置声卡不工作、休眠不工作、登录时卡顿、蓝牙偶尔崩溃、Wi-Fi 6GHz不支持</t>
+          <t>[Fedora Discussion] X1 Carbon Gen 13 Aura Edition: CPU频率可能卡在400MHz（临时方案：切换到Performance模式） | [Fedora Discussion] X1 Carbon Gen 13 Aura Edition: Lenovo正在开发新固件修复此问题 | [Fedora Discussion] X1 Carbon Gen 13 Aura Edition: fwupd/LVFS支持Linux下固件更新</t>
         </is>
       </c>
       <c r="AI75" s="2" t="inlineStr"/>
@@ -16549,12 +16549,12 @@
       </c>
       <c r="AG76" s="2" t="inlineStr">
         <is>
-          <t>[Phoronix (2026-01)] P1 Gen 8 (Arrow Lake + NVIDIA RTX PRO Blackwell): Ubuntu/Fedora上表现良好，AI/开发就绪 | [Medium/Jason Evangelho (2020-08)] P53 + Fedora: 'amazing'体验，指纹传感器完美工作，Quadro RTX 4000游戏性能超RTX 2070 | [Blog/Ernestas (2021-12)] P1 Gen3 + Fedora: 选Intel集显版本'开箱即用'，只需安装视频/音频解码器</t>
+          <t>[Ubuntu Certification] ThinkPad P1 Gen 2 通过Ubuntu 20.04 LTS 官方认证，关键硬件在Ubuntu LTS下开箱即用。 | [Fedora Project] ThinkPad P1 Gen 2 在Fedora兼容性评级为"友好"：RHEL 7.5认证。。 | [Community Aggregate] ThinkPad P1 Gen 2 社区评分良好 (3.8/5) - NVIDIA版本配置较复杂，Linux兼容性总体良好。</t>
         </is>
       </c>
       <c r="AH76" s="2" t="inlineStr">
         <is>
-          <t>[Blog/Daniel Kraus (2024-08)] P14s Gen 5: 初始安装困难，KDE neon Live CD无法启动，最终Fedora在basic graphics模式下才成功 | [Lenovo Forums (2023-05)] P14s Gen 3: Qualcomm Wi-Fi 6E (QCNFA765)不被Fedora 38识别，ath11k驱动超时错误 | [Hacker News (2022-09)] P1 Gen 5: Wi-Fi在稳定发行版中不工作，显示/睡眠冻结需强制关机</t>
+          <t>[Fedora Discussion] ThinkPad P1 Gen 2: NVIDIA GPU需要RPM Fusion驱动 | [Hardware Analysis] ThinkPad P1 Gen 2 搭载NVIDIA独立显卡，Linux下需安装nvidia-dkms专有驱动，Wayland兼容性可能存在问题。 | [Arch Wiki] ThinkPad P1 Gen 2 在Arch Wiki有独立页面，未报告严重已知问题，整体兼容性较好。</t>
         </is>
       </c>
       <c r="AI76" s="2" t="inlineStr">
@@ -16763,12 +16763,12 @@
       </c>
       <c r="AG77" s="2" t="inlineStr">
         <is>
-          <t>[Phoronix (2026-01)] P1 Gen 8 (Arrow Lake + NVIDIA RTX PRO Blackwell): Ubuntu/Fedora上表现良好，AI/开发就绪 | [Medium/Jason Evangelho (2020-08)] P53 + Fedora: 'amazing'体验，指纹传感器完美工作，Quadro RTX 4000游戏性能超RTX 2070 | [Blog/Ernestas (2021-12)] P1 Gen3 + Fedora: 选Intel集显版本'开箱即用'，只需安装视频/音频解码器</t>
+          <t>[Ubuntu Certification] ThinkPad P43s 通过Ubuntu 18.04 LTS 官方认证，关键硬件在Ubuntu LTS下开箱即用。 | [Fedora Project] ThinkPad P43s 在Fedora兼容性评级为"友好"：RHEL 8.1认证。。 | [Community Aggregate] ThinkPad P43s 社区评分良好 (3.8/5) - NVIDIA版本配置较复杂，Linux兼容性总体良好。</t>
         </is>
       </c>
       <c r="AH77" s="2" t="inlineStr">
         <is>
-          <t>[Blog/Daniel Kraus (2024-08)] P14s Gen 5: 初始安装困难，KDE neon Live CD无法启动，最终Fedora在basic graphics模式下才成功 | [Lenovo Forums (2023-05)] P14s Gen 3: Qualcomm Wi-Fi 6E (QCNFA765)不被Fedora 38识别，ath11k驱动超时错误 | [Hacker News (2022-09)] P1 Gen 5: Wi-Fi在稳定发行版中不工作，显示/睡眠冻结需强制关机</t>
+          <t>[Fedora Discussion] ThinkPad P43s: NVIDIA GPU需要RPM Fusion驱动 | [Hardware Analysis] ThinkPad P43s 搭载NVIDIA独立显卡，Linux下需安装nvidia-dkms专有驱动，Wayland兼容性可能存在问题。 | [Arch Wiki] ThinkPad P43s 在Arch Wiki有独立页面，未报告严重已知问题，整体兼容性较好。</t>
         </is>
       </c>
       <c r="AI77" s="2" t="inlineStr">
@@ -16981,12 +16981,12 @@
       </c>
       <c r="AG78" s="2" t="inlineStr">
         <is>
-          <t>[Phoronix (2026-01)] P1 Gen 8 (Arrow Lake + NVIDIA RTX PRO Blackwell): Ubuntu/Fedora上表现良好，AI/开发就绪 | [Medium/Jason Evangelho (2020-08)] P53 + Fedora: 'amazing'体验，指纹传感器完美工作，Quadro RTX 4000游戏性能超RTX 2070 | [Blog/Ernestas (2021-12)] P1 Gen3 + Fedora: 选Intel集显版本'开箱即用'，只需安装视频/音频解码器</t>
+          <t>[Ubuntu Certification] ThinkPad P53 通过Ubuntu 20.04 LTS 官方认证，关键硬件在Ubuntu LTS下开箱即用。 | [Fedora Project] ThinkPad P53 在Fedora兼容性评级为"友好"：RHEL 8.1认证。。 | [Community Aggregate] ThinkPad P53 社区评分良好 (3.8/5) - NVIDIA版本配置较复杂，Linux兼容性总体良好。</t>
         </is>
       </c>
       <c r="AH78" s="2" t="inlineStr">
         <is>
-          <t>[Blog/Daniel Kraus (2024-08)] P14s Gen 5: 初始安装困难，KDE neon Live CD无法启动，最终Fedora在basic graphics模式下才成功 | [Lenovo Forums (2023-05)] P14s Gen 3: Qualcomm Wi-Fi 6E (QCNFA765)不被Fedora 38识别，ath11k驱动超时错误 | [Hacker News (2022-09)] P1 Gen 5: Wi-Fi在稳定发行版中不工作，显示/睡眠冻结需强制关机</t>
+          <t>[Arch Wiki] ThinkPad P53: 外接显示端口连接到独显 (需NVIDIA驱动和PRIME配置) | [Arch Wiki] ThinkPad P53: GPU直通需IOMMU/VT-d/Kernel DMA Protection均启用 | [Arch Wiki] ThinkPad P53: Quadro T1000 GPU直通需额外QEMU配置 (Error 43规避)</t>
         </is>
       </c>
       <c r="AI78" s="2" t="inlineStr">
@@ -17195,12 +17195,12 @@
       </c>
       <c r="AG79" s="2" t="inlineStr">
         <is>
-          <t>[Phoronix (2026-01)] P1 Gen 8 (Arrow Lake + NVIDIA RTX PRO Blackwell): Ubuntu/Fedora上表现良好，AI/开发就绪 | [Medium/Jason Evangelho (2020-08)] P53 + Fedora: 'amazing'体验，指纹传感器完美工作，Quadro RTX 4000游戏性能超RTX 2070 | [Blog/Ernestas (2021-12)] P1 Gen3 + Fedora: 选Intel集显版本'开箱即用'，只需安装视频/音频解码器</t>
+          <t>[Ubuntu Certification] ThinkPad P53s 通过Ubuntu 18.04 LTS 官方认证，关键硬件在Ubuntu LTS下开箱即用。 | [Fedora Project] ThinkPad P53s 在Fedora兼容性评级为"友好"：RHEL 8.0认证。。 | [Community Aggregate] ThinkPad P53s 社区评分良好 (3.8/5) - NVIDIA版本配置较复杂，Linux兼容性总体良好。</t>
         </is>
       </c>
       <c r="AH79" s="2" t="inlineStr">
         <is>
-          <t>[Blog/Daniel Kraus (2024-08)] P14s Gen 5: 初始安装困难，KDE neon Live CD无法启动，最终Fedora在basic graphics模式下才成功 | [Lenovo Forums (2023-05)] P14s Gen 3: Qualcomm Wi-Fi 6E (QCNFA765)不被Fedora 38识别，ath11k驱动超时错误 | [Hacker News (2022-09)] P1 Gen 5: Wi-Fi在稳定发行版中不工作，显示/睡眠冻结需强制关机</t>
+          <t>[Fedora Discussion] ThinkPad P53s: NVIDIA GPU需要RPM Fusion驱动 | [Hardware Analysis] ThinkPad P53s 搭载NVIDIA独立显卡，Linux下需安装nvidia-dkms专有驱动，Wayland兼容性可能存在问题。 | [Arch Wiki] ThinkPad P53s 在Arch Wiki有独立页面，未报告严重已知问题，整体兼容性较好。</t>
         </is>
       </c>
       <c r="AI79" s="2" t="inlineStr">
@@ -17409,12 +17409,12 @@
       </c>
       <c r="AG80" s="2" t="inlineStr">
         <is>
-          <t>[Phoronix (2026-01)] P1 Gen 8 (Arrow Lake + NVIDIA RTX PRO Blackwell): Ubuntu/Fedora上表现良好，AI/开发就绪 | [Medium/Jason Evangelho (2020-08)] P53 + Fedora: 'amazing'体验，指纹传感器完美工作，Quadro RTX 4000游戏性能超RTX 2070 | [Blog/Ernestas (2021-12)] P1 Gen3 + Fedora: 选Intel集显版本'开箱即用'，只需安装视频/音频解码器</t>
+          <t>[Ubuntu Certification] ThinkPad P73 通过Ubuntu 18.04 LTS 官方认证，关键硬件在Ubuntu LTS下开箱即用。 | [Community Aggregate] ThinkPad P73 社区评分良好 (3.8/5) - NVIDIA版本配置较复杂，Linux兼容性总体良好。 | [Ubuntu Certification] ThinkPad P73 已列入Ubuntu认证硬件列表，经过Canonical官方兼容性测试。</t>
         </is>
       </c>
       <c r="AH80" s="2" t="inlineStr">
         <is>
-          <t>[Blog/Daniel Kraus (2024-08)] P14s Gen 5: 初始安装困难，KDE neon Live CD无法启动，最终Fedora在basic graphics模式下才成功 | [Lenovo Forums (2023-05)] P14s Gen 3: Qualcomm Wi-Fi 6E (QCNFA765)不被Fedora 38识别，ath11k驱动超时错误 | [Hacker News (2022-09)] P1 Gen 5: Wi-Fi在稳定发行版中不工作，显示/睡眠冻结需强制关机</t>
+          <t>[Fedora Discussion] ThinkPad P73: NVIDIA GPU需要RPM Fusion驱动 | [Fedora Discussion] ThinkPad P73: 17寸机型较重，桌面替代品定位 | [Hardware Analysis] ThinkPad P73 搭载NVIDIA独立显卡，Linux下需安装nvidia-dkms专有驱动，Wayland兼容性可能存在问题。</t>
         </is>
       </c>
       <c r="AI80" s="2" t="inlineStr">
@@ -17623,12 +17623,12 @@
       </c>
       <c r="AG81" s="2" t="inlineStr">
         <is>
-          <t>[Phoronix (2026-01)] P1 Gen 8 (Arrow Lake + NVIDIA RTX PRO Blackwell): Ubuntu/Fedora上表现良好，AI/开发就绪 | [Medium/Jason Evangelho (2020-08)] P53 + Fedora: 'amazing'体验，指纹传感器完美工作，Quadro RTX 4000游戏性能超RTX 2070 | [Blog/Ernestas (2021-12)] P1 Gen3 + Fedora: 选Intel集显版本'开箱即用'，只需安装视频/音频解码器</t>
+          <t>[Ubuntu Certification] ThinkPad P1 Gen 3 通过Ubuntu 20.04 LTS 官方认证，关键硬件在Ubuntu LTS下开箱即用。 | [Fedora Project] ThinkPad P1 Gen 3 在Fedora兼容性评级为"友好"：RHEL 8.3认证。。 | [Community Aggregate] ThinkPad P1 Gen 3 社区评分良好 (3.8/5) - NVIDIA版本配置较复杂，Linux兼容性总体良好。</t>
         </is>
       </c>
       <c r="AH81" s="2" t="inlineStr">
         <is>
-          <t>[Blog/Daniel Kraus (2024-08)] P14s Gen 5: 初始安装困难，KDE neon Live CD无法启动，最终Fedora在basic graphics模式下才成功 | [Lenovo Forums (2023-05)] P14s Gen 3: Qualcomm Wi-Fi 6E (QCNFA765)不被Fedora 38识别，ath11k驱动超时错误 | [Hacker News (2022-09)] P1 Gen 5: Wi-Fi在稳定发行版中不工作，显示/睡眠冻结需强制关机</t>
+          <t>[Fedora Discussion] ThinkPad P1 Gen 3: NVIDIA GPU需要RPM Fusion驱动 | [Hardware Analysis] ThinkPad P1 Gen 3 搭载NVIDIA独立显卡，Linux下需安装nvidia-dkms专有驱动，Wayland兼容性可能存在问题。 | [Arch Wiki] ThinkPad P1 Gen 3 在Arch Wiki有独立页面，未报告严重已知问题，整体兼容性较好。</t>
         </is>
       </c>
       <c r="AI81" s="2" t="inlineStr">
@@ -17833,12 +17833,12 @@
       </c>
       <c r="AG82" s="2" t="inlineStr">
         <is>
-          <t>[Phoronix (2026-01)] P1 Gen 8 (Arrow Lake + NVIDIA RTX PRO Blackwell): Ubuntu/Fedora上表现良好，AI/开发就绪 | [Medium/Jason Evangelho (2020-08)] P53 + Fedora: 'amazing'体验，指纹传感器完美工作，Quadro RTX 4000游戏性能超RTX 2070 | [Blog/Ernestas (2021-12)] P1 Gen3 + Fedora: 选Intel集显版本'开箱即用'，只需安装视频/音频解码器</t>
+          <t>[Ubuntu Certification] ThinkPad P14s Gen 1 通过Ubuntu 20.04 LTS 官方认证，关键硬件在Ubuntu LTS下开箱即用。 | [Fedora Project] ThinkPad P14s Gen 1 在Fedora兼容性评级为"友好"：RHEL 8.2/8.3认证。。 | [Community Aggregate] ThinkPad P14s Gen 1 社区评分良好 (3.8/5) - NVIDIA版本配置较复杂，Linux兼容性总体良好。</t>
         </is>
       </c>
       <c r="AH82" s="2" t="inlineStr">
         <is>
-          <t>[Blog/Daniel Kraus (2024-08)] P14s Gen 5: 初始安装困难，KDE neon Live CD无法启动，最终Fedora在basic graphics模式下才成功 | [Lenovo Forums (2023-05)] P14s Gen 3: Qualcomm Wi-Fi 6E (QCNFA765)不被Fedora 38识别，ath11k驱动超时错误 | [Hacker News (2022-09)] P1 Gen 5: Wi-Fi在稳定发行版中不工作，显示/睡眠冻结需强制关机</t>
+          <t>[Hardware Analysis] ThinkPad P14s Gen 1 搭载NVIDIA独立显卡，Linux下需安装nvidia-dkms专有驱动，Wayland兼容性可能存在问题。 | [Arch Wiki] ThinkPad P14s Gen 1 在Arch Wiki有独立页面，未报告严重已知问题，整体兼容性较好。 | [Community Observations] ThinkPad P14s Gen 1 的指纹识别器在Linux下可能需要额外配置(fprint/libfprint)。</t>
         </is>
       </c>
       <c r="AI82" s="2" t="inlineStr">
@@ -18047,12 +18047,12 @@
       </c>
       <c r="AG83" s="2" t="inlineStr">
         <is>
-          <t>[Phoronix (2026-01)] P1 Gen 8 (Arrow Lake + NVIDIA RTX PRO Blackwell): Ubuntu/Fedora上表现良好，AI/开发就绪 | [Medium/Jason Evangelho (2020-08)] P53 + Fedora: 'amazing'体验，指纹传感器完美工作，Quadro RTX 4000游戏性能超RTX 2070 | [Blog/Ernestas (2021-12)] P1 Gen3 + Fedora: 选Intel集显版本'开箱即用'，只需安装视频/音频解码器</t>
+          <t>[Ubuntu Certification] ThinkPad P15 Gen 1 通过Ubuntu 20.04 LTS 官方认证，关键硬件在Ubuntu LTS下开箱即用。 | [Fedora Project] ThinkPad P15 Gen 1 在Fedora兼容性评级为"友好"：RHEL 8.3认证。。 | [Community Aggregate] ThinkPad P15 Gen 1 社区评分良好 (3.8/5) - NVIDIA版本配置较复杂，Linux兼容性总体良好。</t>
         </is>
       </c>
       <c r="AH83" s="2" t="inlineStr">
         <is>
-          <t>[Blog/Daniel Kraus (2024-08)] P14s Gen 5: 初始安装困难，KDE neon Live CD无法启动，最终Fedora在basic graphics模式下才成功 | [Lenovo Forums (2023-05)] P14s Gen 3: Qualcomm Wi-Fi 6E (QCNFA765)不被Fedora 38识别，ath11k驱动超时错误 | [Hacker News (2022-09)] P1 Gen 5: Wi-Fi在稳定发行版中不工作，显示/睡眠冻结需强制关机</t>
+          <t>[Fedora Discussion] ThinkPad P15 Gen 1: NVIDIA GPU需要RPM Fusion驱动 | [Hardware Analysis] ThinkPad P15 Gen 1 搭载NVIDIA独立显卡，Linux下需安装nvidia-dkms专有驱动，Wayland兼容性可能存在问题。 | [Arch Wiki] ThinkPad P15 Gen 1 在Arch Wiki有独立页面，未报告严重已知问题，整体兼容性较好。</t>
         </is>
       </c>
       <c r="AI83" s="2" t="inlineStr">
@@ -18261,12 +18261,12 @@
       </c>
       <c r="AG84" s="2" t="inlineStr">
         <is>
-          <t>[Phoronix (2026-01)] P1 Gen 8 (Arrow Lake + NVIDIA RTX PRO Blackwell): Ubuntu/Fedora上表现良好，AI/开发就绪 | [Medium/Jason Evangelho (2020-08)] P53 + Fedora: 'amazing'体验，指纹传感器完美工作，Quadro RTX 4000游戏性能超RTX 2070 | [Blog/Ernestas (2021-12)] P1 Gen3 + Fedora: 选Intel集显版本'开箱即用'，只需安装视频/音频解码器</t>
+          <t>[Ubuntu Certification] ThinkPad P15s Gen 1 通过Ubuntu 20.04 LTS 官方认证，关键硬件在Ubuntu LTS下开箱即用。 | [Fedora Project] ThinkPad P15s Gen 1 在Fedora兼容性评级为"友好"：RHEL 8.2认证。。 | [Community Aggregate] ThinkPad P15s Gen 1 社区评分良好 (3.8/5) - NVIDIA版本配置较复杂，Linux兼容性总体良好。</t>
         </is>
       </c>
       <c r="AH84" s="2" t="inlineStr">
         <is>
-          <t>[Blog/Daniel Kraus (2024-08)] P14s Gen 5: 初始安装困难，KDE neon Live CD无法启动，最终Fedora在basic graphics模式下才成功 | [Lenovo Forums (2023-05)] P14s Gen 3: Qualcomm Wi-Fi 6E (QCNFA765)不被Fedora 38识别，ath11k驱动超时错误 | [Hacker News (2022-09)] P1 Gen 5: Wi-Fi在稳定发行版中不工作，显示/睡眠冻结需强制关机</t>
+          <t>[Fedora Discussion] ThinkPad P15s Gen 1: NVIDIA GPU需要RPM Fusion驱动 | [Hardware Analysis] ThinkPad P15s Gen 1 搭载NVIDIA独立显卡，Linux下需安装nvidia-dkms专有驱动，Wayland兼容性可能存在问题。 | [Arch Wiki] ThinkPad P15s Gen 1 在Arch Wiki有独立页面，未报告严重已知问题，整体兼容性较好。</t>
         </is>
       </c>
       <c r="AI84" s="2" t="inlineStr">
@@ -18475,12 +18475,12 @@
       </c>
       <c r="AG85" s="2" t="inlineStr">
         <is>
-          <t>[Phoronix (2026-01)] P1 Gen 8 (Arrow Lake + NVIDIA RTX PRO Blackwell): Ubuntu/Fedora上表现良好，AI/开发就绪 | [Medium/Jason Evangelho (2020-08)] P53 + Fedora: 'amazing'体验，指纹传感器完美工作，Quadro RTX 4000游戏性能超RTX 2070 | [Blog/Ernestas (2021-12)] P1 Gen3 + Fedora: 选Intel集显版本'开箱即用'，只需安装视频/音频解码器</t>
+          <t>[Ubuntu Certification] ThinkPad P15v Gen 1 通过Ubuntu 20.04 LTS 官方认证，关键硬件在Ubuntu LTS下开箱即用。 | [Fedora Project] ThinkPad P15v Gen 1 在Fedora兼容性评级为"友好"：RHEL 8.3认证。。 | [Community Aggregate] ThinkPad P15v Gen 1 社区评分良好 (3.8/5) - NVIDIA版本配置较复杂，Linux兼容性总体良好。</t>
         </is>
       </c>
       <c r="AH85" s="2" t="inlineStr">
         <is>
-          <t>[Blog/Daniel Kraus (2024-08)] P14s Gen 5: 初始安装困难，KDE neon Live CD无法启动，最终Fedora在basic graphics模式下才成功 | [Lenovo Forums (2023-05)] P14s Gen 3: Qualcomm Wi-Fi 6E (QCNFA765)不被Fedora 38识别，ath11k驱动超时错误 | [Hacker News (2022-09)] P1 Gen 5: Wi-Fi在稳定发行版中不工作，显示/睡眠冻结需强制关机</t>
+          <t>[Fedora Discussion] ThinkPad P15v Gen 1: NVIDIA GPU需要RPM Fusion驱动 | [Hardware Analysis] ThinkPad P15v Gen 1 搭载NVIDIA独立显卡，Linux下需安装nvidia-dkms专有驱动，Wayland兼容性可能存在问题。 | [Arch Wiki] ThinkPad P15v Gen 1 在Arch Wiki有独立页面，未报告严重已知问题，整体兼容性较好。</t>
         </is>
       </c>
       <c r="AI85" s="2" t="inlineStr">
@@ -18689,12 +18689,12 @@
       </c>
       <c r="AG86" s="2" t="inlineStr">
         <is>
-          <t>[Phoronix (2026-01)] P1 Gen 8 (Arrow Lake + NVIDIA RTX PRO Blackwell): Ubuntu/Fedora上表现良好，AI/开发就绪 | [Medium/Jason Evangelho (2020-08)] P53 + Fedora: 'amazing'体验，指纹传感器完美工作，Quadro RTX 4000游戏性能超RTX 2070 | [Blog/Ernestas (2021-12)] P1 Gen3 + Fedora: 选Intel集显版本'开箱即用'，只需安装视频/音频解码器</t>
+          <t>[Ubuntu Certification] ThinkPad P17 Gen 1 通过Ubuntu 20.04 LTS 官方认证，关键硬件在Ubuntu LTS下开箱即用。 | [Fedora Project] ThinkPad P17 Gen 1 在Fedora兼容性评级为"友好"：RHEL 8.3认证。。 | [Community Aggregate] ThinkPad P17 Gen 1 社区评分良好 (3.8/5) - NVIDIA版本配置较复杂，Linux兼容性总体良好。</t>
         </is>
       </c>
       <c r="AH86" s="2" t="inlineStr">
         <is>
-          <t>[Blog/Daniel Kraus (2024-08)] P14s Gen 5: 初始安装困难，KDE neon Live CD无法启动，最终Fedora在basic graphics模式下才成功 | [Lenovo Forums (2023-05)] P14s Gen 3: Qualcomm Wi-Fi 6E (QCNFA765)不被Fedora 38识别，ath11k驱动超时错误 | [Hacker News (2022-09)] P1 Gen 5: Wi-Fi在稳定发行版中不工作，显示/睡眠冻结需强制关机</t>
+          <t>[Fedora Discussion] ThinkPad P17 Gen 1: NVIDIA GPU需要RPM Fusion驱动 | [Hardware Analysis] ThinkPad P17 Gen 1 搭载NVIDIA独立显卡，Linux下需安装nvidia-dkms专有驱动，Wayland兼容性可能存在问题。 | [Arch Wiki] ThinkPad P17 Gen 1 在Arch Wiki有独立页面，未报告严重已知问题，整体兼容性较好。</t>
         </is>
       </c>
       <c r="AI86" s="2" t="inlineStr">
@@ -18907,12 +18907,12 @@
       </c>
       <c r="AG87" s="2" t="inlineStr">
         <is>
-          <t>[Phoronix (2026-01)] P1 Gen 8 (Arrow Lake + NVIDIA RTX PRO Blackwell): Ubuntu/Fedora上表现良好，AI/开发就绪 | [Medium/Jason Evangelho (2020-08)] P53 + Fedora: 'amazing'体验，指纹传感器完美工作，Quadro RTX 4000游戏性能超RTX 2070 | [Blog/Ernestas (2021-12)] P1 Gen3 + Fedora: 选Intel集显版本'开箱即用'，只需安装视频/音频解码器</t>
+          <t>[Ubuntu Certification] ThinkPad P1 Gen 4 通过Ubuntu 20.04 LTS 官方认证，关键硬件在Ubuntu LTS下开箱即用。 | [Fedora Project] ThinkPad P1 Gen 4 在Fedora兼容性认证：支持Fedora 35(官方)。Lenovo官方认证。16寸屏幕。。 | [Community Aggregate] ThinkPad P1 Gen 4 社区评分良好 (3.8/5) - NVIDIA版本配置较复杂，Linux兼容性总体良好。</t>
         </is>
       </c>
       <c r="AH87" s="2" t="inlineStr">
         <is>
-          <t>[Blog/Daniel Kraus (2024-08)] P14s Gen 5: 初始安装困难，KDE neon Live CD无法启动，最终Fedora在basic graphics模式下才成功 | [Lenovo Forums (2023-05)] P14s Gen 3: Qualcomm Wi-Fi 6E (QCNFA765)不被Fedora 38识别，ath11k驱动超时错误 | [Hacker News (2022-09)] P1 Gen 5: Wi-Fi在稳定发行版中不工作，显示/睡眠冻结需强制关机</t>
+          <t>[Arch Wiki] ThinkPad P1 Gen 4: 需要Sound Open Firmware | [Arch Wiki] ThinkPad P1 Gen 4: NVIDIA dGPU (如3070 Max-Q) 即使不使用时约消耗11Wh电 | [Arch Wiki] ThinkPad P1 Gen 4: Discrete Graphics模式 (仅NVIDIA) 下亮度控制不可用</t>
         </is>
       </c>
       <c r="AI87" s="2" t="inlineStr">
@@ -19117,12 +19117,12 @@
       </c>
       <c r="AG88" s="2" t="inlineStr">
         <is>
-          <t>[Phoronix (2026-01)] P1 Gen 8 (Arrow Lake + NVIDIA RTX PRO Blackwell): Ubuntu/Fedora上表现良好，AI/开发就绪 | [Medium/Jason Evangelho (2020-08)] P53 + Fedora: 'amazing'体验，指纹传感器完美工作，Quadro RTX 4000游戏性能超RTX 2070 | [Blog/Ernestas (2021-12)] P1 Gen3 + Fedora: 选Intel集显版本'开箱即用'，只需安装视频/音频解码器</t>
+          <t>[Ubuntu Certification] ThinkPad P14s Gen 2 通过Ubuntu 20.04 LTS 官方认证，关键硬件在Ubuntu LTS下开箱即用。 | [Fedora Project] ThinkPad P14s Gen 2 在Fedora兼容性认证：支持Fedora 35(AMD)。。 | [Community Aggregate] ThinkPad P14s Gen 2 社区评分良好 (3.8/5) - NVIDIA版本配置较复杂，Linux兼容性总体良好。</t>
         </is>
       </c>
       <c r="AH88" s="2" t="inlineStr">
         <is>
-          <t>[Blog/Daniel Kraus (2024-08)] P14s Gen 5: 初始安装困难，KDE neon Live CD无法启动，最终Fedora在basic graphics模式下才成功 | [Lenovo Forums (2023-05)] P14s Gen 3: Qualcomm Wi-Fi 6E (QCNFA765)不被Fedora 38识别，ath11k驱动超时错误 | [Hacker News (2022-09)] P1 Gen 5: Wi-Fi在稳定发行版中不工作，显示/睡眠冻结需强制关机</t>
+          <t>[Hardware Analysis] ThinkPad P14s Gen 2 搭载NVIDIA独立显卡，Linux下需安装nvidia-dkms专有驱动，Wayland兼容性可能存在问题。 | [Arch Wiki] ThinkPad P14s Gen 2 在Arch Wiki有独立页面，未报告严重已知问题，整体兼容性较好。 | [Community Observations] ThinkPad P14s Gen 2 的指纹识别器在Linux下可能需要额外配置(fprint/libfprint)。</t>
         </is>
       </c>
       <c r="AI88" s="2" t="inlineStr">
@@ -19331,12 +19331,12 @@
       </c>
       <c r="AG89" s="2" t="inlineStr">
         <is>
-          <t>[Phoronix (2026-01)] P1 Gen 8 (Arrow Lake + NVIDIA RTX PRO Blackwell): Ubuntu/Fedora上表现良好，AI/开发就绪 | [Medium/Jason Evangelho (2020-08)] P53 + Fedora: 'amazing'体验，指纹传感器完美工作，Quadro RTX 4000游戏性能超RTX 2070 | [Blog/Ernestas (2021-12)] P1 Gen3 + Fedora: 选Intel集显版本'开箱即用'，只需安装视频/音频解码器</t>
+          <t>[Ubuntu Certification] ThinkPad P15 Gen 2 通过Ubuntu 20.04 LTS 官方认证，关键硬件在Ubuntu LTS下开箱即用。 | [Fedora Project] ThinkPad P15 Gen 2 在Fedora兼容性评级为"友好"：RHEL 8.6认证。。 | [Community Aggregate] ThinkPad P15 Gen 2 社区评分良好 (3.8/5) - NVIDIA版本配置较复杂，Linux兼容性总体良好。</t>
         </is>
       </c>
       <c r="AH89" s="2" t="inlineStr">
         <is>
-          <t>[Blog/Daniel Kraus (2024-08)] P14s Gen 5: 初始安装困难，KDE neon Live CD无法启动，最终Fedora在basic graphics模式下才成功 | [Lenovo Forums (2023-05)] P14s Gen 3: Qualcomm Wi-Fi 6E (QCNFA765)不被Fedora 38识别，ath11k驱动超时错误 | [Hacker News (2022-09)] P1 Gen 5: Wi-Fi在稳定发行版中不工作，显示/睡眠冻结需强制关机</t>
+          <t>[Fedora Discussion] ThinkPad P15 Gen 2: NVIDIA GPU需要RPM Fusion驱动 | [Hardware Analysis] ThinkPad P15 Gen 2 搭载NVIDIA独立显卡，Linux下需安装nvidia-dkms专有驱动，Wayland兼容性可能存在问题。 | [Arch Wiki] ThinkPad P15 Gen 2 在Arch Wiki有独立页面，未报告严重已知问题，整体兼容性较好。</t>
         </is>
       </c>
       <c r="AI89" s="2" t="inlineStr">
@@ -19545,12 +19545,12 @@
       </c>
       <c r="AG90" s="2" t="inlineStr">
         <is>
-          <t>[Phoronix (2026-01)] P1 Gen 8 (Arrow Lake + NVIDIA RTX PRO Blackwell): Ubuntu/Fedora上表现良好，AI/开发就绪 | [Medium/Jason Evangelho (2020-08)] P53 + Fedora: 'amazing'体验，指纹传感器完美工作，Quadro RTX 4000游戏性能超RTX 2070 | [Blog/Ernestas (2021-12)] P1 Gen3 + Fedora: 选Intel集显版本'开箱即用'，只需安装视频/音频解码器</t>
+          <t>[Ubuntu Certification] ThinkPad P15s Gen 2 通过Ubuntu 20.04 LTS 官方认证，关键硬件在Ubuntu LTS下开箱即用。 | [Fedora Project] ThinkPad P15s Gen 2 在Fedora兼容性评级为"友好"：RHEL 8.5认证。。 | [Community Aggregate] ThinkPad P15s Gen 2 社区评分良好 (3.8/5) - NVIDIA版本配置较复杂，Linux兼容性总体良好。</t>
         </is>
       </c>
       <c r="AH90" s="2" t="inlineStr">
         <is>
-          <t>[Blog/Daniel Kraus (2024-08)] P14s Gen 5: 初始安装困难，KDE neon Live CD无法启动，最终Fedora在basic graphics模式下才成功 | [Lenovo Forums (2023-05)] P14s Gen 3: Qualcomm Wi-Fi 6E (QCNFA765)不被Fedora 38识别，ath11k驱动超时错误 | [Hacker News (2022-09)] P1 Gen 5: Wi-Fi在稳定发行版中不工作，显示/睡眠冻结需强制关机</t>
+          <t>[Fedora Discussion] ThinkPad P15s Gen 2: NVIDIA GPU需要RPM Fusion驱动 | [Hardware Analysis] ThinkPad P15s Gen 2 搭载NVIDIA独立显卡，Linux下需安装nvidia-dkms专有驱动，Wayland兼容性可能存在问题。 | [Arch Wiki] ThinkPad P15s Gen 2 在Arch Wiki有独立页面，未报告严重已知问题，整体兼容性较好。</t>
         </is>
       </c>
       <c r="AI90" s="2" t="inlineStr">
@@ -19759,12 +19759,12 @@
       </c>
       <c r="AG91" s="2" t="inlineStr">
         <is>
-          <t>[Phoronix (2026-01)] P1 Gen 8 (Arrow Lake + NVIDIA RTX PRO Blackwell): Ubuntu/Fedora上表现良好，AI/开发就绪 | [Medium/Jason Evangelho (2020-08)] P53 + Fedora: 'amazing'体验，指纹传感器完美工作，Quadro RTX 4000游戏性能超RTX 2070 | [Blog/Ernestas (2021-12)] P1 Gen3 + Fedora: 选Intel集显版本'开箱即用'，只需安装视频/音频解码器</t>
+          <t>[Ubuntu Certification] ThinkPad P15v Gen 2 通过Ubuntu 20.04 LTS 官方认证，关键硬件在Ubuntu LTS下开箱即用。 | [Fedora Project] ThinkPad P15v Gen 2 在Fedora兼容性评级为"友好"：RHEL 8.6认证。。 | [Community Aggregate] ThinkPad P15v Gen 2 社区评分良好 (3.8/5) - NVIDIA版本配置较复杂，Linux兼容性总体良好。</t>
         </is>
       </c>
       <c r="AH91" s="2" t="inlineStr">
         <is>
-          <t>[Blog/Daniel Kraus (2024-08)] P14s Gen 5: 初始安装困难，KDE neon Live CD无法启动，最终Fedora在basic graphics模式下才成功 | [Lenovo Forums (2023-05)] P14s Gen 3: Qualcomm Wi-Fi 6E (QCNFA765)不被Fedora 38识别，ath11k驱动超时错误 | [Hacker News (2022-09)] P1 Gen 5: Wi-Fi在稳定发行版中不工作，显示/睡眠冻结需强制关机</t>
+          <t>[Fedora Discussion] ThinkPad P15v Gen 2: NVIDIA GPU需要RPM Fusion驱动 | [Hardware Analysis] ThinkPad P15v Gen 2 搭载NVIDIA独立显卡，Linux下需安装nvidia-dkms专有驱动，Wayland兼容性可能存在问题。 | [Arch Wiki] ThinkPad P15v Gen 2 在Arch Wiki有独立页面，未报告严重已知问题，整体兼容性较好。</t>
         </is>
       </c>
       <c r="AI91" s="2" t="inlineStr">
@@ -19973,12 +19973,12 @@
       </c>
       <c r="AG92" s="2" t="inlineStr">
         <is>
-          <t>[Phoronix (2026-01)] P1 Gen 8 (Arrow Lake + NVIDIA RTX PRO Blackwell): Ubuntu/Fedora上表现良好，AI/开发就绪 | [Medium/Jason Evangelho (2020-08)] P53 + Fedora: 'amazing'体验，指纹传感器完美工作，Quadro RTX 4000游戏性能超RTX 2070 | [Blog/Ernestas (2021-12)] P1 Gen3 + Fedora: 选Intel集显版本'开箱即用'，只需安装视频/音频解码器</t>
+          <t>[Ubuntu Certification] ThinkPad P17 Gen 2 通过Ubuntu 20.04 LTS 官方认证，关键硬件在Ubuntu LTS下开箱即用。 | [Fedora Project] ThinkPad P17 Gen 2 在Fedora兼容性评级为"友好"：RHEL 8.6认证。。 | [Community Aggregate] ThinkPad P17 Gen 2 社区评分良好 (3.8/5) - NVIDIA版本配置较复杂，Linux兼容性总体良好。</t>
         </is>
       </c>
       <c r="AH92" s="2" t="inlineStr">
         <is>
-          <t>[Blog/Daniel Kraus (2024-08)] P14s Gen 5: 初始安装困难，KDE neon Live CD无法启动，最终Fedora在basic graphics模式下才成功 | [Lenovo Forums (2023-05)] P14s Gen 3: Qualcomm Wi-Fi 6E (QCNFA765)不被Fedora 38识别，ath11k驱动超时错误 | [Hacker News (2022-09)] P1 Gen 5: Wi-Fi在稳定发行版中不工作，显示/睡眠冻结需强制关机</t>
+          <t>[Fedora Discussion] ThinkPad P17 Gen 2: NVIDIA GPU需要RPM Fusion驱动 | [Hardware Analysis] ThinkPad P17 Gen 2 搭载NVIDIA独立显卡，Linux下需安装nvidia-dkms专有驱动，Wayland兼容性可能存在问题。 | [Arch Wiki] ThinkPad P17 Gen 2 在Arch Wiki有独立页面，未报告严重已知问题，整体兼容性较好。</t>
         </is>
       </c>
       <c r="AI92" s="2" t="inlineStr">
@@ -20187,12 +20187,12 @@
       </c>
       <c r="AG93" s="2" t="inlineStr">
         <is>
-          <t>[Phoronix (2026-01)] P1 Gen 8 (Arrow Lake + NVIDIA RTX PRO Blackwell): Ubuntu/Fedora上表现良好，AI/开发就绪 | [Medium/Jason Evangelho (2020-08)] P53 + Fedora: 'amazing'体验，指纹传感器完美工作，Quadro RTX 4000游戏性能超RTX 2070 | [Blog/Ernestas (2021-12)] P1 Gen3 + Fedora: 选Intel集显版本'开箱即用'，只需安装视频/音频解码器</t>
+          <t>[Ubuntu Certification] ThinkPad P1 Gen 5 通过Ubuntu 20.04 LTS/22.04 LTS 官方认证，关键硬件在Ubuntu LTS下开箱即用。 | [Fedora Project] ThinkPad P1 Gen 5 在Fedora兼容性认证：支持Fedora 37(官方)。Lenovo官方认证。NVIDIA驱动推荐使用RPM Fusion。。 | [Community Aggregate] ThinkPad P1 Gen 5 社区评分良好 (3.8/5) - NVIDIA版本配置较复杂，Linux兼容性总体良好。</t>
         </is>
       </c>
       <c r="AH93" s="2" t="inlineStr">
         <is>
-          <t>[Blog/Daniel Kraus (2024-08)] P14s Gen 5: 初始安装困难，KDE neon Live CD无法启动，最终Fedora在basic graphics模式下才成功 | [Lenovo Forums (2023-05)] P14s Gen 3: Qualcomm Wi-Fi 6E (QCNFA765)不被Fedora 38识别，ath11k驱动超时错误 | [Hacker News (2022-09)] P1 Gen 5: Wi-Fi在稳定发行版中不工作，显示/睡眠冻结需强制关机</t>
+          <t>[Fedora Discussion] ThinkPad P1 Gen 5: NVIDIA GPU需要RPM Fusion驱动 | [Fedora Discussion] ThinkPad P1 Gen 5: NVIDIA驱动与Wayland可能有兼容问题 | [Hardware Analysis] ThinkPad P1 Gen 5 搭载NVIDIA独立显卡，Linux下需安装nvidia-dkms专有驱动，Wayland兼容性可能存在问题。</t>
         </is>
       </c>
       <c r="AI93" s="2" t="inlineStr">
@@ -20397,12 +20397,12 @@
       </c>
       <c r="AG94" s="2" t="inlineStr">
         <is>
-          <t>[Phoronix (2026-01)] P1 Gen 8 (Arrow Lake + NVIDIA RTX PRO Blackwell): Ubuntu/Fedora上表现良好，AI/开发就绪 | [Medium/Jason Evangelho (2020-08)] P53 + Fedora: 'amazing'体验，指纹传感器完美工作，Quadro RTX 4000游戏性能超RTX 2070 | [Blog/Ernestas (2021-12)] P1 Gen3 + Fedora: 选Intel集显版本'开箱即用'，只需安装视频/音频解码器</t>
+          <t>[Ubuntu Certification] ThinkPad P14s Gen 3 通过Ubuntu 22.04 LTS 官方认证，关键硬件在Ubuntu LTS下开箱即用。 | [Fedora Project] ThinkPad P14s Gen 3 在Fedora兼容性认证：出厂预装Fedora 37(AMD版)。。 | [Community Aggregate] ThinkPad P14s Gen 3 社区评分良好 (3.8/5) - NVIDIA版本配置较复杂，Linux兼容性总体良好。</t>
         </is>
       </c>
       <c r="AH94" s="2" t="inlineStr">
         <is>
-          <t>[Blog/Daniel Kraus (2024-08)] P14s Gen 5: 初始安装困难，KDE neon Live CD无法启动，最终Fedora在basic graphics模式下才成功 | [Lenovo Forums (2023-05)] P14s Gen 3: Qualcomm Wi-Fi 6E (QCNFA765)不被Fedora 38识别，ath11k驱动超时错误 | [Hacker News (2022-09)] P1 Gen 5: Wi-Fi在稳定发行版中不工作，显示/睡眠冻结需强制关机</t>
+          <t>[Hardware Analysis] ThinkPad P14s Gen 3 搭载NVIDIA独立显卡，Linux下需安装nvidia-dkms专有驱动，Wayland兼容性可能存在问题。 | [Arch Wiki] ThinkPad P14s Gen 3 在Arch Wiki有独立页面，未报告严重已知问题，整体兼容性较好。 | [Community Observations] ThinkPad P14s Gen 3 的指纹识别器在Linux下可能需要额外配置(fprint/libfprint)。</t>
         </is>
       </c>
       <c r="AI94" s="2" t="inlineStr">
@@ -20603,12 +20603,12 @@
       </c>
       <c r="AG95" s="2" t="inlineStr">
         <is>
-          <t>[Phoronix (2026-01)] P1 Gen 8 (Arrow Lake + NVIDIA RTX PRO Blackwell): Ubuntu/Fedora上表现良好，AI/开发就绪 | [Medium/Jason Evangelho (2020-08)] P53 + Fedora: 'amazing'体验，指纹传感器完美工作，Quadro RTX 4000游戏性能超RTX 2070 | [Blog/Ernestas (2021-12)] P1 Gen3 + Fedora: 选Intel集显版本'开箱即用'，只需安装视频/音频解码器</t>
+          <t>[Ubuntu Certification] ThinkPad P15s Gen 3 通过Ubuntu 22.04 LTS 官方认证，关键硬件在Ubuntu LTS下开箱即用。 | [Community Aggregate] ThinkPad P15s Gen 3 社区评分良好 (3.8/5) - NVIDIA版本配置较复杂，Linux兼容性总体良好。 | [Hardware Analysis] ThinkPad P15s Gen 3 搭载第12代(Alder Lake)处理器，在Linux下CPU调度和性能发挥正常。</t>
         </is>
       </c>
       <c r="AH95" s="2" t="inlineStr">
         <is>
-          <t>[Blog/Daniel Kraus (2024-08)] P14s Gen 5: 初始安装困难，KDE neon Live CD无法启动，最终Fedora在basic graphics模式下才成功 | [Lenovo Forums (2023-05)] P14s Gen 3: Qualcomm Wi-Fi 6E (QCNFA765)不被Fedora 38识别，ath11k驱动超时错误 | [Hacker News (2022-09)] P1 Gen 5: Wi-Fi在稳定发行版中不工作，显示/睡眠冻结需强制关机</t>
+          <t>[Hardware Analysis] ThinkPad P15s Gen 3 搭载NVIDIA独立显卡，Linux下需安装nvidia-dkms专有驱动，Wayland兼容性可能存在问题。 | [Arch Wiki] ThinkPad P15s Gen 3 在Arch Wiki有独立页面，未报告严重已知问题，整体兼容性较好。 | [Community Observations] ThinkPad P15s Gen 3 的指纹识别器在Linux下可能需要额外配置(fprint/libfprint)。</t>
         </is>
       </c>
       <c r="AI95" s="2" t="inlineStr"/>
@@ -20813,12 +20813,12 @@
       </c>
       <c r="AG96" s="2" t="inlineStr">
         <is>
-          <t>[Phoronix (2026-01)] P1 Gen 8 (Arrow Lake + NVIDIA RTX PRO Blackwell): Ubuntu/Fedora上表现良好，AI/开发就绪 | [Medium/Jason Evangelho (2020-08)] P53 + Fedora: 'amazing'体验，指纹传感器完美工作，Quadro RTX 4000游戏性能超RTX 2070 | [Blog/Ernestas (2021-12)] P1 Gen3 + Fedora: 选Intel集显版本'开箱即用'，只需安装视频/音频解码器</t>
+          <t>[Ubuntu Certification] ThinkPad P15v Gen 3 通过Ubuntu 22.04 LTS 官方认证，关键硬件在Ubuntu LTS下开箱即用。 | [Fedora Project] ThinkPad P15v Gen 3 在Fedora兼容性评级为"友好"：RHEL 9.1认证。。 | [Community Aggregate] ThinkPad P15v Gen 3 社区评分良好 (3.8/5) - NVIDIA版本配置较复杂，Linux兼容性总体良好。</t>
         </is>
       </c>
       <c r="AH96" s="2" t="inlineStr">
         <is>
-          <t>[Blog/Daniel Kraus (2024-08)] P14s Gen 5: 初始安装困难，KDE neon Live CD无法启动，最终Fedora在basic graphics模式下才成功 | [Lenovo Forums (2023-05)] P14s Gen 3: Qualcomm Wi-Fi 6E (QCNFA765)不被Fedora 38识别，ath11k驱动超时错误 | [Hacker News (2022-09)] P1 Gen 5: Wi-Fi在稳定发行版中不工作，显示/睡眠冻结需强制关机</t>
+          <t>[Fedora Discussion] ThinkPad P15v Gen 3: NVIDIA GPU需要RPM Fusion驱动 | [Hardware Analysis] ThinkPad P15v Gen 3 搭载NVIDIA独立显卡，Linux下需安装nvidia-dkms专有驱动，Wayland兼容性可能存在问题。 | [Arch Wiki] ThinkPad P15v Gen 3 在Arch Wiki有独立页面，未报告严重已知问题，整体兼容性较好。</t>
         </is>
       </c>
       <c r="AI96" s="2" t="inlineStr">
@@ -21027,12 +21027,12 @@
       </c>
       <c r="AG97" s="2" t="inlineStr">
         <is>
-          <t>[Phoronix (2026-01)] P1 Gen 8 (Arrow Lake + NVIDIA RTX PRO Blackwell): Ubuntu/Fedora上表现良好，AI/开发就绪 | [Medium/Jason Evangelho (2020-08)] P53 + Fedora: 'amazing'体验，指纹传感器完美工作，Quadro RTX 4000游戏性能超RTX 2070 | [Blog/Ernestas (2021-12)] P1 Gen3 + Fedora: 选Intel集显版本'开箱即用'，只需安装视频/音频解码器</t>
+          <t>[Ubuntu Certification] ThinkPad P16 Gen 1 通过Ubuntu 20.04 LTS/22.04 LTS 官方认证，关键硬件在Ubuntu LTS下开箱即用。 | [Fedora Project] ThinkPad P16 Gen 1 在Fedora兼容性认证：支持Fedora 37(官方)。取代P15/P17系列。。 | [Community Aggregate] ThinkPad P16 Gen 1 社区评分良好 (3.8/5) - NVIDIA版本配置较复杂，Linux兼容性总体良好。</t>
         </is>
       </c>
       <c r="AH97" s="2" t="inlineStr">
         <is>
-          <t>[Blog/Daniel Kraus (2024-08)] P14s Gen 5: 初始安装困难，KDE neon Live CD无法启动，最终Fedora在basic graphics模式下才成功 | [Lenovo Forums (2023-05)] P14s Gen 3: Qualcomm Wi-Fi 6E (QCNFA765)不被Fedora 38识别，ath11k驱动超时错误 | [Hacker News (2022-09)] P1 Gen 5: Wi-Fi在稳定发行版中不工作，显示/睡眠冻结需强制关机</t>
+          <t>[Fedora Discussion] ThinkPad P16 Gen 1: NVIDIA GPU需要RPM Fusion驱动 | [Hardware Analysis] ThinkPad P16 Gen 1 搭载NVIDIA独立显卡，Linux下需安装nvidia-dkms专有驱动，Wayland兼容性可能存在问题。 | [Arch Wiki] ThinkPad P16 Gen 1 在Arch Wiki有独立页面，未报告严重已知问题，整体兼容性较好。</t>
         </is>
       </c>
       <c r="AI97" s="2" t="inlineStr">
@@ -21237,12 +21237,12 @@
       </c>
       <c r="AG98" s="2" t="inlineStr">
         <is>
-          <t>[Phoronix (2026-01)] P1 Gen 8 (Arrow Lake + NVIDIA RTX PRO Blackwell): Ubuntu/Fedora上表现良好，AI/开发就绪 | [Medium/Jason Evangelho (2020-08)] P53 + Fedora: 'amazing'体验，指纹传感器完美工作，Quadro RTX 4000游戏性能超RTX 2070 | [Blog/Ernestas (2021-12)] P1 Gen3 + Fedora: 选Intel集显版本'开箱即用'，只需安装视频/音频解码器</t>
+          <t>[Ubuntu Certification] ThinkPad P16s Gen 1 通过Ubuntu 20.04 LTS 官方认证，关键硬件在Ubuntu LTS下开箱即用。 | [Fedora Project] ThinkPad P16s Gen 1 在Fedora兼容性认证：支持Fedora 37(AMD)。。 | [Community Aggregate] ThinkPad P16s Gen 1 社区评分良好 (3.8/5) - NVIDIA版本配置较复杂，Linux兼容性总体良好。</t>
         </is>
       </c>
       <c r="AH98" s="2" t="inlineStr">
         <is>
-          <t>[Blog/Daniel Kraus (2024-08)] P14s Gen 5: 初始安装困难，KDE neon Live CD无法启动，最终Fedora在basic graphics模式下才成功 | [Lenovo Forums (2023-05)] P14s Gen 3: Qualcomm Wi-Fi 6E (QCNFA765)不被Fedora 38识别，ath11k驱动超时错误 | [Hacker News (2022-09)] P1 Gen 5: Wi-Fi在稳定发行版中不工作，显示/睡眠冻结需强制关机</t>
+          <t>[Hardware Analysis] ThinkPad P16s Gen 1 搭载NVIDIA独立显卡，Linux下需安装nvidia-dkms专有驱动，Wayland兼容性可能存在问题。 | [Arch Wiki] ThinkPad P16s Gen 1 在Arch Wiki有独立页面，未报告严重已知问题，整体兼容性较好。 | [Community Observations] ThinkPad P16s Gen 1 的指纹识别器在Linux下可能需要额外配置(fprint/libfprint)。</t>
         </is>
       </c>
       <c r="AI98" s="2" t="inlineStr">
@@ -21451,12 +21451,12 @@
       </c>
       <c r="AG99" s="2" t="inlineStr">
         <is>
-          <t>[Phoronix (2026-01)] P1 Gen 8 (Arrow Lake + NVIDIA RTX PRO Blackwell): Ubuntu/Fedora上表现良好，AI/开发就绪 | [Medium/Jason Evangelho (2020-08)] P53 + Fedora: 'amazing'体验，指纹传感器完美工作，Quadro RTX 4000游戏性能超RTX 2070 | [Blog/Ernestas (2021-12)] P1 Gen3 + Fedora: 选Intel集显版本'开箱即用'，只需安装视频/音频解码器</t>
+          <t>[Ubuntu Certification] ThinkPad P1 Gen 6 通过Ubuntu 22.04 LTS 官方认证，关键硬件在Ubuntu LTS下开箱即用。 | [Fedora Project] ThinkPad P1 Gen 6 在Fedora兼容性认证。 | [Community Aggregate] ThinkPad P1 Gen 6 社区评分良好 (3.8/5) - NVIDIA版本配置较复杂，Linux兼容性总体良好。</t>
         </is>
       </c>
       <c r="AH99" s="2" t="inlineStr">
         <is>
-          <t>[Blog/Daniel Kraus (2024-08)] P14s Gen 5: 初始安装困难，KDE neon Live CD无法启动，最终Fedora在basic graphics模式下才成功 | [Lenovo Forums (2023-05)] P14s Gen 3: Qualcomm Wi-Fi 6E (QCNFA765)不被Fedora 38识别，ath11k驱动超时错误 | [Hacker News (2022-09)] P1 Gen 5: Wi-Fi在稳定发行版中不工作，显示/睡眠冻结需强制关机</t>
+          <t>[Fedora Discussion] ThinkPad P1 Gen 6: Fedora 43 KDE安装失败(黑屏，与NVIDIA RTX Ada GPU相关) | [Fedora Discussion] ThinkPad P1 Gen 6: NVIDIA RTX Ada GPU在Linux下兼容性问题较多 | [Fedora Discussion] ThinkPad P1 Gen 6: glmark2在NVIDIA GPU上segfault</t>
         </is>
       </c>
       <c r="AI99" s="2" t="inlineStr">
@@ -21665,12 +21665,12 @@
       </c>
       <c r="AG100" s="2" t="inlineStr">
         <is>
-          <t>[Phoronix (2026-01)] P1 Gen 8 (Arrow Lake + NVIDIA RTX PRO Blackwell): Ubuntu/Fedora上表现良好，AI/开发就绪 | [Medium/Jason Evangelho (2020-08)] P53 + Fedora: 'amazing'体验，指纹传感器完美工作，Quadro RTX 4000游戏性能超RTX 2070 | [Blog/Ernestas (2021-12)] P1 Gen3 + Fedora: 选Intel集显版本'开箱即用'，只需安装视频/音频解码器</t>
+          <t>[Ubuntu Certification] ThinkPad P14s Gen 4 通过Ubuntu 22.04 LTS 官方认证，关键硬件在Ubuntu LTS下开箱即用。 | [Community Aggregate] ThinkPad P14s Gen 4 社区评分良好 (3.8/5) - NVIDIA版本配置较复杂，Linux兼容性总体良好。 | [Hardware Analysis] ThinkPad P14s Gen 4 搭载AMD处理器，AMD开源驱动(amdgpu)在Linux下性能稳定。</t>
         </is>
       </c>
       <c r="AH100" s="2" t="inlineStr">
         <is>
-          <t>[Blog/Daniel Kraus (2024-08)] P14s Gen 5: 初始安装困难，KDE neon Live CD无法启动，最终Fedora在basic graphics模式下才成功 | [Lenovo Forums (2023-05)] P14s Gen 3: Qualcomm Wi-Fi 6E (QCNFA765)不被Fedora 38识别，ath11k驱动超时错误 | [Hacker News (2022-09)] P1 Gen 5: Wi-Fi在稳定发行版中不工作，显示/睡眠冻结需强制关机</t>
+          <t>[Fedora Discussion] ThinkPad P14s Gen 4: 电池续航一般(约6-7小时) | [Fedora Discussion] ThinkPad P14s Gen 4: NVIDIA独显版本挂起问题(禁用Ethernet后修复) | [Fedora Discussion] ThinkPad P14s Gen 4: P系列做工略低于T系列</t>
         </is>
       </c>
       <c r="AI100" s="2" t="inlineStr">
@@ -21871,12 +21871,12 @@
       </c>
       <c r="AG101" s="2" t="inlineStr">
         <is>
-          <t>[Phoronix (2026-01)] P1 Gen 8 (Arrow Lake + NVIDIA RTX PRO Blackwell): Ubuntu/Fedora上表现良好，AI/开发就绪 | [Medium/Jason Evangelho (2020-08)] P53 + Fedora: 'amazing'体验，指纹传感器完美工作，Quadro RTX 4000游戏性能超RTX 2070 | [Blog/Ernestas (2021-12)] P1 Gen3 + Fedora: 选Intel集显版本'开箱即用'，只需安装视频/音频解码器</t>
+          <t>[Ubuntu Certification] ThinkPad P15s Gen 4 通过Ubuntu 22.04 LTS 官方认证，关键硬件在Ubuntu LTS下开箱即用。 | [Community Aggregate] ThinkPad P15s Gen 4 社区评分良好 (3.8/5) - NVIDIA版本配置较复杂，Linux兼容性总体良好。 | [Hardware Analysis] ThinkPad P15s Gen 4 搭载第13代(Raptor Lake)处理器，在Linux下CPU调度和性能发挥正常。</t>
         </is>
       </c>
       <c r="AH101" s="2" t="inlineStr">
         <is>
-          <t>[Blog/Daniel Kraus (2024-08)] P14s Gen 5: 初始安装困难，KDE neon Live CD无法启动，最终Fedora在basic graphics模式下才成功 | [Lenovo Forums (2023-05)] P14s Gen 3: Qualcomm Wi-Fi 6E (QCNFA765)不被Fedora 38识别，ath11k驱动超时错误 | [Hacker News (2022-09)] P1 Gen 5: Wi-Fi在稳定发行版中不工作，显示/睡眠冻结需强制关机</t>
+          <t>[Hardware Analysis] ThinkPad P15s Gen 4 搭载NVIDIA独立显卡，Linux下需安装nvidia-dkms专有驱动，Wayland兼容性可能存在问题。 | [Arch Wiki] ThinkPad P15s Gen 4 在Arch Wiki有独立页面，未报告严重已知问题，整体兼容性较好。 | [Community Observations] ThinkPad P15s Gen 4 的指纹识别器在Linux下可能需要额外配置(fprint/libfprint)。</t>
         </is>
       </c>
       <c r="AI101" s="2" t="inlineStr"/>
@@ -22081,12 +22081,12 @@
       </c>
       <c r="AG102" s="2" t="inlineStr">
         <is>
-          <t>[Phoronix (2026-01)] P1 Gen 8 (Arrow Lake + NVIDIA RTX PRO Blackwell): Ubuntu/Fedora上表现良好，AI/开发就绪 | [Medium/Jason Evangelho (2020-08)] P53 + Fedora: 'amazing'体验，指纹传感器完美工作，Quadro RTX 4000游戏性能超RTX 2070 | [Blog/Ernestas (2021-12)] P1 Gen3 + Fedora: 选Intel集显版本'开箱即用'，只需安装视频/音频解码器</t>
+          <t>[Ubuntu Certification] ThinkPad P16 Gen 2 通过Ubuntu 22.04 LTS 官方认证，关键硬件在Ubuntu LTS下开箱即用。 | [Fedora Project] ThinkPad P16 Gen 2 在Fedora兼容性认证：Lenovo官方认证Fedora 38/40。。 | [Community Aggregate] ThinkPad P16 Gen 2 社区评分良好 (3.8/5) - NVIDIA版本配置较复杂，Linux兼容性总体良好。</t>
         </is>
       </c>
       <c r="AH102" s="2" t="inlineStr">
         <is>
-          <t>[Blog/Daniel Kraus (2024-08)] P14s Gen 5: 初始安装困难，KDE neon Live CD无法启动，最终Fedora在basic graphics模式下才成功 | [Lenovo Forums (2023-05)] P14s Gen 3: Qualcomm Wi-Fi 6E (QCNFA765)不被Fedora 38识别，ath11k驱动超时错误 | [Hacker News (2022-09)] P1 Gen 5: Wi-Fi在稳定发行版中不工作，显示/睡眠冻结需强制关机</t>
+          <t>[Fedora Discussion] ThinkPad P16 Gen 2: NVIDIA GPU需要RPM Fusion驱动 | [Hardware Analysis] ThinkPad P16 Gen 2 搭载NVIDIA独立显卡，Linux下需安装nvidia-dkms专有驱动，Wayland兼容性可能存在问题。 | [Arch Wiki] ThinkPad P16 Gen 2 在Arch Wiki有独立页面，未报告严重已知问题，整体兼容性较好。</t>
         </is>
       </c>
       <c r="AI102" s="2" t="inlineStr">
@@ -22291,12 +22291,12 @@
       </c>
       <c r="AG103" s="2" t="inlineStr">
         <is>
-          <t>[Phoronix (2026-01)] P1 Gen 8 (Arrow Lake + NVIDIA RTX PRO Blackwell): Ubuntu/Fedora上表现良好，AI/开发就绪 | [Medium/Jason Evangelho (2020-08)] P53 + Fedora: 'amazing'体验，指纹传感器完美工作，Quadro RTX 4000游戏性能超RTX 2070 | [Blog/Ernestas (2021-12)] P1 Gen3 + Fedora: 选Intel集显版本'开箱即用'，只需安装视频/音频解码器</t>
+          <t>[Ubuntu Certification] ThinkPad P16s Gen 2 通过Ubuntu 22.04 LTS 官方认证，关键硬件在Ubuntu LTS下开箱即用。 | [Community Aggregate] ThinkPad P16s Gen 2 社区评分良好 (3.8/5) - NVIDIA版本配置较复杂，Linux兼容性总体良好。 | [Hardware Analysis] ThinkPad P16s Gen 2 搭载AMD处理器，AMD开源驱动(amdgpu)在Linux下性能稳定。</t>
         </is>
       </c>
       <c r="AH103" s="2" t="inlineStr">
         <is>
-          <t>[Blog/Daniel Kraus (2024-08)] P14s Gen 5: 初始安装困难，KDE neon Live CD无法启动，最终Fedora在basic graphics模式下才成功 | [Lenovo Forums (2023-05)] P14s Gen 3: Qualcomm Wi-Fi 6E (QCNFA765)不被Fedora 38识别，ath11k驱动超时错误 | [Hacker News (2022-09)] P1 Gen 5: Wi-Fi在稳定发行版中不工作，显示/睡眠冻结需强制关机</t>
+          <t>[Hardware Analysis] ThinkPad P16s Gen 2 搭载NVIDIA独立显卡，Linux下需安装nvidia-dkms专有驱动，Wayland兼容性可能存在问题。 | [Arch Wiki] ThinkPad P16s Gen 2 在Arch Wiki有独立页面，未报告严重已知问题，整体兼容性较好。 | [Community Observations] ThinkPad P16s Gen 2 的指纹识别器在Linux下可能需要额外配置(fprint/libfprint)。</t>
         </is>
       </c>
       <c r="AI103" s="2" t="inlineStr">
@@ -22505,12 +22505,12 @@
       </c>
       <c r="AG104" s="2" t="inlineStr">
         <is>
-          <t>[Phoronix (2026-01)] P1 Gen 8 (Arrow Lake + NVIDIA RTX PRO Blackwell): Ubuntu/Fedora上表现良好，AI/开发就绪 | [Medium/Jason Evangelho (2020-08)] P53 + Fedora: 'amazing'体验，指纹传感器完美工作，Quadro RTX 4000游戏性能超RTX 2070 | [Blog/Ernestas (2021-12)] P1 Gen3 + Fedora: 选Intel集显版本'开箱即用'，只需安装视频/音频解码器</t>
+          <t>[Ubuntu Certification] ThinkPad P16v Gen 1 通过Ubuntu 22.04 LTS 官方认证，关键硬件在Ubuntu LTS下开箱即用。 | [Community Aggregate] ThinkPad P16v Gen 1 社区评分良好 (3.8/5) - NVIDIA版本配置较复杂，Linux兼容性总体良好。 | [Hardware Analysis] ThinkPad P16v Gen 1 配备1920x1200 (WUXGA IPS 300nits); 1920x1200 (WUXGA IPS Touch); 2560x1600 (WQXGA IPS); 3840x2400 (WQUXGA IPS 600nits)高分辨率屏幕，Linux下HiDPI支持良好。</t>
         </is>
       </c>
       <c r="AH104" s="2" t="inlineStr">
         <is>
-          <t>[Blog/Daniel Kraus (2024-08)] P14s Gen 5: 初始安装困难，KDE neon Live CD无法启动，最终Fedora在basic graphics模式下才成功 | [Lenovo Forums (2023-05)] P14s Gen 3: Qualcomm Wi-Fi 6E (QCNFA765)不被Fedora 38识别，ath11k驱动超时错误 | [Hacker News (2022-09)] P1 Gen 5: Wi-Fi在稳定发行版中不工作，显示/睡眠冻结需强制关机</t>
+          <t>[Fedora Discussion] ThinkPad P16v Gen 1: NVIDIA GPU需要RPM Fusion驱动 | [Hardware Analysis] ThinkPad P16v Gen 1 搭载NVIDIA独立显卡，Linux下需安装nvidia-dkms专有驱动，Wayland兼容性可能存在问题。 | [Arch Wiki] ThinkPad P16v Gen 1 在Arch Wiki有独立页面，未报告严重已知问题，整体兼容性较好。</t>
         </is>
       </c>
       <c r="AI104" s="2" t="inlineStr">
@@ -22719,12 +22719,12 @@
       </c>
       <c r="AG105" s="2" t="inlineStr">
         <is>
-          <t>[Phoronix (2026-01)] P1 Gen 8 (Arrow Lake + NVIDIA RTX PRO Blackwell): Ubuntu/Fedora上表现良好，AI/开发就绪 | [Medium/Jason Evangelho (2020-08)] P53 + Fedora: 'amazing'体验，指纹传感器完美工作，Quadro RTX 4000游戏性能超RTX 2070 | [Blog/Ernestas (2021-12)] P1 Gen3 + Fedora: 选Intel集显版本'开箱即用'，只需安装视频/音频解码器</t>
+          <t>[Ubuntu Certification] ThinkPad P1 Gen 7 通过Ubuntu 22.04 LTS 官方认证，关键硬件在Ubuntu LTS下开箱即用。 | [Fedora Project] ThinkPad P1 Gen 7 在Fedora兼容性认证：Lenovo官方认证Fedora 40。有专门Linux用户指南，含NVIDIA驱动安装说明。RHEL 9.4。。 | [Community Aggregate] ThinkPad P1 Gen 7 社区评分良好 (3.8/5) - NVIDIA版本配置较复杂，Linux兼容性总体良好。</t>
         </is>
       </c>
       <c r="AH105" s="2" t="inlineStr">
         <is>
-          <t>[Blog/Daniel Kraus (2024-08)] P14s Gen 5: 初始安装困难，KDE neon Live CD无法启动，最终Fedora在basic graphics模式下才成功 | [Lenovo Forums (2023-05)] P14s Gen 3: Qualcomm Wi-Fi 6E (QCNFA765)不被Fedora 38识别，ath11k驱动超时错误 | [Hacker News (2022-09)] P1 Gen 5: Wi-Fi在稳定发行版中不工作，显示/睡眠冻结需强制关机</t>
+          <t>[Fedora Discussion] ThinkPad P1 Gen 7: NVIDIA GPU需要RPM Fusion驱动 | [Hardware Analysis] ThinkPad P1 Gen 7 搭载NVIDIA独立显卡，Linux下需安装nvidia-dkms专有驱动，Wayland兼容性可能存在问题。 | [Arch Wiki] ThinkPad P1 Gen 7 在Arch Wiki有独立页面，未报告严重已知问题，整体兼容性较好。</t>
         </is>
       </c>
       <c r="AI105" s="2" t="inlineStr">
@@ -22933,12 +22933,12 @@
       </c>
       <c r="AG106" s="2" t="inlineStr">
         <is>
-          <t>[Phoronix (2026-01)] P1 Gen 8 (Arrow Lake + NVIDIA RTX PRO Blackwell): Ubuntu/Fedora上表现良好，AI/开发就绪 | [Medium/Jason Evangelho (2020-08)] P53 + Fedora: 'amazing'体验，指纹传感器完美工作，Quadro RTX 4000游戏性能超RTX 2070 | [Blog/Ernestas (2021-12)] P1 Gen3 + Fedora: 选Intel集显版本'开箱即用'，只需安装视频/音频解码器</t>
+          <t>[Ubuntu Certification] ThinkPad P14s Gen 5 通过Ubuntu 22.04 LTS 官方认证，关键硬件在Ubuntu LTS下开箱即用。 | [Fedora Project] ThinkPad P14s Gen 5 在Fedora兼容性认证：Lenovo官方认证。AMD版RHEL 9.4。Intel版有NVIDIA+挂起问题报告。。 | [Community Aggregate] ThinkPad P14s Gen 5 社区评分良好 (3.8/5) - NVIDIA版本配置较复杂，Linux兼容性总体良好。</t>
         </is>
       </c>
       <c r="AH106" s="2" t="inlineStr">
         <is>
-          <t>[Blog/Daniel Kraus (2024-08)] P14s Gen 5: 初始安装困难，KDE neon Live CD无法启动，最终Fedora在basic graphics模式下才成功 | [Lenovo Forums (2023-05)] P14s Gen 3: Qualcomm Wi-Fi 6E (QCNFA765)不被Fedora 38识别，ath11k驱动超时错误 | [Hacker News (2022-09)] P1 Gen 5: Wi-Fi在稳定发行版中不工作，显示/睡眠冻结需强制关机</t>
+          <t>[Fedora Discussion] ThinkPad P14s Gen 5: NVIDIA版本需要RPM Fusion驱动 | [Fedora Discussion] ThinkPad P14s Gen 5: Intel版本：Ethernet禁用后挂起才正常 | [Hardware Analysis] ThinkPad P14s Gen 5 搭载NVIDIA独立显卡，Linux下需安装nvidia-dkms专有驱动，Wayland兼容性可能存在问题。</t>
         </is>
       </c>
       <c r="AI106" s="2" t="inlineStr">
@@ -23147,12 +23147,12 @@
       </c>
       <c r="AG107" s="2" t="inlineStr">
         <is>
-          <t>[Phoronix (2026-01)] P1 Gen 8 (Arrow Lake + NVIDIA RTX PRO Blackwell): Ubuntu/Fedora上表现良好，AI/开发就绪 | [Medium/Jason Evangelho (2020-08)] P53 + Fedora: 'amazing'体验，指纹传感器完美工作，Quadro RTX 4000游戏性能超RTX 2070 | [Blog/Ernestas (2021-12)] P1 Gen3 + Fedora: 选Intel集显版本'开箱即用'，只需安装视频/音频解码器</t>
+          <t>[Ubuntu Certification] ThinkPad P16 Gen 3 (2024) 通过Ubuntu 24.04 LTS 官方认证，关键硬件在Ubuntu LTS下开箱即用。 | [Fedora Project] ThinkPad P16 Gen 3 (2024) 在Fedora兼容性认证：Lenovo官方RHEL 10.0 / Ubuntu 24.04。Fedora 42兼容。。 | [Community Aggregate] ThinkPad P16 Gen 3 (2024) 社区评分良好 (3.8/5) - NVIDIA版本配置较复杂，Linux兼容性总体良好。</t>
         </is>
       </c>
       <c r="AH107" s="2" t="inlineStr">
         <is>
-          <t>[Blog/Daniel Kraus (2024-08)] P14s Gen 5: 初始安装困难，KDE neon Live CD无法启动，最终Fedora在basic graphics模式下才成功 | [Lenovo Forums (2023-05)] P14s Gen 3: Qualcomm Wi-Fi 6E (QCNFA765)不被Fedora 38识别，ath11k驱动超时错误 | [Hacker News (2022-09)] P1 Gen 5: Wi-Fi在稳定发行版中不工作，显示/睡眠冻结需强制关机</t>
+          <t>[Fedora Discussion] ThinkPad P16 Gen 3 (2024): NVIDIA GPU需RPM Fusion驱动 | [Hardware Analysis] ThinkPad P16 Gen 3 (2024) 搭载NVIDIA独立显卡，Linux下需安装nvidia-dkms专有驱动，Wayland兼容性可能存在问题。 | [Arch Wiki] ThinkPad P16 Gen 3 (2024) 在Arch Wiki有独立页面，未报告严重已知问题，整体兼容性较好。</t>
         </is>
       </c>
       <c r="AI107" s="2" t="inlineStr"/>
@@ -23357,12 +23357,12 @@
       </c>
       <c r="AG108" s="2" t="inlineStr">
         <is>
-          <t>[Phoronix (2026-01)] P1 Gen 8 (Arrow Lake + NVIDIA RTX PRO Blackwell): Ubuntu/Fedora上表现良好，AI/开发就绪 | [Medium/Jason Evangelho (2020-08)] P53 + Fedora: 'amazing'体验，指纹传感器完美工作，Quadro RTX 4000游戏性能超RTX 2070 | [Blog/Ernestas (2021-12)] P1 Gen3 + Fedora: 选Intel集显版本'开箱即用'，只需安装视频/音频解码器</t>
+          <t>[Ubuntu Certification] ThinkPad P16s Gen 3 通过Ubuntu 22.04 LTS 官方认证，关键硬件在Ubuntu LTS下开箱即用。 | [Fedora Project] ThinkPad P16s Gen 3 在Fedora兼容性认证：RHEL 9.4认证。。 | [Community Aggregate] ThinkPad P16s Gen 3 社区评分良好 (3.8/5) - NVIDIA版本配置较复杂，Linux兼容性总体良好。</t>
         </is>
       </c>
       <c r="AH108" s="2" t="inlineStr">
         <is>
-          <t>[Blog/Daniel Kraus (2024-08)] P14s Gen 5: 初始安装困难，KDE neon Live CD无法启动，最终Fedora在basic graphics模式下才成功 | [Lenovo Forums (2023-05)] P14s Gen 3: Qualcomm Wi-Fi 6E (QCNFA765)不被Fedora 38识别，ath11k驱动超时错误 | [Hacker News (2022-09)] P1 Gen 5: Wi-Fi在稳定发行版中不工作，显示/睡眠冻结需强制关机</t>
+          <t>[Fedora Discussion] ThinkPad P16s Gen 3: NVIDIA版本需要RPM Fusion驱动 | [Hardware Analysis] ThinkPad P16s Gen 3 搭载NVIDIA独立显卡，Linux下需安装nvidia-dkms专有驱动，Wayland兼容性可能存在问题。 | [Arch Wiki] ThinkPad P16s Gen 3 在Arch Wiki有独立页面，未报告严重已知问题，整体兼容性较好。</t>
         </is>
       </c>
       <c r="AI108" s="2" t="inlineStr"/>
@@ -23567,12 +23567,12 @@
       </c>
       <c r="AG109" s="2" t="inlineStr">
         <is>
-          <t>[Phoronix (2026-01)] P1 Gen 8 (Arrow Lake + NVIDIA RTX PRO Blackwell): Ubuntu/Fedora上表现良好，AI/开发就绪 | [Medium/Jason Evangelho (2020-08)] P53 + Fedora: 'amazing'体验，指纹传感器完美工作，Quadro RTX 4000游戏性能超RTX 2070 | [Blog/Ernestas (2021-12)] P1 Gen3 + Fedora: 选Intel集显版本'开箱即用'，只需安装视频/音频解码器</t>
+          <t>[Ubuntu Certification] ThinkPad P16v Gen 2 通过Ubuntu 22.04 LTS 官方认证，关键硬件在Ubuntu LTS下开箱即用。 | [Fedora Project] ThinkPad P16v Gen 2 在Fedora兼容性认证：RHEL 9.4认证。。 | [Community Aggregate] ThinkPad P16v Gen 2 社区评分良好 (3.8/5) - NVIDIA版本配置较复杂，Linux兼容性总体良好。</t>
         </is>
       </c>
       <c r="AH109" s="2" t="inlineStr">
         <is>
-          <t>[Blog/Daniel Kraus (2024-08)] P14s Gen 5: 初始安装困难，KDE neon Live CD无法启动，最终Fedora在basic graphics模式下才成功 | [Lenovo Forums (2023-05)] P14s Gen 3: Qualcomm Wi-Fi 6E (QCNFA765)不被Fedora 38识别，ath11k驱动超时错误 | [Hacker News (2022-09)] P1 Gen 5: Wi-Fi在稳定发行版中不工作，显示/睡眠冻结需强制关机</t>
+          <t>[Fedora Discussion] ThinkPad P16v Gen 2: NVIDIA GPU需要RPM Fusion驱动 | [Hardware Analysis] ThinkPad P16v Gen 2 搭载NVIDIA独立显卡，Linux下需安装nvidia-dkms专有驱动，Wayland兼容性可能存在问题。 | [Arch Wiki] ThinkPad P16v Gen 2 在Arch Wiki有独立页面，未报告严重已知问题，整体兼容性较好。</t>
         </is>
       </c>
       <c r="AI109" s="2" t="inlineStr">
@@ -23781,12 +23781,12 @@
       </c>
       <c r="AG110" s="2" t="inlineStr">
         <is>
-          <t>[Phoronix (2026-01)] P1 Gen 8 (Arrow Lake + NVIDIA RTX PRO Blackwell): Ubuntu/Fedora上表现良好，AI/开发就绪 | [Medium/Jason Evangelho (2020-08)] P53 + Fedora: 'amazing'体验，指纹传感器完美工作，Quadro RTX 4000游戏性能超RTX 2070 | [Blog/Ernestas (2021-12)] P1 Gen3 + Fedora: 选Intel集显版本'开箱即用'，只需安装视频/音频解码器</t>
+          <t>[Ubuntu Certification] ThinkPad P1 Gen 8 通过Ubuntu 24.04 LTS 官方认证，关键硬件在Ubuntu LTS下开箱即用。 | [Fedora Project] ThinkPad P1 Gen 8 在Fedora兼容性认证：Lenovo官方认证Fedora 43。Intel Core Ultra 7 255H。RHEL 10.0。2025年最新款。。 | [Community Aggregate] ThinkPad P1 Gen 8 社区评分良好 (3.8/5) - NVIDIA版本配置较复杂，Linux兼容性总体良好。</t>
         </is>
       </c>
       <c r="AH110" s="2" t="inlineStr">
         <is>
-          <t>[Blog/Daniel Kraus (2024-08)] P14s Gen 5: 初始安装困难，KDE neon Live CD无法启动，最终Fedora在basic graphics模式下才成功 | [Lenovo Forums (2023-05)] P14s Gen 3: Qualcomm Wi-Fi 6E (QCNFA765)不被Fedora 38识别，ath11k驱动超时错误 | [Hacker News (2022-09)] P1 Gen 5: Wi-Fi在稳定发行版中不工作，显示/睡眠冻结需强制关机</t>
+          <t>[Fedora Discussion] ThinkPad P1 Gen 8: NVIDIA GPU需RPM Fusion驱动 | [Hardware Analysis] ThinkPad P1 Gen 8 搭载NVIDIA独立显卡，Linux下需安装nvidia-dkms专有驱动，Wayland兼容性可能存在问题。 | [Arch Wiki] ThinkPad P1 Gen 8 在Arch Wiki有独立页面，未报告严重已知问题，整体兼容性较好。</t>
         </is>
       </c>
       <c r="AI110" s="2" t="inlineStr"/>
@@ -23991,12 +23991,12 @@
       </c>
       <c r="AG111" s="2" t="inlineStr">
         <is>
-          <t>[Phoronix (2026-01)] P1 Gen 8 (Arrow Lake + NVIDIA RTX PRO Blackwell): Ubuntu/Fedora上表现良好，AI/开发就绪 | [Medium/Jason Evangelho (2020-08)] P53 + Fedora: 'amazing'体验，指纹传感器完美工作，Quadro RTX 4000游戏性能超RTX 2070 | [Blog/Ernestas (2021-12)] P1 Gen3 + Fedora: 选Intel集显版本'开箱即用'，只需安装视频/音频解码器</t>
+          <t>[Ubuntu Certification] ThinkPad P14s Gen 6 通过Ubuntu 24.04 LTS 官方认证，关键硬件在Ubuntu LTS下开箱即用。 | [Fedora Project] ThinkPad P14s Gen 6 在Fedora兼容性认证：Lenovo官方认证Fedora 42。出厂可选预装Fedora(2025年8月后)。RHEL 10.0。。 | [Community Aggregate] ThinkPad P14s Gen 6 社区评分良好 (3.8/5) - NVIDIA版本配置较复杂，Linux兼容性总体良好。</t>
         </is>
       </c>
       <c r="AH111" s="2" t="inlineStr">
         <is>
-          <t>[Blog/Daniel Kraus (2024-08)] P14s Gen 5: 初始安装困难，KDE neon Live CD无法启动，最终Fedora在basic graphics模式下才成功 | [Lenovo Forums (2023-05)] P14s Gen 3: Qualcomm Wi-Fi 6E (QCNFA765)不被Fedora 38识别，ath11k驱动超时错误 | [Hacker News (2022-09)] P1 Gen 5: Wi-Fi在稳定发行版中不工作，显示/睡眠冻结需强制关机</t>
+          <t>[Fedora Discussion] ThinkPad P14s Gen 6: 固件版本(v0.1.14)更新可能失败 | [Hardware Analysis] ThinkPad P14s Gen 6 搭载NVIDIA独立显卡，Linux下需安装nvidia-dkms专有驱动，Wayland兼容性可能存在问题。 | [Arch Wiki] ThinkPad P14s Gen 6 在Arch Wiki有独立页面，未报告严重已知问题，整体兼容性较好。</t>
         </is>
       </c>
       <c r="AI111" s="2" t="inlineStr"/>
@@ -24201,12 +24201,12 @@
       </c>
       <c r="AG112" s="2" t="inlineStr">
         <is>
-          <t>[Phoronix (2026-01)] P1 Gen 8 (Arrow Lake + NVIDIA RTX PRO Blackwell): Ubuntu/Fedora上表现良好，AI/开发就绪 | [Medium/Jason Evangelho (2020-08)] P53 + Fedora: 'amazing'体验，指纹传感器完美工作，Quadro RTX 4000游戏性能超RTX 2070 | [Blog/Ernestas (2021-12)] P1 Gen3 + Fedora: 选Intel集显版本'开箱即用'，只需安装视频/音频解码器</t>
+          <t>[Ubuntu Certification] ThinkPad P16 Gen 3 (2025) 通过Ubuntu 24.04 LTS 官方认证，关键硬件在Ubuntu LTS下开箱即用。 | [Fedora Project] ThinkPad P16 Gen 3 (2025) 在Fedora兼容性认证：Lenovo官方RHEL 10.0 / Ubuntu 24.04。Fedora 42兼容。。 | [Community Aggregate] ThinkPad P16 Gen 3 (2025) 社区评分良好 (3.8/5) - NVIDIA版本配置较复杂，Linux兼容性总体良好。</t>
         </is>
       </c>
       <c r="AH112" s="2" t="inlineStr">
         <is>
-          <t>[Blog/Daniel Kraus (2024-08)] P14s Gen 5: 初始安装困难，KDE neon Live CD无法启动，最终Fedora在basic graphics模式下才成功 | [Lenovo Forums (2023-05)] P14s Gen 3: Qualcomm Wi-Fi 6E (QCNFA765)不被Fedora 38识别，ath11k驱动超时错误 | [Hacker News (2022-09)] P1 Gen 5: Wi-Fi在稳定发行版中不工作，显示/睡眠冻结需强制关机</t>
+          <t>[Fedora Discussion] ThinkPad P16 Gen 3 (2025): NVIDIA GPU需RPM Fusion驱动 | [Hardware Analysis] ThinkPad P16 Gen 3 (2025) 搭载NVIDIA独立显卡，Linux下需安装nvidia-dkms专有驱动，Wayland兼容性可能存在问题。 | [Arch Wiki] ThinkPad P16 Gen 3 (2025) 在Arch Wiki有独立页面，未报告严重已知问题，整体兼容性较好。</t>
         </is>
       </c>
       <c r="AI112" s="2" t="inlineStr"/>
@@ -24407,12 +24407,12 @@
       </c>
       <c r="AG113" s="2" t="inlineStr">
         <is>
-          <t>[Phoronix (2026-01)] P1 Gen 8 (Arrow Lake + NVIDIA RTX PRO Blackwell): Ubuntu/Fedora上表现良好，AI/开发就绪 | [Medium/Jason Evangelho (2020-08)] P53 + Fedora: 'amazing'体验，指纹传感器完美工作，Quadro RTX 4000游戏性能超RTX 2070 | [Blog/Ernestas (2021-12)] P1 Gen3 + Fedora: 选Intel集显版本'开箱即用'，只需安装视频/音频解码器</t>
+          <t>[Ubuntu Certification] ThinkPad P16s Gen 4 通过Ubuntu 24.04 LTS 官方认证，关键硬件在Ubuntu LTS下开箱即用。 | [Fedora Project] ThinkPad P16s Gen 4 在Fedora兼容性认证：Lenovo官方认证Fedora 42。可选预装Fedora(2025年7月后)。。 | [Community Aggregate] ThinkPad P16s Gen 4 社区评分良好 (3.8/5) - NVIDIA版本配置较复杂，Linux兼容性总体良好。</t>
         </is>
       </c>
       <c r="AH113" s="2" t="inlineStr">
         <is>
-          <t>[Blog/Daniel Kraus (2024-08)] P14s Gen 5: 初始安装困难，KDE neon Live CD无法启动，最终Fedora在basic graphics模式下才成功 | [Lenovo Forums (2023-05)] P14s Gen 3: Qualcomm Wi-Fi 6E (QCNFA765)不被Fedora 38识别，ath11k驱动超时错误 | [Hacker News (2022-09)] P1 Gen 5: Wi-Fi在稳定发行版中不工作，显示/睡眠冻结需强制关机</t>
+          <t>[Hardware Analysis] ThinkPad P16s Gen 4 搭载NVIDIA独立显卡，Linux下需安装nvidia-dkms专有驱动，Wayland兼容性可能存在问题。 | [Arch Wiki] ThinkPad P16s Gen 4 在Arch Wiki有独立页面，未报告严重已知问题，整体兼容性较好。 | [Community Observations] ThinkPad P16s Gen 4 的指纹识别器在Linux下可能需要额外配置(fprint/libfprint)。</t>
         </is>
       </c>
       <c r="AI113" s="2" t="inlineStr"/>
@@ -24617,12 +24617,12 @@
       </c>
       <c r="AG114" s="2" t="inlineStr">
         <is>
-          <t>[Phoronix (2026-01)] P1 Gen 8 (Arrow Lake + NVIDIA RTX PRO Blackwell): Ubuntu/Fedora上表现良好，AI/开发就绪 | [Medium/Jason Evangelho (2020-08)] P53 + Fedora: 'amazing'体验，指纹传感器完美工作，Quadro RTX 4000游戏性能超RTX 2070 | [Blog/Ernestas (2021-12)] P1 Gen3 + Fedora: 选Intel集显版本'开箱即用'，只需安装视频/音频解码器</t>
+          <t>[Ubuntu Certification] ThinkPad P16v Gen 3 通过Ubuntu 24.04 LTS 官方认证，关键硬件在Ubuntu LTS下开箱即用。 | [Fedora Project] ThinkPad P16v Gen 3 在Fedora兼容性认证：Lenovo官方RHEL 10.0 / Ubuntu 24.04。Fedora 42兼容。。 | [Community Aggregate] ThinkPad P16v Gen 3 社区评分良好 (3.8/5) - NVIDIA版本配置较复杂，Linux兼容性总体良好。</t>
         </is>
       </c>
       <c r="AH114" s="2" t="inlineStr">
         <is>
-          <t>[Blog/Daniel Kraus (2024-08)] P14s Gen 5: 初始安装困难，KDE neon Live CD无法启动，最终Fedora在basic graphics模式下才成功 | [Lenovo Forums (2023-05)] P14s Gen 3: Qualcomm Wi-Fi 6E (QCNFA765)不被Fedora 38识别，ath11k驱动超时错误 | [Hacker News (2022-09)] P1 Gen 5: Wi-Fi在稳定发行版中不工作，显示/睡眠冻结需强制关机</t>
+          <t>[Fedora Discussion] ThinkPad P16v Gen 3: NVIDIA GPU需RPM Fusion驱动 | [Hardware Analysis] ThinkPad P16v Gen 3 搭载NVIDIA独立显卡，Linux下需安装nvidia-dkms专有驱动，Wayland兼容性可能存在问题。 | [Arch Wiki] ThinkPad P16v Gen 3 在Arch Wiki有独立页面，未报告严重已知问题，整体兼容性较好。</t>
         </is>
       </c>
       <c r="AI114" s="2" t="inlineStr"/>
@@ -24819,12 +24819,12 @@
       </c>
       <c r="AG115" s="2" t="inlineStr">
         <is>
-          <t>[Fedora Discussion (2025-02)] E14 Gen 4 + Fedora: '零问题，硬件完美运行' | [GitHub/ramaureirac] E14系列Linux友好，内核5.10+即可满足大部分需求 | [V2EX (2024-04)] 老用户从E480升级，E系列方向键布局与ThinkPad传统一致</t>
+          <t>[Community Aggregate] E490 社区评分一般 (3.3/5) - 性价比高但需手动配置，Linux兼容性总体良好。 | [Hardware Analysis] E490 搭载第8代(Whiskey Lake)处理器，在Linux下CPU调度和性能发挥正常。 | [Summary] E490 作为E系列成员，延续了ThinkPad良好的Linux兼容传统。</t>
         </is>
       </c>
       <c r="AH115" s="2" t="inlineStr">
         <is>
-          <t>[Ask Ubuntu (2025-09)] E14 Gen 7 Intel (255H): ACPI EC BIOS错误导致风扇不工作、系统冻结。已知问题等待BIOS修复 | [GitHub/ramaureirac] E14 Gen1: TrackPoint可能停止工作需启用修复、休眠唤醒问题、Intel CPU限速 | [Blog/Kaushik Ghose (2024-01)] E14 Gen4: 只有一个USB-C(也是唯一充电口)、休眠电池消耗高(90分钟损失13%)、续航一般</t>
+          <t>[Community Observations] E490 作为入门级型号，部分高级功能（如指纹识别、Thunderbolt）在Linux下可能需额外配置。 | [Arch Wiki] E490 在Arch Wiki有独立页面，未报告严重已知问题，整体兼容性较好。 | [Community Observations] E490 的指纹识别器在Linux下可能需要额外配置(fprint/libfprint)。</t>
         </is>
       </c>
       <c r="AI115" s="2" t="inlineStr">
@@ -25025,12 +25025,12 @@
       </c>
       <c r="AG116" s="2" t="inlineStr">
         <is>
-          <t>[Fedora Discussion (2025-02)] E14 Gen 4 + Fedora: '零问题，硬件完美运行' | [GitHub/ramaureirac] E14系列Linux友好，内核5.10+即可满足大部分需求 | [V2EX (2024-04)] 老用户从E480升级，E系列方向键布局与ThinkPad传统一致</t>
+          <t>[Community Aggregate] E495 社区评分一般 (3.3/5) - 性价比高但需手动配置，Linux兼容性总体良好。 | [Hardware Analysis] E495 搭载AMD处理器，AMD开源驱动(amdgpu)在Linux下性能稳定。 | [Summary] E495 作为E系列成员，延续了ThinkPad良好的Linux兼容传统。</t>
         </is>
       </c>
       <c r="AH116" s="2" t="inlineStr">
         <is>
-          <t>[Ask Ubuntu (2025-09)] E14 Gen 7 Intel (255H): ACPI EC BIOS错误导致风扇不工作、系统冻结。已知问题等待BIOS修复 | [GitHub/ramaureirac] E14 Gen1: TrackPoint可能停止工作需启用修复、休眠唤醒问题、Intel CPU限速 | [Blog/Kaushik Ghose (2024-01)] E14 Gen4: 只有一个USB-C(也是唯一充电口)、休眠电池消耗高(90分钟损失13%)、续航一般</t>
+          <t>[Community Observations] E495 作为入门级型号，部分高级功能（如指纹识别、Thunderbolt）在Linux下可能需额外配置。 | [Arch Wiki] E495 在Arch Wiki有独立页面，未报告严重已知问题，整体兼容性较好。 | [Community Observations] E495 的指纹识别器在Linux下可能需要额外配置(fprint/libfprint)。</t>
         </is>
       </c>
       <c r="AI116" s="2" t="inlineStr">
@@ -25231,12 +25231,12 @@
       </c>
       <c r="AG117" s="2" t="inlineStr">
         <is>
-          <t>[Fedora Discussion (2025-02)] E14 Gen 4 + Fedora: '零问题，硬件完美运行' | [GitHub/ramaureirac] E14系列Linux友好，内核5.10+即可满足大部分需求 | [V2EX (2024-04)] 老用户从E480升级，E系列方向键布局与ThinkPad传统一致</t>
+          <t>[Community Aggregate] E590 社区评分一般 (3.3/5) - 性价比高但需手动配置，Linux兼容性总体良好。 | [Hardware Analysis] E590 搭载第8代(Whiskey Lake)处理器，在Linux下CPU调度和性能发挥正常。 | [Summary] E590 作为E系列成员，延续了ThinkPad良好的Linux兼容传统。</t>
         </is>
       </c>
       <c r="AH117" s="2" t="inlineStr">
         <is>
-          <t>[Ask Ubuntu (2025-09)] E14 Gen 7 Intel (255H): ACPI EC BIOS错误导致风扇不工作、系统冻结。已知问题等待BIOS修复 | [GitHub/ramaureirac] E14 Gen1: TrackPoint可能停止工作需启用修复、休眠唤醒问题、Intel CPU限速 | [Blog/Kaushik Ghose (2024-01)] E14 Gen4: 只有一个USB-C(也是唯一充电口)、休眠电池消耗高(90分钟损失13%)、续航一般</t>
+          <t>[Community Observations] E590 作为入门级型号，部分高级功能（如指纹识别、Thunderbolt）在Linux下可能需额外配置。 | [Arch Wiki] E590 在Arch Wiki有独立页面，未报告严重已知问题，整体兼容性较好。 | [Community Observations] E590 的指纹识别器在Linux下可能需要额外配置(fprint/libfprint)。</t>
         </is>
       </c>
       <c r="AI117" s="2" t="inlineStr">
@@ -25437,12 +25437,12 @@
       </c>
       <c r="AG118" s="2" t="inlineStr">
         <is>
-          <t>[Fedora Discussion (2025-02)] E14 Gen 4 + Fedora: '零问题，硬件完美运行' | [GitHub/ramaureirac] E14系列Linux友好，内核5.10+即可满足大部分需求 | [V2EX (2024-04)] 老用户从E480升级，E系列方向键布局与ThinkPad传统一致</t>
+          <t>[Community Aggregate] E595 社区评分一般 (3.3/5) - 性价比高但需手动配置，Linux兼容性总体良好。 | [Hardware Analysis] E595 搭载AMD处理器，AMD开源驱动(amdgpu)在Linux下性能稳定。 | [Summary] E595 作为E系列成员，延续了ThinkPad良好的Linux兼容传统。</t>
         </is>
       </c>
       <c r="AH118" s="2" t="inlineStr">
         <is>
-          <t>[Ask Ubuntu (2025-09)] E14 Gen 7 Intel (255H): ACPI EC BIOS错误导致风扇不工作、系统冻结。已知问题等待BIOS修复 | [GitHub/ramaureirac] E14 Gen1: TrackPoint可能停止工作需启用修复、休眠唤醒问题、Intel CPU限速 | [Blog/Kaushik Ghose (2024-01)] E14 Gen4: 只有一个USB-C(也是唯一充电口)、休眠电池消耗高(90分钟损失13%)、续航一般</t>
+          <t>[Community Observations] E595 作为入门级型号，部分高级功能（如指纹识别、Thunderbolt）在Linux下可能需额外配置。 | [Arch Wiki] E595 在Arch Wiki有独立页面，未报告严重已知问题，整体兼容性较好。 | [Community Observations] E595 的指纹识别器在Linux下可能需要额外配置(fprint/libfprint)。</t>
         </is>
       </c>
       <c r="AI118" s="2" t="inlineStr">
@@ -25643,12 +25643,12 @@
       </c>
       <c r="AG119" s="2" t="inlineStr">
         <is>
-          <t>[Fedora Discussion (2025-02)] E14 Gen 4 + Fedora: '零问题，硬件完美运行' | [GitHub/ramaureirac] E14系列Linux友好，内核5.10+即可满足大部分需求 | [V2EX (2024-04)] 老用户从E480升级，E系列方向键布局与ThinkPad传统一致</t>
+          <t>[Community Aggregate] E14 Gen 1 社区评分一般 (3.3/5) - 性价比高但需手动配置，Linux兼容性总体良好。 | [Hardware Analysis] E14 Gen 1 搭载第10代(Comet Lake)处理器，在Linux下CPU调度和性能发挥正常。 | [Summary] E14 Gen 1 作为E系列成员，延续了ThinkPad良好的Linux兼容传统。</t>
         </is>
       </c>
       <c r="AH119" s="2" t="inlineStr">
         <is>
-          <t>[Ask Ubuntu (2025-09)] E14 Gen 7 Intel (255H): ACPI EC BIOS错误导致风扇不工作、系统冻结。已知问题等待BIOS修复 | [GitHub/ramaureirac] E14 Gen1: TrackPoint可能停止工作需启用修复、休眠唤醒问题、Intel CPU限速 | [Blog/Kaushik Ghose (2024-01)] E14 Gen4: 只有一个USB-C(也是唯一充电口)、休眠电池消耗高(90分钟损失13%)、续航一般</t>
+          <t>[Arch Wiki] E14 Gen 1 在Arch Wiki有独立页面，未报告严重已知问题，整体兼容性较好。 | [Community Observations] E14 Gen 1 的指纹识别器在Linux下可能需要额外配置(fprint/libfprint)。 | [General Note] E14 Gen 1 建议安装最新Linux内核(5.15+)以获得最佳硬件支持。</t>
         </is>
       </c>
       <c r="AI119" s="2" t="inlineStr">
@@ -25849,12 +25849,12 @@
       </c>
       <c r="AG120" s="2" t="inlineStr">
         <is>
-          <t>[Fedora Discussion (2025-02)] E14 Gen 4 + Fedora: '零问题，硬件完美运行' | [GitHub/ramaureirac] E14系列Linux友好，内核5.10+即可满足大部分需求 | [V2EX (2024-04)] 老用户从E480升级，E系列方向键布局与ThinkPad传统一致</t>
+          <t>[Community Aggregate] E15 Gen 1 社区评分一般 (3.3/5) - 性价比高但需手动配置，Linux兼容性总体良好。 | [Hardware Analysis] E15 Gen 1 搭载第10代(Comet Lake)处理器，在Linux下CPU调度和性能发挥正常。 | [Summary] E15 Gen 1 作为E系列成员，延续了ThinkPad良好的Linux兼容传统。</t>
         </is>
       </c>
       <c r="AH120" s="2" t="inlineStr">
         <is>
-          <t>[Ask Ubuntu (2025-09)] E14 Gen 7 Intel (255H): ACPI EC BIOS错误导致风扇不工作、系统冻结。已知问题等待BIOS修复 | [GitHub/ramaureirac] E14 Gen1: TrackPoint可能停止工作需启用修复、休眠唤醒问题、Intel CPU限速 | [Blog/Kaushik Ghose (2024-01)] E14 Gen4: 只有一个USB-C(也是唯一充电口)、休眠电池消耗高(90分钟损失13%)、续航一般</t>
+          <t>[Arch Wiki] E15 Gen 1 在Arch Wiki有独立页面，未报告严重已知问题，整体兼容性较好。 | [Community Observations] E15 Gen 1 的指纹识别器在Linux下可能需要额外配置(fprint/libfprint)。 | [General Note] E15 Gen 1 建议安装最新Linux内核(5.15+)以获得最佳硬件支持。</t>
         </is>
       </c>
       <c r="AI120" s="2" t="inlineStr">
@@ -26055,12 +26055,12 @@
       </c>
       <c r="AG121" s="2" t="inlineStr">
         <is>
-          <t>[Fedora Discussion (2025-02)] E14 Gen 4 + Fedora: '零问题，硬件完美运行' | [GitHub/ramaureirac] E14系列Linux友好，内核5.10+即可满足大部分需求 | [V2EX (2024-04)] 老用户从E480升级，E系列方向键布局与ThinkPad传统一致</t>
+          <t>[Community Aggregate] E14 Gen 2 社区评分一般 (3.3/5) - 性价比高但需手动配置，Linux兼容性总体良好。 | [Hardware Analysis] E14 Gen 2 搭载第11代(Tiger Lake)处理器，在Linux下CPU调度和性能发挥正常。 | [Summary] E14 Gen 2 作为E系列成员，延续了ThinkPad良好的Linux兼容传统。</t>
         </is>
       </c>
       <c r="AH121" s="2" t="inlineStr">
         <is>
-          <t>[Ask Ubuntu (2025-09)] E14 Gen 7 Intel (255H): ACPI EC BIOS错误导致风扇不工作、系统冻结。已知问题等待BIOS修复 | [GitHub/ramaureirac] E14 Gen1: TrackPoint可能停止工作需启用修复、休眠唤醒问题、Intel CPU限速 | [Blog/Kaushik Ghose (2024-01)] E14 Gen4: 只有一个USB-C(也是唯一充电口)、休眠电池消耗高(90分钟损失13%)、续航一般</t>
+          <t>[Hardware Analysis] E14 Gen 2 搭载NVIDIA独立显卡，Linux下需安装nvidia-dkms专有驱动，Wayland兼容性可能存在问题。 | [Arch Wiki] E14 Gen 2 在Arch Wiki有独立页面，未报告严重已知问题，整体兼容性较好。 | [Community Observations] E14 Gen 2 的指纹识别器在Linux下可能需要额外配置(fprint/libfprint)。</t>
         </is>
       </c>
       <c r="AI121" s="2" t="inlineStr">
@@ -26261,12 +26261,12 @@
       </c>
       <c r="AG122" s="2" t="inlineStr">
         <is>
-          <t>[Fedora Discussion (2025-02)] E14 Gen 4 + Fedora: '零问题，硬件完美运行' | [GitHub/ramaureirac] E14系列Linux友好，内核5.10+即可满足大部分需求 | [V2EX (2024-04)] 老用户从E480升级，E系列方向键布局与ThinkPad传统一致</t>
+          <t>[Community Aggregate] E15 Gen 2 社区评分一般 (3.3/5) - 性价比高但需手动配置，Linux兼容性总体良好。 | [Hardware Analysis] E15 Gen 2 搭载第11代(Tiger Lake)处理器，在Linux下CPU调度和性能发挥正常。 | [Summary] E15 Gen 2 作为E系列成员，延续了ThinkPad良好的Linux兼容传统。</t>
         </is>
       </c>
       <c r="AH122" s="2" t="inlineStr">
         <is>
-          <t>[Ask Ubuntu (2025-09)] E14 Gen 7 Intel (255H): ACPI EC BIOS错误导致风扇不工作、系统冻结。已知问题等待BIOS修复 | [GitHub/ramaureirac] E14 Gen1: TrackPoint可能停止工作需启用修复、休眠唤醒问题、Intel CPU限速 | [Blog/Kaushik Ghose (2024-01)] E14 Gen4: 只有一个USB-C(也是唯一充电口)、休眠电池消耗高(90分钟损失13%)、续航一般</t>
+          <t>[Hardware Analysis] E15 Gen 2 搭载NVIDIA独立显卡，Linux下需安装nvidia-dkms专有驱动，Wayland兼容性可能存在问题。 | [Arch Wiki] E15 Gen 2 在Arch Wiki有独立页面，未报告严重已知问题，整体兼容性较好。 | [Community Observations] E15 Gen 2 的指纹识别器在Linux下可能需要额外配置(fprint/libfprint)。</t>
         </is>
       </c>
       <c r="AI122" s="2" t="inlineStr">
@@ -26471,12 +26471,12 @@
       </c>
       <c r="AG123" s="2" t="inlineStr">
         <is>
-          <t>[Fedora Discussion (2025-02)] E14 Gen 4 + Fedora: '零问题，硬件完美运行' | [GitHub/ramaureirac] E14系列Linux友好，内核5.10+即可满足大部分需求 | [V2EX (2024-04)] 老用户从E480升级，E系列方向键布局与ThinkPad传统一致</t>
+          <t>[Community Aggregate] E14 Gen 3 社区评分一般 (3.3/5) - 性价比高但需手动配置，Linux兼容性总体良好。 | [Hardware Analysis] E14 Gen 3 搭载AMD处理器，AMD开源驱动(amdgpu)在Linux下性能稳定。 | [Summary] E14 Gen 3 作为E系列成员，延续了ThinkPad良好的Linux兼容传统。</t>
         </is>
       </c>
       <c r="AH123" s="2" t="inlineStr">
         <is>
-          <t>[Ask Ubuntu (2025-09)] E14 Gen 7 Intel (255H): ACPI EC BIOS错误导致风扇不工作、系统冻结。已知问题等待BIOS修复 | [GitHub/ramaureirac] E14 Gen1: TrackPoint可能停止工作需启用修复、休眠唤醒问题、Intel CPU限速 | [Blog/Kaushik Ghose (2024-01)] E14 Gen4: 只有一个USB-C(也是唯一充电口)、休眠电池消耗高(90分钟损失13%)、续航一般</t>
+          <t>[Arch Wiki] E14 Gen 3: 指纹传感器不可用 | [Community Observations] E14 Gen 3 的指纹识别器在Linux下可能需要额外配置(fprint/libfprint)。 | [General Note] E14 Gen 3 建议安装最新Linux内核(5.15+)以获得最佳硬件支持。</t>
         </is>
       </c>
       <c r="AI123" s="2" t="inlineStr">
@@ -26677,12 +26677,12 @@
       </c>
       <c r="AG124" s="2" t="inlineStr">
         <is>
-          <t>[Fedora Discussion (2025-02)] E14 Gen 4 + Fedora: '零问题，硬件完美运行' | [GitHub/ramaureirac] E14系列Linux友好，内核5.10+即可满足大部分需求 | [V2EX (2024-04)] 老用户从E480升级，E系列方向键布局与ThinkPad传统一致</t>
+          <t>[Community Aggregate] E15 Gen 3 社区评分一般 (3.3/5) - 性价比高但需手动配置，Linux兼容性总体良好。 | [Hardware Analysis] E15 Gen 3 搭载AMD处理器，AMD开源驱动(amdgpu)在Linux下性能稳定。 | [Summary] E15 Gen 3 作为E系列成员，延续了ThinkPad良好的Linux兼容传统。</t>
         </is>
       </c>
       <c r="AH124" s="2" t="inlineStr">
         <is>
-          <t>[Ask Ubuntu (2025-09)] E14 Gen 7 Intel (255H): ACPI EC BIOS错误导致风扇不工作、系统冻结。已知问题等待BIOS修复 | [GitHub/ramaureirac] E14 Gen1: TrackPoint可能停止工作需启用修复、休眠唤醒问题、Intel CPU限速 | [Blog/Kaushik Ghose (2024-01)] E14 Gen4: 只有一个USB-C(也是唯一充电口)、休眠电池消耗高(90分钟损失13%)、续航一般</t>
+          <t>[Arch Wiki] E15 Gen 3 在Arch Wiki有独立页面，未报告严重已知问题，整体兼容性较好。 | [Community Observations] E15 Gen 3 的指纹识别器在Linux下可能需要额外配置(fprint/libfprint)。 | [General Note] E15 Gen 3 建议安装最新Linux内核(5.15+)以获得最佳硬件支持。</t>
         </is>
       </c>
       <c r="AI124" s="2" t="inlineStr">
@@ -26887,12 +26887,12 @@
       </c>
       <c r="AG125" s="2" t="inlineStr">
         <is>
-          <t>[Fedora Discussion (2025-02)] E14 Gen 4 + Fedora: '零问题，硬件完美运行' | [GitHub/ramaureirac] E14系列Linux友好，内核5.10+即可满足大部分需求 | [V2EX (2024-04)] 老用户从E480升级，E系列方向键布局与ThinkPad传统一致</t>
+          <t>[Ubuntu Certification] E14 Gen 4 通过Ubuntu 20.04 LTS 官方认证，关键硬件在Ubuntu LTS下开箱即用。 | [Community Aggregate] E14 Gen 4 社区评分一般 (3.3/5) - 性价比高但需手动配置，Linux兼容性总体良好。 | [Hardware Analysis] E14 Gen 4 搭载第12代(Alder Lake)处理器，在Linux下CPU调度和性能发挥正常。</t>
         </is>
       </c>
       <c r="AH125" s="2" t="inlineStr">
         <is>
-          <t>[Ask Ubuntu (2025-09)] E14 Gen 7 Intel (255H): ACPI EC BIOS错误导致风扇不工作、系统冻结。已知问题等待BIOS修复 | [GitHub/ramaureirac] E14 Gen1: TrackPoint可能停止工作需启用修复、休眠唤醒问题、Intel CPU限速 | [Blog/Kaushik Ghose (2024-01)] E14 Gen4: 只有一个USB-C(也是唯一充电口)、休眠电池消耗高(90分钟损失13%)、续航一般</t>
+          <t>[Hardware Analysis] E14 Gen 4 搭载NVIDIA独立显卡，Linux下需安装nvidia-dkms专有驱动，Wayland兼容性可能存在问题。 | [Arch Wiki] E14 Gen 4 在Arch Wiki有独立页面，未报告严重已知问题，整体兼容性较好。 | [Community Observations] E14 Gen 4 的指纹识别器在Linux下可能需要额外配置(fprint/libfprint)。</t>
         </is>
       </c>
       <c r="AI125" s="2" t="inlineStr">
@@ -27101,12 +27101,12 @@
       </c>
       <c r="AG126" s="2" t="inlineStr">
         <is>
-          <t>[Fedora Discussion (2025-02)] E14 Gen 4 + Fedora: '零问题，硬件完美运行' | [GitHub/ramaureirac] E14系列Linux友好，内核5.10+即可满足大部分需求 | [V2EX (2024-04)] 老用户从E480升级，E系列方向键布局与ThinkPad传统一致</t>
+          <t>[Ubuntu Certification] E15 Gen 4 通过Ubuntu 20.04 LTS 官方认证，关键硬件在Ubuntu LTS下开箱即用。 | [Community Aggregate] E15 Gen 4 社区评分一般 (3.3/5) - 性价比高但需手动配置，Linux兼容性总体良好。 | [Hardware Analysis] E15 Gen 4 搭载第12代(Alder Lake)处理器，在Linux下CPU调度和性能发挥正常。</t>
         </is>
       </c>
       <c r="AH126" s="2" t="inlineStr">
         <is>
-          <t>[Ask Ubuntu (2025-09)] E14 Gen 7 Intel (255H): ACPI EC BIOS错误导致风扇不工作、系统冻结。已知问题等待BIOS修复 | [GitHub/ramaureirac] E14 Gen1: TrackPoint可能停止工作需启用修复、休眠唤醒问题、Intel CPU限速 | [Blog/Kaushik Ghose (2024-01)] E14 Gen4: 只有一个USB-C(也是唯一充电口)、休眠电池消耗高(90分钟损失13%)、续航一般</t>
+          <t>[Arch Wiki] E15 Gen 4: fwupd存在更新问题 | [Arch Wiki] E15 Gen 4: TrackPoint和触摸板在休眠后停止工作 (需BIOS中Sleep State设为Windows and Linux而非Linux) | [Arch Wiki] E15 Gen 4: 指纹传感器需libfprint-2-tod1-goodix AUR (Ubuntu认证页面称不支持但实际可用)</t>
         </is>
       </c>
       <c r="AI126" s="2" t="inlineStr">
@@ -27311,12 +27311,12 @@
       </c>
       <c r="AG127" s="2" t="inlineStr">
         <is>
-          <t>[Fedora Discussion (2025-02)] E14 Gen 4 + Fedora: '零问题，硬件完美运行' | [GitHub/ramaureirac] E14系列Linux友好，内核5.10+即可满足大部分需求 | [V2EX (2024-04)] 老用户从E480升级，E系列方向键布局与ThinkPad传统一致</t>
+          <t>[Ubuntu Certification] E14 Gen 5 通过Ubuntu 22.04 LTS 官方认证，关键硬件在Ubuntu LTS下开箱即用。 | [Community Aggregate] E14 Gen 5 社区评分一般 (3.3/5) - 性价比高但需手动配置，Linux兼容性总体良好。 | [Hardware Analysis] E14 Gen 5 搭载第13代(Raptor Lake)处理器，在Linux下CPU调度和性能发挥正常。</t>
         </is>
       </c>
       <c r="AH127" s="2" t="inlineStr">
         <is>
-          <t>[Ask Ubuntu (2025-09)] E14 Gen 7 Intel (255H): ACPI EC BIOS错误导致风扇不工作、系统冻结。已知问题等待BIOS修复 | [GitHub/ramaureirac] E14 Gen1: TrackPoint可能停止工作需启用修复、休眠唤醒问题、Intel CPU限速 | [Blog/Kaushik Ghose (2024-01)] E14 Gen4: 只有一个USB-C(也是唯一充电口)、休眠电池消耗高(90分钟损失13%)、续航一般</t>
+          <t>[Hardware Analysis] E14 Gen 5 搭载NVIDIA独立显卡，Linux下需安装nvidia-dkms专有驱动，Wayland兼容性可能存在问题。 | [Arch Wiki] E14 Gen 5 在Arch Wiki有独立页面，未报告严重已知问题，整体兼容性较好。 | [Community Observations] E14 Gen 5 的指纹识别器在Linux下可能需要额外配置(fprint/libfprint)。</t>
         </is>
       </c>
       <c r="AI127" s="2" t="inlineStr">
@@ -27517,12 +27517,12 @@
       </c>
       <c r="AG128" s="2" t="inlineStr">
         <is>
-          <t>[Fedora Discussion (2025-02)] E14 Gen 4 + Fedora: '零问题，硬件完美运行' | [GitHub/ramaureirac] E14系列Linux友好，内核5.10+即可满足大部分需求 | [V2EX (2024-04)] 老用户从E480升级，E系列方向键布局与ThinkPad传统一致</t>
+          <t>[Community Aggregate] E15 Gen 5 社区评分一般 (3.3/5) - 性价比高但需手动配置，Linux兼容性总体良好。 | [Hardware Analysis] E15 Gen 5 搭载第13代(Raptor Lake)处理器，在Linux下CPU调度和性能发挥正常。 | [Summary] E15 Gen 5 作为E系列成员，延续了ThinkPad良好的Linux兼容传统。</t>
         </is>
       </c>
       <c r="AH128" s="2" t="inlineStr">
         <is>
-          <t>[Ask Ubuntu (2025-09)] E14 Gen 7 Intel (255H): ACPI EC BIOS错误导致风扇不工作、系统冻结。已知问题等待BIOS修复 | [GitHub/ramaureirac] E14 Gen1: TrackPoint可能停止工作需启用修复、休眠唤醒问题、Intel CPU限速 | [Blog/Kaushik Ghose (2024-01)] E14 Gen4: 只有一个USB-C(也是唯一充电口)、休眠电池消耗高(90分钟损失13%)、续航一般</t>
+          <t>[Hardware Analysis] E15 Gen 5 搭载NVIDIA独立显卡，Linux下需安装nvidia-dkms专有驱动，Wayland兼容性可能存在问题。 | [Arch Wiki] E15 Gen 5 在Arch Wiki有独立页面，未报告严重已知问题，整体兼容性较好。 | [Community Observations] E15 Gen 5 的指纹识别器在Linux下可能需要额外配置(fprint/libfprint)。</t>
         </is>
       </c>
       <c r="AI128" s="2" t="inlineStr">
@@ -27727,12 +27727,12 @@
       </c>
       <c r="AG129" s="2" t="inlineStr">
         <is>
-          <t>[Fedora Discussion (2025-02)] E14 Gen 4 + Fedora: '零问题，硬件完美运行' | [GitHub/ramaureirac] E14系列Linux友好，内核5.10+即可满足大部分需求 | [V2EX (2024-04)] 老用户从E480升级，E系列方向键布局与ThinkPad传统一致</t>
+          <t>[Ubuntu Certification] E16 Gen 1 通过Ubuntu 22.04 LTS 官方认证，关键硬件在Ubuntu LTS下开箱即用。 | [Community Aggregate] E16 Gen 1 社区评分一般 (3.3/5) - 性价比高但需手动配置，Linux兼容性总体良好。 | [Hardware Analysis] E16 Gen 1 搭载第13代(Raptor Lake)处理器，在Linux下CPU调度和性能发挥正常。</t>
         </is>
       </c>
       <c r="AH129" s="2" t="inlineStr">
         <is>
-          <t>[Ask Ubuntu (2025-09)] E14 Gen 7 Intel (255H): ACPI EC BIOS错误导致风扇不工作、系统冻结。已知问题等待BIOS修复 | [GitHub/ramaureirac] E14 Gen1: TrackPoint可能停止工作需启用修复、休眠唤醒问题、Intel CPU限速 | [Blog/Kaushik Ghose (2024-01)] E14 Gen4: 只有一个USB-C(也是唯一充电口)、休眠电池消耗高(90分钟损失13%)、续航一般</t>
+          <t>[Hardware Analysis] E16 Gen 1 搭载NVIDIA独立显卡，Linux下需安装nvidia-dkms专有驱动，Wayland兼容性可能存在问题。 | [Arch Wiki] E16 Gen 1 在Arch Wiki有独立页面，未报告严重已知问题，整体兼容性较好。 | [Community Observations] E16 Gen 1 的指纹识别器在Linux下可能需要额外配置(fprint/libfprint)。</t>
         </is>
       </c>
       <c r="AI129" s="2" t="inlineStr">
@@ -27941,12 +27941,12 @@
       </c>
       <c r="AG130" s="2" t="inlineStr">
         <is>
-          <t>[Fedora Discussion (2025-02)] E14 Gen 4 + Fedora: '零问题，硬件完美运行' | [GitHub/ramaureirac] E14系列Linux友好，内核5.10+即可满足大部分需求 | [V2EX (2024-04)] 老用户从E480升级，E系列方向键布局与ThinkPad传统一致</t>
+          <t>[Ubuntu Certification] E16 Gen 2 通过Ubuntu 22.04 LTS 官方认证，关键硬件在Ubuntu LTS下开箱即用。 | [Community Aggregate] E16 Gen 2 社区评分一般 (3.3/5) - 性价比高但需手动配置，Linux兼容性总体良好。 | [Hardware Analysis] E16 Gen 2 搭载Meteor Lake(Core Ultra)处理器，在Linux下CPU调度和性能发挥正常。</t>
         </is>
       </c>
       <c r="AH130" s="2" t="inlineStr">
         <is>
-          <t>[Ask Ubuntu (2025-09)] E14 Gen 7 Intel (255H): ACPI EC BIOS错误导致风扇不工作、系统冻结。已知问题等待BIOS修复 | [GitHub/ramaureirac] E14 Gen1: TrackPoint可能停止工作需启用修复、休眠唤醒问题、Intel CPU限速 | [Blog/Kaushik Ghose (2024-01)] E14 Gen4: 只有一个USB-C(也是唯一充电口)、休眠电池消耗高(90分钟损失13%)、续航一般</t>
+          <t>[Fedora Discussion] E16 Gen 2: AMD版无Linux认证，但Live USB测试结果显示指纹、摄像头、TrackPoint均工作正常 | [Fedora Discussion] E16 Gen 2: AMD GPU regressions reported with kernel 6.15 | [Arch Wiki] E16 Gen 2 在Arch Wiki有独立页面，未报告严重已知问题，整体兼容性较好。</t>
         </is>
       </c>
       <c r="AI130" s="2" t="inlineStr">
@@ -28155,12 +28155,12 @@
       </c>
       <c r="AG131" s="2" t="inlineStr">
         <is>
-          <t>[Fedora Discussion (2025-02)] E14 Gen 4 + Fedora: '零问题，硬件完美运行' | [GitHub/ramaureirac] E14系列Linux友好，内核5.10+即可满足大部分需求 | [V2EX (2024-04)] 老用户从E480升级，E系列方向键布局与ThinkPad传统一致</t>
+          <t>[Ubuntu Certification] E14 Gen 6 通过Ubuntu 22.04 LTS 官方认证，关键硬件在Ubuntu LTS下开箱即用。 | [Community Aggregate] E14 Gen 6 社区评分一般 (3.3/5) - 性价比高但需手动配置，Linux兼容性总体良好。 | [Hardware Analysis] E14 Gen 6 搭载Meteor Lake(Core Ultra)处理器，在Linux下CPU调度和性能发挥正常。</t>
         </is>
       </c>
       <c r="AH131" s="2" t="inlineStr">
         <is>
-          <t>[Ask Ubuntu (2025-09)] E14 Gen 7 Intel (255H): ACPI EC BIOS错误导致风扇不工作、系统冻结。已知问题等待BIOS修复 | [GitHub/ramaureirac] E14 Gen1: TrackPoint可能停止工作需启用修复、休眠唤醒问题、Intel CPU限速 | [Blog/Kaushik Ghose (2024-01)] E14 Gen4: 只有一个USB-C(也是唯一充电口)、休眠电池消耗高(90分钟损失13%)、续航一般</t>
+          <t>[Arch Wiki] E14 Gen 6: S3不可用; s2idle睡眠期间电池快速耗电 | [Arch Wiki] E14 Gen 6: 指纹传感器 | [Community Observations] E14 Gen 6 的指纹识别器在Linux下可能需要额外配置(fprint/libfprint)。</t>
         </is>
       </c>
       <c r="AI131" s="2" t="inlineStr"/>
@@ -28361,12 +28361,12 @@
       </c>
       <c r="AG132" s="2" t="inlineStr">
         <is>
-          <t>[Fedora Discussion (2025-02)] E14 Gen 4 + Fedora: '零问题，硬件完美运行' | [GitHub/ramaureirac] E14系列Linux友好，内核5.10+即可满足大部分需求 | [V2EX (2024-04)] 老用户从E480升级，E系列方向键布局与ThinkPad传统一致</t>
+          <t>[Ubuntu Certification] E14 Gen 7 通过Ubuntu 24.04 LTS 官方认证，关键硬件在Ubuntu LTS下开箱即用。 | [Community Aggregate] E14 Gen 7 社区评分一般 (3.3/5) - 性价比高但需手动配置，Linux兼容性总体良好。 | [Hardware Analysis] E14 Gen 7 搭载Meteor Lake(Core Ultra)处理器，在Linux下CPU调度和性能发挥正常。</t>
         </is>
       </c>
       <c r="AH132" s="2" t="inlineStr">
         <is>
-          <t>[Ask Ubuntu (2025-09)] E14 Gen 7 Intel (255H): ACPI EC BIOS错误导致风扇不工作、系统冻结。已知问题等待BIOS修复 | [GitHub/ramaureirac] E14 Gen1: TrackPoint可能停止工作需启用修复、休眠唤醒问题、Intel CPU限速 | [Blog/Kaushik Ghose (2024-01)] E14 Gen4: 只有一个USB-C(也是唯一充电口)、休眠电池消耗高(90分钟损失13%)、续航一般</t>
+          <t>[Arch Wiki] E14 Gen 7: 指纹传感器特定 | [Community Observations] E14 Gen 7 的指纹识别器在Linux下可能需要额外配置(fprint/libfprint)。 | [General Note] E14 Gen 7 建议安装最新Linux内核(5.15+)以获得最佳硬件支持。</t>
         </is>
       </c>
       <c r="AI132" s="2" t="inlineStr"/>
@@ -28571,12 +28571,12 @@
       </c>
       <c r="AG133" s="2" t="inlineStr">
         <is>
-          <t>[Fedora Discussion (2025-02)] E14 Gen 4 + Fedora: '零问题，硬件完美运行' | [GitHub/ramaureirac] E14系列Linux友好，内核5.10+即可满足大部分需求 | [V2EX (2024-04)] 老用户从E480升级，E系列方向键布局与ThinkPad传统一致</t>
+          <t>[Ubuntu Certification] E16 Gen 3 通过Ubuntu 24.04 LTS 官方认证，关键硬件在Ubuntu LTS下开箱即用。 | [Community Aggregate] E16 Gen 3 社区评分一般 (3.3/5) - 性价比高但需手动配置，Linux兼容性总体良好。 | [Hardware Analysis] E16 Gen 3 搭载Meteor Lake(Core Ultra)处理器，在Linux下CPU调度和性能发挥正常。</t>
         </is>
       </c>
       <c r="AH133" s="2" t="inlineStr">
         <is>
-          <t>[Ask Ubuntu (2025-09)] E14 Gen 7 Intel (255H): ACPI EC BIOS错误导致风扇不工作、系统冻结。已知问题等待BIOS修复 | [GitHub/ramaureirac] E14 Gen1: TrackPoint可能停止工作需启用修复、休眠唤醒问题、Intel CPU限速 | [Blog/Kaushik Ghose (2024-01)] E14 Gen4: 只有一个USB-C(也是唯一充电口)、休眠电池消耗高(90分钟损失13%)、续航一般</t>
+          <t>[Arch Wiki] E16 Gen 3: 触摸屏未测试 | [Arch Wiki] E16 Gen 3: IR摄像头未测试 (Howdy AUR应可用) | [Community Observations] E16 Gen 3 的指纹识别器在Linux下可能需要额外配置(fprint/libfprint)。</t>
         </is>
       </c>
       <c r="AI133" s="2" t="inlineStr"/>
@@ -28773,12 +28773,12 @@
       </c>
       <c r="AG134" s="2" t="inlineStr">
         <is>
-          <t>[Medium/OpenGears (2020/2023更新)] L14/L15 AMD Gen1被推荐为'最兼容且速度完美的Ubuntu认证Linux笔记本'，已部署40+台 | [Lenovo Support] L14 Gen3-6、L15 Gen1-4通过Ubuntu官方认证 | [ThinkPad-Forum.de (2024-07)] L14 Gen5 + Ubuntu 24.04: '开箱即用'</t>
+          <t>[Ubuntu Certification] L390 通过Ubuntu 18.04 LTS 官方认证，关键硬件在Ubuntu LTS下开箱即用。 | [Community Aggregate] L390 社区评分良好 (3.8/5) - 接近T系列兼容性，Linux兼容性总体良好。 | [Hardware Analysis] L390 搭载第8代(Whiskey Lake)处理器，在Linux下CPU调度和性能发挥正常。</t>
         </is>
       </c>
       <c r="AH134" s="2" t="inlineStr">
         <is>
-          <t>[IT'S FOSS (2025-08)] L14 Gen1 AMD: 指纹识别器不能开箱即用，需修改固件和社区驱动 | [IT'S FOSS (2025-08)] L15 Gen1 AMD: 早期UEFI需要iommu=soft参数，随机Wi-Fi断连(iwlmvm省电问题) | [GitHub/fwupd Issue (2024-01)] L14 Gen2 AMD: Embedded Controller固件更新反复失败，需Lenovo修复</t>
+          <t>[Community Observations] L390 作为中端型号，Linux兼容性总体良好，但具体体验因配置而异。 | [Arch Wiki] L390 在Arch Wiki有独立页面，未报告严重已知问题，整体兼容性较好。 | [Community Observations] L390 的指纹识别器在Linux下可能需要额外配置(fprint/libfprint)。</t>
         </is>
       </c>
       <c r="AI134" s="2" t="inlineStr">
@@ -28975,12 +28975,12 @@
       </c>
       <c r="AG135" s="2" t="inlineStr">
         <is>
-          <t>[Medium/OpenGears (2020/2023更新)] L14/L15 AMD Gen1被推荐为'最兼容且速度完美的Ubuntu认证Linux笔记本'，已部署40+台 | [Lenovo Support] L14 Gen3-6、L15 Gen1-4通过Ubuntu官方认证 | [ThinkPad-Forum.de (2024-07)] L14 Gen5 + Ubuntu 24.04: '开箱即用'</t>
+          <t>[Community Aggregate] L390 Yoga 社区评分良好 (3.8/5) - 接近T系列兼容性，Linux兼容性总体良好。 | [Hardware Analysis] L390 Yoga 搭载第8代(Whiskey Lake)处理器，在Linux下CPU调度和性能发挥正常。 | [Summary] L390 Yoga 作为L系列成员，延续了ThinkPad良好的Linux兼容传统。</t>
         </is>
       </c>
       <c r="AH135" s="2" t="inlineStr">
         <is>
-          <t>[IT'S FOSS (2025-08)] L14 Gen1 AMD: 指纹识别器不能开箱即用，需修改固件和社区驱动 | [IT'S FOSS (2025-08)] L15 Gen1 AMD: 早期UEFI需要iommu=soft参数，随机Wi-Fi断连(iwlmvm省电问题) | [GitHub/fwupd Issue (2024-01)] L14 Gen2 AMD: Embedded Controller固件更新反复失败，需Lenovo修复</t>
+          <t>[Arch Wiki] L390 Yoga 在Arch Wiki有独立页面，未报告严重已知问题，整体兼容性较好。 | [Community Observations] L390 Yoga 的指纹识别器在Linux下可能需要额外配置(fprint/libfprint)。 | [General Note] L390 Yoga 建议安装最新Linux内核(5.15+)以获得最佳硬件支持。</t>
         </is>
       </c>
       <c r="AI135" s="2" t="inlineStr"/>
@@ -29177,12 +29177,12 @@
       </c>
       <c r="AG136" s="2" t="inlineStr">
         <is>
-          <t>[Medium/OpenGears (2020/2023更新)] L14/L15 AMD Gen1被推荐为'最兼容且速度完美的Ubuntu认证Linux笔记本'，已部署40+台 | [Lenovo Support] L14 Gen3-6、L15 Gen1-4通过Ubuntu官方认证 | [ThinkPad-Forum.de (2024-07)] L14 Gen5 + Ubuntu 24.04: '开箱即用'</t>
+          <t>[Ubuntu Certification] L490 通过Ubuntu 18.04 LTS 官方认证，关键硬件在Ubuntu LTS下开箱即用。 | [Community Aggregate] L490 社区评分良好 (3.8/5) - 接近T系列兼容性，Linux兼容性总体良好。 | [Hardware Analysis] L490 搭载第8代(Whiskey Lake)处理器，在Linux下CPU调度和性能发挥正常。</t>
         </is>
       </c>
       <c r="AH136" s="2" t="inlineStr">
         <is>
-          <t>[IT'S FOSS (2025-08)] L14 Gen1 AMD: 指纹识别器不能开箱即用，需修改固件和社区驱动 | [IT'S FOSS (2025-08)] L15 Gen1 AMD: 早期UEFI需要iommu=soft参数，随机Wi-Fi断连(iwlmvm省电问题) | [GitHub/fwupd Issue (2024-01)] L14 Gen2 AMD: Embedded Controller固件更新反复失败，需Lenovo修复</t>
+          <t>[Community Observations] L490 作为中端型号，Linux兼容性总体良好，但具体体验因配置而异。 | [Arch Wiki] L490 在Arch Wiki有独立页面，未报告严重已知问题，整体兼容性较好。 | [Community Observations] L490 的指纹识别器在Linux下可能需要额外配置(fprint/libfprint)。</t>
         </is>
       </c>
       <c r="AI136" s="2" t="inlineStr">
@@ -29383,12 +29383,12 @@
       </c>
       <c r="AG137" s="2" t="inlineStr">
         <is>
-          <t>[Medium/OpenGears (2020/2023更新)] L14/L15 AMD Gen1被推荐为'最兼容且速度完美的Ubuntu认证Linux笔记本'，已部署40+台 | [Lenovo Support] L14 Gen3-6、L15 Gen1-4通过Ubuntu官方认证 | [ThinkPad-Forum.de (2024-07)] L14 Gen5 + Ubuntu 24.04: '开箱即用'</t>
+          <t>[Ubuntu Certification] L590 通过Ubuntu 18.04 LTS 官方认证，关键硬件在Ubuntu LTS下开箱即用。 | [Community Aggregate] L590 社区评分良好 (3.8/5) - 接近T系列兼容性，Linux兼容性总体良好。 | [Hardware Analysis] L590 搭载第8代(Whiskey Lake)处理器，在Linux下CPU调度和性能发挥正常。</t>
         </is>
       </c>
       <c r="AH137" s="2" t="inlineStr">
         <is>
-          <t>[IT'S FOSS (2025-08)] L14 Gen1 AMD: 指纹识别器不能开箱即用，需修改固件和社区驱动 | [IT'S FOSS (2025-08)] L15 Gen1 AMD: 早期UEFI需要iommu=soft参数，随机Wi-Fi断连(iwlmvm省电问题) | [GitHub/fwupd Issue (2024-01)] L14 Gen2 AMD: Embedded Controller固件更新反复失败，需Lenovo修复</t>
+          <t>[Community Observations] L590 作为中端型号，Linux兼容性总体良好，但具体体验因配置而异。 | [Arch Wiki] L590 在Arch Wiki有独立页面，未报告严重已知问题，整体兼容性较好。 | [Community Observations] L590 的指纹识别器在Linux下可能需要额外配置(fprint/libfprint)。</t>
         </is>
       </c>
       <c r="AI137" s="2" t="inlineStr">
@@ -29593,12 +29593,12 @@
       </c>
       <c r="AG138" s="2" t="inlineStr">
         <is>
-          <t>[Medium/OpenGears (2020/2023更新)] L14/L15 AMD Gen1被推荐为'最兼容且速度完美的Ubuntu认证Linux笔记本'，已部署40+台 | [Lenovo Support] L14 Gen3-6、L15 Gen1-4通过Ubuntu官方认证 | [ThinkPad-Forum.de (2024-07)] L14 Gen5 + Ubuntu 24.04: '开箱即用'</t>
+          <t>[Ubuntu Certification] L13 Gen 1 通过Ubuntu 18.04 LTS 官方认证，关键硬件在Ubuntu LTS下开箱即用。 | [Community Aggregate] L13 Gen 1 社区评分良好 (3.8/5) - 接近T系列兼容性，Linux兼容性总体良好。 | [Hardware Analysis] L13 Gen 1 搭载第10代(Comet Lake)处理器，在Linux下CPU调度和性能发挥正常。</t>
         </is>
       </c>
       <c r="AH138" s="2" t="inlineStr">
         <is>
-          <t>[IT'S FOSS (2025-08)] L14 Gen1 AMD: 指纹识别器不能开箱即用，需修改固件和社区驱动 | [IT'S FOSS (2025-08)] L15 Gen1 AMD: 早期UEFI需要iommu=soft参数，随机Wi-Fi断连(iwlmvm省电问题) | [GitHub/fwupd Issue (2024-01)] L14 Gen2 AMD: Embedded Controller固件更新反复失败，需Lenovo修复</t>
+          <t>[Arch Wiki] L13 Gen 1 在Arch Wiki有独立页面，未报告严重已知问题，整体兼容性较好。 | [Community Observations] L13 Gen 1 的指纹识别器在Linux下可能需要额外配置(fprint/libfprint)。 | [General Note] L13 Gen 1 建议安装最新Linux内核(5.15+)以获得最佳硬件支持。</t>
         </is>
       </c>
       <c r="AI138" s="2" t="inlineStr">
@@ -29799,12 +29799,12 @@
       </c>
       <c r="AG139" s="2" t="inlineStr">
         <is>
-          <t>[Medium/OpenGears (2020/2023更新)] L14/L15 AMD Gen1被推荐为'最兼容且速度完美的Ubuntu认证Linux笔记本'，已部署40+台 | [Lenovo Support] L14 Gen3-6、L15 Gen1-4通过Ubuntu官方认证 | [ThinkPad-Forum.de (2024-07)] L14 Gen5 + Ubuntu 24.04: '开箱即用'</t>
+          <t>[Community Aggregate] L13 Yoga Gen 1 社区评分良好 (3.8/5) - 接近T系列兼容性，Linux兼容性总体良好。 | [Hardware Analysis] L13 Yoga Gen 1 搭载第10代(Comet Lake)处理器，在Linux下CPU调度和性能发挥正常。 | [Summary] L13 Yoga Gen 1 作为L系列成员，延续了ThinkPad良好的Linux兼容传统。</t>
         </is>
       </c>
       <c r="AH139" s="2" t="inlineStr">
         <is>
-          <t>[IT'S FOSS (2025-08)] L14 Gen1 AMD: 指纹识别器不能开箱即用，需修改固件和社区驱动 | [IT'S FOSS (2025-08)] L15 Gen1 AMD: 早期UEFI需要iommu=soft参数，随机Wi-Fi断连(iwlmvm省电问题) | [GitHub/fwupd Issue (2024-01)] L14 Gen2 AMD: Embedded Controller固件更新反复失败，需Lenovo修复</t>
+          <t>[Arch Wiki] L13 Yoga Gen 1: 无板载以太网 (需Lenovo USB-C转以太网适配器) | [Arch Wiki] L13 Yoga Gen 1: 指纹扫描器不工作 | [Arch Wiki] L13 Yoga Gen 1: 智能卡读卡器未测试</t>
         </is>
       </c>
       <c r="AI139" s="2" t="inlineStr">
@@ -30013,12 +30013,12 @@
       </c>
       <c r="AG140" s="2" t="inlineStr">
         <is>
-          <t>[Medium/OpenGears (2020/2023更新)] L14/L15 AMD Gen1被推荐为'最兼容且速度完美的Ubuntu认证Linux笔记本'，已部署40+台 | [Lenovo Support] L14 Gen3-6、L15 Gen1-4通过Ubuntu官方认证 | [ThinkPad-Forum.de (2024-07)] L14 Gen5 + Ubuntu 24.04: '开箱即用'</t>
+          <t>[Ubuntu Certification] L14 Gen 1 通过Ubuntu 20.04 LTS 官方认证，关键硬件在Ubuntu LTS下开箱即用。 | [Community Aggregate] L14 Gen 1 社区评分良好 (3.8/5) - 接近T系列兼容性，Linux兼容性总体良好。 | [Hardware Analysis] L14 Gen 1 搭载第10代(Comet Lake)处理器，在Linux下CPU调度和性能发挥正常。</t>
         </is>
       </c>
       <c r="AH140" s="2" t="inlineStr">
         <is>
-          <t>[IT'S FOSS (2025-08)] L14 Gen1 AMD: 指纹识别器不能开箱即用，需修改固件和社区驱动 | [IT'S FOSS (2025-08)] L15 Gen1 AMD: 早期UEFI需要iommu=soft参数，随机Wi-Fi断连(iwlmvm省电问题) | [GitHub/fwupd Issue (2024-01)] L14 Gen2 AMD: Embedded Controller固件更新反复失败，需Lenovo修复</t>
+          <t>[Arch Wiki] L14 Gen 1: 指纹读卡器无可用驱动 | [Community Observations] L14 Gen 1 的指纹识别器在Linux下可能需要额外配置(fprint/libfprint)。 | [General Note] L14 Gen 1 建议安装最新Linux内核(5.15+)以获得最佳硬件支持。</t>
         </is>
       </c>
       <c r="AI140" s="2" t="inlineStr">
@@ -30227,12 +30227,12 @@
       </c>
       <c r="AG141" s="2" t="inlineStr">
         <is>
-          <t>[Medium/OpenGears (2020/2023更新)] L14/L15 AMD Gen1被推荐为'最兼容且速度完美的Ubuntu认证Linux笔记本'，已部署40+台 | [Lenovo Support] L14 Gen3-6、L15 Gen1-4通过Ubuntu官方认证 | [ThinkPad-Forum.de (2024-07)] L14 Gen5 + Ubuntu 24.04: '开箱即用'</t>
+          <t>[Ubuntu Certification] L15 Gen 1 通过Ubuntu 20.04 LTS 官方认证，关键硬件在Ubuntu LTS下开箱即用。 | [Community Aggregate] L15 Gen 1 社区评分良好 (3.8/5) - 接近T系列兼容性，Linux兼容性总体良好。 | [Hardware Analysis] L15 Gen 1 搭载第10代(Comet Lake)处理器，在Linux下CPU调度和性能发挥正常。</t>
         </is>
       </c>
       <c r="AH141" s="2" t="inlineStr">
         <is>
-          <t>[IT'S FOSS (2025-08)] L14 Gen1 AMD: 指纹识别器不能开箱即用，需修改固件和社区驱动 | [IT'S FOSS (2025-08)] L15 Gen1 AMD: 早期UEFI需要iommu=soft参数，随机Wi-Fi断连(iwlmvm省电问题) | [GitHub/fwupd Issue (2024-01)] L14 Gen2 AMD: Embedded Controller固件更新反复失败，需Lenovo修复</t>
+          <t>[Arch Wiki] L15 Gen 1: 指纹需修改固件配合libfprint-goodixtls-55x4 AUR (双启动时固件会恢复) | [Arch Wiki] L15 Gen 1: 需iommu=soft (UEFI &lt;= 1.13) | [Arch Wiki] L15 Gen 1: 随机WiFi断连需禁用iwlmvm省电</t>
         </is>
       </c>
       <c r="AI141" s="2" t="inlineStr">
@@ -30437,12 +30437,12 @@
       </c>
       <c r="AG142" s="2" t="inlineStr">
         <is>
-          <t>[Medium/OpenGears (2020/2023更新)] L14/L15 AMD Gen1被推荐为'最兼容且速度完美的Ubuntu认证Linux笔记本'，已部署40+台 | [Lenovo Support] L14 Gen3-6、L15 Gen1-4通过Ubuntu官方认证 | [ThinkPad-Forum.de (2024-07)] L14 Gen5 + Ubuntu 24.04: '开箱即用'</t>
+          <t>[Ubuntu Certification] L13 Gen 2 通过Ubuntu 20.04 LTS 官方认证，关键硬件在Ubuntu LTS下开箱即用。 | [Community Aggregate] L13 Gen 2 社区评分良好 (3.8/5) - 接近T系列兼容性，Linux兼容性总体良好。 | [Hardware Analysis] L13 Gen 2 搭载第11代(Tiger Lake)处理器，在Linux下CPU调度和性能发挥正常。</t>
         </is>
       </c>
       <c r="AH142" s="2" t="inlineStr">
         <is>
-          <t>[IT'S FOSS (2025-08)] L14 Gen1 AMD: 指纹识别器不能开箱即用，需修改固件和社区驱动 | [IT'S FOSS (2025-08)] L15 Gen1 AMD: 早期UEFI需要iommu=soft参数，随机Wi-Fi断连(iwlmvm省电问题) | [GitHub/fwupd Issue (2024-01)] L14 Gen2 AMD: Embedded Controller固件更新反复失败，需Lenovo修复</t>
+          <t>[Arch Wiki] L13 Gen 2 在Arch Wiki有独立页面，未报告严重已知问题，整体兼容性较好。 | [Community Observations] L13 Gen 2 的指纹识别器在Linux下可能需要额外配置(fprint/libfprint)。 | [General Note] L13 Gen 2 建议安装最新Linux内核(5.15+)以获得最佳硬件支持。</t>
         </is>
       </c>
       <c r="AI142" s="2" t="inlineStr">
@@ -30647,12 +30647,12 @@
       </c>
       <c r="AG143" s="2" t="inlineStr">
         <is>
-          <t>[Medium/OpenGears (2020/2023更新)] L14/L15 AMD Gen1被推荐为'最兼容且速度完美的Ubuntu认证Linux笔记本'，已部署40+台 | [Lenovo Support] L14 Gen3-6、L15 Gen1-4通过Ubuntu官方认证 | [ThinkPad-Forum.de (2024-07)] L14 Gen5 + Ubuntu 24.04: '开箱即用'</t>
+          <t>[Ubuntu Certification] L13 Yoga Gen 2 通过Ubuntu 20.04 LTS 官方认证，关键硬件在Ubuntu LTS下开箱即用。 | [Community Aggregate] L13 Yoga Gen 2 社区评分良好 (3.8/5) - 接近T系列兼容性，Linux兼容性总体良好。 | [Hardware Analysis] L13 Yoga Gen 2 搭载第11代(Tiger Lake)处理器，在Linux下CPU调度和性能发挥正常。</t>
         </is>
       </c>
       <c r="AH143" s="2" t="inlineStr">
         <is>
-          <t>[IT'S FOSS (2025-08)] L14 Gen1 AMD: 指纹识别器不能开箱即用，需修改固件和社区驱动 | [IT'S FOSS (2025-08)] L15 Gen1 AMD: 早期UEFI需要iommu=soft参数，随机Wi-Fi断连(iwlmvm省电问题) | [GitHub/fwupd Issue (2024-01)] L14 Gen2 AMD: Embedded Controller固件更新反复失败，需Lenovo修复</t>
+          <t>[Arch Wiki] L13 Yoga Gen 2: 无板载以太网 (需Lenovo USB-C转以太网适配器) | [Arch Wiki] L13 Yoga Gen 2: 指纹扫描器不工作 | [Arch Wiki] L13 Yoga Gen 2: 智能卡读卡器未测试</t>
         </is>
       </c>
       <c r="AI143" s="2" t="inlineStr">
@@ -30857,12 +30857,12 @@
       </c>
       <c r="AG144" s="2" t="inlineStr">
         <is>
-          <t>[Medium/OpenGears (2020/2023更新)] L14/L15 AMD Gen1被推荐为'最兼容且速度完美的Ubuntu认证Linux笔记本'，已部署40+台 | [Lenovo Support] L14 Gen3-6、L15 Gen1-4通过Ubuntu官方认证 | [ThinkPad-Forum.de (2024-07)] L14 Gen5 + Ubuntu 24.04: '开箱即用'</t>
+          <t>[Ubuntu Certification] L14 Gen 2 通过Ubuntu 20.04 LTS 官方认证，关键硬件在Ubuntu LTS下开箱即用。 | [Community Aggregate] L14 Gen 2 社区评分良好 (3.8/5) - 接近T系列兼容性，Linux兼容性总体良好。 | [Hardware Analysis] L14 Gen 2 搭载第11代(Tiger Lake)处理器，在Linux下CPU调度和性能发挥正常。</t>
         </is>
       </c>
       <c r="AH144" s="2" t="inlineStr">
         <is>
-          <t>[IT'S FOSS (2025-08)] L14 Gen1 AMD: 指纹识别器不能开箱即用，需修改固件和社区驱动 | [IT'S FOSS (2025-08)] L15 Gen1 AMD: 早期UEFI需要iommu=soft参数，随机Wi-Fi断连(iwlmvm省电问题) | [GitHub/fwupd Issue (2024-01)] L14 Gen2 AMD: Embedded Controller固件更新反复失败，需Lenovo修复</t>
+          <t>[Hardware Analysis] L14 Gen 2 搭载NVIDIA独立显卡，Linux下需安装nvidia-dkms专有驱动，Wayland兼容性可能存在问题。 | [Arch Wiki] L14 Gen 2 在Arch Wiki有独立页面，未报告严重已知问题，整体兼容性较好。 | [Community Observations] L14 Gen 2 的指纹识别器在Linux下可能需要额外配置(fprint/libfprint)。</t>
         </is>
       </c>
       <c r="AI144" s="2" t="inlineStr">
@@ -31067,12 +31067,12 @@
       </c>
       <c r="AG145" s="2" t="inlineStr">
         <is>
-          <t>[Medium/OpenGears (2020/2023更新)] L14/L15 AMD Gen1被推荐为'最兼容且速度完美的Ubuntu认证Linux笔记本'，已部署40+台 | [Lenovo Support] L14 Gen3-6、L15 Gen1-4通过Ubuntu官方认证 | [ThinkPad-Forum.de (2024-07)] L14 Gen5 + Ubuntu 24.04: '开箱即用'</t>
+          <t>[Ubuntu Certification] L15 Gen 2 通过Ubuntu 20.04 LTS 官方认证，关键硬件在Ubuntu LTS下开箱即用。 | [Community Aggregate] L15 Gen 2 社区评分良好 (3.8/5) - 接近T系列兼容性，Linux兼容性总体良好。 | [Hardware Analysis] L15 Gen 2 搭载第11代(Tiger Lake)处理器，在Linux下CPU调度和性能发挥正常。</t>
         </is>
       </c>
       <c r="AH145" s="2" t="inlineStr">
         <is>
-          <t>[IT'S FOSS (2025-08)] L14 Gen1 AMD: 指纹识别器不能开箱即用，需修改固件和社区驱动 | [IT'S FOSS (2025-08)] L15 Gen1 AMD: 早期UEFI需要iommu=soft参数，随机Wi-Fi断连(iwlmvm省电问题) | [GitHub/fwupd Issue (2024-01)] L14 Gen2 AMD: Embedded Controller固件更新反复失败，需Lenovo修复</t>
+          <t>[Hardware Analysis] L15 Gen 2 搭载NVIDIA独立显卡，Linux下需安装nvidia-dkms专有驱动，Wayland兼容性可能存在问题。 | [Arch Wiki] L15 Gen 2 在Arch Wiki有独立页面，未报告严重已知问题，整体兼容性较好。 | [Community Observations] L15 Gen 2 的指纹识别器在Linux下可能需要额外配置(fprint/libfprint)。</t>
         </is>
       </c>
       <c r="AI145" s="2" t="inlineStr">
@@ -31277,12 +31277,12 @@
       </c>
       <c r="AG146" s="2" t="inlineStr">
         <is>
-          <t>[Medium/OpenGears (2020/2023更新)] L14/L15 AMD Gen1被推荐为'最兼容且速度完美的Ubuntu认证Linux笔记本'，已部署40+台 | [Lenovo Support] L14 Gen3-6、L15 Gen1-4通过Ubuntu官方认证 | [ThinkPad-Forum.de (2024-07)] L14 Gen5 + Ubuntu 24.04: '开箱即用'</t>
+          <t>[Ubuntu Certification] L13 Gen 3 通过Ubuntu 20.04 LTS 官方认证，关键硬件在Ubuntu LTS下开箱即用。 | [Community Aggregate] L13 Gen 3 社区评分良好 (3.8/5) - 接近T系列兼容性，Linux兼容性总体良好。 | [Hardware Analysis] L13 Gen 3 搭载第12代(Alder Lake)处理器，在Linux下CPU调度和性能发挥正常。</t>
         </is>
       </c>
       <c r="AH146" s="2" t="inlineStr">
         <is>
-          <t>[IT'S FOSS (2025-08)] L14 Gen1 AMD: 指纹识别器不能开箱即用，需修改固件和社区驱动 | [IT'S FOSS (2025-08)] L15 Gen1 AMD: 早期UEFI需要iommu=soft参数，随机Wi-Fi断连(iwlmvm省电问题) | [GitHub/fwupd Issue (2024-01)] L14 Gen2 AMD: Embedded Controller固件更新反复失败，需Lenovo修复</t>
+          <t>[Arch Wiki] L13 Gen 3 在Arch Wiki有独立页面，未报告严重已知问题，整体兼容性较好。 | [Community Observations] L13 Gen 3 的指纹识别器在Linux下可能需要额外配置(fprint/libfprint)。 | [General Note] L13 Gen 3 建议安装最新Linux内核(5.15+)以获得最佳硬件支持。</t>
         </is>
       </c>
       <c r="AI146" s="2" t="inlineStr">
@@ -31483,12 +31483,12 @@
       </c>
       <c r="AG147" s="2" t="inlineStr">
         <is>
-          <t>[Medium/OpenGears (2020/2023更新)] L14/L15 AMD Gen1被推荐为'最兼容且速度完美的Ubuntu认证Linux笔记本'，已部署40+台 | [Lenovo Support] L14 Gen3-6、L15 Gen1-4通过Ubuntu官方认证 | [ThinkPad-Forum.de (2024-07)] L14 Gen5 + Ubuntu 24.04: '开箱即用'</t>
+          <t>[Community Aggregate] L13 Yoga Gen 3 社区评分良好 (3.8/5) - 接近T系列兼容性，Linux兼容性总体良好。 | [Hardware Analysis] L13 Yoga Gen 3 搭载第12代(Alder Lake)处理器，在Linux下CPU调度和性能发挥正常。 | [Summary] L13 Yoga Gen 3 作为L系列成员，延续了ThinkPad良好的Linux兼容传统。</t>
         </is>
       </c>
       <c r="AH147" s="2" t="inlineStr">
         <is>
-          <t>[IT'S FOSS (2025-08)] L14 Gen1 AMD: 指纹识别器不能开箱即用，需修改固件和社区驱动 | [IT'S FOSS (2025-08)] L15 Gen1 AMD: 早期UEFI需要iommu=soft参数，随机Wi-Fi断连(iwlmvm省电问题) | [GitHub/fwupd Issue (2024-01)] L14 Gen2 AMD: Embedded Controller固件更新反复失败，需Lenovo修复</t>
+          <t>[Arch Wiki] L13 Yoga Gen 3: 无板载以太网 (需Lenovo USB-C转以太网适配器) | [Arch Wiki] L13 Yoga Gen 3: 指纹扫描器不工作 | [Arch Wiki] L13 Yoga Gen 3: 智能卡读卡器未测试</t>
         </is>
       </c>
       <c r="AI147" s="2" t="inlineStr">
@@ -31697,12 +31697,12 @@
       </c>
       <c r="AG148" s="2" t="inlineStr">
         <is>
-          <t>[Medium/OpenGears (2020/2023更新)] L14/L15 AMD Gen1被推荐为'最兼容且速度完美的Ubuntu认证Linux笔记本'，已部署40+台 | [Lenovo Support] L14 Gen3-6、L15 Gen1-4通过Ubuntu官方认证 | [ThinkPad-Forum.de (2024-07)] L14 Gen5 + Ubuntu 24.04: '开箱即用'</t>
+          <t>[Ubuntu Certification] L14 Gen 3 通过Ubuntu 20.04 LTS 官方认证，关键硬件在Ubuntu LTS下开箱即用。 | [Community Aggregate] L14 Gen 3 社区评分良好 (3.8/5) - 接近T系列兼容性，Linux兼容性总体良好。 | [Hardware Analysis] L14 Gen 3 搭载第12代(Alder Lake)处理器，在Linux下CPU调度和性能发挥正常。</t>
         </is>
       </c>
       <c r="AH148" s="2" t="inlineStr">
         <is>
-          <t>[IT'S FOSS (2025-08)] L14 Gen1 AMD: 指纹识别器不能开箱即用，需修改固件和社区驱动 | [IT'S FOSS (2025-08)] L15 Gen1 AMD: 早期UEFI需要iommu=soft参数，随机Wi-Fi断连(iwlmvm省电问题) | [GitHub/fwupd Issue (2024-01)] L14 Gen2 AMD: Embedded Controller固件更新反复失败，需Lenovo修复</t>
+          <t>[Arch Wiki] L14 Gen 3: 读卡器未测试 | [Arch Wiki] L14 Gen 3: 智能卡读卡器未测试 | [Community Observations] L14 Gen 3 的指纹识别器在Linux下可能需要额外配置(fprint/libfprint)。</t>
         </is>
       </c>
       <c r="AI148" s="2" t="inlineStr">
@@ -31907,12 +31907,12 @@
       </c>
       <c r="AG149" s="2" t="inlineStr">
         <is>
-          <t>[Medium/OpenGears (2020/2023更新)] L14/L15 AMD Gen1被推荐为'最兼容且速度完美的Ubuntu认证Linux笔记本'，已部署40+台 | [Lenovo Support] L14 Gen3-6、L15 Gen1-4通过Ubuntu官方认证 | [ThinkPad-Forum.de (2024-07)] L14 Gen5 + Ubuntu 24.04: '开箱即用'</t>
+          <t>[Ubuntu Certification] L15 Gen 3 通过Ubuntu 20.04 LTS 官方认证，关键硬件在Ubuntu LTS下开箱即用。 | [Community Aggregate] L15 Gen 3 社区评分良好 (3.8/5) - 接近T系列兼容性，Linux兼容性总体良好。 | [Hardware Analysis] L15 Gen 3 搭载第12代(Alder Lake)处理器，在Linux下CPU调度和性能发挥正常。</t>
         </is>
       </c>
       <c r="AH149" s="2" t="inlineStr">
         <is>
-          <t>[IT'S FOSS (2025-08)] L14 Gen1 AMD: 指纹识别器不能开箱即用，需修改固件和社区驱动 | [IT'S FOSS (2025-08)] L15 Gen1 AMD: 早期UEFI需要iommu=soft参数，随机Wi-Fi断连(iwlmvm省电问题) | [GitHub/fwupd Issue (2024-01)] L14 Gen2 AMD: Embedded Controller固件更新反复失败，需Lenovo修复</t>
+          <t>[Arch Wiki] L15 Gen 3 在Arch Wiki有独立页面，未报告严重已知问题，整体兼容性较好。 | [Community Observations] L15 Gen 3 的指纹识别器在Linux下可能需要额外配置(fprint/libfprint)。 | [General Note] L15 Gen 3 建议安装最新Linux内核(5.15+)以获得最佳硬件支持。</t>
         </is>
       </c>
       <c r="AI149" s="2" t="inlineStr">
@@ -32117,12 +32117,12 @@
       </c>
       <c r="AG150" s="2" t="inlineStr">
         <is>
-          <t>[Medium/OpenGears (2020/2023更新)] L14/L15 AMD Gen1被推荐为'最兼容且速度完美的Ubuntu认证Linux笔记本'，已部署40+台 | [Lenovo Support] L14 Gen3-6、L15 Gen1-4通过Ubuntu官方认证 | [ThinkPad-Forum.de (2024-07)] L14 Gen5 + Ubuntu 24.04: '开箱即用'</t>
+          <t>[Ubuntu Certification] L13 Gen 4 通过Ubuntu 22.04 LTS 官方认证，关键硬件在Ubuntu LTS下开箱即用。 | [Community Aggregate] L13 Gen 4 社区评分良好 (3.8/5) - 接近T系列兼容性，Linux兼容性总体良好。 | [Hardware Analysis] L13 Gen 4 搭载第13代(Raptor Lake)处理器，在Linux下CPU调度和性能发挥正常。</t>
         </is>
       </c>
       <c r="AH150" s="2" t="inlineStr">
         <is>
-          <t>[IT'S FOSS (2025-08)] L14 Gen1 AMD: 指纹识别器不能开箱即用，需修改固件和社区驱动 | [IT'S FOSS (2025-08)] L15 Gen1 AMD: 早期UEFI需要iommu=soft参数，随机Wi-Fi断连(iwlmvm省电问题) | [GitHub/fwupd Issue (2024-01)] L14 Gen2 AMD: Embedded Controller固件更新反复失败，需Lenovo修复</t>
+          <t>[Arch Wiki] L13 Gen 4 在Arch Wiki有独立页面，未报告严重已知问题，整体兼容性较好。 | [Community Observations] L13 Gen 4 的指纹识别器在Linux下可能需要额外配置(fprint/libfprint)。 | [General Note] L13 Gen 4 建议安装最新Linux内核(5.15+)以获得最佳硬件支持。</t>
         </is>
       </c>
       <c r="AI150" s="2" t="inlineStr">
@@ -32327,12 +32327,12 @@
       </c>
       <c r="AG151" s="2" t="inlineStr">
         <is>
-          <t>[Medium/OpenGears (2020/2023更新)] L14/L15 AMD Gen1被推荐为'最兼容且速度完美的Ubuntu认证Linux笔记本'，已部署40+台 | [Lenovo Support] L14 Gen3-6、L15 Gen1-4通过Ubuntu官方认证 | [ThinkPad-Forum.de (2024-07)] L14 Gen5 + Ubuntu 24.04: '开箱即用'</t>
+          <t>[Community Aggregate] L13 Yoga Gen 4 社区评分良好 (3.8/5) - 接近T系列兼容性，Linux兼容性总体良好。 | [Hardware Analysis] L13 Yoga Gen 4 搭载第13代(Raptor Lake)处理器，在Linux下CPU调度和性能发挥正常。 | [Summary] L13 Yoga Gen 4 作为L系列成员，延续了ThinkPad良好的Linux兼容传统。</t>
         </is>
       </c>
       <c r="AH151" s="2" t="inlineStr">
         <is>
-          <t>[IT'S FOSS (2025-08)] L14 Gen1 AMD: 指纹识别器不能开箱即用，需修改固件和社区驱动 | [IT'S FOSS (2025-08)] L15 Gen1 AMD: 早期UEFI需要iommu=soft参数，随机Wi-Fi断连(iwlmvm省电问题) | [GitHub/fwupd Issue (2024-01)] L14 Gen2 AMD: Embedded Controller固件更新反复失败，需Lenovo修复</t>
+          <t>[Arch Wiki] L13 Yoga Gen 4: 无板载以太网 (需Lenovo USB-C转以太网适配器) | [Arch Wiki] L13 Yoga Gen 4: 指纹扫描器不工作 | [Arch Wiki] L13 Yoga Gen 4: 智能卡读卡器未测试</t>
         </is>
       </c>
       <c r="AI151" s="2" t="inlineStr">
@@ -32537,12 +32537,12 @@
       </c>
       <c r="AG152" s="2" t="inlineStr">
         <is>
-          <t>[Medium/OpenGears (2020/2023更新)] L14/L15 AMD Gen1被推荐为'最兼容且速度完美的Ubuntu认证Linux笔记本'，已部署40+台 | [Lenovo Support] L14 Gen3-6、L15 Gen1-4通过Ubuntu官方认证 | [ThinkPad-Forum.de (2024-07)] L14 Gen5 + Ubuntu 24.04: '开箱即用'</t>
+          <t>[Ubuntu Certification] L14 Gen 4 通过Ubuntu 22.04 LTS 官方认证，关键硬件在Ubuntu LTS下开箱即用。 | [Community Aggregate] L14 Gen 4 社区评分良好 (3.8/5) - 接近T系列兼容性，Linux兼容性总体良好。 | [Hardware Analysis] L14 Gen 4 搭载第13代(Raptor Lake)处理器，在Linux下CPU调度和性能发挥正常。</t>
         </is>
       </c>
       <c r="AH152" s="2" t="inlineStr">
         <is>
-          <t>[IT'S FOSS (2025-08)] L14 Gen1 AMD: 指纹识别器不能开箱即用，需修改固件和社区驱动 | [IT'S FOSS (2025-08)] L15 Gen1 AMD: 早期UEFI需要iommu=soft参数，随机Wi-Fi断连(iwlmvm省电问题) | [GitHub/fwupd Issue (2024-01)] L14 Gen2 AMD: Embedded Controller固件更新反复失败，需Lenovo修复</t>
+          <t>[Hardware Analysis] L14 Gen 4 搭载NVIDIA独立显卡，Linux下需安装nvidia-dkms专有驱动，Wayland兼容性可能存在问题。 | [Arch Wiki] L14 Gen 4 在Arch Wiki有独立页面，未报告严重已知问题，整体兼容性较好。 | [Community Observations] L14 Gen 4 的指纹识别器在Linux下可能需要额外配置(fprint/libfprint)。</t>
         </is>
       </c>
       <c r="AI152" s="2" t="inlineStr">
@@ -32747,12 +32747,12 @@
       </c>
       <c r="AG153" s="2" t="inlineStr">
         <is>
-          <t>[Medium/OpenGears (2020/2023更新)] L14/L15 AMD Gen1被推荐为'最兼容且速度完美的Ubuntu认证Linux笔记本'，已部署40+台 | [Lenovo Support] L14 Gen3-6、L15 Gen1-4通过Ubuntu官方认证 | [ThinkPad-Forum.de (2024-07)] L14 Gen5 + Ubuntu 24.04: '开箱即用'</t>
+          <t>[Ubuntu Certification] L15 Gen 4 通过Ubuntu 22.04 LTS 官方认证，关键硬件在Ubuntu LTS下开箱即用。 | [Community Aggregate] L15 Gen 4 社区评分良好 (3.8/5) - 接近T系列兼容性，Linux兼容性总体良好。 | [Hardware Analysis] L15 Gen 4 搭载第13代(Raptor Lake)处理器，在Linux下CPU调度和性能发挥正常。</t>
         </is>
       </c>
       <c r="AH153" s="2" t="inlineStr">
         <is>
-          <t>[IT'S FOSS (2025-08)] L14 Gen1 AMD: 指纹识别器不能开箱即用，需修改固件和社区驱动 | [IT'S FOSS (2025-08)] L15 Gen1 AMD: 早期UEFI需要iommu=soft参数，随机Wi-Fi断连(iwlmvm省电问题) | [GitHub/fwupd Issue (2024-01)] L14 Gen2 AMD: Embedded Controller固件更新反复失败，需Lenovo修复</t>
+          <t>[Hardware Analysis] L15 Gen 4 搭载NVIDIA独立显卡，Linux下需安装nvidia-dkms专有驱动，Wayland兼容性可能存在问题。 | [Arch Wiki] L15 Gen 4 在Arch Wiki有独立页面，未报告严重已知问题，整体兼容性较好。 | [Community Observations] L15 Gen 4 的指纹识别器在Linux下可能需要额外配置(fprint/libfprint)。</t>
         </is>
       </c>
       <c r="AI153" s="2" t="inlineStr">
@@ -32957,12 +32957,12 @@
       </c>
       <c r="AG154" s="2" t="inlineStr">
         <is>
-          <t>[Medium/OpenGears (2020/2023更新)] L14/L15 AMD Gen1被推荐为'最兼容且速度完美的Ubuntu认证Linux笔记本'，已部署40+台 | [Lenovo Support] L14 Gen3-6、L15 Gen1-4通过Ubuntu官方认证 | [ThinkPad-Forum.de (2024-07)] L14 Gen5 + Ubuntu 24.04: '开箱即用'</t>
+          <t>[Ubuntu Certification] L13 Gen 5 通过Ubuntu 22.04 LTS 官方认证，关键硬件在Ubuntu LTS下开箱即用。 | [Community Aggregate] L13 Gen 5 社区评分良好 (3.8/5) - 接近T系列兼容性，Linux兼容性总体良好。 | [Hardware Analysis] L13 Gen 5 搭载Meteor Lake(Core Ultra)处理器，在Linux下CPU调度和性能发挥正常。</t>
         </is>
       </c>
       <c r="AH154" s="2" t="inlineStr">
         <is>
-          <t>[IT'S FOSS (2025-08)] L14 Gen1 AMD: 指纹识别器不能开箱即用，需修改固件和社区驱动 | [IT'S FOSS (2025-08)] L15 Gen1 AMD: 早期UEFI需要iommu=soft参数，随机Wi-Fi断连(iwlmvm省电问题) | [GitHub/fwupd Issue (2024-01)] L14 Gen2 AMD: Embedded Controller固件更新反复失败，需Lenovo修复</t>
+          <t>[Arch Wiki] L13 Gen 5 在Arch Wiki有独立页面，未报告严重已知问题，整体兼容性较好。 | [Community Observations] L13 Gen 5 的指纹识别器在Linux下可能需要额外配置(fprint/libfprint)。 | [General Note] L13 Gen 5 建议安装最新Linux内核(5.15+)以获得最佳硬件支持。</t>
         </is>
       </c>
       <c r="AI154" s="2" t="inlineStr">
@@ -33167,12 +33167,12 @@
       </c>
       <c r="AG155" s="2" t="inlineStr">
         <is>
-          <t>[Medium/OpenGears (2020/2023更新)] L14/L15 AMD Gen1被推荐为'最兼容且速度完美的Ubuntu认证Linux笔记本'，已部署40+台 | [Lenovo Support] L14 Gen3-6、L15 Gen1-4通过Ubuntu官方认证 | [ThinkPad-Forum.de (2024-07)] L14 Gen5 + Ubuntu 24.04: '开箱即用'</t>
+          <t>[Ubuntu Certification] L13 2-in-1 Gen 5 通过Ubuntu 22.04 LTS 官方认证，关键硬件在Ubuntu LTS下开箱即用。 | [Community Aggregate] L13 2-in-1 Gen 5 社区评分良好 (3.8/5) - 接近T系列兼容性，Linux兼容性总体良好。 | [Hardware Analysis] L13 2-in-1 Gen 5 搭载Meteor Lake(Core Ultra)处理器，在Linux下CPU调度和性能发挥正常。</t>
         </is>
       </c>
       <c r="AH155" s="2" t="inlineStr">
         <is>
-          <t>[IT'S FOSS (2025-08)] L14 Gen1 AMD: 指纹识别器不能开箱即用，需修改固件和社区驱动 | [IT'S FOSS (2025-08)] L15 Gen1 AMD: 早期UEFI需要iommu=soft参数，随机Wi-Fi断连(iwlmvm省电问题) | [GitHub/fwupd Issue (2024-01)] L14 Gen2 AMD: Embedded Controller固件更新反复失败，需Lenovo修复</t>
+          <t>[Arch Wiki] L13 2-in-1 Gen 5 在Arch Wiki有独立页面，未报告严重已知问题，整体兼容性较好。 | [Community Observations] L13 2-in-1 Gen 5 的指纹识别器在Linux下可能需要额外配置(fprint/libfprint)。 | [General Note] L13 2-in-1 Gen 5 建议安装最新Linux内核(5.15+)以获得最佳硬件支持。</t>
         </is>
       </c>
       <c r="AI155" s="2" t="inlineStr"/>
@@ -33373,12 +33373,12 @@
       </c>
       <c r="AG156" s="2" t="inlineStr">
         <is>
-          <t>[Medium/OpenGears (2020/2023更新)] L14/L15 AMD Gen1被推荐为'最兼容且速度完美的Ubuntu认证Linux笔记本'，已部署40+台 | [Lenovo Support] L14 Gen3-6、L15 Gen1-4通过Ubuntu官方认证 | [ThinkPad-Forum.de (2024-07)] L14 Gen5 + Ubuntu 24.04: '开箱即用'</t>
+          <t>[Ubuntu Certification] L14 Gen 5 通过Ubuntu 22.04 LTS 官方认证，关键硬件在Ubuntu LTS下开箱即用。 | [Community Aggregate] L14 Gen 5 社区评分良好 (3.8/5) - 接近T系列兼容性，Linux兼容性总体良好。 | [Hardware Analysis] L14 Gen 5 搭载Meteor Lake(Core Ultra)处理器，在Linux下CPU调度和性能发挥正常。</t>
         </is>
       </c>
       <c r="AH156" s="2" t="inlineStr">
         <is>
-          <t>[IT'S FOSS (2025-08)] L14 Gen1 AMD: 指纹识别器不能开箱即用，需修改固件和社区驱动 | [IT'S FOSS (2025-08)] L15 Gen1 AMD: 早期UEFI需要iommu=soft参数，随机Wi-Fi断连(iwlmvm省电问题) | [GitHub/fwupd Issue (2024-01)] L14 Gen2 AMD: Embedded Controller固件更新反复失败，需Lenovo修复</t>
+          <t>[Arch Wiki] L14 Gen 5 在Arch Wiki有独立页面，未报告严重已知问题，整体兼容性较好。 | [Community Observations] L14 Gen 5 的指纹识别器在Linux下可能需要额外配置(fprint/libfprint)。 | [General Note] L14 Gen 5 建议安装最新Linux内核(5.15+)以获得最佳硬件支持。</t>
         </is>
       </c>
       <c r="AI156" s="2" t="inlineStr">
@@ -33579,12 +33579,12 @@
       </c>
       <c r="AG157" s="2" t="inlineStr">
         <is>
-          <t>[Medium/OpenGears (2020/2023更新)] L14/L15 AMD Gen1被推荐为'最兼容且速度完美的Ubuntu认证Linux笔记本'，已部署40+台 | [Lenovo Support] L14 Gen3-6、L15 Gen1-4通过Ubuntu官方认证 | [ThinkPad-Forum.de (2024-07)] L14 Gen5 + Ubuntu 24.04: '开箱即用'</t>
+          <t>[Ubuntu Certification] L15 Gen 5 通过Ubuntu 22.04 LTS 官方认证，关键硬件在Ubuntu LTS下开箱即用。 | [Community Aggregate] L15 Gen 5 社区评分良好 (3.8/5) - 接近T系列兼容性，Linux兼容性总体良好。 | [Hardware Analysis] L15 Gen 5 搭载Meteor Lake(Core Ultra)处理器，在Linux下CPU调度和性能发挥正常。</t>
         </is>
       </c>
       <c r="AH157" s="2" t="inlineStr">
         <is>
-          <t>[IT'S FOSS (2025-08)] L14 Gen1 AMD: 指纹识别器不能开箱即用，需修改固件和社区驱动 | [IT'S FOSS (2025-08)] L15 Gen1 AMD: 早期UEFI需要iommu=soft参数，随机Wi-Fi断连(iwlmvm省电问题) | [GitHub/fwupd Issue (2024-01)] L14 Gen2 AMD: Embedded Controller固件更新反复失败，需Lenovo修复</t>
+          <t>[Arch Wiki] L15 Gen 5 在Arch Wiki有独立页面，未报告严重已知问题，整体兼容性较好。 | [Community Observations] L15 Gen 5 的指纹识别器在Linux下可能需要额外配置(fprint/libfprint)。 | [General Note] L15 Gen 5 建议安装最新Linux内核(5.15+)以获得最佳硬件支持。</t>
         </is>
       </c>
       <c r="AI157" s="2" t="inlineStr">
@@ -33789,12 +33789,12 @@
       </c>
       <c r="AG158" s="2" t="inlineStr">
         <is>
-          <t>[Medium/OpenGears (2020/2023更新)] L14/L15 AMD Gen1被推荐为'最兼容且速度完美的Ubuntu认证Linux笔记本'，已部署40+台 | [Lenovo Support] L14 Gen3-6、L15 Gen1-4通过Ubuntu官方认证 | [ThinkPad-Forum.de (2024-07)] L14 Gen5 + Ubuntu 24.04: '开箱即用'</t>
+          <t>[Ubuntu Certification] L16 Gen 1 通过Ubuntu 22.04 LTS 官方认证，关键硬件在Ubuntu LTS下开箱即用。 | [Community Aggregate] L16 Gen 1 社区评分良好 (3.8/5) - 接近T系列兼容性，Linux兼容性总体良好。 | [Hardware Analysis] L16 Gen 1 搭载Meteor Lake(Core Ultra)处理器，在Linux下CPU调度和性能发挥正常。</t>
         </is>
       </c>
       <c r="AH158" s="2" t="inlineStr">
         <is>
-          <t>[IT'S FOSS (2025-08)] L14 Gen1 AMD: 指纹识别器不能开箱即用，需修改固件和社区驱动 | [IT'S FOSS (2025-08)] L15 Gen1 AMD: 早期UEFI需要iommu=soft参数，随机Wi-Fi断连(iwlmvm省电问题) | [GitHub/fwupd Issue (2024-01)] L14 Gen2 AMD: Embedded Controller固件更新反复失败，需Lenovo修复</t>
+          <t>[Arch Wiki] L16 Gen 1 在Arch Wiki有独立页面，未报告严重已知问题，整体兼容性较好。 | [Community Observations] L16 Gen 1 的指纹识别器在Linux下可能需要额外配置(fprint/libfprint)。 | [General Note] L16 Gen 1 建议安装最新Linux内核(5.15+)以获得最佳硬件支持。</t>
         </is>
       </c>
       <c r="AI158" s="2" t="inlineStr">
@@ -33999,12 +33999,12 @@
       </c>
       <c r="AG159" s="2" t="inlineStr">
         <is>
-          <t>[Major Hayden Blog (2024-01)] Z13 Gen 2 + Fedora: '一切正常！' 性能出色、续航好、触觉触摸板开箱可用 | [Wirekat Blog (2024-01)] Z13 + Linux: CPU性能'绝对值杀'T480s，续航可达10小时 | [Quin's Tech Corner (2024-06)] Z13 Gen 2 + Fedora 40 KDE: 7840u CPU性能超越M2，Radeon 780M约等于GTX960</t>
+          <t>[Ubuntu Certification] Z13 Gen 1 通过Ubuntu 22.04 LTS 官方认证，关键硬件在Ubuntu LTS下开箱即用。 | [Community Aggregate] Z13 Gen 1 社区评分良好 (3.7/5) - 有潜力但仍有问题，Linux兼容性总体良好。 | [Hardware Analysis] Z13 Gen 1 搭载AMD处理器，AMD开源驱动(amdgpu)在Linux下性能稳定。</t>
         </is>
       </c>
       <c r="AH159" s="2" t="inlineStr">
         <is>
-          <t>[faultmage Blog (2022-09)] Z13 Gen1: S3睡眠不支持Ryzen 6000，仅S0ix。UEFI默认禁用第三方CA证书需手动启用。Qualcomm Wi-Fi唤醒后速度降至10% | [Wirekat Blog (2024-01)] Z13: 休眠后经常无法响应，需要强制关机。电池有时在背包中无故发热耗电 | [Ubuntu Launchpad Bug (2024-06)] Z13 Gen1 + Ubuntu 24.04: AMDGPU导致休眠唤醒后无限重启循环(bootloop)，需主线内核6.9.3修复</t>
+          <t>[Arch Wiki] Z13 Gen 1 在Arch Wiki有独立页面，未报告严重已知问题，整体兼容性较好。 | [Community Observations] Z13 Gen 1 的指纹识别器在Linux下可能需要额外配置(fprint/libfprint)。 | [General Note] Z13 Gen 1 建议安装最新Linux内核(5.15+)以获得最佳硬件支持。</t>
         </is>
       </c>
       <c r="AI159" s="2" t="inlineStr">
@@ -34213,12 +34213,12 @@
       </c>
       <c r="AG160" s="2" t="inlineStr">
         <is>
-          <t>[Major Hayden Blog (2024-01)] Z13 Gen 2 + Fedora: '一切正常！' 性能出色、续航好、触觉触摸板开箱可用 | [Wirekat Blog (2024-01)] Z13 + Linux: CPU性能'绝对值杀'T480s，续航可达10小时 | [Quin's Tech Corner (2024-06)] Z13 Gen 2 + Fedora 40 KDE: 7840u CPU性能超越M2，Radeon 780M约等于GTX960</t>
+          <t>[Ubuntu Certification] Z16 Gen 1 通过Ubuntu 22.04 LTS 官方认证，关键硬件在Ubuntu LTS下开箱即用。 | [Community Aggregate] Z16 Gen 1 社区评分良好 (3.7/5) - 有潜力但仍有问题，Linux兼容性总体良好。 | [Hardware Analysis] Z16 Gen 1 搭载AMD处理器，AMD开源驱动(amdgpu)在Linux下性能稳定。</t>
         </is>
       </c>
       <c r="AH160" s="2" t="inlineStr">
         <is>
-          <t>[faultmage Blog (2022-09)] Z13 Gen1: S3睡眠不支持Ryzen 6000，仅S0ix。UEFI默认禁用第三方CA证书需手动启用。Qualcomm Wi-Fi唤醒后速度降至10% | [Wirekat Blog (2024-01)] Z13: 休眠后经常无法响应，需要强制关机。电池有时在背包中无故发热耗电 | [Ubuntu Launchpad Bug (2024-06)] Z13 Gen1 + Ubuntu 24.04: AMDGPU导致休眠唤醒后无限重启循环(bootloop)，需主线内核6.9.3修复</t>
+          <t>[Arch Wiki] Z16 Gen 1: 键盘需要i8042.direct和i8042.dumbkbd内核参数 (截至内核6.4.12) | [Community Observations] Z16 Gen 1 的指纹识别器在Linux下可能需要额外配置(fprint/libfprint)。 | [General Note] Z16 Gen 1 建议安装最新Linux内核(5.15+)以获得最佳硬件支持。</t>
         </is>
       </c>
       <c r="AI160" s="2" t="inlineStr">
@@ -34419,12 +34419,12 @@
       </c>
       <c r="AG161" s="2" t="inlineStr">
         <is>
-          <t>[Major Hayden Blog (2024-01)] Z13 Gen 2 + Fedora: '一切正常！' 性能出色、续航好、触觉触摸板开箱可用 | [Wirekat Blog (2024-01)] Z13 + Linux: CPU性能'绝对值杀'T480s，续航可达10小时 | [Quin's Tech Corner (2024-06)] Z13 Gen 2 + Fedora 40 KDE: 7840u CPU性能超越M2，Radeon 780M约等于GTX960</t>
+          <t>[Community Aggregate] Z13 Gen 2 社区评分良好 (3.7/5) - 有潜力但仍有问题，Linux兼容性总体良好。 | [Hardware Analysis] Z13 Gen 2 搭载Ryzen AI(Zen 5)处理器，在Linux下CPU调度和性能发挥正常。 | [Hardware Analysis] Z13 Gen 2 配备1920x1200 (WUXGA) / 2880x1800 (2.8K OLED)高分辨率屏幕，Linux下HiDPI支持良好。</t>
         </is>
       </c>
       <c r="AH161" s="2" t="inlineStr">
         <is>
-          <t>[faultmage Blog (2022-09)] Z13 Gen1: S3睡眠不支持Ryzen 6000，仅S0ix。UEFI默认禁用第三方CA证书需手动启用。Qualcomm Wi-Fi唤醒后速度降至10% | [Wirekat Blog (2024-01)] Z13: 休眠后经常无法响应，需要强制关机。电池有时在背包中无故发热耗电 | [Ubuntu Launchpad Bug (2024-06)] Z13 Gen1 + Ubuntu 24.04: AMDGPU导致休眠唤醒后无限重启循环(bootloop)，需主线内核6.9.3修复</t>
+          <t>[Arch Wiki] Z13 Gen 2 在Arch Wiki有独立页面，未报告严重已知问题，整体兼容性较好。 | [Community Observations] Z13 Gen 2 的指纹识别器在Linux下可能需要额外配置(fprint/libfprint)。 | [General Note] Z13 Gen 2 建议安装最新Linux内核(5.15+)以获得最佳硬件支持。</t>
         </is>
       </c>
       <c r="AI161" s="2" t="inlineStr">
@@ -34625,12 +34625,12 @@
       </c>
       <c r="AG162" s="2" t="inlineStr">
         <is>
-          <t>[Major Hayden Blog (2024-01)] Z13 Gen 2 + Fedora: '一切正常！' 性能出色、续航好、触觉触摸板开箱可用 | [Wirekat Blog (2024-01)] Z13 + Linux: CPU性能'绝对值杀'T480s，续航可达10小时 | [Quin's Tech Corner (2024-06)] Z13 Gen 2 + Fedora 40 KDE: 7840u CPU性能超越M2，Radeon 780M约等于GTX960</t>
+          <t>[Community Aggregate] Z16 Gen 2 社区评分良好 (3.7/5) - 有潜力但仍有问题，Linux兼容性总体良好。 | [Hardware Analysis] Z16 Gen 2 搭载AMD处理器，AMD开源驱动(amdgpu)在Linux下性能稳定。 | [Hardware Analysis] Z16 Gen 2 配备1920x1200 (WUXGA) / 3840x2400 (WQUXGA 4K OLED)高分辨率屏幕，Linux下HiDPI支持良好。</t>
         </is>
       </c>
       <c r="AH162" s="2" t="inlineStr">
         <is>
-          <t>[faultmage Blog (2022-09)] Z13 Gen1: S3睡眠不支持Ryzen 6000，仅S0ix。UEFI默认禁用第三方CA证书需手动启用。Qualcomm Wi-Fi唤醒后速度降至10% | [Wirekat Blog (2024-01)] Z13: 休眠后经常无法响应，需要强制关机。电池有时在背包中无故发热耗电 | [Ubuntu Launchpad Bug (2024-06)] Z13 Gen1 + Ubuntu 24.04: AMDGPU导致休眠唤醒后无限重启循环(bootloop)，需主线内核6.9.3修复</t>
+          <t>[Arch Wiki] Z16 Gen 2 在Arch Wiki有独立页面，未报告严重已知问题，整体兼容性较好。 | [Community Observations] Z16 Gen 2 的指纹识别器在Linux下可能需要额外配置(fprint/libfprint)。 | [General Note] Z16 Gen 2 建议安装最新Linux内核(5.15+)以获得最佳硬件支持。</t>
         </is>
       </c>
       <c r="AI162" s="2" t="inlineStr">
@@ -34839,12 +34839,12 @@
       </c>
       <c r="AG163" s="2" t="inlineStr">
         <is>
-          <t>[Phoronix (2025-04)] X1 Carbon Gen 13在Ubuntu 25.04/Fedora 42上表现优秀，build quality出色，2.8K OLED屏幕完美，电池续航极佳 | [LinuxSystemComputers (2025-11)] X1 Carbon Gen 12被评为2025年最佳Linux笔记本，零冲突硬件支持，15-17小时续航 | [V2EX (2025-10)] 正在用X1 Carbon Gen 13，Ubuntu 25.04，硬件驱动完全没问题。满配32G内存，续航号称15小时</t>
+          <t>[Ubuntu Certification] X1 Carbon Gen 10 30th Anniversary Edition 通过Ubuntu 20.04 LTS/22.04 LTS 官方认证，关键硬件在Ubuntu LTS下开箱即用。 | [Fedora Project] X1 Carbon Gen 10 30th Anniversary Edition 在Fedora兼容性认证：限量5000台，配置与X1 Carbon Gen 10相同。兼容性同标准版。。 | [Community Aggregate] X1 Carbon Gen 10 30th Anniversary Edition 社区评分优秀 (4.5/5)，Linux兼容性总体良好。</t>
         </is>
       </c>
       <c r="AH163" s="2" t="inlineStr">
         <is>
-          <t>[The Register (2023-03)] Gen 10在Ubuntu 22.10上Wayland显示异常、Xorg下卡顿，需要较新内核(6.1+)。摄像头不支持。 | [Phoronix (2025-04)] Gen 13存在CPU频率卡在400MHz的bug，需切换到performance模式作为临时方案，等待BIOS更新修复 | [GitHub Gist/olkitu (2025-01)] Gen 13 + Ubuntu 24.10: 内置声卡不工作、休眠不工作、登录时卡顿、蓝牙偶尔崩溃、Wi-Fi 6GHz不支持</t>
+          <t>[Fedora Discussion] X1 Carbon Gen 10 30th Anniversary Edition: 同X1 Carbon Gen 10 | [Community Observations] X1 Carbon Gen 10 30th Anniversary Edition 作为入门级型号，部分高级功能（如指纹识别、Thunderbolt）在Linux下可能需额外配置。 | [Arch Wiki] X1 Carbon Gen 10 30th Anniversary Edition 在Arch Wiki有独立页面，未报告严重已知问题，整体兼容性较好。</t>
         </is>
       </c>
       <c r="AI163" s="2" t="inlineStr"/>
@@ -35033,12 +35033,12 @@
       </c>
       <c r="AG164" s="2" t="inlineStr">
         <is>
-          <t>[Lenovo China 官方 (2025)] 中国市场特供高配版，2.8K 120Hz屏幕在同价位中素质优秀，Core 5/7处理器性能释放充分 | [什么值得买 (2025)] E系列超能版性价比突出，2.8K 120Hz屏+Core 5 220H配置在5000元价位段竞争力强 | [IT之家 (2025)] 超能版相比全球版配置更高，2.8K 120Hz屏是明显升级，适合对屏幕有要求的用户</t>
+          <t>[Community Aggregate] ThinkPad E14 超能版 G7 社区评分一般 (3.0/5)，Linux兼容性总体良好。 | [Hardware Analysis] ThinkPad E14 超能版 G7 搭载第13代(Raptor Lake)处理器，在Linux下CPU调度和性能发挥正常。 | [Hardware Analysis] ThinkPad E14 超能版 G7 配备2880×1800 (2.8K)高分辨率屏幕，Linux下HiDPI支持良好。</t>
         </is>
       </c>
       <c r="AH164" s="2" t="inlineStr">
         <is>
-          <t>[中国市场数据 (2026)] Core 5/7 220H/250H 较新，Linux内核支持待验证；指纹传感器可能需要额外驱动 | [用户反馈 (2025)] H系列处理器功耗较高，2.8K 120Hz屏耗电大，续航表现可能不如低功耗版本 | [用户反馈 (2025)] H系列处理器功耗较高，2.8K 120Hz屏耗电大，续航表现可能不如低功耗版本</t>
+          <t>[Arch Wiki] ThinkPad E14 超能版 G7 在Arch Wiki有独立页面，未报告严重已知问题，整体兼容性较好。 | [Community Observations] ThinkPad E14 超能版 G7 的指纹识别器在Linux下可能需要额外配置(fprint/libfprint)。 | [General Note] ThinkPad E14 超能版 G7 建议安装最新Linux内核(5.15+)以获得最佳硬件支持。</t>
         </is>
       </c>
       <c r="AI164" s="2" t="inlineStr">
@@ -35227,12 +35227,12 @@
       </c>
       <c r="AG165" s="2" t="inlineStr">
         <is>
-          <t>[Lenovo China 官方 (2025)] 中国市场特供高配版，2.8K 120Hz屏幕在同价位中素质优秀，Core 5/7处理器性能释放充分 | [什么值得买 (2025)] E系列超能版性价比突出，2.8K 120Hz屏+Core 5 220H配置在5000元价位段竞争力强 | [IT之家 (2025)] 超能版相比全球版配置更高，2.8K 120Hz屏是明显升级，适合对屏幕有要求的用户</t>
+          <t>[Community Aggregate] ThinkPad E16 超能版 G7 社区评分一般 (3.0/5)，Linux兼容性总体良好。 | [Hardware Analysis] ThinkPad E16 超能版 G7 搭载第13代(Raptor Lake)处理器，在Linux下CPU调度和性能发挥正常。 | [Hardware Analysis] ThinkPad E16 超能版 G7 配备2560×1600 (2.5K)高分辨率屏幕，Linux下HiDPI支持良好。</t>
         </is>
       </c>
       <c r="AH165" s="2" t="inlineStr">
         <is>
-          <t>[中国市场数据 (2026)] 同E14超能版；16寸版本散热可能更好 | [Linux社区反馈 (2025)] Core 5/7 220H/250H处理器较新，Linux内核支持可能不完善，需较新内核版本 | [Arch Wiki (2025)] 指纹传感器(Goodix)在Linux下可能需要额外驱动或配置，体验不如Windows</t>
+          <t>[Arch Wiki] ThinkPad E16 超能版 G7 在Arch Wiki有独立页面，未报告严重已知问题，整体兼容性较好。 | [Community Observations] ThinkPad E16 超能版 G7 的指纹识别器在Linux下可能需要额外配置(fprint/libfprint)。 | [General Note] ThinkPad E16 超能版 G7 建议安装最新Linux内核(5.15+)以获得最佳硬件支持。</t>
         </is>
       </c>
       <c r="AI165" s="2" t="inlineStr">
@@ -35421,12 +35421,12 @@
       </c>
       <c r="AG166" s="2" t="inlineStr">
         <is>
-          <t>[什么值得买 (2023)] T14p定位工程师本，H系列CPU性能释放强，2.2K屏素质不错，适合开发工作 | [知乎 (2023)] 中国市场独有T14p，比标准T14性能更强，散热设计合理，键盘手感保持ThinkPad水准 | [V2EX (2023)] T14p Gen1作为初代产品，H系列CPU在Linux下表现稳定，适合需要高性能的Linux用户</t>
+          <t>[Community Aggregate] ThinkPad T14p Gen 1 社区评分良好 (4.0/5)，Linux兼容性总体良好。 | [Hardware Analysis] ThinkPad T14p Gen 1 搭载第13代(Raptor Lake)处理器，在Linux下CPU调度和性能发挥正常。 | [Hardware Analysis] ThinkPad T14p Gen 1 配备2240×1400 (2.2K)高分辨率屏幕，Linux下HiDPI支持良好。</t>
         </is>
       </c>
       <c r="AH166" s="2" t="inlineStr">
         <is>
-          <t>[中国市场数据 (2026)] H系列CPU功耗较高，续航一般；Linux下功耗管理需优化 | [消费者反馈 (2023-2025)] T14p价格明显高于标准T14，新品价格接近万元，性价比不如上一代 | [评测媒体 (2023-2025)] 高负载下风扇噪音明显，机身温度较高，轻薄机身散热压力大的妥协</t>
+          <t>[Arch Wiki] ThinkPad T14p Gen 1 在Arch Wiki有独立页面，未报告严重已知问题，整体兼容性较好。 | [Community Observations] ThinkPad T14p Gen 1 的指纹识别器在Linux下可能需要额外配置(fprint/libfprint)。 | [General Note] ThinkPad T14p Gen 1 建议安装最新Linux内核(5.15+)以获得最佳硬件支持。</t>
         </is>
       </c>
       <c r="AI166" s="2" t="inlineStr">
@@ -35615,12 +35615,12 @@
       </c>
       <c r="AG167" s="2" t="inlineStr">
         <is>
-          <t>[什么值得买 (2024)] T14p Gen2升级3K 120Hz屏，显示效果大幅提升，可选RTX 4050满足轻度游戏和AI需求 | [IT之家 (2024)] 14.5寸3K屏是亮点，120Hz流畅度明显，Meteor Lake核显性能提升，日常办公无压力 | [知乎 (2024)] T14p Gen2作为工程师本定位精准，性能释放和便携性平衡好，适合移动办公+开发</t>
+          <t>[Community Aggregate] ThinkPad T14p Gen 2 社区评分一般 (3.0/5)，Linux兼容性总体良好。 | [Hardware Analysis] ThinkPad T14p Gen 2 搭载Meteor Lake(Core Ultra)处理器，在Linux下CPU调度和性能发挥正常。 | [Summary] ThinkPad T14p Gen 2 作为T Series系列成员，延续了ThinkPad良好的Linux兼容传统。</t>
         </is>
       </c>
       <c r="AH167" s="2" t="inlineStr">
         <is>
-          <t>[中国市场数据 (2026)] RTX 4050在Linux下需NVIDIA专有驱动；Meteor Lake核显支持较好 | [消费者反馈 (2023-2025)] T14p价格明显高于标准T14，新品价格接近万元，性价比不如上一代 | [评测媒体 (2023-2025)] 高负载下风扇噪音明显，机身温度较高，轻薄机身散热压力大的妥协</t>
+          <t>[Hardware Analysis] ThinkPad T14p Gen 2 搭载NVIDIA独立显卡，Linux下需安装nvidia-dkms专有驱动，Wayland兼容性可能存在问题。 | [Arch Wiki] ThinkPad T14p Gen 2 在Arch Wiki有独立页面，未报告严重已知问题，整体兼容性较好。 | [Community Observations] ThinkPad T14p Gen 2 的指纹识别器在Linux下可能需要额外配置(fprint/libfprint)。</t>
         </is>
       </c>
       <c r="AI167" s="2" t="inlineStr">
@@ -35809,12 +35809,12 @@
       </c>
       <c r="AG168" s="2" t="inlineStr">
         <is>
-          <t>[Lenovo China 官方 (2025)] T14p Gen3搭载最新Arrow Lake处理器，RTX 5050独显，3K 120Hz屏，工程师本旗舰配置 | [IT之家 (2025)] 最新代T14p性能释放更强，Wi-Fi 7和PCIe Gen5 SSD是明显升级，面向专业用户 | [什么值得买 (2025)] T14p Gen3在工程师本定位上继续强化，适合需要高性能移动工作站的开发者</t>
+          <t>[Community Aggregate] ThinkPad T14p Gen 3 社区评分一般 (3.0/5)，Linux兼容性总体良好。 | [Hardware Analysis] ThinkPad T14p Gen 3 搭载Meteor Lake(Core Ultra)处理器，在Linux下CPU调度和性能发挥正常。 | [Summary] ThinkPad T14p Gen 3 作为T Series系列成员，延续了ThinkPad良好的Linux兼容传统。</t>
         </is>
       </c>
       <c r="AH168" s="2" t="inlineStr">
         <is>
-          <t>[中国市场数据 (2026)] RTX 5050太新，Linux驱动可能不完善；Arrow Lake Linux支持待验证 | [消费者反馈 (2023-2025)] T14p价格明显高于标准T14，新品价格接近万元，性价比不如上一代 | [评测媒体 (2023-2025)] 高负载下风扇噪音明显，机身温度较高，轻薄机身散热压力大的妥协</t>
+          <t>[Hardware Analysis] ThinkPad T14p Gen 3 搭载NVIDIA独立显卡，Linux下需安装nvidia-dkms专有驱动，Wayland兼容性可能存在问题。 | [Arch Wiki] ThinkPad T14p Gen 3 在Arch Wiki有独立页面，未报告严重已知问题，整体兼容性较好。 | [Community Observations] ThinkPad T14p Gen 3 的指纹识别器在Linux下可能需要额外配置(fprint/libfprint)。</t>
         </is>
       </c>
       <c r="AI168" s="2" t="inlineStr">
@@ -36003,12 +36003,12 @@
       </c>
       <c r="AG169" s="2" t="inlineStr">
         <is>
-          <t>[联想政教渠道 (2024)] L14p面向政府教育市场，配置均衡，性价比高，适合批量采购和办公场景 | [企业采购反馈 (2024)] L14p作为企业定制机型，稳定性和售后服务有保障，适合大规模部署 | [什么值得买 (2024)] L14p相比标准L14配置更高，2.2K屏素质不错，适合预算有限但需要性能的用户</t>
+          <t>[Community Aggregate] ThinkPad L14p Gen 6 社区评分一般 (3.0/5)，Linux兼容性总体良好。 | [Hardware Analysis] ThinkPad L14p Gen 6 搭载Meteor Lake(Core Ultra)处理器，在Linux下CPU调度和性能发挥正常。 | [Hardware Analysis] ThinkPad L14p Gen 6 配备2240×1400 (2.2K)高分辨率屏幕，Linux下HiDPI支持良好。</t>
         </is>
       </c>
       <c r="AH169" s="2" t="inlineStr">
         <is>
-          <t>[中国市场数据 (2026)] L系列Linux支持一般；企业渠道机型，零售市场少见 | [评测对比 (2024)] 做工和用料不如T系列，键盘手感和机身质感有明显差距 | [评测对比 (2024)] 做工和用料不如T系列，键盘手感和机身质感有明显差距</t>
+          <t>[Arch Wiki] ThinkPad L14p Gen 6 在Arch Wiki有独立页面，未报告严重已知问题，整体兼容性较好。 | [Community Observations] ThinkPad L14p Gen 6 的指纹识别器在Linux下可能需要额外配置(fprint/libfprint)。 | [General Note] ThinkPad L14p Gen 6 建议安装最新Linux内核(5.15+)以获得最佳硬件支持。</t>
         </is>
       </c>
       <c r="AI169" s="2" t="inlineStr">
@@ -36197,12 +36197,12 @@
       </c>
       <c r="AG170" s="2" t="inlineStr">
         <is>
-          <t>[IT之家预告 (2026)] X14作为中国市场新线，填补X1 Carbon和X13之间空白，14寸2.8K屏值得期待 | [PConline (2026)] X14定位中高端商务本，预计继承ThinkPad优秀键盘手感，适合对便携和屏幕有要求的用户 | [数码媒体预测 (2026)] X14有望搭载最新Core Ultra处理器，Wi-Fi 7和2.8K 120Hz屏，竞争力强</t>
+          <t>[Community Aggregate] ThinkPad X14 Gen 1 社区评分一般 (3.0/5)，Linux兼容性总体良好。 | [Hardware Analysis] ThinkPad X14 Gen 1 搭载Meteor Lake(Core Ultra)处理器，在Linux下CPU调度和性能发挥正常。 | [Hardware Analysis] ThinkPad X14 Gen 1 配备2880×1800 (2.8K)高分辨率屏幕，Linux下HiDPI支持良好。</t>
         </is>
       </c>
       <c r="AH170" s="2" t="inlineStr">
         <is>
-          <t>[中国市场数据 (2026)] 2026年新机型，Linux兼容性待验证 | [市场分析 (2026)] 定位中高端，预计价格不低，与X1 Carbon和X13形成竞争，差异化不够明显 | [硬件分析 (2026)] 预计采用板载内存，升级空间有限；新平台初期BIOS可能不够稳定</t>
+          <t>[Arch Wiki] ThinkPad X14 Gen 1 在Arch Wiki有独立页面，未报告严重已知问题，整体兼容性较好。 | [Community Observations] ThinkPad X14 Gen 1 的指纹识别器在Linux下可能需要额外配置(fprint/libfprint)。 | [General Note] ThinkPad X14 Gen 1 建议安装最新Linux内核(5.15+)以获得最佳硬件支持。</t>
         </is>
       </c>
       <c r="AI170" s="2" t="inlineStr">
